--- a/docs/設計/部品在庫管理/機能仕様書_部品在庫照会API.xlsx
+++ b/docs/設計/部品在庫管理/機能仕様書_部品在庫照会API.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryota\git\development-Java-apiCourse\docs\設計\部品在庫管理\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usaposu\git\Java-apiCourse-staffservice\docs\設計\部品在庫管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A645D3FC-AFE6-48AA-B629-84B049738788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A204A9D-3B21-45FF-9AE2-5B6FBB5C790A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="9766" windowHeight="10882" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="19" r:id="rId1"/>
@@ -21,18 +21,18 @@
     <sheet name="処理詳細" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">シーケンス!$A$1:$V$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">リクエスト!$A$1:$Y$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">レスポンス!$A$1:$V$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">シーケンス!$A$1:$V$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">リクエスト!$A$1:$AA$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">レスポンス!$A$1:$V$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">機能概要!$A$1:$AH$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">処理詳細!$A$1:$Q$72</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">処理詳細!$A$1:$Q$80</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="261">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -143,9 +143,6 @@
   </si>
   <si>
     <t>◯</t>
-  </si>
-  <si>
-    <t>リクエスト</t>
   </si>
   <si>
     <t>エンドポイント</t>
@@ -880,13 +877,316 @@
   <si>
     <t>(1) 4. の処理でマッピングしたDTOを、APIの共通レスポンス（ApiResponse）に内包されている返却用ラッパー（PagedResponse）に設定し、返却する</t>
     <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>宇佐美大成</t>
+  </si>
+  <si>
+    <t>管理者情報テーブル</t>
+    <rPh sb="0" eb="3">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>リクエスト</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>トランザクションID</t>
+  </si>
+  <si>
+    <t>UUID v4 形式</t>
+  </si>
+  <si>
+    <t>123e4567-e89b-12d3-a456-426614174000</t>
+  </si>
+  <si>
+    <t>　リクエストトレーシング（必須）</t>
+    <rPh sb="13" eb="15">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>TransactionId</t>
+  </si>
+  <si>
+    <t>トランザクションID</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>Transaction_id</t>
+  </si>
+  <si>
+    <t>Transaction_id = NULL</t>
+  </si>
+  <si>
+    <t>Transaction_idは必須項目です。</t>
+    <rPh sb="15" eb="17">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>管理者ID</t>
+    <rPh sb="0" eb="3">
+      <t>カンリシャ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>管理者情報テーブル.管理者ID</t>
+    <rPh sb="0" eb="3">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>カンリシャ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>管理者名</t>
+    <rPh sb="0" eb="3">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>管理者情報テーブル.管理者名</t>
+    <rPh sb="0" eb="3">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>管理者メアド</t>
+    <rPh sb="0" eb="3">
+      <t>カンリシャ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>管理者情報テーブル.メールアドレス</t>
+    <rPh sb="0" eb="3">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>管理者IDが指定リストに含まれる場合に絞り込み</t>
+    <rPh sb="0" eb="3">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>シボ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>管理者名が指定リストに含まれる場合に絞り込み</t>
+    <rPh sb="0" eb="4">
+      <t>カンリシャメイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>シボ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>管理者メールアドレスが指定リストに含まれる場合に絞り込み</t>
+    <rPh sb="0" eb="3">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>シボ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>Transaction-id</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>"id": 123,"name": "Taro Yamada","email": "taro@example.com"</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>【機能概要シート】管理者情報テーブルの項番を追加</t>
+    <rPh sb="1" eb="3">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コウバン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>【リクエストシート】トランザクションIDの項番を追加</t>
+    <rPh sb="21" eb="23">
+      <t>コウバン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>【レスポンスシート】成功レスポンスにTransaction-idを追加</t>
+    <rPh sb="10" eb="12">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>【処理詳細シート】パラメータ設定にTransactionIDを追加/入力チェックにTransaction_idを追加/部品在庫検索に管理者ID,管理者名、管理者メアドを追加</t>
+    <rPh sb="1" eb="3">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="66" eb="69">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="72" eb="75">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="77" eb="80">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>【シーケンスシート】シーケンス図に管理者情報検索/管理者データを追加</t>
+    <rPh sb="15" eb="16">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -987,6 +1287,21 @@
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1182,15 +1497,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="217">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1440,6 +1758,60 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1447,6 +1819,132 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1482,162 +1980,45 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1647,8 +2028,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1659,11 +2049,29 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1677,73 +2085,86 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="標準 2 2" xfId="2" xr:uid="{C8EE0B67-CD5F-4194-A49B-70DDC19B80AD}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1856,14 +2277,14 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>212913</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>110415</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>112060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>134471</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>89647</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>235325</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1878,8 +2299,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5233148" y="3315297"/>
-          <a:ext cx="2308411" cy="1951468"/>
+          <a:off x="5233148" y="3563472"/>
+          <a:ext cx="2308411" cy="2644588"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartMagneticDisk">
           <a:avLst/>
@@ -1959,6 +2380,43 @@
             </a:rPr>
             <a:t>・在庫センター情報テーブル</a:t>
           </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>・管理者情報テーブル</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2102,13 +2560,13 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>224155</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>100031</xdr:rowOff>
+      <xdr:rowOff>108884</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>212913</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>111685</xdr:rowOff>
+      <xdr:rowOff>173692</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2125,9 +2583,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="4616861" y="4291031"/>
-          <a:ext cx="616287" cy="11654"/>
+        <a:xfrm>
+          <a:off x="4616861" y="4820958"/>
+          <a:ext cx="616287" cy="64808"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2162,23 +2620,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>12065</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>1215390</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>93617</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>141194</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>161760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0D23A42-D473-7DF2-879E-350535A55D3D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2187,24 +2645,25 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="314325" y="2054225"/>
-          <a:ext cx="7435850" cy="6207760"/>
+          <a:off x="627529" y="2017059"/>
+          <a:ext cx="7772400" cy="7221466"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2471,7 +2930,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E69"/>
-  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="16.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="16.5" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="4"/>
     <col min="2" max="2" width="5.109375" style="68" customWidth="1"/>
@@ -2481,12 +2940,12 @@
     <col min="6" max="16384" width="3.6640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.8">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B2" s="69" t="s">
         <v>1</v>
       </c>
@@ -2500,7 +2959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B3" s="71" t="s">
         <v>5</v>
       </c>
@@ -2514,397 +2973,437 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B4" s="71"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="27"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B5" s="71"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="27"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B6" s="71"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B7" s="71"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B8" s="71"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.8">
+      <c r="B4" s="86" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="87">
+        <v>45935</v>
+      </c>
+      <c r="D4" s="75" t="s">
+        <v>233</v>
+      </c>
+      <c r="E4" s="85" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.8">
+      <c r="B5" s="86" t="s">
+        <v>232</v>
+      </c>
+      <c r="C5" s="87">
+        <v>45935</v>
+      </c>
+      <c r="D5" s="75" t="s">
+        <v>233</v>
+      </c>
+      <c r="E5" s="85" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.8">
+      <c r="B6" s="86" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" s="87">
+        <v>45935</v>
+      </c>
+      <c r="D6" s="75" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="85" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.8">
+      <c r="B7" s="86" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" s="87">
+        <v>45935</v>
+      </c>
+      <c r="D7" s="75" t="s">
+        <v>233</v>
+      </c>
+      <c r="E7" s="85" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="33" x14ac:dyDescent="0.8">
+      <c r="B8" s="86" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" s="87">
+        <v>45935</v>
+      </c>
+      <c r="D8" s="75" t="s">
+        <v>233</v>
+      </c>
+      <c r="E8" s="85" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B9" s="71"/>
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
       <c r="E9" s="26"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B10" s="71"/>
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B11" s="71"/>
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
       <c r="E11" s="26"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B12" s="71"/>
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
       <c r="E12" s="26"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B13" s="71"/>
       <c r="C13" s="26"/>
       <c r="D13" s="26"/>
       <c r="E13" s="26"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B14" s="71"/>
       <c r="C14" s="26"/>
       <c r="D14" s="26"/>
       <c r="E14" s="26"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B15" s="71"/>
       <c r="C15" s="26"/>
       <c r="D15" s="26"/>
       <c r="E15" s="26"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.8">
       <c r="B16" s="71"/>
       <c r="C16" s="26"/>
       <c r="D16" s="26"/>
       <c r="E16" s="26"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B17" s="71"/>
       <c r="C17" s="26"/>
       <c r="D17" s="26"/>
       <c r="E17" s="26"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B18" s="71"/>
       <c r="C18" s="26"/>
       <c r="D18" s="26"/>
       <c r="E18" s="26"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B19" s="71"/>
       <c r="C19" s="26"/>
       <c r="D19" s="26"/>
       <c r="E19" s="26"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B20" s="71"/>
       <c r="C20" s="26"/>
       <c r="D20" s="26"/>
       <c r="E20" s="26"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B21" s="71"/>
       <c r="C21" s="26"/>
       <c r="D21" s="26"/>
       <c r="E21" s="26"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B22" s="71"/>
       <c r="C22" s="26"/>
       <c r="D22" s="26"/>
       <c r="E22" s="26"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B23" s="71"/>
       <c r="C23" s="26"/>
       <c r="D23" s="26"/>
       <c r="E23" s="26"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B24" s="71"/>
       <c r="C24" s="26"/>
       <c r="D24" s="26"/>
       <c r="E24" s="26"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B25" s="71"/>
       <c r="C25" s="26"/>
       <c r="D25" s="26"/>
       <c r="E25" s="26"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B26" s="71"/>
       <c r="C26" s="26"/>
       <c r="D26" s="26"/>
       <c r="E26" s="26"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B27" s="71"/>
       <c r="C27" s="26"/>
       <c r="D27" s="26"/>
       <c r="E27" s="26"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B28" s="71"/>
       <c r="C28" s="26"/>
       <c r="D28" s="26"/>
       <c r="E28" s="26"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B29" s="71"/>
       <c r="C29" s="26"/>
       <c r="D29" s="26"/>
       <c r="E29" s="26"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B30" s="71"/>
       <c r="C30" s="26"/>
       <c r="D30" s="26"/>
       <c r="E30" s="26"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B31" s="71"/>
       <c r="C31" s="26"/>
       <c r="D31" s="26"/>
       <c r="E31" s="26"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B32" s="71"/>
       <c r="C32" s="26"/>
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B33" s="71"/>
       <c r="C33" s="26"/>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B34" s="71"/>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
       <c r="E34" s="26"/>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B35" s="71"/>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B36" s="71"/>
       <c r="C36" s="26"/>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B37" s="71"/>
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B38" s="71"/>
       <c r="C38" s="26"/>
       <c r="D38" s="26"/>
       <c r="E38" s="26"/>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B39" s="71"/>
       <c r="C39" s="26"/>
       <c r="D39" s="26"/>
       <c r="E39" s="26"/>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B40" s="71"/>
       <c r="C40" s="26"/>
       <c r="D40" s="26"/>
       <c r="E40" s="26"/>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B41" s="71"/>
       <c r="C41" s="26"/>
       <c r="D41" s="26"/>
       <c r="E41" s="26"/>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B42" s="71"/>
       <c r="C42" s="26"/>
       <c r="D42" s="26"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B43" s="71"/>
       <c r="C43" s="26"/>
       <c r="D43" s="26"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B44" s="71"/>
       <c r="C44" s="26"/>
       <c r="D44" s="26"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B45" s="71"/>
       <c r="C45" s="26"/>
       <c r="D45" s="26"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B46" s="71"/>
       <c r="C46" s="26"/>
       <c r="D46" s="26"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B47" s="71"/>
       <c r="C47" s="26"/>
       <c r="D47" s="26"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B48" s="71"/>
       <c r="C48" s="26"/>
       <c r="D48" s="26"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B49" s="71"/>
       <c r="C49" s="26"/>
       <c r="D49" s="26"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B50" s="71"/>
       <c r="C50" s="26"/>
       <c r="D50" s="26"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B51" s="71"/>
       <c r="C51" s="26"/>
       <c r="D51" s="26"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B52" s="71"/>
       <c r="C52" s="26"/>
       <c r="D52" s="26"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B53" s="71"/>
       <c r="C53" s="26"/>
       <c r="D53" s="26"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B54" s="71"/>
       <c r="C54" s="26"/>
       <c r="D54" s="26"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B55" s="71"/>
       <c r="C55" s="26"/>
       <c r="D55" s="26"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B56" s="71"/>
       <c r="C56" s="26"/>
       <c r="D56" s="26"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B57" s="71"/>
       <c r="C57" s="26"/>
       <c r="D57" s="26"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B58" s="71"/>
       <c r="C58" s="26"/>
       <c r="D58" s="26"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B59" s="71"/>
       <c r="C59" s="26"/>
       <c r="D59" s="26"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B60" s="71"/>
       <c r="C60" s="26"/>
       <c r="D60" s="26"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B61" s="71"/>
       <c r="C61" s="26"/>
       <c r="D61" s="26"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B62" s="71"/>
       <c r="C62" s="26"/>
       <c r="D62" s="26"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B63" s="71"/>
       <c r="C63" s="26"/>
       <c r="D63" s="26"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B64" s="71"/>
       <c r="C64" s="26"/>
       <c r="D64" s="26"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B65" s="71"/>
       <c r="C65" s="26"/>
       <c r="D65" s="26"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B66" s="71"/>
       <c r="C66" s="26"/>
       <c r="D66" s="26"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B67" s="71"/>
       <c r="C67" s="26"/>
       <c r="D67" s="26"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B68" s="71"/>
       <c r="C68" s="26"/>
       <c r="D68" s="26"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.8">
       <c r="B69" s="71"/>
       <c r="C69" s="26"/>
       <c r="D69" s="26"/>
@@ -2918,8 +3417,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AH27"/>
-  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AH28"/>
+  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="20" width="3.6640625" style="60"/>
     <col min="21" max="21" width="5.88671875" style="60" customWidth="1"/>
@@ -2928,488 +3427,488 @@
     <col min="35" max="16384" width="3.6640625" style="60"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="120" t="s">
+    <row r="1" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A1" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="129" t="s">
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="130"/>
-      <c r="N1" s="130"/>
-      <c r="O1" s="130"/>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="135" t="s">
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="136"/>
-      <c r="S1" s="136"/>
-      <c r="T1" s="136"/>
-      <c r="U1" s="136"/>
-      <c r="V1" s="103" t="s">
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
+      <c r="V1" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="103"/>
-      <c r="X1" s="103"/>
-      <c r="Y1" s="114" t="s">
+      <c r="W1" s="123"/>
+      <c r="X1" s="123"/>
+      <c r="Y1" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="115"/>
-      <c r="AA1" s="115"/>
-      <c r="AB1" s="116"/>
-      <c r="AC1" s="108" t="s">
+      <c r="Z1" s="135"/>
+      <c r="AA1" s="135"/>
+      <c r="AB1" s="136"/>
+      <c r="AC1" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="AD1" s="109"/>
-      <c r="AE1" s="110"/>
-      <c r="AF1" s="104" t="s">
+      <c r="AD1" s="129"/>
+      <c r="AE1" s="130"/>
+      <c r="AF1" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="105"/>
-      <c r="AH1" s="105"/>
-    </row>
-    <row r="2" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="123"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="125"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="133"/>
-      <c r="N2" s="133"/>
-      <c r="O2" s="133"/>
-      <c r="P2" s="134"/>
-      <c r="Q2" s="137"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="103"/>
-      <c r="W2" s="103"/>
-      <c r="X2" s="103"/>
-      <c r="Y2" s="117"/>
-      <c r="Z2" s="118"/>
-      <c r="AA2" s="118"/>
-      <c r="AB2" s="119"/>
-      <c r="AC2" s="111"/>
-      <c r="AD2" s="112"/>
-      <c r="AE2" s="113"/>
-      <c r="AF2" s="106"/>
-      <c r="AG2" s="107"/>
-      <c r="AH2" s="107"/>
-    </row>
-    <row r="3" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="123"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="124"/>
-      <c r="K3" s="125"/>
-      <c r="L3" s="129" t="s">
+      <c r="AG1" s="125"/>
+      <c r="AH1" s="125"/>
+    </row>
+    <row r="2" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A2" s="107"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
+      <c r="P2" s="118"/>
+      <c r="Q2" s="121"/>
+      <c r="R2" s="122"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="122"/>
+      <c r="U2" s="122"/>
+      <c r="V2" s="123"/>
+      <c r="W2" s="123"/>
+      <c r="X2" s="123"/>
+      <c r="Y2" s="137"/>
+      <c r="Z2" s="138"/>
+      <c r="AA2" s="138"/>
+      <c r="AB2" s="139"/>
+      <c r="AC2" s="131"/>
+      <c r="AD2" s="132"/>
+      <c r="AE2" s="133"/>
+      <c r="AF2" s="126"/>
+      <c r="AG2" s="127"/>
+      <c r="AH2" s="127"/>
+    </row>
+    <row r="3" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A3" s="107"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="108"/>
+      <c r="K3" s="109"/>
+      <c r="L3" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="130"/>
-      <c r="N3" s="130"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="131"/>
-      <c r="Q3" s="135" t="s">
+      <c r="M3" s="114"/>
+      <c r="N3" s="114"/>
+      <c r="O3" s="114"/>
+      <c r="P3" s="115"/>
+      <c r="Q3" s="119" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="136"/>
-      <c r="S3" s="136"/>
-      <c r="T3" s="136"/>
-      <c r="U3" s="136"/>
-      <c r="V3" s="103" t="s">
+      <c r="R3" s="120"/>
+      <c r="S3" s="120"/>
+      <c r="T3" s="120"/>
+      <c r="U3" s="120"/>
+      <c r="V3" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="W3" s="103"/>
-      <c r="X3" s="103"/>
-      <c r="Y3" s="114" t="s">
+      <c r="W3" s="123"/>
+      <c r="X3" s="123"/>
+      <c r="Y3" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="Z3" s="115"/>
-      <c r="AA3" s="115"/>
-      <c r="AB3" s="116"/>
-      <c r="AC3" s="103" t="s">
+      <c r="Z3" s="135"/>
+      <c r="AA3" s="135"/>
+      <c r="AB3" s="136"/>
+      <c r="AC3" s="123" t="s">
         <v>16</v>
       </c>
-      <c r="AD3" s="103"/>
-      <c r="AE3" s="103"/>
-      <c r="AF3" s="104" t="s">
+      <c r="AD3" s="123"/>
+      <c r="AE3" s="123"/>
+      <c r="AF3" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="AG3" s="105"/>
-      <c r="AH3" s="105"/>
-    </row>
-    <row r="4" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="126"/>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="127"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="133"/>
-      <c r="N4" s="133"/>
-      <c r="O4" s="133"/>
-      <c r="P4" s="134"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="138"/>
-      <c r="S4" s="138"/>
-      <c r="T4" s="138"/>
-      <c r="U4" s="138"/>
-      <c r="V4" s="103"/>
-      <c r="W4" s="103"/>
-      <c r="X4" s="103"/>
-      <c r="Y4" s="117"/>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="119"/>
-      <c r="AC4" s="103"/>
-      <c r="AD4" s="103"/>
-      <c r="AE4" s="103"/>
-      <c r="AF4" s="106"/>
-      <c r="AG4" s="107"/>
-      <c r="AH4" s="107"/>
-    </row>
-    <row r="5" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="86" t="s">
+      <c r="AG3" s="125"/>
+      <c r="AH3" s="125"/>
+    </row>
+    <row r="4" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="117"/>
+      <c r="N4" s="117"/>
+      <c r="O4" s="117"/>
+      <c r="P4" s="118"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="122"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="123"/>
+      <c r="W4" s="123"/>
+      <c r="X4" s="123"/>
+      <c r="Y4" s="137"/>
+      <c r="Z4" s="138"/>
+      <c r="AA4" s="138"/>
+      <c r="AB4" s="139"/>
+      <c r="AC4" s="123"/>
+      <c r="AD4" s="123"/>
+      <c r="AE4" s="123"/>
+      <c r="AF4" s="126"/>
+      <c r="AG4" s="127"/>
+      <c r="AH4" s="127"/>
+    </row>
+    <row r="5" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A5" s="146" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="87"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="88"/>
-      <c r="H5" s="89" t="s">
+      <c r="B5" s="147"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="147"/>
+      <c r="E5" s="147"/>
+      <c r="F5" s="147"/>
+      <c r="G5" s="148"/>
+      <c r="H5" s="149" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="90"/>
-      <c r="J5" s="90"/>
-      <c r="K5" s="90"/>
-      <c r="L5" s="90"/>
-      <c r="M5" s="90"/>
-      <c r="N5" s="90"/>
-      <c r="O5" s="90"/>
-      <c r="P5" s="90"/>
-      <c r="Q5" s="90"/>
-      <c r="R5" s="90"/>
-      <c r="S5" s="90"/>
-      <c r="T5" s="90"/>
-      <c r="U5" s="90"/>
-      <c r="V5" s="90"/>
-      <c r="W5" s="90"/>
-      <c r="X5" s="90"/>
-      <c r="Y5" s="90"/>
-      <c r="Z5" s="90"/>
-      <c r="AA5" s="90"/>
-      <c r="AB5" s="90"/>
-      <c r="AC5" s="90"/>
-      <c r="AD5" s="90"/>
-      <c r="AE5" s="90"/>
-      <c r="AF5" s="90"/>
-      <c r="AG5" s="90"/>
-      <c r="AH5" s="90"/>
-    </row>
-    <row r="6" spans="1:34" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="86" t="s">
+      <c r="I5" s="150"/>
+      <c r="J5" s="150"/>
+      <c r="K5" s="150"/>
+      <c r="L5" s="150"/>
+      <c r="M5" s="150"/>
+      <c r="N5" s="150"/>
+      <c r="O5" s="150"/>
+      <c r="P5" s="150"/>
+      <c r="Q5" s="150"/>
+      <c r="R5" s="150"/>
+      <c r="S5" s="150"/>
+      <c r="T5" s="150"/>
+      <c r="U5" s="150"/>
+      <c r="V5" s="150"/>
+      <c r="W5" s="150"/>
+      <c r="X5" s="150"/>
+      <c r="Y5" s="150"/>
+      <c r="Z5" s="150"/>
+      <c r="AA5" s="150"/>
+      <c r="AB5" s="150"/>
+      <c r="AC5" s="150"/>
+      <c r="AD5" s="150"/>
+      <c r="AE5" s="150"/>
+      <c r="AF5" s="150"/>
+      <c r="AG5" s="150"/>
+      <c r="AH5" s="150"/>
+    </row>
+    <row r="6" spans="1:34" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A6" s="146" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="87"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="87"/>
-      <c r="E6" s="87"/>
-      <c r="F6" s="87"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="91" t="s">
-        <v>197</v>
-      </c>
-      <c r="I6" s="90"/>
-      <c r="J6" s="90"/>
-      <c r="K6" s="90"/>
-      <c r="L6" s="90"/>
-      <c r="M6" s="90"/>
-      <c r="N6" s="90"/>
-      <c r="O6" s="90"/>
-      <c r="P6" s="90"/>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90"/>
-      <c r="T6" s="90"/>
-      <c r="U6" s="90"/>
-      <c r="V6" s="90"/>
-      <c r="W6" s="90"/>
-      <c r="X6" s="90"/>
-      <c r="Y6" s="90"/>
-      <c r="Z6" s="90"/>
-      <c r="AA6" s="90"/>
-      <c r="AB6" s="90"/>
-      <c r="AC6" s="90"/>
-      <c r="AD6" s="90"/>
-      <c r="AE6" s="90"/>
-      <c r="AF6" s="90"/>
-      <c r="AG6" s="90"/>
-      <c r="AH6" s="90"/>
-    </row>
-    <row r="7" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="86" t="s">
+      <c r="B6" s="147"/>
+      <c r="C6" s="147"/>
+      <c r="D6" s="147"/>
+      <c r="E6" s="147"/>
+      <c r="F6" s="147"/>
+      <c r="G6" s="148"/>
+      <c r="H6" s="151" t="s">
+        <v>196</v>
+      </c>
+      <c r="I6" s="150"/>
+      <c r="J6" s="150"/>
+      <c r="K6" s="150"/>
+      <c r="L6" s="150"/>
+      <c r="M6" s="150"/>
+      <c r="N6" s="150"/>
+      <c r="O6" s="150"/>
+      <c r="P6" s="150"/>
+      <c r="Q6" s="150"/>
+      <c r="R6" s="150"/>
+      <c r="S6" s="150"/>
+      <c r="T6" s="150"/>
+      <c r="U6" s="150"/>
+      <c r="V6" s="150"/>
+      <c r="W6" s="150"/>
+      <c r="X6" s="150"/>
+      <c r="Y6" s="150"/>
+      <c r="Z6" s="150"/>
+      <c r="AA6" s="150"/>
+      <c r="AB6" s="150"/>
+      <c r="AC6" s="150"/>
+      <c r="AD6" s="150"/>
+      <c r="AE6" s="150"/>
+      <c r="AF6" s="150"/>
+      <c r="AG6" s="150"/>
+      <c r="AH6" s="150"/>
+    </row>
+    <row r="7" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A7" s="146" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="87"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="89" t="s">
+      <c r="B7" s="147"/>
+      <c r="C7" s="147"/>
+      <c r="D7" s="147"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="148"/>
+      <c r="H7" s="149" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="90"/>
-      <c r="J7" s="90"/>
-      <c r="K7" s="90"/>
-      <c r="L7" s="90"/>
-      <c r="M7" s="90"/>
-      <c r="N7" s="90"/>
-      <c r="O7" s="90"/>
-      <c r="P7" s="90"/>
-      <c r="Q7" s="90"/>
-      <c r="R7" s="90"/>
-      <c r="S7" s="90"/>
-      <c r="T7" s="90"/>
-      <c r="U7" s="90"/>
-      <c r="V7" s="90"/>
-      <c r="W7" s="90"/>
-      <c r="X7" s="90"/>
-      <c r="Y7" s="90"/>
-      <c r="Z7" s="90"/>
-      <c r="AA7" s="90"/>
-      <c r="AB7" s="90"/>
-      <c r="AC7" s="90"/>
-      <c r="AD7" s="90"/>
-      <c r="AE7" s="90"/>
-      <c r="AF7" s="90"/>
-      <c r="AG7" s="90"/>
-      <c r="AH7" s="90"/>
-    </row>
-    <row r="8" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="86" t="s">
+      <c r="I7" s="150"/>
+      <c r="J7" s="150"/>
+      <c r="K7" s="150"/>
+      <c r="L7" s="150"/>
+      <c r="M7" s="150"/>
+      <c r="N7" s="150"/>
+      <c r="O7" s="150"/>
+      <c r="P7" s="150"/>
+      <c r="Q7" s="150"/>
+      <c r="R7" s="150"/>
+      <c r="S7" s="150"/>
+      <c r="T7" s="150"/>
+      <c r="U7" s="150"/>
+      <c r="V7" s="150"/>
+      <c r="W7" s="150"/>
+      <c r="X7" s="150"/>
+      <c r="Y7" s="150"/>
+      <c r="Z7" s="150"/>
+      <c r="AA7" s="150"/>
+      <c r="AB7" s="150"/>
+      <c r="AC7" s="150"/>
+      <c r="AD7" s="150"/>
+      <c r="AE7" s="150"/>
+      <c r="AF7" s="150"/>
+      <c r="AG7" s="150"/>
+      <c r="AH7" s="150"/>
+    </row>
+    <row r="8" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A8" s="146" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="87"/>
-      <c r="C8" s="87"/>
-      <c r="D8" s="87"/>
-      <c r="E8" s="87"/>
-      <c r="F8" s="87"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="89" t="s">
+      <c r="B8" s="147"/>
+      <c r="C8" s="147"/>
+      <c r="D8" s="147"/>
+      <c r="E8" s="147"/>
+      <c r="F8" s="147"/>
+      <c r="G8" s="148"/>
+      <c r="H8" s="149" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="90"/>
-      <c r="J8" s="90"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="90"/>
-      <c r="M8" s="90"/>
-      <c r="N8" s="90"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="90"/>
-      <c r="Q8" s="90"/>
-      <c r="R8" s="90"/>
-      <c r="S8" s="90"/>
-      <c r="T8" s="90"/>
-      <c r="U8" s="90"/>
-      <c r="V8" s="90"/>
-      <c r="W8" s="90"/>
-      <c r="X8" s="90"/>
-      <c r="Y8" s="90"/>
-      <c r="Z8" s="90"/>
-      <c r="AA8" s="90"/>
-      <c r="AB8" s="90"/>
-      <c r="AC8" s="90"/>
-      <c r="AD8" s="90"/>
-      <c r="AE8" s="90"/>
-      <c r="AF8" s="90"/>
-      <c r="AG8" s="90"/>
-      <c r="AH8" s="90"/>
-    </row>
-    <row r="9" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="86" t="s">
+      <c r="I8" s="150"/>
+      <c r="J8" s="150"/>
+      <c r="K8" s="150"/>
+      <c r="L8" s="150"/>
+      <c r="M8" s="150"/>
+      <c r="N8" s="150"/>
+      <c r="O8" s="150"/>
+      <c r="P8" s="150"/>
+      <c r="Q8" s="150"/>
+      <c r="R8" s="150"/>
+      <c r="S8" s="150"/>
+      <c r="T8" s="150"/>
+      <c r="U8" s="150"/>
+      <c r="V8" s="150"/>
+      <c r="W8" s="150"/>
+      <c r="X8" s="150"/>
+      <c r="Y8" s="150"/>
+      <c r="Z8" s="150"/>
+      <c r="AA8" s="150"/>
+      <c r="AB8" s="150"/>
+      <c r="AC8" s="150"/>
+      <c r="AD8" s="150"/>
+      <c r="AE8" s="150"/>
+      <c r="AF8" s="150"/>
+      <c r="AG8" s="150"/>
+      <c r="AH8" s="150"/>
+    </row>
+    <row r="9" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A9" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="87"/>
-      <c r="C9" s="87"/>
-      <c r="D9" s="87"/>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="88"/>
-      <c r="H9" s="89" t="s">
+      <c r="B9" s="147"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="147"/>
+      <c r="E9" s="147"/>
+      <c r="F9" s="147"/>
+      <c r="G9" s="148"/>
+      <c r="H9" s="149" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="90"/>
-      <c r="J9" s="90"/>
-      <c r="K9" s="90"/>
-      <c r="L9" s="90"/>
-      <c r="M9" s="90"/>
-      <c r="N9" s="90"/>
-      <c r="O9" s="90"/>
-      <c r="P9" s="90"/>
-      <c r="Q9" s="90"/>
-      <c r="R9" s="90"/>
-      <c r="S9" s="90"/>
-      <c r="T9" s="90"/>
-      <c r="U9" s="90"/>
-      <c r="V9" s="90"/>
-      <c r="W9" s="90"/>
-      <c r="X9" s="90"/>
-      <c r="Y9" s="90"/>
-      <c r="Z9" s="90"/>
-      <c r="AA9" s="90"/>
-      <c r="AB9" s="90"/>
-      <c r="AC9" s="90"/>
-      <c r="AD9" s="90"/>
-      <c r="AE9" s="90"/>
-      <c r="AF9" s="90"/>
-      <c r="AG9" s="90"/>
-      <c r="AH9" s="90"/>
-    </row>
-    <row r="10" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="92" t="s">
+      <c r="I9" s="150"/>
+      <c r="J9" s="150"/>
+      <c r="K9" s="150"/>
+      <c r="L9" s="150"/>
+      <c r="M9" s="150"/>
+      <c r="N9" s="150"/>
+      <c r="O9" s="150"/>
+      <c r="P9" s="150"/>
+      <c r="Q9" s="150"/>
+      <c r="R9" s="150"/>
+      <c r="S9" s="150"/>
+      <c r="T9" s="150"/>
+      <c r="U9" s="150"/>
+      <c r="V9" s="150"/>
+      <c r="W9" s="150"/>
+      <c r="X9" s="150"/>
+      <c r="Y9" s="150"/>
+      <c r="Z9" s="150"/>
+      <c r="AA9" s="150"/>
+      <c r="AB9" s="150"/>
+      <c r="AC9" s="150"/>
+      <c r="AD9" s="150"/>
+      <c r="AE9" s="150"/>
+      <c r="AF9" s="150"/>
+      <c r="AG9" s="150"/>
+      <c r="AH9" s="150"/>
+    </row>
+    <row r="10" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A10" s="152" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="93"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="95" t="s">
+      <c r="B10" s="153"/>
+      <c r="C10" s="153"/>
+      <c r="D10" s="153"/>
+      <c r="E10" s="153"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="154"/>
+      <c r="H10" s="155" t="s">
         <v>26</v>
       </c>
-      <c r="I10" s="96"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="96"/>
-      <c r="O10" s="96"/>
-      <c r="P10" s="96"/>
-      <c r="Q10" s="96"/>
-      <c r="R10" s="96"/>
-      <c r="S10" s="96"/>
-      <c r="T10" s="96"/>
-      <c r="U10" s="96"/>
-      <c r="V10" s="96"/>
-      <c r="W10" s="96"/>
-      <c r="X10" s="96"/>
-      <c r="Y10" s="96"/>
-      <c r="Z10" s="96"/>
-      <c r="AA10" s="96"/>
-      <c r="AB10" s="96"/>
-      <c r="AC10" s="96"/>
-      <c r="AD10" s="96"/>
-      <c r="AE10" s="96"/>
-      <c r="AF10" s="96"/>
-      <c r="AG10" s="96"/>
-      <c r="AH10" s="96"/>
-    </row>
-    <row r="11" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="97" t="s">
+      <c r="I10" s="156"/>
+      <c r="J10" s="156"/>
+      <c r="K10" s="156"/>
+      <c r="L10" s="156"/>
+      <c r="M10" s="156"/>
+      <c r="N10" s="156"/>
+      <c r="O10" s="156"/>
+      <c r="P10" s="156"/>
+      <c r="Q10" s="156"/>
+      <c r="R10" s="156"/>
+      <c r="S10" s="156"/>
+      <c r="T10" s="156"/>
+      <c r="U10" s="156"/>
+      <c r="V10" s="156"/>
+      <c r="W10" s="156"/>
+      <c r="X10" s="156"/>
+      <c r="Y10" s="156"/>
+      <c r="Z10" s="156"/>
+      <c r="AA10" s="156"/>
+      <c r="AB10" s="156"/>
+      <c r="AC10" s="156"/>
+      <c r="AD10" s="156"/>
+      <c r="AE10" s="156"/>
+      <c r="AF10" s="156"/>
+      <c r="AG10" s="156"/>
+      <c r="AH10" s="156"/>
+    </row>
+    <row r="11" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A11" s="140" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="98"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98"/>
-      <c r="K11" s="98"/>
-      <c r="L11" s="98"/>
-      <c r="M11" s="98"/>
-      <c r="N11" s="98"/>
-      <c r="O11" s="98"/>
-      <c r="P11" s="98"/>
-      <c r="Q11" s="98"/>
-      <c r="R11" s="98"/>
-      <c r="S11" s="98"/>
-      <c r="T11" s="98"/>
-      <c r="U11" s="98"/>
-      <c r="V11" s="98"/>
-      <c r="W11" s="98"/>
-      <c r="X11" s="98"/>
-      <c r="Y11" s="98"/>
-      <c r="Z11" s="98"/>
-      <c r="AA11" s="98"/>
-      <c r="AB11" s="98"/>
-      <c r="AC11" s="98"/>
-      <c r="AD11" s="98"/>
-      <c r="AE11" s="98"/>
-      <c r="AF11" s="98"/>
-      <c r="AG11" s="98"/>
-      <c r="AH11" s="98"/>
-    </row>
-    <row r="12" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="141"/>
+      <c r="C11" s="141"/>
+      <c r="D11" s="141"/>
+      <c r="E11" s="141"/>
+      <c r="F11" s="141"/>
+      <c r="G11" s="141"/>
+      <c r="H11" s="141"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="141"/>
+      <c r="K11" s="141"/>
+      <c r="L11" s="141"/>
+      <c r="M11" s="141"/>
+      <c r="N11" s="141"/>
+      <c r="O11" s="141"/>
+      <c r="P11" s="141"/>
+      <c r="Q11" s="141"/>
+      <c r="R11" s="141"/>
+      <c r="S11" s="141"/>
+      <c r="T11" s="141"/>
+      <c r="U11" s="141"/>
+      <c r="V11" s="141"/>
+      <c r="W11" s="141"/>
+      <c r="X11" s="141"/>
+      <c r="Y11" s="141"/>
+      <c r="Z11" s="141"/>
+      <c r="AA11" s="141"/>
+      <c r="AB11" s="141"/>
+      <c r="AC11" s="141"/>
+      <c r="AD11" s="141"/>
+      <c r="AE11" s="141"/>
+      <c r="AF11" s="141"/>
+      <c r="AG11" s="141"/>
+      <c r="AH11" s="141"/>
+    </row>
+    <row r="12" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A12" s="61"/>
     </row>
-    <row r="13" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A13" s="61"/>
     </row>
-    <row r="14" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A14" s="61"/>
     </row>
-    <row r="15" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A15" s="61"/>
     </row>
-    <row r="16" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A16" s="61"/>
     </row>
-    <row r="17" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A17" s="61"/>
     </row>
-    <row r="18" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A18" s="61"/>
     </row>
-    <row r="19" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A19" s="61"/>
     </row>
-    <row r="20" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A20" s="61"/>
     </row>
-    <row r="21" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A21" s="61"/>
     </row>
-    <row r="22" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A22" s="61"/>
     </row>
-    <row r="23" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A23" s="62"/>
       <c r="B23" s="58"/>
       <c r="C23" s="58"/>
@@ -3445,21 +3944,21 @@
       <c r="AG23" s="58"/>
       <c r="AH23" s="58"/>
     </row>
-    <row r="24" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="99" t="s">
+    <row r="24" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A24" s="142" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="100"/>
-      <c r="C24" s="99" t="s">
+      <c r="B24" s="143"/>
+      <c r="C24" s="142" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="101"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="101"/>
-      <c r="G24" s="101"/>
-      <c r="H24" s="101"/>
-      <c r="I24" s="101"/>
-      <c r="J24" s="100"/>
+      <c r="D24" s="144"/>
+      <c r="E24" s="144"/>
+      <c r="F24" s="144"/>
+      <c r="G24" s="144"/>
+      <c r="H24" s="144"/>
+      <c r="I24" s="144"/>
+      <c r="J24" s="143"/>
       <c r="K24" s="66" t="s">
         <v>30</v>
       </c>
@@ -3472,34 +3971,34 @@
       <c r="N24" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="O24" s="102" t="s">
+      <c r="O24" s="145" t="s">
         <v>34</v>
       </c>
-      <c r="P24" s="102"/>
-      <c r="Q24" s="102"/>
-      <c r="R24" s="102"/>
-      <c r="S24" s="102"/>
-      <c r="T24" s="102"/>
-      <c r="U24" s="102"/>
-      <c r="V24" s="102"/>
-      <c r="W24" s="102"/>
-      <c r="X24" s="102"/>
-      <c r="Y24" s="102"/>
-      <c r="Z24" s="102"/>
-      <c r="AA24" s="102"/>
-      <c r="AB24" s="102"/>
-      <c r="AC24" s="102"/>
-      <c r="AD24" s="102"/>
-      <c r="AE24" s="102"/>
-      <c r="AF24" s="102"/>
-      <c r="AG24" s="102"/>
-      <c r="AH24" s="102"/>
-    </row>
-    <row r="25" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="83">
+      <c r="P24" s="145"/>
+      <c r="Q24" s="145"/>
+      <c r="R24" s="145"/>
+      <c r="S24" s="145"/>
+      <c r="T24" s="145"/>
+      <c r="U24" s="145"/>
+      <c r="V24" s="145"/>
+      <c r="W24" s="145"/>
+      <c r="X24" s="145"/>
+      <c r="Y24" s="145"/>
+      <c r="Z24" s="145"/>
+      <c r="AA24" s="145"/>
+      <c r="AB24" s="145"/>
+      <c r="AC24" s="145"/>
+      <c r="AD24" s="145"/>
+      <c r="AE24" s="145"/>
+      <c r="AF24" s="145"/>
+      <c r="AG24" s="145"/>
+      <c r="AH24" s="145"/>
+    </row>
+    <row r="25" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A25" s="101">
         <v>1</v>
       </c>
-      <c r="B25" s="84"/>
+      <c r="B25" s="102"/>
       <c r="C25" s="64" t="s">
         <v>35</v>
       </c>
@@ -3516,34 +4015,34 @@
       <c r="L25" s="67"/>
       <c r="M25" s="67"/>
       <c r="N25" s="64"/>
-      <c r="O25" s="85"/>
-      <c r="P25" s="85"/>
-      <c r="Q25" s="85"/>
-      <c r="R25" s="85"/>
-      <c r="S25" s="85"/>
-      <c r="T25" s="85"/>
-      <c r="U25" s="85"/>
-      <c r="V25" s="85"/>
-      <c r="W25" s="85"/>
-      <c r="X25" s="85"/>
-      <c r="Y25" s="85"/>
-      <c r="Z25" s="85"/>
-      <c r="AA25" s="85"/>
-      <c r="AB25" s="85"/>
-      <c r="AC25" s="85"/>
-      <c r="AD25" s="85"/>
-      <c r="AE25" s="85"/>
-      <c r="AF25" s="85"/>
-      <c r="AG25" s="85"/>
-      <c r="AH25" s="85"/>
-    </row>
-    <row r="26" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="83">
+      <c r="O25" s="103"/>
+      <c r="P25" s="103"/>
+      <c r="Q25" s="103"/>
+      <c r="R25" s="103"/>
+      <c r="S25" s="103"/>
+      <c r="T25" s="103"/>
+      <c r="U25" s="103"/>
+      <c r="V25" s="103"/>
+      <c r="W25" s="103"/>
+      <c r="X25" s="103"/>
+      <c r="Y25" s="103"/>
+      <c r="Z25" s="103"/>
+      <c r="AA25" s="103"/>
+      <c r="AB25" s="103"/>
+      <c r="AC25" s="103"/>
+      <c r="AD25" s="103"/>
+      <c r="AE25" s="103"/>
+      <c r="AF25" s="103"/>
+      <c r="AG25" s="103"/>
+      <c r="AH25" s="103"/>
+    </row>
+    <row r="26" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A26" s="101">
         <v>2</v>
       </c>
-      <c r="B26" s="84"/>
+      <c r="B26" s="102"/>
       <c r="C26" s="78" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="65"/>
@@ -3558,34 +4057,34 @@
       <c r="L26" s="67"/>
       <c r="M26" s="67"/>
       <c r="N26" s="64"/>
-      <c r="O26" s="85"/>
-      <c r="P26" s="85"/>
-      <c r="Q26" s="85"/>
-      <c r="R26" s="85"/>
-      <c r="S26" s="85"/>
-      <c r="T26" s="85"/>
-      <c r="U26" s="85"/>
-      <c r="V26" s="85"/>
-      <c r="W26" s="85"/>
-      <c r="X26" s="85"/>
-      <c r="Y26" s="85"/>
-      <c r="Z26" s="85"/>
-      <c r="AA26" s="85"/>
-      <c r="AB26" s="85"/>
-      <c r="AC26" s="85"/>
-      <c r="AD26" s="85"/>
-      <c r="AE26" s="85"/>
-      <c r="AF26" s="85"/>
-      <c r="AG26" s="85"/>
-      <c r="AH26" s="85"/>
-    </row>
-    <row r="27" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="83">
+      <c r="O26" s="103"/>
+      <c r="P26" s="103"/>
+      <c r="Q26" s="103"/>
+      <c r="R26" s="103"/>
+      <c r="S26" s="103"/>
+      <c r="T26" s="103"/>
+      <c r="U26" s="103"/>
+      <c r="V26" s="103"/>
+      <c r="W26" s="103"/>
+      <c r="X26" s="103"/>
+      <c r="Y26" s="103"/>
+      <c r="Z26" s="103"/>
+      <c r="AA26" s="103"/>
+      <c r="AB26" s="103"/>
+      <c r="AC26" s="103"/>
+      <c r="AD26" s="103"/>
+      <c r="AE26" s="103"/>
+      <c r="AF26" s="103"/>
+      <c r="AG26" s="103"/>
+      <c r="AH26" s="103"/>
+    </row>
+    <row r="27" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A27" s="101">
         <v>3</v>
       </c>
-      <c r="B27" s="84"/>
+      <c r="B27" s="102"/>
       <c r="C27" s="78" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="65"/>
@@ -3600,48 +4099,71 @@
       <c r="L27" s="67"/>
       <c r="M27" s="67"/>
       <c r="N27" s="64"/>
-      <c r="O27" s="85"/>
-      <c r="P27" s="85"/>
-      <c r="Q27" s="85"/>
-      <c r="R27" s="85"/>
-      <c r="S27" s="85"/>
-      <c r="T27" s="85"/>
-      <c r="U27" s="85"/>
-      <c r="V27" s="85"/>
-      <c r="W27" s="85"/>
-      <c r="X27" s="85"/>
-      <c r="Y27" s="85"/>
-      <c r="Z27" s="85"/>
-      <c r="AA27" s="85"/>
-      <c r="AB27" s="85"/>
-      <c r="AC27" s="85"/>
-      <c r="AD27" s="85"/>
-      <c r="AE27" s="85"/>
-      <c r="AF27" s="85"/>
-      <c r="AG27" s="85"/>
-      <c r="AH27" s="85"/>
+      <c r="O27" s="103"/>
+      <c r="P27" s="103"/>
+      <c r="Q27" s="103"/>
+      <c r="R27" s="103"/>
+      <c r="S27" s="103"/>
+      <c r="T27" s="103"/>
+      <c r="U27" s="103"/>
+      <c r="V27" s="103"/>
+      <c r="W27" s="103"/>
+      <c r="X27" s="103"/>
+      <c r="Y27" s="103"/>
+      <c r="Z27" s="103"/>
+      <c r="AA27" s="103"/>
+      <c r="AB27" s="103"/>
+      <c r="AC27" s="103"/>
+      <c r="AD27" s="103"/>
+      <c r="AE27" s="103"/>
+      <c r="AF27" s="103"/>
+      <c r="AG27" s="103"/>
+      <c r="AH27" s="103"/>
+    </row>
+    <row r="28" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A28" s="101">
+        <v>4</v>
+      </c>
+      <c r="B28" s="102"/>
+      <c r="C28" s="78" t="s">
+        <v>234</v>
+      </c>
+      <c r="D28" s="65"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="65"/>
+      <c r="K28" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="L28" s="67"/>
+      <c r="M28" s="67"/>
+      <c r="N28" s="64"/>
+      <c r="O28" s="103"/>
+      <c r="P28" s="103"/>
+      <c r="Q28" s="103"/>
+      <c r="R28" s="103"/>
+      <c r="S28" s="103"/>
+      <c r="T28" s="103"/>
+      <c r="U28" s="103"/>
+      <c r="V28" s="103"/>
+      <c r="W28" s="103"/>
+      <c r="X28" s="103"/>
+      <c r="Y28" s="103"/>
+      <c r="Z28" s="103"/>
+      <c r="AA28" s="103"/>
+      <c r="AB28" s="103"/>
+      <c r="AC28" s="103"/>
+      <c r="AD28" s="103"/>
+      <c r="AE28" s="103"/>
+      <c r="AF28" s="103"/>
+      <c r="AG28" s="103"/>
+      <c r="AH28" s="103"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="A1:K4"/>
-    <mergeCell ref="L1:P2"/>
-    <mergeCell ref="Q1:U2"/>
-    <mergeCell ref="L3:P4"/>
-    <mergeCell ref="Q3:U4"/>
-    <mergeCell ref="V3:X4"/>
-    <mergeCell ref="AC3:AE4"/>
-    <mergeCell ref="AF3:AH4"/>
-    <mergeCell ref="V1:X2"/>
-    <mergeCell ref="AC1:AE2"/>
-    <mergeCell ref="AF1:AH2"/>
-    <mergeCell ref="Y1:AB2"/>
-    <mergeCell ref="Y3:AB4"/>
-    <mergeCell ref="A11:AH11"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:J24"/>
-    <mergeCell ref="O24:AH24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="O25:AH25"/>
+  <mergeCells count="37">
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="O27:AH27"/>
     <mergeCell ref="A26:B26"/>
@@ -3658,6 +4180,27 @@
     <mergeCell ref="H9:AH9"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="H10:AH10"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="O24:AH24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="O25:AH25"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="O28:AH28"/>
+    <mergeCell ref="A1:K4"/>
+    <mergeCell ref="L1:P2"/>
+    <mergeCell ref="Q1:U2"/>
+    <mergeCell ref="L3:P4"/>
+    <mergeCell ref="Q3:U4"/>
+    <mergeCell ref="V3:X4"/>
+    <mergeCell ref="AC3:AE4"/>
+    <mergeCell ref="AF3:AH4"/>
+    <mergeCell ref="V1:X2"/>
+    <mergeCell ref="AC1:AE2"/>
+    <mergeCell ref="AF1:AH2"/>
+    <mergeCell ref="Y1:AB2"/>
+    <mergeCell ref="Y3:AB4"/>
+    <mergeCell ref="A11:AH11"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3669,7 +4212,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Y19"/>
-  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="6" style="34" customWidth="1"/>
     <col min="2" max="8" width="3.6640625" style="34"/>
@@ -3682,573 +4225,613 @@
     <col min="22" max="22" width="8.33203125" style="34" customWidth="1"/>
     <col min="23" max="23" width="12.33203125" style="34" customWidth="1"/>
     <col min="24" max="24" width="7.44140625" style="34" customWidth="1"/>
-    <col min="25" max="25" width="7.6640625" style="34" customWidth="1"/>
+    <col min="25" max="25" width="32.77734375" style="34" customWidth="1"/>
     <col min="26" max="16384" width="3.6640625" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="120" t="s">
+    <row r="1" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A1" s="164" t="s">
+        <v>235</v>
+      </c>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="113" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="119" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="123" t="s">
+        <v>3</v>
+      </c>
+      <c r="U1" s="134" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1" s="135"/>
+      <c r="W1" s="128" t="s">
+        <v>11</v>
+      </c>
+      <c r="X1" s="124" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y1" s="125"/>
+    </row>
+    <row r="2" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A2" s="107"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="118"/>
+      <c r="O2" s="121"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="122"/>
+      <c r="R2" s="122"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="123"/>
+      <c r="U2" s="137"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="131"/>
+      <c r="X2" s="126"/>
+      <c r="Y2" s="127"/>
+    </row>
+    <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A3" s="107"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="113" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="114"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="119" t="s">
+        <v>14</v>
+      </c>
+      <c r="P3" s="120"/>
+      <c r="Q3" s="120"/>
+      <c r="R3" s="120"/>
+      <c r="S3" s="120"/>
+      <c r="T3" s="123" t="s">
+        <v>15</v>
+      </c>
+      <c r="U3" s="134" t="s">
+        <v>6</v>
+      </c>
+      <c r="V3" s="135"/>
+      <c r="W3" s="123" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="124" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y3" s="125"/>
+    </row>
+    <row r="4" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="117"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="121"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="123"/>
+      <c r="U4" s="137"/>
+      <c r="V4" s="138"/>
+      <c r="W4" s="123"/>
+      <c r="X4" s="126"/>
+      <c r="Y4" s="127"/>
+    </row>
+    <row r="5" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A5" s="182" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="129" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="130"/>
-      <c r="L1" s="130"/>
-      <c r="M1" s="130"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="135" t="s">
-        <v>10</v>
-      </c>
-      <c r="P1" s="136"/>
-      <c r="Q1" s="136"/>
-      <c r="R1" s="136"/>
-      <c r="S1" s="136"/>
-      <c r="T1" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="U1" s="114" t="s">
-        <v>6</v>
-      </c>
-      <c r="V1" s="115"/>
-      <c r="W1" s="108" t="s">
-        <v>11</v>
-      </c>
-      <c r="X1" s="104" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y1" s="105"/>
-    </row>
-    <row r="2" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="123"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="133"/>
-      <c r="M2" s="133"/>
-      <c r="N2" s="134"/>
-      <c r="O2" s="137"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="103"/>
-      <c r="U2" s="117"/>
-      <c r="V2" s="118"/>
-      <c r="W2" s="111"/>
-      <c r="X2" s="106"/>
-      <c r="Y2" s="107"/>
-    </row>
-    <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="123"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="129" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="130"/>
-      <c r="N3" s="131"/>
-      <c r="O3" s="135" t="s">
-        <v>14</v>
-      </c>
-      <c r="P3" s="136"/>
-      <c r="Q3" s="136"/>
-      <c r="R3" s="136"/>
-      <c r="S3" s="136"/>
-      <c r="T3" s="103" t="s">
-        <v>15</v>
-      </c>
-      <c r="U3" s="114" t="s">
-        <v>6</v>
-      </c>
-      <c r="V3" s="115"/>
-      <c r="W3" s="103" t="s">
-        <v>16</v>
-      </c>
-      <c r="X3" s="104" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y3" s="105"/>
-    </row>
-    <row r="4" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="126"/>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="133"/>
-      <c r="L4" s="133"/>
-      <c r="M4" s="133"/>
-      <c r="N4" s="134"/>
-      <c r="O4" s="137"/>
-      <c r="P4" s="138"/>
-      <c r="Q4" s="138"/>
-      <c r="R4" s="138"/>
-      <c r="S4" s="138"/>
-      <c r="T4" s="103"/>
-      <c r="U4" s="117"/>
-      <c r="V4" s="118"/>
-      <c r="W4" s="103"/>
-      <c r="X4" s="106"/>
-      <c r="Y4" s="107"/>
-    </row>
-    <row r="5" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="139" t="s">
+      <c r="B5" s="182"/>
+      <c r="C5" s="182"/>
+      <c r="D5" s="182"/>
+      <c r="E5" s="182"/>
+      <c r="F5" s="183" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="183"/>
+      <c r="H5" s="183"/>
+      <c r="I5" s="183"/>
+      <c r="J5" s="182" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="139"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="139"/>
-      <c r="E5" s="139"/>
-      <c r="F5" s="140" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="140"/>
-      <c r="H5" s="140"/>
-      <c r="I5" s="140"/>
-      <c r="J5" s="139" t="s">
+      <c r="K5" s="182"/>
+      <c r="L5" s="182"/>
+      <c r="M5" s="182"/>
+      <c r="N5" s="182"/>
+      <c r="O5" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="P5" s="183"/>
+      <c r="Q5" s="183"/>
+      <c r="R5" s="183"/>
+      <c r="S5" s="183"/>
+      <c r="T5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="139"/>
-      <c r="L5" s="139"/>
-      <c r="M5" s="139"/>
-      <c r="N5" s="139"/>
-      <c r="O5" s="140" t="s">
-        <v>20</v>
-      </c>
-      <c r="P5" s="140"/>
-      <c r="Q5" s="140"/>
-      <c r="R5" s="140"/>
-      <c r="S5" s="140"/>
-      <c r="T5" s="6" t="s">
+      <c r="U5" s="183" t="s">
+        <v>26</v>
+      </c>
+      <c r="V5" s="183"/>
+      <c r="W5" s="183"/>
+      <c r="X5" s="183"/>
+      <c r="Y5" s="183"/>
+    </row>
+    <row r="6" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A6" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="U5" s="140" t="s">
-        <v>26</v>
-      </c>
-      <c r="V5" s="140"/>
-      <c r="W5" s="140"/>
-      <c r="X5" s="140"/>
-      <c r="Y5" s="140"/>
-    </row>
-    <row r="6" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="35" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" s="32" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:25" s="32" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A7" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="123" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="123"/>
+      <c r="H7" s="123"/>
+      <c r="I7" s="123"/>
+      <c r="J7" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="59" t="s">
+      <c r="K7" s="175" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="141" t="s">
+      <c r="L7" s="176"/>
+      <c r="M7" s="176"/>
+      <c r="N7" s="181"/>
+      <c r="O7" s="123" t="s">
         <v>44</v>
       </c>
-      <c r="L7" s="142"/>
-      <c r="M7" s="142"/>
-      <c r="N7" s="143"/>
-      <c r="O7" s="103" t="s">
+      <c r="P7" s="123"/>
+      <c r="Q7" s="123"/>
+      <c r="R7" s="123"/>
+      <c r="S7" s="123" t="s">
         <v>45</v>
       </c>
-      <c r="P7" s="103"/>
-      <c r="Q7" s="103"/>
-      <c r="R7" s="103"/>
-      <c r="S7" s="103" t="s">
+      <c r="T7" s="123"/>
+      <c r="U7" s="175" t="s">
         <v>46</v>
       </c>
-      <c r="T7" s="103"/>
-      <c r="U7" s="141" t="s">
-        <v>47</v>
-      </c>
-      <c r="V7" s="142"/>
-      <c r="W7" s="142"/>
-      <c r="X7" s="142"/>
-      <c r="Y7" s="142"/>
-    </row>
-    <row r="8" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="V7" s="176"/>
+      <c r="W7" s="176"/>
+      <c r="X7" s="176"/>
+      <c r="Y7" s="176"/>
+    </row>
+    <row r="8" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A8" s="44">
         <v>1</v>
       </c>
-      <c r="B8" s="144" t="s">
+      <c r="B8" s="180" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="180"/>
+      <c r="D8" s="180"/>
+      <c r="E8" s="180"/>
+      <c r="F8" s="180"/>
+      <c r="G8" s="180"/>
+      <c r="H8" s="180"/>
+      <c r="I8" s="180"/>
+      <c r="J8" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="144"/>
-      <c r="D8" s="144"/>
-      <c r="E8" s="144"/>
-      <c r="F8" s="144"/>
-      <c r="G8" s="144"/>
-      <c r="H8" s="144"/>
-      <c r="I8" s="144"/>
-      <c r="J8" s="55" t="s">
+      <c r="K8" s="166" t="s">
         <v>49</v>
       </c>
-      <c r="K8" s="145" t="s">
+      <c r="L8" s="169"/>
+      <c r="M8" s="169"/>
+      <c r="N8" s="167"/>
+      <c r="O8" s="165">
+        <v>4000</v>
+      </c>
+      <c r="P8" s="165"/>
+      <c r="Q8" s="165"/>
+      <c r="R8" s="165"/>
+      <c r="S8" s="165" t="s">
         <v>50</v>
       </c>
-      <c r="L8" s="146"/>
-      <c r="M8" s="146"/>
-      <c r="N8" s="147"/>
-      <c r="O8" s="148">
-        <v>4000</v>
-      </c>
-      <c r="P8" s="148"/>
-      <c r="Q8" s="148"/>
-      <c r="R8" s="148"/>
-      <c r="S8" s="148" t="s">
+      <c r="T8" s="165"/>
+      <c r="U8" s="166" t="s">
         <v>51</v>
       </c>
-      <c r="T8" s="148"/>
-      <c r="U8" s="145" t="s">
+      <c r="V8" s="169"/>
+      <c r="W8" s="169"/>
+      <c r="X8" s="169"/>
+      <c r="Y8" s="169"/>
+    </row>
+    <row r="9" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A9" s="35"/>
+    </row>
+    <row r="10" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A10" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="V8" s="146"/>
-      <c r="W8" s="146"/>
-      <c r="X8" s="146"/>
-      <c r="Y8" s="146"/>
-    </row>
-    <row r="9" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="35"/>
-    </row>
-    <row r="10" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="35" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" s="32" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:25" s="32" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A11" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="103" t="s">
+      <c r="B11" s="123" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="123"/>
+      <c r="D11" s="123"/>
+      <c r="E11" s="123"/>
+      <c r="F11" s="123" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="123"/>
+      <c r="H11" s="123"/>
+      <c r="I11" s="123"/>
+      <c r="J11" s="123"/>
+      <c r="K11" s="123" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="103"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="103"/>
-      <c r="F11" s="103" t="s">
+      <c r="L11" s="123"/>
+      <c r="M11" s="123"/>
+      <c r="N11" s="123"/>
+      <c r="O11" s="123" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="103"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="103"/>
-      <c r="J11" s="103"/>
-      <c r="K11" s="103" t="s">
+      <c r="P11" s="123"/>
+      <c r="Q11" s="179" t="s">
+        <v>45</v>
+      </c>
+      <c r="R11" s="179"/>
+      <c r="S11" s="179"/>
+      <c r="T11" s="179"/>
+      <c r="U11" s="123" t="s">
         <v>55</v>
       </c>
-      <c r="L11" s="103"/>
-      <c r="M11" s="103"/>
-      <c r="N11" s="103"/>
-      <c r="O11" s="103" t="s">
-        <v>43</v>
-      </c>
-      <c r="P11" s="103"/>
-      <c r="Q11" s="155" t="s">
-        <v>46</v>
-      </c>
-      <c r="R11" s="155"/>
-      <c r="S11" s="155"/>
-      <c r="T11" s="155"/>
-      <c r="U11" s="103" t="s">
+      <c r="V11" s="123"/>
+      <c r="W11" s="123"/>
+      <c r="X11" s="175" t="s">
         <v>56</v>
       </c>
-      <c r="V11" s="103"/>
-      <c r="W11" s="103"/>
-      <c r="X11" s="141" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y11" s="142"/>
-    </row>
-    <row r="12" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="Y11" s="176"/>
+    </row>
+    <row r="12" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A12" s="44">
         <v>1</v>
       </c>
-      <c r="B12" s="148" t="s">
+      <c r="B12" s="165" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="165"/>
+      <c r="D12" s="165"/>
+      <c r="E12" s="165"/>
+      <c r="F12" s="165" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="148"/>
-      <c r="D12" s="148"/>
-      <c r="E12" s="148"/>
-      <c r="F12" s="148" t="s">
+      <c r="G12" s="165"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="165"/>
+      <c r="J12" s="165"/>
+      <c r="K12" s="166" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="148"/>
-      <c r="H12" s="148"/>
-      <c r="I12" s="148"/>
-      <c r="J12" s="148"/>
-      <c r="K12" s="145" t="s">
+      <c r="L12" s="169"/>
+      <c r="M12" s="169"/>
+      <c r="N12" s="167"/>
+      <c r="O12" s="170" t="s">
+        <v>48</v>
+      </c>
+      <c r="P12" s="171"/>
+      <c r="Q12" s="172" t="s">
+        <v>57</v>
+      </c>
+      <c r="R12" s="165"/>
+      <c r="S12" s="165"/>
+      <c r="T12" s="165"/>
+      <c r="U12" s="168" t="s">
         <v>60</v>
       </c>
-      <c r="L12" s="146"/>
-      <c r="M12" s="146"/>
-      <c r="N12" s="147"/>
-      <c r="O12" s="149" t="s">
-        <v>49</v>
-      </c>
-      <c r="P12" s="150"/>
-      <c r="Q12" s="151" t="s">
-        <v>58</v>
-      </c>
-      <c r="R12" s="148"/>
-      <c r="S12" s="148"/>
-      <c r="T12" s="148"/>
-      <c r="U12" s="152" t="s">
+      <c r="V12" s="165"/>
+      <c r="W12" s="165"/>
+      <c r="X12" s="177" t="s">
         <v>61</v>
       </c>
-      <c r="V12" s="148"/>
-      <c r="W12" s="148"/>
-      <c r="X12" s="153" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y12" s="154"/>
-    </row>
-    <row r="13" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="Y12" s="178"/>
+    </row>
+    <row r="13" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A13" s="44">
         <v>2</v>
       </c>
-      <c r="B13" s="148" t="s">
+      <c r="B13" s="165" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="165"/>
+      <c r="D13" s="165"/>
+      <c r="E13" s="165"/>
+      <c r="F13" s="165" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="148"/>
-      <c r="D13" s="148"/>
-      <c r="E13" s="148"/>
-      <c r="F13" s="148" t="s">
+      <c r="G13" s="165"/>
+      <c r="H13" s="165"/>
+      <c r="I13" s="165"/>
+      <c r="J13" s="165"/>
+      <c r="K13" s="166" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="169"/>
+      <c r="M13" s="169"/>
+      <c r="N13" s="167"/>
+      <c r="O13" s="170"/>
+      <c r="P13" s="171"/>
+      <c r="Q13" s="172" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="148"/>
-      <c r="H13" s="148"/>
-      <c r="I13" s="148"/>
-      <c r="J13" s="148"/>
-      <c r="K13" s="145" t="s">
+      <c r="R13" s="165"/>
+      <c r="S13" s="165"/>
+      <c r="T13" s="165"/>
+      <c r="U13" s="168" t="s">
         <v>60</v>
       </c>
-      <c r="L13" s="146"/>
-      <c r="M13" s="146"/>
-      <c r="N13" s="147"/>
-      <c r="O13" s="149"/>
-      <c r="P13" s="150"/>
-      <c r="Q13" s="151" t="s">
+      <c r="V13" s="165"/>
+      <c r="W13" s="165"/>
+      <c r="X13" s="165" t="s">
         <v>65</v>
       </c>
-      <c r="R13" s="148"/>
-      <c r="S13" s="148"/>
-      <c r="T13" s="148"/>
-      <c r="U13" s="152" t="s">
-        <v>61</v>
-      </c>
-      <c r="V13" s="148"/>
-      <c r="W13" s="148"/>
-      <c r="X13" s="148" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y13" s="148"/>
-    </row>
-    <row r="14" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="Y13" s="165"/>
+    </row>
+    <row r="14" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A14" s="44">
         <v>3</v>
       </c>
-      <c r="B14" s="148" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="148"/>
-      <c r="D14" s="148"/>
-      <c r="E14" s="148"/>
-      <c r="F14" s="148" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14" s="148"/>
-      <c r="H14" s="148"/>
-      <c r="I14" s="148"/>
-      <c r="J14" s="148"/>
-      <c r="K14" s="145" t="s">
+      <c r="B14" s="165" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="165"/>
+      <c r="D14" s="165"/>
+      <c r="E14" s="165"/>
+      <c r="F14" s="165" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="165"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="165"/>
+      <c r="J14" s="165"/>
+      <c r="K14" s="166" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="169"/>
+      <c r="M14" s="169"/>
+      <c r="N14" s="167"/>
+      <c r="O14" s="170"/>
+      <c r="P14" s="171"/>
+      <c r="Q14" s="172" t="s">
+        <v>64</v>
+      </c>
+      <c r="R14" s="165"/>
+      <c r="S14" s="165"/>
+      <c r="T14" s="165"/>
+      <c r="U14" s="168" t="s">
         <v>60</v>
       </c>
-      <c r="L14" s="146"/>
-      <c r="M14" s="146"/>
-      <c r="N14" s="147"/>
-      <c r="O14" s="149"/>
-      <c r="P14" s="150"/>
-      <c r="Q14" s="151" t="s">
-        <v>65</v>
-      </c>
-      <c r="R14" s="148"/>
-      <c r="S14" s="148"/>
-      <c r="T14" s="148"/>
-      <c r="U14" s="152" t="s">
-        <v>61</v>
-      </c>
-      <c r="V14" s="148"/>
-      <c r="W14" s="148"/>
-      <c r="X14" s="156">
+      <c r="V14" s="165"/>
+      <c r="W14" s="165"/>
+      <c r="X14" s="173">
         <v>1</v>
       </c>
-      <c r="Y14" s="157"/>
-    </row>
-    <row r="15" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="Y14" s="174"/>
+    </row>
+    <row r="15" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A15" s="44">
         <v>4</v>
       </c>
-      <c r="B15" s="148" t="s">
+      <c r="B15" s="165" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="165"/>
+      <c r="D15" s="165"/>
+      <c r="E15" s="165"/>
+      <c r="F15" s="165" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="148"/>
-      <c r="D15" s="148"/>
-      <c r="E15" s="148"/>
-      <c r="F15" s="148" t="s">
+      <c r="G15" s="165"/>
+      <c r="H15" s="165"/>
+      <c r="I15" s="165"/>
+      <c r="J15" s="165"/>
+      <c r="K15" s="166" t="s">
         <v>69</v>
       </c>
-      <c r="G15" s="148"/>
-      <c r="H15" s="148"/>
-      <c r="I15" s="148"/>
-      <c r="J15" s="148"/>
-      <c r="K15" s="145" t="s">
+      <c r="L15" s="169"/>
+      <c r="M15" s="169"/>
+      <c r="N15" s="167"/>
+      <c r="O15" s="170"/>
+      <c r="P15" s="171"/>
+      <c r="Q15" s="172" t="s">
+        <v>67</v>
+      </c>
+      <c r="R15" s="165"/>
+      <c r="S15" s="165"/>
+      <c r="T15" s="165"/>
+      <c r="U15" s="165" t="s">
         <v>70</v>
       </c>
-      <c r="L15" s="146"/>
-      <c r="M15" s="146"/>
-      <c r="N15" s="147"/>
-      <c r="O15" s="149"/>
-      <c r="P15" s="150"/>
-      <c r="Q15" s="151" t="s">
-        <v>68</v>
-      </c>
-      <c r="R15" s="148"/>
-      <c r="S15" s="148"/>
-      <c r="T15" s="148"/>
-      <c r="U15" s="148" t="s">
+      <c r="V15" s="165"/>
+      <c r="W15" s="165"/>
+      <c r="X15" s="166" t="s">
         <v>71</v>
       </c>
-      <c r="V15" s="148"/>
-      <c r="W15" s="148"/>
-      <c r="X15" s="145" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y15" s="147"/>
-    </row>
-    <row r="16" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="Y15" s="167"/>
+    </row>
+    <row r="16" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A16" s="44">
         <v>5</v>
       </c>
-      <c r="B16" s="148" t="s">
+      <c r="B16" s="165" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="165"/>
+      <c r="D16" s="165"/>
+      <c r="E16" s="165"/>
+      <c r="F16" s="165" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="148"/>
-      <c r="D16" s="148"/>
-      <c r="E16" s="148"/>
-      <c r="F16" s="148" t="s">
+      <c r="G16" s="165"/>
+      <c r="H16" s="165"/>
+      <c r="I16" s="165"/>
+      <c r="J16" s="165"/>
+      <c r="K16" s="166" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" s="169"/>
+      <c r="M16" s="169"/>
+      <c r="N16" s="167"/>
+      <c r="O16" s="170"/>
+      <c r="P16" s="171"/>
+      <c r="Q16" s="172" t="s">
         <v>74</v>
       </c>
-      <c r="G16" s="148"/>
-      <c r="H16" s="148"/>
-      <c r="I16" s="148"/>
-      <c r="J16" s="148"/>
-      <c r="K16" s="145" t="s">
-        <v>60</v>
-      </c>
-      <c r="L16" s="146"/>
-      <c r="M16" s="146"/>
-      <c r="N16" s="147"/>
-      <c r="O16" s="149"/>
-      <c r="P16" s="150"/>
-      <c r="Q16" s="151" t="s">
+      <c r="R16" s="165"/>
+      <c r="S16" s="165"/>
+      <c r="T16" s="165"/>
+      <c r="U16" s="165" t="s">
         <v>75</v>
       </c>
-      <c r="R16" s="148"/>
-      <c r="S16" s="148"/>
-      <c r="T16" s="148"/>
-      <c r="U16" s="148" t="s">
-        <v>76</v>
-      </c>
-      <c r="V16" s="148"/>
-      <c r="W16" s="148"/>
-      <c r="X16" s="145">
+      <c r="V16" s="165"/>
+      <c r="W16" s="165"/>
+      <c r="X16" s="166">
         <v>10</v>
       </c>
-      <c r="Y16" s="147"/>
-    </row>
-    <row r="17" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="Y16" s="167"/>
+    </row>
+    <row r="17" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A17" s="44">
         <v>6</v>
       </c>
-      <c r="B17" s="148" t="s">
+      <c r="B17" s="165" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="165"/>
+      <c r="D17" s="165"/>
+      <c r="E17" s="165"/>
+      <c r="F17" s="165" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="148"/>
-      <c r="D17" s="148"/>
-      <c r="E17" s="148"/>
-      <c r="F17" s="148" t="s">
+      <c r="G17" s="165"/>
+      <c r="H17" s="165"/>
+      <c r="I17" s="165"/>
+      <c r="J17" s="165"/>
+      <c r="K17" s="166" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="169"/>
+      <c r="M17" s="169"/>
+      <c r="N17" s="167"/>
+      <c r="O17" s="170"/>
+      <c r="P17" s="171"/>
+      <c r="Q17" s="172" t="s">
         <v>78</v>
       </c>
-      <c r="G17" s="148"/>
-      <c r="H17" s="148"/>
-      <c r="I17" s="148"/>
-      <c r="J17" s="148"/>
-      <c r="K17" s="145" t="s">
-        <v>60</v>
-      </c>
-      <c r="L17" s="146"/>
-      <c r="M17" s="146"/>
-      <c r="N17" s="147"/>
-      <c r="O17" s="149"/>
-      <c r="P17" s="150"/>
-      <c r="Q17" s="151" t="s">
-        <v>79</v>
-      </c>
-      <c r="R17" s="148"/>
-      <c r="S17" s="148"/>
-      <c r="T17" s="148"/>
-      <c r="U17" s="148" t="s">
-        <v>76</v>
-      </c>
-      <c r="V17" s="148"/>
-      <c r="W17" s="148"/>
-      <c r="X17" s="145">
+      <c r="R17" s="165"/>
+      <c r="S17" s="165"/>
+      <c r="T17" s="165"/>
+      <c r="U17" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="V17" s="165"/>
+      <c r="W17" s="165"/>
+      <c r="X17" s="166">
         <v>100</v>
       </c>
-      <c r="Y17" s="147"/>
-    </row>
-    <row r="18" spans="1:25" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="36"/>
-    </row>
-    <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y17" s="167"/>
+    </row>
+    <row r="18" spans="1:25" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A18" s="89">
+        <v>7</v>
+      </c>
+      <c r="B18" s="157" t="s">
+        <v>236</v>
+      </c>
+      <c r="C18" s="157"/>
+      <c r="D18" s="157"/>
+      <c r="E18" s="157"/>
+      <c r="F18" s="157" t="s">
+        <v>254</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="157"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="157"/>
+      <c r="K18" s="158" t="s">
+        <v>69</v>
+      </c>
+      <c r="L18" s="160"/>
+      <c r="M18" s="160"/>
+      <c r="N18" s="159"/>
+      <c r="O18" s="161" t="s">
+        <v>48</v>
+      </c>
+      <c r="P18" s="162"/>
+      <c r="Q18" s="163" t="s">
+        <v>236</v>
+      </c>
+      <c r="R18" s="157"/>
+      <c r="S18" s="157"/>
+      <c r="T18" s="157"/>
+      <c r="U18" s="157" t="s">
+        <v>237</v>
+      </c>
+      <c r="V18" s="157"/>
+      <c r="W18" s="157"/>
+      <c r="X18" s="158" t="s">
+        <v>238</v>
+      </c>
+      <c r="Y18" s="159"/>
+    </row>
+    <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A19" s="58"/>
       <c r="B19" s="58"/>
       <c r="C19" s="58"/>
@@ -4276,12 +4859,63 @@
       <c r="Y19" s="58"/>
     </row>
   </sheetData>
-  <mergeCells count="77">
-    <mergeCell ref="J1:N2"/>
-    <mergeCell ref="O1:S2"/>
-    <mergeCell ref="A1:I4"/>
-    <mergeCell ref="J3:N4"/>
-    <mergeCell ref="O3:S4"/>
+  <mergeCells count="84">
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="U5:Y5"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="U7:Y7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="U8:Y8"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="Q12:T12"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="K13:N13"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="Q14:T14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="Q15:T15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:T17"/>
     <mergeCell ref="U17:W17"/>
     <mergeCell ref="X17:Y17"/>
     <mergeCell ref="T1:T2"/>
@@ -4298,62 +4932,18 @@
     <mergeCell ref="X16:Y16"/>
     <mergeCell ref="U13:W13"/>
     <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:T17"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="K16:N16"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:T16"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="Q15:T15"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="K13:N13"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="Q12:T12"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="Q11:T11"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="S8:T8"/>
-    <mergeCell ref="U8:Y8"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="U7:Y7"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="U5:Y5"/>
+    <mergeCell ref="J1:N2"/>
+    <mergeCell ref="O1:S2"/>
+    <mergeCell ref="A1:I4"/>
+    <mergeCell ref="J3:N4"/>
+    <mergeCell ref="O3:S4"/>
+    <mergeCell ref="U18:W18"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:T18"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4363,8 +4953,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:V33"/>
-  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:V34"/>
+  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="6.44140625" style="34" customWidth="1"/>
     <col min="2" max="7" width="3.6640625" style="34"/>
@@ -4379,169 +4969,169 @@
     <col min="19" max="19" width="8" style="34" customWidth="1"/>
     <col min="20" max="20" width="21.44140625" style="34" customWidth="1"/>
     <col min="21" max="21" width="10.88671875" style="34" customWidth="1"/>
-    <col min="22" max="22" width="22" style="34" customWidth="1"/>
+    <col min="22" max="22" width="24.44140625" style="34" customWidth="1"/>
     <col min="23" max="16384" width="3.6640625" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="120" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="129" t="s">
+    <row r="1" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A1" s="104" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="130"/>
-      <c r="K1" s="130"/>
-      <c r="L1" s="130"/>
-      <c r="M1" s="135" t="s">
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="136"/>
-      <c r="O1" s="136"/>
-      <c r="P1" s="136"/>
-      <c r="Q1" s="103" t="s">
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="114" t="s">
+      <c r="R1" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="115"/>
-      <c r="T1" s="108" t="s">
+      <c r="S1" s="135"/>
+      <c r="T1" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="104" t="s">
+      <c r="U1" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="166"/>
-    </row>
-    <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="123"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="133"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="133"/>
-      <c r="M2" s="137"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="117"/>
-      <c r="S2" s="118"/>
-      <c r="T2" s="111"/>
-      <c r="U2" s="106"/>
-      <c r="V2" s="167"/>
-    </row>
-    <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="123"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="129" t="s">
+      <c r="V1" s="186"/>
+    </row>
+    <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A2" s="107"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="123"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="131"/>
+      <c r="U2" s="126"/>
+      <c r="V2" s="187"/>
+    </row>
+    <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A3" s="107"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="135" t="s">
+      <c r="J3" s="114"/>
+      <c r="K3" s="114"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="119" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="136"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="136"/>
-      <c r="Q3" s="103" t="s">
+      <c r="N3" s="120"/>
+      <c r="O3" s="120"/>
+      <c r="P3" s="120"/>
+      <c r="Q3" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="114" t="s">
+      <c r="R3" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="115"/>
-      <c r="T3" s="103" t="s">
+      <c r="S3" s="135"/>
+      <c r="T3" s="123" t="s">
         <v>16</v>
       </c>
-      <c r="U3" s="104" t="s">
+      <c r="U3" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="V3" s="166"/>
-    </row>
-    <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="126"/>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="132"/>
-      <c r="J4" s="133"/>
-      <c r="K4" s="133"/>
-      <c r="L4" s="133"/>
-      <c r="M4" s="137"/>
-      <c r="N4" s="138"/>
-      <c r="O4" s="138"/>
-      <c r="P4" s="138"/>
-      <c r="Q4" s="103"/>
-      <c r="R4" s="117"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="103"/>
-      <c r="U4" s="106"/>
-      <c r="V4" s="167"/>
-    </row>
-    <row r="5" spans="1:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="139" t="s">
+      <c r="V3" s="186"/>
+    </row>
+    <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="123"/>
+      <c r="R4" s="137"/>
+      <c r="S4" s="138"/>
+      <c r="T4" s="123"/>
+      <c r="U4" s="126"/>
+      <c r="V4" s="187"/>
+    </row>
+    <row r="5" spans="1:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A5" s="182" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="182"/>
+      <c r="C5" s="182"/>
+      <c r="D5" s="182"/>
+      <c r="E5" s="183" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="183"/>
+      <c r="G5" s="183"/>
+      <c r="H5" s="183"/>
+      <c r="I5" s="182" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="139"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="139"/>
-      <c r="E5" s="140" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="140"/>
-      <c r="G5" s="140"/>
-      <c r="H5" s="140"/>
-      <c r="I5" s="139" t="s">
+      <c r="J5" s="182"/>
+      <c r="K5" s="182"/>
+      <c r="L5" s="182"/>
+      <c r="M5" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="183"/>
+      <c r="O5" s="183"/>
+      <c r="P5" s="183"/>
+      <c r="Q5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="139"/>
-      <c r="K5" s="139"/>
-      <c r="L5" s="139"/>
-      <c r="M5" s="140" t="s">
-        <v>20</v>
-      </c>
-      <c r="N5" s="140"/>
-      <c r="O5" s="140"/>
-      <c r="P5" s="140"/>
-      <c r="Q5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="R5" s="140" t="s">
+      <c r="R5" s="183" t="s">
         <v>26</v>
       </c>
-      <c r="S5" s="140"/>
-      <c r="T5" s="140"/>
-      <c r="U5" s="140"/>
-      <c r="V5" s="140"/>
-    </row>
-    <row r="6" spans="1:22" s="32" customFormat="1" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="S5" s="183"/>
+      <c r="T5" s="183"/>
+      <c r="U5" s="183"/>
+      <c r="V5" s="183"/>
+    </row>
+    <row r="6" spans="1:22" s="32" customFormat="1" ht="18.75" x14ac:dyDescent="0.8">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="40"/>
@@ -4565,9 +5155,9 @@
       <c r="U6" s="40"/>
       <c r="V6" s="40"/>
     </row>
-    <row r="7" spans="1:22" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:22" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A7" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
@@ -4591,84 +5181,84 @@
       <c r="U7" s="42"/>
       <c r="V7" s="56"/>
     </row>
-    <row r="8" spans="1:22" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:22" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A8" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="158" t="s">
+      <c r="B8" s="188" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="188"/>
+      <c r="D8" s="188"/>
+      <c r="E8" s="188"/>
+      <c r="F8" s="188"/>
+      <c r="G8" s="188"/>
+      <c r="H8" s="188"/>
+      <c r="I8" s="188" t="s">
+        <v>54</v>
+      </c>
+      <c r="J8" s="188"/>
+      <c r="K8" s="188"/>
+      <c r="L8" s="188"/>
+      <c r="M8" s="188" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="158"/>
-      <c r="D8" s="158"/>
-      <c r="E8" s="158"/>
-      <c r="F8" s="158"/>
-      <c r="G8" s="158"/>
-      <c r="H8" s="158"/>
-      <c r="I8" s="158" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" s="158"/>
-      <c r="K8" s="158"/>
-      <c r="L8" s="158"/>
-      <c r="M8" s="158" t="s">
-        <v>43</v>
-      </c>
-      <c r="N8" s="158"/>
-      <c r="O8" s="158"/>
-      <c r="P8" s="159" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q8" s="159"/>
-      <c r="R8" s="159"/>
-      <c r="S8" s="159"/>
-      <c r="T8" s="111" t="s">
-        <v>82</v>
-      </c>
-      <c r="U8" s="112"/>
-      <c r="V8" s="113"/>
-    </row>
-    <row r="9" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="N8" s="188"/>
+      <c r="O8" s="188"/>
+      <c r="P8" s="189" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q8" s="189"/>
+      <c r="R8" s="189"/>
+      <c r="S8" s="189"/>
+      <c r="T8" s="131" t="s">
+        <v>81</v>
+      </c>
+      <c r="U8" s="132"/>
+      <c r="V8" s="133"/>
+    </row>
+    <row r="9" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A9" s="44">
         <v>1</v>
       </c>
-      <c r="B9" s="160" t="s">
+      <c r="B9" s="190" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="191"/>
+      <c r="D9" s="191"/>
+      <c r="E9" s="191"/>
+      <c r="F9" s="191"/>
+      <c r="G9" s="191"/>
+      <c r="H9" s="191"/>
+      <c r="I9" s="166" t="s">
+        <v>69</v>
+      </c>
+      <c r="J9" s="169"/>
+      <c r="K9" s="169"/>
+      <c r="L9" s="167"/>
+      <c r="M9" s="184" t="s">
+        <v>48</v>
+      </c>
+      <c r="N9" s="180"/>
+      <c r="O9" s="180"/>
+      <c r="P9" s="172" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="161"/>
-      <c r="D9" s="161"/>
-      <c r="E9" s="161"/>
-      <c r="F9" s="161"/>
-      <c r="G9" s="161"/>
-      <c r="H9" s="161"/>
-      <c r="I9" s="145" t="s">
-        <v>70</v>
-      </c>
-      <c r="J9" s="146"/>
-      <c r="K9" s="146"/>
-      <c r="L9" s="147"/>
-      <c r="M9" s="162" t="s">
-        <v>49</v>
-      </c>
-      <c r="N9" s="144"/>
-      <c r="O9" s="144"/>
-      <c r="P9" s="151" t="s">
+      <c r="Q9" s="165"/>
+      <c r="R9" s="165"/>
+      <c r="S9" s="165"/>
+      <c r="T9" s="165" t="s">
         <v>84</v>
       </c>
-      <c r="Q9" s="148"/>
-      <c r="R9" s="148"/>
-      <c r="S9" s="148"/>
-      <c r="T9" s="148" t="s">
-        <v>85</v>
-      </c>
-      <c r="U9" s="148"/>
-      <c r="V9" s="148"/>
-    </row>
-    <row r="10" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="U9" s="165"/>
+      <c r="V9" s="165"/>
+    </row>
+    <row r="10" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A10" s="44">
         <v>2</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" s="47"/>
       <c r="D10" s="46"/>
@@ -4676,718 +5266,718 @@
       <c r="F10" s="46"/>
       <c r="G10" s="46"/>
       <c r="H10" s="46"/>
-      <c r="I10" s="145" t="s">
-        <v>70</v>
-      </c>
-      <c r="J10" s="146"/>
-      <c r="K10" s="146"/>
-      <c r="L10" s="147"/>
-      <c r="M10" s="162" t="s">
-        <v>49</v>
-      </c>
-      <c r="N10" s="144"/>
-      <c r="O10" s="144"/>
-      <c r="P10" s="151" t="s">
+      <c r="I10" s="166" t="s">
+        <v>69</v>
+      </c>
+      <c r="J10" s="169"/>
+      <c r="K10" s="169"/>
+      <c r="L10" s="167"/>
+      <c r="M10" s="184" t="s">
+        <v>48</v>
+      </c>
+      <c r="N10" s="180"/>
+      <c r="O10" s="180"/>
+      <c r="P10" s="172" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q10" s="165"/>
+      <c r="R10" s="165"/>
+      <c r="S10" s="165"/>
+      <c r="T10" s="165" t="s">
         <v>87</v>
       </c>
-      <c r="Q10" s="148"/>
-      <c r="R10" s="148"/>
-      <c r="S10" s="148"/>
-      <c r="T10" s="148" t="s">
-        <v>88</v>
-      </c>
-      <c r="U10" s="148"/>
-      <c r="V10" s="148"/>
-    </row>
-    <row r="11" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="U10" s="165"/>
+      <c r="V10" s="165"/>
+    </row>
+    <row r="11" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A11" s="44">
         <v>3</v>
       </c>
-      <c r="B11" s="165"/>
+      <c r="B11" s="185"/>
       <c r="C11" s="48" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="50"/>
       <c r="F11" s="50"/>
       <c r="G11" s="50"/>
       <c r="H11" s="50"/>
-      <c r="I11" s="148" t="s">
+      <c r="I11" s="165" t="s">
+        <v>89</v>
+      </c>
+      <c r="J11" s="165"/>
+      <c r="K11" s="165"/>
+      <c r="L11" s="165"/>
+      <c r="M11" s="184" t="s">
+        <v>48</v>
+      </c>
+      <c r="N11" s="180"/>
+      <c r="O11" s="180"/>
+      <c r="P11" s="172" t="s">
         <v>90</v>
       </c>
-      <c r="J11" s="148"/>
-      <c r="K11" s="148"/>
-      <c r="L11" s="148"/>
-      <c r="M11" s="162" t="s">
-        <v>49</v>
-      </c>
-      <c r="N11" s="144"/>
-      <c r="O11" s="144"/>
-      <c r="P11" s="151" t="s">
+      <c r="Q11" s="165"/>
+      <c r="R11" s="165"/>
+      <c r="S11" s="165"/>
+      <c r="T11" s="172" t="s">
         <v>91</v>
       </c>
-      <c r="Q11" s="148"/>
-      <c r="R11" s="148"/>
-      <c r="S11" s="148"/>
-      <c r="T11" s="151" t="s">
-        <v>92</v>
-      </c>
-      <c r="U11" s="148"/>
-      <c r="V11" s="148"/>
-    </row>
-    <row r="12" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="U11" s="165"/>
+      <c r="V11" s="165"/>
+    </row>
+    <row r="12" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A12" s="44">
         <v>4</v>
       </c>
-      <c r="B12" s="165"/>
-      <c r="C12" s="165"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="185"/>
       <c r="D12" s="48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E12" s="50"/>
       <c r="F12" s="50"/>
       <c r="G12" s="50"/>
       <c r="H12" s="50"/>
-      <c r="I12" s="148" t="s">
+      <c r="I12" s="165" t="s">
+        <v>93</v>
+      </c>
+      <c r="J12" s="165"/>
+      <c r="K12" s="165"/>
+      <c r="L12" s="165"/>
+      <c r="M12" s="184" t="s">
+        <v>48</v>
+      </c>
+      <c r="N12" s="180"/>
+      <c r="O12" s="180"/>
+      <c r="P12" s="172" t="s">
         <v>94</v>
       </c>
-      <c r="J12" s="148"/>
-      <c r="K12" s="148"/>
-      <c r="L12" s="148"/>
-      <c r="M12" s="162" t="s">
-        <v>49</v>
-      </c>
-      <c r="N12" s="144"/>
-      <c r="O12" s="144"/>
-      <c r="P12" s="151" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q12" s="148"/>
-      <c r="R12" s="148"/>
-      <c r="S12" s="148"/>
-      <c r="T12" s="151" t="s">
-        <v>92</v>
-      </c>
-      <c r="U12" s="148"/>
-      <c r="V12" s="148"/>
-    </row>
-    <row r="13" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Q12" s="165"/>
+      <c r="R12" s="165"/>
+      <c r="S12" s="165"/>
+      <c r="T12" s="172" t="s">
+        <v>91</v>
+      </c>
+      <c r="U12" s="165"/>
+      <c r="V12" s="165"/>
+    </row>
+    <row r="13" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A13" s="44">
         <v>5</v>
       </c>
-      <c r="B13" s="165"/>
-      <c r="C13" s="165"/>
-      <c r="D13" s="165"/>
+      <c r="B13" s="185"/>
+      <c r="C13" s="185"/>
+      <c r="D13" s="185"/>
       <c r="E13" s="44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F13" s="51"/>
       <c r="G13" s="50"/>
       <c r="H13" s="50"/>
-      <c r="I13" s="145" t="s">
-        <v>60</v>
-      </c>
-      <c r="J13" s="146"/>
-      <c r="K13" s="146"/>
-      <c r="L13" s="147"/>
-      <c r="M13" s="162" t="s">
-        <v>49</v>
-      </c>
-      <c r="N13" s="144"/>
-      <c r="O13" s="144"/>
-      <c r="P13" s="151" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q13" s="148"/>
-      <c r="R13" s="148"/>
-      <c r="S13" s="148"/>
-      <c r="T13" s="148">
+      <c r="I13" s="166" t="s">
+        <v>59</v>
+      </c>
+      <c r="J13" s="169"/>
+      <c r="K13" s="169"/>
+      <c r="L13" s="167"/>
+      <c r="M13" s="184" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13" s="180"/>
+      <c r="O13" s="180"/>
+      <c r="P13" s="172" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q13" s="165"/>
+      <c r="R13" s="165"/>
+      <c r="S13" s="165"/>
+      <c r="T13" s="165">
         <v>1</v>
       </c>
-      <c r="U13" s="148"/>
-      <c r="V13" s="148"/>
-    </row>
-    <row r="14" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="U13" s="165"/>
+      <c r="V13" s="165"/>
+    </row>
+    <row r="14" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A14" s="44">
         <v>6</v>
       </c>
-      <c r="B14" s="165"/>
-      <c r="C14" s="165"/>
-      <c r="D14" s="165"/>
+      <c r="B14" s="185"/>
+      <c r="C14" s="185"/>
+      <c r="D14" s="185"/>
       <c r="E14" s="44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F14" s="51"/>
       <c r="G14" s="50"/>
       <c r="H14" s="50"/>
-      <c r="I14" s="145" t="s">
-        <v>70</v>
-      </c>
-      <c r="J14" s="146"/>
-      <c r="K14" s="146"/>
-      <c r="L14" s="147"/>
-      <c r="M14" s="144"/>
-      <c r="N14" s="144"/>
-      <c r="O14" s="144"/>
-      <c r="P14" s="151" t="s">
+      <c r="I14" s="166" t="s">
+        <v>69</v>
+      </c>
+      <c r="J14" s="169"/>
+      <c r="K14" s="169"/>
+      <c r="L14" s="167"/>
+      <c r="M14" s="180"/>
+      <c r="N14" s="180"/>
+      <c r="O14" s="180"/>
+      <c r="P14" s="172" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q14" s="165"/>
+      <c r="R14" s="165"/>
+      <c r="S14" s="165"/>
+      <c r="T14" s="165" t="s">
         <v>99</v>
       </c>
-      <c r="Q14" s="148"/>
-      <c r="R14" s="148"/>
-      <c r="S14" s="148"/>
-      <c r="T14" s="148" t="s">
-        <v>100</v>
-      </c>
-      <c r="U14" s="148"/>
-      <c r="V14" s="148"/>
-    </row>
-    <row r="15" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="U14" s="165"/>
+      <c r="V14" s="165"/>
+    </row>
+    <row r="15" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A15" s="44">
         <v>7</v>
       </c>
-      <c r="B15" s="165"/>
-      <c r="C15" s="165"/>
-      <c r="D15" s="165"/>
+      <c r="B15" s="185"/>
+      <c r="C15" s="185"/>
+      <c r="D15" s="185"/>
       <c r="E15" s="44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F15" s="51"/>
       <c r="G15" s="50"/>
       <c r="H15" s="50"/>
-      <c r="I15" s="145" t="s">
-        <v>70</v>
-      </c>
-      <c r="J15" s="146"/>
-      <c r="K15" s="146"/>
-      <c r="L15" s="147"/>
-      <c r="M15" s="144"/>
-      <c r="N15" s="144"/>
-      <c r="O15" s="144"/>
-      <c r="P15" s="151" t="s">
+      <c r="I15" s="166" t="s">
+        <v>69</v>
+      </c>
+      <c r="J15" s="169"/>
+      <c r="K15" s="169"/>
+      <c r="L15" s="167"/>
+      <c r="M15" s="180"/>
+      <c r="N15" s="180"/>
+      <c r="O15" s="180"/>
+      <c r="P15" s="172" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q15" s="165"/>
+      <c r="R15" s="165"/>
+      <c r="S15" s="165"/>
+      <c r="T15" s="165" t="s">
         <v>102</v>
       </c>
-      <c r="Q15" s="148"/>
-      <c r="R15" s="148"/>
-      <c r="S15" s="148"/>
-      <c r="T15" s="148" t="s">
-        <v>103</v>
-      </c>
-      <c r="U15" s="148"/>
-      <c r="V15" s="148"/>
-    </row>
-    <row r="16" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="U15" s="165"/>
+      <c r="V15" s="165"/>
+    </row>
+    <row r="16" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A16" s="44">
         <v>8</v>
       </c>
-      <c r="B16" s="165"/>
-      <c r="C16" s="165"/>
-      <c r="D16" s="165"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="185"/>
+      <c r="D16" s="185"/>
       <c r="E16" s="44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F16" s="51"/>
       <c r="G16" s="50"/>
       <c r="H16" s="50"/>
-      <c r="I16" s="145" t="s">
-        <v>70</v>
-      </c>
-      <c r="J16" s="146"/>
-      <c r="K16" s="146"/>
-      <c r="L16" s="147"/>
-      <c r="M16" s="144"/>
-      <c r="N16" s="144"/>
-      <c r="O16" s="144"/>
-      <c r="P16" s="151" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q16" s="148"/>
-      <c r="R16" s="148"/>
-      <c r="S16" s="148"/>
-      <c r="T16" s="148" t="s">
-        <v>105</v>
-      </c>
-      <c r="U16" s="148"/>
-      <c r="V16" s="148"/>
-    </row>
-    <row r="17" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="I16" s="166" t="s">
+        <v>69</v>
+      </c>
+      <c r="J16" s="169"/>
+      <c r="K16" s="169"/>
+      <c r="L16" s="167"/>
+      <c r="M16" s="180"/>
+      <c r="N16" s="180"/>
+      <c r="O16" s="180"/>
+      <c r="P16" s="172" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q16" s="165"/>
+      <c r="R16" s="165"/>
+      <c r="S16" s="165"/>
+      <c r="T16" s="165" t="s">
+        <v>104</v>
+      </c>
+      <c r="U16" s="165"/>
+      <c r="V16" s="165"/>
+    </row>
+    <row r="17" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A17" s="44">
         <v>9</v>
       </c>
-      <c r="B17" s="165"/>
-      <c r="C17" s="165"/>
-      <c r="D17" s="165"/>
+      <c r="B17" s="185"/>
+      <c r="C17" s="185"/>
+      <c r="D17" s="185"/>
       <c r="E17" s="44" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F17" s="51"/>
       <c r="G17" s="50"/>
       <c r="H17" s="50"/>
-      <c r="I17" s="145" t="s">
-        <v>60</v>
-      </c>
-      <c r="J17" s="146"/>
-      <c r="K17" s="146"/>
-      <c r="L17" s="147"/>
-      <c r="M17" s="144"/>
-      <c r="N17" s="144"/>
-      <c r="O17" s="144"/>
-      <c r="P17" s="151" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q17" s="148"/>
-      <c r="R17" s="148"/>
-      <c r="S17" s="148"/>
-      <c r="T17" s="148">
+      <c r="I17" s="166" t="s">
+        <v>59</v>
+      </c>
+      <c r="J17" s="169"/>
+      <c r="K17" s="169"/>
+      <c r="L17" s="167"/>
+      <c r="M17" s="180"/>
+      <c r="N17" s="180"/>
+      <c r="O17" s="180"/>
+      <c r="P17" s="172" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q17" s="165"/>
+      <c r="R17" s="165"/>
+      <c r="S17" s="165"/>
+      <c r="T17" s="165">
         <v>75</v>
       </c>
-      <c r="U17" s="148"/>
-      <c r="V17" s="148"/>
-    </row>
-    <row r="18" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="U17" s="165"/>
+      <c r="V17" s="165"/>
+    </row>
+    <row r="18" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A18" s="44">
         <v>10</v>
       </c>
-      <c r="B18" s="165"/>
-      <c r="C18" s="165"/>
-      <c r="D18" s="165"/>
+      <c r="B18" s="185"/>
+      <c r="C18" s="185"/>
+      <c r="D18" s="185"/>
       <c r="E18" s="44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F18" s="51"/>
       <c r="G18" s="50"/>
       <c r="H18" s="50"/>
-      <c r="I18" s="145" t="s">
-        <v>70</v>
-      </c>
-      <c r="J18" s="146"/>
-      <c r="K18" s="146"/>
-      <c r="L18" s="147"/>
-      <c r="M18" s="144"/>
-      <c r="N18" s="144"/>
-      <c r="O18" s="144"/>
-      <c r="P18" s="151" t="s">
+      <c r="I18" s="166" t="s">
+        <v>69</v>
+      </c>
+      <c r="J18" s="169"/>
+      <c r="K18" s="169"/>
+      <c r="L18" s="167"/>
+      <c r="M18" s="180"/>
+      <c r="N18" s="180"/>
+      <c r="O18" s="180"/>
+      <c r="P18" s="172" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q18" s="165"/>
+      <c r="R18" s="165"/>
+      <c r="S18" s="165"/>
+      <c r="T18" s="165" t="s">
         <v>109</v>
       </c>
-      <c r="Q18" s="148"/>
-      <c r="R18" s="148"/>
-      <c r="S18" s="148"/>
-      <c r="T18" s="148" t="s">
-        <v>110</v>
-      </c>
-      <c r="U18" s="148"/>
-      <c r="V18" s="148"/>
-    </row>
-    <row r="19" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="U18" s="165"/>
+      <c r="V18" s="165"/>
+    </row>
+    <row r="19" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A19" s="44">
         <v>11</v>
       </c>
-      <c r="B19" s="156"/>
-      <c r="C19" s="156"/>
-      <c r="D19" s="44" t="s">
+      <c r="B19" s="185"/>
+      <c r="C19" s="185"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="89" t="s">
+        <v>254</v>
+      </c>
+      <c r="F19" s="88"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="158" t="s">
+        <v>69</v>
+      </c>
+      <c r="J19" s="160"/>
+      <c r="K19" s="160"/>
+      <c r="L19" s="159"/>
+      <c r="M19" s="194" t="s">
+        <v>48</v>
+      </c>
+      <c r="N19" s="194"/>
+      <c r="O19" s="194"/>
+      <c r="P19" s="163" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q19" s="157"/>
+      <c r="R19" s="157"/>
+      <c r="S19" s="157"/>
+      <c r="T19" s="195" t="s">
+        <v>255</v>
+      </c>
+      <c r="U19" s="157"/>
+      <c r="V19" s="157"/>
+    </row>
+    <row r="20" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A20" s="44">
+        <v>12</v>
+      </c>
+      <c r="B20" s="173"/>
+      <c r="C20" s="173"/>
+      <c r="D20" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="E20" s="44"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="166" t="s">
+        <v>59</v>
+      </c>
+      <c r="J20" s="169"/>
+      <c r="K20" s="169"/>
+      <c r="L20" s="167"/>
+      <c r="M20" s="184" t="s">
+        <v>48</v>
+      </c>
+      <c r="N20" s="180"/>
+      <c r="O20" s="180"/>
+      <c r="P20" s="172" t="s">
         <v>111</v>
       </c>
-      <c r="E19" s="44"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="145" t="s">
-        <v>60</v>
-      </c>
-      <c r="J19" s="146"/>
-      <c r="K19" s="146"/>
-      <c r="L19" s="147"/>
-      <c r="M19" s="162" t="s">
-        <v>49</v>
-      </c>
-      <c r="N19" s="144"/>
-      <c r="O19" s="144"/>
-      <c r="P19" s="151" t="s">
+      <c r="Q20" s="165"/>
+      <c r="R20" s="165"/>
+      <c r="S20" s="165"/>
+      <c r="T20" s="165">
+        <v>3</v>
+      </c>
+      <c r="U20" s="165"/>
+      <c r="V20" s="165"/>
+    </row>
+    <row r="21" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A21" s="39"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="40"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="40"/>
+      <c r="R21" s="40"/>
+      <c r="S21" s="40"/>
+      <c r="T21" s="40"/>
+      <c r="U21" s="40"/>
+      <c r="V21" s="40"/>
+    </row>
+    <row r="22" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A22" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="Q19" s="148"/>
-      <c r="R19" s="148"/>
-      <c r="S19" s="148"/>
-      <c r="T19" s="148">
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="53"/>
+      <c r="M22" s="53"/>
+      <c r="N22" s="53"/>
+      <c r="O22" s="53"/>
+      <c r="P22" s="53"/>
+      <c r="Q22" s="53"/>
+      <c r="R22" s="53"/>
+      <c r="S22" s="53"/>
+      <c r="T22" s="53"/>
+      <c r="U22" s="53"/>
+      <c r="V22" s="57"/>
+    </row>
+    <row r="23" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A23" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="188" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="188"/>
+      <c r="D23" s="188"/>
+      <c r="E23" s="188"/>
+      <c r="F23" s="188"/>
+      <c r="G23" s="188"/>
+      <c r="H23" s="188"/>
+      <c r="I23" s="188" t="s">
+        <v>54</v>
+      </c>
+      <c r="J23" s="188"/>
+      <c r="K23" s="188"/>
+      <c r="L23" s="188"/>
+      <c r="M23" s="188" t="s">
+        <v>42</v>
+      </c>
+      <c r="N23" s="188"/>
+      <c r="O23" s="188"/>
+      <c r="P23" s="189" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q23" s="189"/>
+      <c r="R23" s="189"/>
+      <c r="S23" s="189"/>
+      <c r="T23" s="131" t="s">
+        <v>81</v>
+      </c>
+      <c r="U23" s="132"/>
+      <c r="V23" s="133"/>
+    </row>
+    <row r="24" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A24" s="44">
+        <v>1</v>
+      </c>
+      <c r="B24" s="190" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="191"/>
+      <c r="D24" s="191"/>
+      <c r="E24" s="191"/>
+      <c r="F24" s="191"/>
+      <c r="G24" s="191"/>
+      <c r="H24" s="191"/>
+      <c r="I24" s="166" t="s">
+        <v>69</v>
+      </c>
+      <c r="J24" s="169"/>
+      <c r="K24" s="169"/>
+      <c r="L24" s="167"/>
+      <c r="M24" s="184" t="s">
+        <v>48</v>
+      </c>
+      <c r="N24" s="180"/>
+      <c r="O24" s="180"/>
+      <c r="P24" s="172" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q24" s="165"/>
+      <c r="R24" s="165"/>
+      <c r="S24" s="165"/>
+      <c r="T24" s="165" t="s">
+        <v>113</v>
+      </c>
+      <c r="U24" s="165"/>
+      <c r="V24" s="165"/>
+    </row>
+    <row r="25" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A25" s="44">
+        <v>2</v>
+      </c>
+      <c r="B25" s="190" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="191"/>
+      <c r="D25" s="191"/>
+      <c r="E25" s="191"/>
+      <c r="F25" s="191"/>
+      <c r="G25" s="191"/>
+      <c r="H25" s="191"/>
+      <c r="I25" s="166" t="s">
+        <v>69</v>
+      </c>
+      <c r="J25" s="169"/>
+      <c r="K25" s="169"/>
+      <c r="L25" s="167"/>
+      <c r="M25" s="184" t="s">
+        <v>48</v>
+      </c>
+      <c r="N25" s="180"/>
+      <c r="O25" s="180"/>
+      <c r="P25" s="172" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q25" s="165"/>
+      <c r="R25" s="165"/>
+      <c r="S25" s="165"/>
+      <c r="T25" s="165" t="s">
+        <v>115</v>
+      </c>
+      <c r="U25" s="165"/>
+      <c r="V25" s="165"/>
+    </row>
+    <row r="26" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A26" s="44">
         <v>3</v>
       </c>
-      <c r="U19" s="148"/>
-      <c r="V19" s="148"/>
-    </row>
-    <row r="20" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="39"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="40"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="40"/>
-      <c r="P20" s="40"/>
-      <c r="Q20" s="40"/>
-      <c r="R20" s="40"/>
-      <c r="S20" s="40"/>
-      <c r="T20" s="40"/>
-      <c r="U20" s="40"/>
-      <c r="V20" s="40"/>
-    </row>
-    <row r="21" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="52" t="s">
+      <c r="B26" s="192" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="191"/>
+      <c r="D26" s="191"/>
+      <c r="E26" s="191"/>
+      <c r="F26" s="191"/>
+      <c r="G26" s="191"/>
+      <c r="H26" s="193"/>
+      <c r="I26" s="166" t="s">
+        <v>69</v>
+      </c>
+      <c r="J26" s="169"/>
+      <c r="K26" s="169"/>
+      <c r="L26" s="167"/>
+      <c r="M26" s="184" t="s">
+        <v>48</v>
+      </c>
+      <c r="N26" s="180"/>
+      <c r="O26" s="180"/>
+      <c r="P26" s="165" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q26" s="165"/>
+      <c r="R26" s="165"/>
+      <c r="S26" s="165"/>
+      <c r="T26" s="165" t="s">
+        <v>118</v>
+      </c>
+      <c r="U26" s="165"/>
+      <c r="V26" s="165"/>
+    </row>
+    <row r="27" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A28" s="52" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="53"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="53"/>
+      <c r="R28" s="53"/>
+      <c r="S28" s="53"/>
+      <c r="T28" s="53"/>
+      <c r="U28" s="53"/>
+      <c r="V28" s="57"/>
+    </row>
+    <row r="29" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A29" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="188" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="188"/>
+      <c r="D29" s="188"/>
+      <c r="E29" s="188"/>
+      <c r="F29" s="188"/>
+      <c r="G29" s="188"/>
+      <c r="H29" s="188"/>
+      <c r="I29" s="188" t="s">
+        <v>54</v>
+      </c>
+      <c r="J29" s="188"/>
+      <c r="K29" s="188"/>
+      <c r="L29" s="188"/>
+      <c r="M29" s="188" t="s">
+        <v>42</v>
+      </c>
+      <c r="N29" s="188"/>
+      <c r="O29" s="188"/>
+      <c r="P29" s="189" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q29" s="189"/>
+      <c r="R29" s="189"/>
+      <c r="S29" s="189"/>
+      <c r="T29" s="131" t="s">
+        <v>81</v>
+      </c>
+      <c r="U29" s="132"/>
+      <c r="V29" s="133"/>
+    </row>
+    <row r="30" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A30" s="44">
+        <v>1</v>
+      </c>
+      <c r="B30" s="190" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="191"/>
+      <c r="D30" s="191"/>
+      <c r="E30" s="191"/>
+      <c r="F30" s="191"/>
+      <c r="G30" s="191"/>
+      <c r="H30" s="191"/>
+      <c r="I30" s="166" t="s">
+        <v>69</v>
+      </c>
+      <c r="J30" s="169"/>
+      <c r="K30" s="169"/>
+      <c r="L30" s="167"/>
+      <c r="M30" s="184" t="s">
+        <v>48</v>
+      </c>
+      <c r="N30" s="180"/>
+      <c r="O30" s="180"/>
+      <c r="P30" s="172" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q30" s="165"/>
+      <c r="R30" s="165"/>
+      <c r="S30" s="165"/>
+      <c r="T30" s="165" t="s">
         <v>113</v>
       </c>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="53"/>
-      <c r="P21" s="53"/>
-      <c r="Q21" s="53"/>
-      <c r="R21" s="53"/>
-      <c r="S21" s="53"/>
-      <c r="T21" s="53"/>
-      <c r="U21" s="53"/>
-      <c r="V21" s="57"/>
-    </row>
-    <row r="22" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="158" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="158"/>
-      <c r="D22" s="158"/>
-      <c r="E22" s="158"/>
-      <c r="F22" s="158"/>
-      <c r="G22" s="158"/>
-      <c r="H22" s="158"/>
-      <c r="I22" s="158" t="s">
-        <v>55</v>
-      </c>
-      <c r="J22" s="158"/>
-      <c r="K22" s="158"/>
-      <c r="L22" s="158"/>
-      <c r="M22" s="158" t="s">
-        <v>43</v>
-      </c>
-      <c r="N22" s="158"/>
-      <c r="O22" s="158"/>
-      <c r="P22" s="159" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q22" s="159"/>
-      <c r="R22" s="159"/>
-      <c r="S22" s="159"/>
-      <c r="T22" s="111" t="s">
-        <v>82</v>
-      </c>
-      <c r="U22" s="112"/>
-      <c r="V22" s="113"/>
-    </row>
-    <row r="23" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="44">
-        <v>1</v>
-      </c>
-      <c r="B23" s="160" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="161"/>
-      <c r="D23" s="161"/>
-      <c r="E23" s="161"/>
-      <c r="F23" s="161"/>
-      <c r="G23" s="161"/>
-      <c r="H23" s="161"/>
-      <c r="I23" s="145" t="s">
-        <v>70</v>
-      </c>
-      <c r="J23" s="146"/>
-      <c r="K23" s="146"/>
-      <c r="L23" s="147"/>
-      <c r="M23" s="162" t="s">
-        <v>49</v>
-      </c>
-      <c r="N23" s="144"/>
-      <c r="O23" s="144"/>
-      <c r="P23" s="151" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q23" s="148"/>
-      <c r="R23" s="148"/>
-      <c r="S23" s="148"/>
-      <c r="T23" s="148" t="s">
+      <c r="U30" s="165"/>
+      <c r="V30" s="165"/>
+    </row>
+    <row r="31" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A31" s="44">
+        <v>2</v>
+      </c>
+      <c r="B31" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="166" t="s">
+        <v>69</v>
+      </c>
+      <c r="J31" s="169"/>
+      <c r="K31" s="169"/>
+      <c r="L31" s="167"/>
+      <c r="M31" s="184" t="s">
+        <v>48</v>
+      </c>
+      <c r="N31" s="180"/>
+      <c r="O31" s="180"/>
+      <c r="P31" s="172" t="s">
         <v>114</v>
       </c>
-      <c r="U23" s="148"/>
-      <c r="V23" s="148"/>
-    </row>
-    <row r="24" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="44">
-        <v>2</v>
-      </c>
-      <c r="B24" s="160" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="161"/>
-      <c r="D24" s="161"/>
-      <c r="E24" s="161"/>
-      <c r="F24" s="161"/>
-      <c r="G24" s="161"/>
-      <c r="H24" s="161"/>
-      <c r="I24" s="145" t="s">
-        <v>70</v>
-      </c>
-      <c r="J24" s="146"/>
-      <c r="K24" s="146"/>
-      <c r="L24" s="147"/>
-      <c r="M24" s="162" t="s">
-        <v>49</v>
-      </c>
-      <c r="N24" s="144"/>
-      <c r="O24" s="144"/>
-      <c r="P24" s="151" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q24" s="148"/>
-      <c r="R24" s="148"/>
-      <c r="S24" s="148"/>
-      <c r="T24" s="148" t="s">
-        <v>116</v>
-      </c>
-      <c r="U24" s="148"/>
-      <c r="V24" s="148"/>
-    </row>
-    <row r="25" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="44">
+      <c r="Q31" s="165"/>
+      <c r="R31" s="165"/>
+      <c r="S31" s="165"/>
+      <c r="T31" s="165" t="s">
+        <v>120</v>
+      </c>
+      <c r="U31" s="165"/>
+      <c r="V31" s="165"/>
+    </row>
+    <row r="32" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A32" s="44">
         <v>3</v>
       </c>
-      <c r="B25" s="163" t="s">
-        <v>117</v>
-      </c>
-      <c r="C25" s="161"/>
-      <c r="D25" s="161"/>
-      <c r="E25" s="161"/>
-      <c r="F25" s="161"/>
-      <c r="G25" s="161"/>
-      <c r="H25" s="164"/>
-      <c r="I25" s="145" t="s">
-        <v>70</v>
-      </c>
-      <c r="J25" s="146"/>
-      <c r="K25" s="146"/>
-      <c r="L25" s="147"/>
-      <c r="M25" s="162" t="s">
-        <v>49</v>
-      </c>
-      <c r="N25" s="144"/>
-      <c r="O25" s="144"/>
-      <c r="P25" s="148" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q25" s="148"/>
-      <c r="R25" s="148"/>
-      <c r="S25" s="148"/>
-      <c r="T25" s="148" t="s">
-        <v>119</v>
-      </c>
-      <c r="U25" s="148"/>
-      <c r="V25" s="148"/>
-    </row>
-    <row r="26" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="52" t="s">
-        <v>120</v>
-      </c>
-      <c r="B27" s="53"/>
-      <c r="C27" s="53"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="53"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="53"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="53"/>
-      <c r="P27" s="53"/>
-      <c r="Q27" s="53"/>
-      <c r="R27" s="53"/>
-      <c r="S27" s="53"/>
-      <c r="T27" s="53"/>
-      <c r="U27" s="53"/>
-      <c r="V27" s="57"/>
-    </row>
-    <row r="28" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="158" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="158"/>
-      <c r="D28" s="158"/>
-      <c r="E28" s="158"/>
-      <c r="F28" s="158"/>
-      <c r="G28" s="158"/>
-      <c r="H28" s="158"/>
-      <c r="I28" s="158" t="s">
-        <v>55</v>
-      </c>
-      <c r="J28" s="158"/>
-      <c r="K28" s="158"/>
-      <c r="L28" s="158"/>
-      <c r="M28" s="158" t="s">
-        <v>43</v>
-      </c>
-      <c r="N28" s="158"/>
-      <c r="O28" s="158"/>
-      <c r="P28" s="159" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q28" s="159"/>
-      <c r="R28" s="159"/>
-      <c r="S28" s="159"/>
-      <c r="T28" s="111" t="s">
-        <v>82</v>
-      </c>
-      <c r="U28" s="112"/>
-      <c r="V28" s="113"/>
-    </row>
-    <row r="29" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="44">
-        <v>1</v>
-      </c>
-      <c r="B29" s="160" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" s="161"/>
-      <c r="D29" s="161"/>
-      <c r="E29" s="161"/>
-      <c r="F29" s="161"/>
-      <c r="G29" s="161"/>
-      <c r="H29" s="161"/>
-      <c r="I29" s="145" t="s">
-        <v>70</v>
-      </c>
-      <c r="J29" s="146"/>
-      <c r="K29" s="146"/>
-      <c r="L29" s="147"/>
-      <c r="M29" s="162" t="s">
-        <v>49</v>
-      </c>
-      <c r="N29" s="144"/>
-      <c r="O29" s="144"/>
-      <c r="P29" s="151" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q29" s="148"/>
-      <c r="R29" s="148"/>
-      <c r="S29" s="148"/>
-      <c r="T29" s="148" t="s">
-        <v>114</v>
-      </c>
-      <c r="U29" s="148"/>
-      <c r="V29" s="148"/>
-    </row>
-    <row r="30" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="44">
-        <v>2</v>
-      </c>
-      <c r="B30" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="145" t="s">
-        <v>70</v>
-      </c>
-      <c r="J30" s="146"/>
-      <c r="K30" s="146"/>
-      <c r="L30" s="147"/>
-      <c r="M30" s="162" t="s">
-        <v>49</v>
-      </c>
-      <c r="N30" s="144"/>
-      <c r="O30" s="144"/>
-      <c r="P30" s="151" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q30" s="148"/>
-      <c r="R30" s="148"/>
-      <c r="S30" s="148"/>
-      <c r="T30" s="148" t="s">
+      <c r="B32" s="51" t="s">
         <v>121</v>
-      </c>
-      <c r="U30" s="148"/>
-      <c r="V30" s="148"/>
-    </row>
-    <row r="31" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="44">
-        <v>3</v>
-      </c>
-      <c r="B31" s="51" t="s">
-        <v>122</v>
-      </c>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="145" t="s">
-        <v>70</v>
-      </c>
-      <c r="J31" s="146"/>
-      <c r="K31" s="146"/>
-      <c r="L31" s="147"/>
-      <c r="M31" s="162" t="s">
-        <v>49</v>
-      </c>
-      <c r="N31" s="144"/>
-      <c r="O31" s="144"/>
-      <c r="P31" s="148" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q31" s="148"/>
-      <c r="R31" s="148"/>
-      <c r="S31" s="148"/>
-      <c r="T31" s="151" t="s">
-        <v>123</v>
-      </c>
-      <c r="U31" s="148"/>
-      <c r="V31" s="148"/>
-    </row>
-    <row r="32" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="44">
-        <v>4</v>
-      </c>
-      <c r="B32" s="51" t="s">
-        <v>124</v>
       </c>
       <c r="C32" s="50"/>
       <c r="D32" s="50"/>
@@ -5395,35 +5985,35 @@
       <c r="F32" s="50"/>
       <c r="G32" s="50"/>
       <c r="H32" s="54"/>
-      <c r="I32" s="145" t="s">
-        <v>70</v>
-      </c>
-      <c r="J32" s="146"/>
-      <c r="K32" s="146"/>
-      <c r="L32" s="147"/>
-      <c r="M32" s="162" t="s">
-        <v>49</v>
-      </c>
-      <c r="N32" s="144"/>
-      <c r="O32" s="144"/>
-      <c r="P32" s="148" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q32" s="148"/>
-      <c r="R32" s="148"/>
-      <c r="S32" s="148"/>
-      <c r="T32" s="148" t="s">
-        <v>126</v>
-      </c>
-      <c r="U32" s="148"/>
-      <c r="V32" s="148"/>
-    </row>
-    <row r="33" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="I32" s="166" t="s">
+        <v>69</v>
+      </c>
+      <c r="J32" s="169"/>
+      <c r="K32" s="169"/>
+      <c r="L32" s="167"/>
+      <c r="M32" s="184" t="s">
+        <v>48</v>
+      </c>
+      <c r="N32" s="180"/>
+      <c r="O32" s="180"/>
+      <c r="P32" s="165" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q32" s="165"/>
+      <c r="R32" s="165"/>
+      <c r="S32" s="165"/>
+      <c r="T32" s="172" t="s">
+        <v>122</v>
+      </c>
+      <c r="U32" s="165"/>
+      <c r="V32" s="165"/>
+    </row>
+    <row r="33" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A33" s="44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B33" s="51" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C33" s="50"/>
       <c r="D33" s="50"/>
@@ -5431,37 +6021,170 @@
       <c r="F33" s="50"/>
       <c r="G33" s="50"/>
       <c r="H33" s="54"/>
-      <c r="I33" s="145" t="s">
-        <v>70</v>
-      </c>
-      <c r="J33" s="146"/>
-      <c r="K33" s="146"/>
-      <c r="L33" s="147"/>
-      <c r="M33" s="162" t="s">
-        <v>49</v>
-      </c>
-      <c r="N33" s="144"/>
-      <c r="O33" s="144"/>
-      <c r="P33" s="148" t="s">
+      <c r="I33" s="166" t="s">
+        <v>69</v>
+      </c>
+      <c r="J33" s="169"/>
+      <c r="K33" s="169"/>
+      <c r="L33" s="167"/>
+      <c r="M33" s="184" t="s">
+        <v>48</v>
+      </c>
+      <c r="N33" s="180"/>
+      <c r="O33" s="180"/>
+      <c r="P33" s="165" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q33" s="165"/>
+      <c r="R33" s="165"/>
+      <c r="S33" s="165"/>
+      <c r="T33" s="165" t="s">
+        <v>125</v>
+      </c>
+      <c r="U33" s="165"/>
+      <c r="V33" s="165"/>
+    </row>
+    <row r="34" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A34" s="44">
+        <v>5</v>
+      </c>
+      <c r="B34" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="C34" s="50"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="166" t="s">
+        <v>69</v>
+      </c>
+      <c r="J34" s="169"/>
+      <c r="K34" s="169"/>
+      <c r="L34" s="167"/>
+      <c r="M34" s="184" t="s">
+        <v>48</v>
+      </c>
+      <c r="N34" s="180"/>
+      <c r="O34" s="180"/>
+      <c r="P34" s="165" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q34" s="165"/>
+      <c r="R34" s="165"/>
+      <c r="S34" s="165"/>
+      <c r="T34" s="165" t="s">
         <v>128</v>
       </c>
-      <c r="Q33" s="148"/>
-      <c r="R33" s="148"/>
-      <c r="S33" s="148"/>
-      <c r="T33" s="148" t="s">
-        <v>129</v>
-      </c>
-      <c r="U33" s="148"/>
-      <c r="V33" s="148"/>
+      <c r="U34" s="165"/>
+      <c r="V34" s="165"/>
     </row>
   </sheetData>
-  <mergeCells count="117">
+  <mergeCells count="121">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="P8:S8"/>
+    <mergeCell ref="T8:V8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="T9:V9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="P10:S10"/>
+    <mergeCell ref="T10:V10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="P11:S11"/>
+    <mergeCell ref="T11:V11"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="P12:S12"/>
+    <mergeCell ref="T12:V12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="P13:S13"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="P14:S14"/>
+    <mergeCell ref="T14:V14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="P15:S15"/>
+    <mergeCell ref="T15:V15"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="P16:S16"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="P17:S17"/>
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="P18:S18"/>
+    <mergeCell ref="T18:V18"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="P20:S20"/>
+    <mergeCell ref="T20:V20"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="P19:S19"/>
+    <mergeCell ref="T19:V19"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="P23:S23"/>
+    <mergeCell ref="T23:V23"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P24:S24"/>
+    <mergeCell ref="T24:V24"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="P25:S25"/>
+    <mergeCell ref="T25:V25"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="P26:S26"/>
+    <mergeCell ref="T26:V26"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="P32:S32"/>
+    <mergeCell ref="T32:V32"/>
     <mergeCell ref="I33:L33"/>
     <mergeCell ref="M33:O33"/>
     <mergeCell ref="P33:S33"/>
     <mergeCell ref="T33:V33"/>
-    <mergeCell ref="B11:B19"/>
-    <mergeCell ref="C12:C19"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="P29:S29"/>
+    <mergeCell ref="T29:V29"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="P30:S30"/>
+    <mergeCell ref="T30:V30"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="P34:S34"/>
+    <mergeCell ref="T34:V34"/>
+    <mergeCell ref="B11:B20"/>
+    <mergeCell ref="C12:C20"/>
     <mergeCell ref="D13:D18"/>
     <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="Q3:Q4"/>
@@ -5476,103 +6199,10 @@
     <mergeCell ref="M1:P2"/>
     <mergeCell ref="I3:L4"/>
     <mergeCell ref="M3:P4"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="P30:S30"/>
-    <mergeCell ref="T30:V30"/>
     <mergeCell ref="I31:L31"/>
     <mergeCell ref="M31:O31"/>
     <mergeCell ref="P31:S31"/>
     <mergeCell ref="T31:V31"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="M32:O32"/>
-    <mergeCell ref="P32:S32"/>
-    <mergeCell ref="T32:V32"/>
-    <mergeCell ref="B28:H28"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="P28:S28"/>
-    <mergeCell ref="T28:V28"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="P29:S29"/>
-    <mergeCell ref="T29:V29"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P24:S24"/>
-    <mergeCell ref="T24:V24"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="P25:S25"/>
-    <mergeCell ref="T25:V25"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="P22:S22"/>
-    <mergeCell ref="T22:V22"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="P23:S23"/>
-    <mergeCell ref="T23:V23"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="P17:S17"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="P18:S18"/>
-    <mergeCell ref="T18:V18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="P19:S19"/>
-    <mergeCell ref="T19:V19"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="P14:S14"/>
-    <mergeCell ref="T14:V14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="P15:S15"/>
-    <mergeCell ref="T15:V15"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="P16:S16"/>
-    <mergeCell ref="T16:V16"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="P11:S11"/>
-    <mergeCell ref="T11:V11"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="P12:S12"/>
-    <mergeCell ref="T12:V12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="P13:S13"/>
-    <mergeCell ref="T13:V13"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="T9:V9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="P10:S10"/>
-    <mergeCell ref="T10:V10"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="R5:V5"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="P8:S8"/>
-    <mergeCell ref="T8:V8"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5583,7 +6213,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:V30"/>
-  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="7" width="3.6640625" style="34"/>
     <col min="8" max="8" width="16.33203125" style="34" customWidth="1"/>
@@ -5598,244 +6228,254 @@
     <col min="23" max="16384" width="3.6640625" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="120" t="s">
+    <row r="1" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A1" s="104" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="113" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="119" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="123" t="s">
+        <v>3</v>
+      </c>
+      <c r="R1" s="134" t="s">
+        <v>6</v>
+      </c>
+      <c r="S1" s="135"/>
+      <c r="T1" s="128" t="s">
+        <v>11</v>
+      </c>
+      <c r="U1" s="124" t="s">
+        <v>12</v>
+      </c>
+      <c r="V1" s="125"/>
+    </row>
+    <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A2" s="107"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="123"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="131"/>
+      <c r="U2" s="126"/>
+      <c r="V2" s="127"/>
+    </row>
+    <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A3" s="107"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="113" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="114"/>
+      <c r="K3" s="114"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="119" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="120"/>
+      <c r="O3" s="120"/>
+      <c r="P3" s="120"/>
+      <c r="Q3" s="123" t="s">
+        <v>15</v>
+      </c>
+      <c r="R3" s="134" t="s">
+        <v>6</v>
+      </c>
+      <c r="S3" s="135"/>
+      <c r="T3" s="123" t="s">
+        <v>16</v>
+      </c>
+      <c r="U3" s="124" t="s">
+        <v>12</v>
+      </c>
+      <c r="V3" s="125"/>
+    </row>
+    <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="123"/>
+      <c r="R4" s="137"/>
+      <c r="S4" s="138"/>
+      <c r="T4" s="123"/>
+      <c r="U4" s="126"/>
+      <c r="V4" s="127"/>
+    </row>
+    <row r="5" spans="1:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A5" s="182" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="182"/>
+      <c r="C5" s="182"/>
+      <c r="D5" s="182"/>
+      <c r="E5" s="183" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="183"/>
+      <c r="G5" s="183"/>
+      <c r="H5" s="183"/>
+      <c r="I5" s="182" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="182"/>
+      <c r="K5" s="182"/>
+      <c r="L5" s="182"/>
+      <c r="M5" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="183"/>
+      <c r="O5" s="183"/>
+      <c r="P5" s="183"/>
+      <c r="Q5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R5" s="183" t="s">
+        <v>26</v>
+      </c>
+      <c r="S5" s="183"/>
+      <c r="T5" s="183"/>
+      <c r="U5" s="183"/>
+      <c r="V5" s="183"/>
+    </row>
+    <row r="6" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A6" s="35"/>
+    </row>
+    <row r="7" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A7" s="35"/>
+    </row>
+    <row r="8" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A8" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="129" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="130"/>
-      <c r="K1" s="130"/>
-      <c r="L1" s="130"/>
-      <c r="M1" s="135" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="136"/>
-      <c r="O1" s="136"/>
-      <c r="P1" s="136"/>
-      <c r="Q1" s="103" t="s">
-        <v>3</v>
-      </c>
-      <c r="R1" s="114" t="s">
-        <v>6</v>
-      </c>
-      <c r="S1" s="115"/>
-      <c r="T1" s="108" t="s">
-        <v>11</v>
-      </c>
-      <c r="U1" s="104" t="s">
-        <v>12</v>
-      </c>
-      <c r="V1" s="105"/>
-    </row>
-    <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="123"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="133"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="133"/>
-      <c r="M2" s="137"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="117"/>
-      <c r="S2" s="118"/>
-      <c r="T2" s="111"/>
-      <c r="U2" s="106"/>
-      <c r="V2" s="107"/>
-    </row>
-    <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="123"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="129" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="135" t="s">
-        <v>14</v>
-      </c>
-      <c r="N3" s="136"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="136"/>
-      <c r="Q3" s="103" t="s">
-        <v>15</v>
-      </c>
-      <c r="R3" s="114" t="s">
-        <v>6</v>
-      </c>
-      <c r="S3" s="115"/>
-      <c r="T3" s="103" t="s">
-        <v>16</v>
-      </c>
-      <c r="U3" s="104" t="s">
-        <v>12</v>
-      </c>
-      <c r="V3" s="105"/>
-    </row>
-    <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="126"/>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="132"/>
-      <c r="J4" s="133"/>
-      <c r="K4" s="133"/>
-      <c r="L4" s="133"/>
-      <c r="M4" s="137"/>
-      <c r="N4" s="138"/>
-      <c r="O4" s="138"/>
-      <c r="P4" s="138"/>
-      <c r="Q4" s="103"/>
-      <c r="R4" s="117"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="103"/>
-      <c r="U4" s="106"/>
-      <c r="V4" s="107"/>
-    </row>
-    <row r="5" spans="1:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="139" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="139"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="139"/>
-      <c r="E5" s="140" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="140"/>
-      <c r="G5" s="140"/>
-      <c r="H5" s="140"/>
-      <c r="I5" s="139" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="139"/>
-      <c r="K5" s="139"/>
-      <c r="L5" s="139"/>
-      <c r="M5" s="140" t="s">
-        <v>20</v>
-      </c>
-      <c r="N5" s="140"/>
-      <c r="O5" s="140"/>
-      <c r="P5" s="140"/>
-      <c r="Q5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="R5" s="140" t="s">
-        <v>26</v>
-      </c>
-      <c r="S5" s="140"/>
-      <c r="T5" s="140"/>
-      <c r="U5" s="140"/>
-      <c r="V5" s="140"/>
-    </row>
-    <row r="6" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="35"/>
-    </row>
-    <row r="7" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="35"/>
-    </row>
-    <row r="8" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="35" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A9" s="35"/>
     </row>
-    <row r="10" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A10" s="35"/>
     </row>
-    <row r="11" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A11" s="35"/>
     </row>
-    <row r="12" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A12" s="35"/>
     </row>
-    <row r="13" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A13" s="35"/>
     </row>
-    <row r="14" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A14" s="35"/>
     </row>
-    <row r="15" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A15" s="35"/>
     </row>
-    <row r="16" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A16" s="35"/>
     </row>
-    <row r="17" spans="1:3" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A17" s="35"/>
     </row>
-    <row r="18" spans="1:3" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A18" s="35"/>
     </row>
-    <row r="19" spans="1:3" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A19" s="35"/>
     </row>
-    <row r="20" spans="1:3" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A20" s="35"/>
     </row>
-    <row r="21" spans="1:3" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A21" s="35"/>
     </row>
-    <row r="22" spans="1:3" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A22" s="35"/>
     </row>
-    <row r="23" spans="1:3" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A23" s="35"/>
     </row>
-    <row r="24" spans="1:3" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A24" s="35"/>
     </row>
-    <row r="25" spans="1:3" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A25" s="36"/>
       <c r="C25" s="37"/>
     </row>
-    <row r="26" spans="1:3" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A26" s="36"/>
     </row>
-    <row r="27" spans="1:3" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A27" s="36"/>
     </row>
-    <row r="28" spans="1:3" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A28" s="36"/>
     </row>
-    <row r="29" spans="1:3" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A29" s="36"/>
     </row>
-    <row r="30" spans="1:3" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A30" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="A1:H4"/>
+    <mergeCell ref="I1:L2"/>
+    <mergeCell ref="M1:P2"/>
+    <mergeCell ref="I3:L4"/>
+    <mergeCell ref="M3:P4"/>
     <mergeCell ref="U1:V2"/>
     <mergeCell ref="U3:V4"/>
     <mergeCell ref="Q1:Q2"/>
@@ -5844,16 +6484,6 @@
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="R1:S2"/>
     <mergeCell ref="R3:S4"/>
-    <mergeCell ref="A1:H4"/>
-    <mergeCell ref="I1:L2"/>
-    <mergeCell ref="M1:P2"/>
-    <mergeCell ref="I3:L4"/>
-    <mergeCell ref="M3:P4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="R5:V5"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5864,8 +6494,8 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Q75"/>
-  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:Q83"/>
+  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="6" width="3.6640625" style="5"/>
     <col min="7" max="7" width="14.77734375" style="5" customWidth="1"/>
@@ -5882,167 +6512,167 @@
     <col min="18" max="16384" width="3.6640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="120" t="s">
-        <v>132</v>
-      </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="129" t="s">
+    <row r="1" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A1" s="104" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="130"/>
-      <c r="K1" s="135" t="s">
+      <c r="J1" s="114"/>
+      <c r="K1" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="108" t="s">
+      <c r="L1" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="114" t="s">
+      <c r="M1" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="103" t="s">
+      <c r="N1" s="123" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="103"/>
-      <c r="P1" s="104" t="s">
+      <c r="O1" s="123"/>
+      <c r="P1" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="105"/>
-    </row>
-    <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="123"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="133"/>
-      <c r="K2" s="137"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="117"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="103"/>
-      <c r="P2" s="106"/>
-      <c r="Q2" s="107"/>
-    </row>
-    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="123"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="129" t="s">
+      <c r="Q1" s="125"/>
+    </row>
+    <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A2" s="107"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="131"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="123"/>
+      <c r="P2" s="126"/>
+      <c r="Q2" s="127"/>
+    </row>
+    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A3" s="107"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="130"/>
-      <c r="K3" s="135" t="s">
+      <c r="J3" s="114"/>
+      <c r="K3" s="119" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="108" t="s">
+      <c r="L3" s="128" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="114" t="s">
+      <c r="M3" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="103" t="s">
+      <c r="N3" s="123" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="103"/>
-      <c r="P3" s="104" t="s">
+      <c r="O3" s="123"/>
+      <c r="P3" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="105"/>
-    </row>
-    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="126"/>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="132"/>
-      <c r="J4" s="133"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="111"/>
-      <c r="M4" s="117"/>
-      <c r="N4" s="103"/>
-      <c r="O4" s="103"/>
-      <c r="P4" s="106"/>
-      <c r="Q4" s="107"/>
-    </row>
-    <row r="5" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="139" t="s">
+      <c r="Q3" s="125"/>
+    </row>
+    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="131"/>
+      <c r="M4" s="137"/>
+      <c r="N4" s="123"/>
+      <c r="O4" s="123"/>
+      <c r="P4" s="126"/>
+      <c r="Q4" s="127"/>
+    </row>
+    <row r="5" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A5" s="182" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="182"/>
+      <c r="C5" s="182"/>
+      <c r="D5" s="182"/>
+      <c r="E5" s="183" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="183"/>
+      <c r="G5" s="183"/>
+      <c r="H5" s="183"/>
+      <c r="I5" s="182" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="139"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="139"/>
-      <c r="E5" s="140" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="140"/>
-      <c r="G5" s="140"/>
-      <c r="H5" s="140"/>
-      <c r="I5" s="139" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="139"/>
+      <c r="J5" s="182"/>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="140" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" s="183" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="140"/>
-      <c r="O5" s="140"/>
-      <c r="P5" s="140"/>
-      <c r="Q5" s="140"/>
-    </row>
-    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="171" t="s">
+      <c r="N5" s="183"/>
+      <c r="O5" s="183"/>
+      <c r="P5" s="183"/>
+      <c r="Q5" s="183"/>
+    </row>
+    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A6" s="210" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="210"/>
+      <c r="C6" s="210"/>
+      <c r="D6" s="210"/>
+      <c r="E6" s="210"/>
+      <c r="F6" s="210"/>
+      <c r="G6" s="210"/>
+      <c r="H6" s="211" t="s">
         <v>133</v>
       </c>
-      <c r="B6" s="171"/>
-      <c r="C6" s="171"/>
-      <c r="D6" s="171"/>
-      <c r="E6" s="171"/>
-      <c r="F6" s="171"/>
-      <c r="G6" s="171"/>
-      <c r="H6" s="172" t="s">
+      <c r="I6" s="212"/>
+      <c r="J6" s="212"/>
+      <c r="K6" s="212"/>
+      <c r="L6" s="212"/>
+      <c r="M6" s="212"/>
+      <c r="N6" s="212"/>
+      <c r="O6" s="211" t="s">
         <v>134</v>
       </c>
-      <c r="I6" s="173"/>
-      <c r="J6" s="173"/>
-      <c r="K6" s="173"/>
-      <c r="L6" s="173"/>
-      <c r="M6" s="173"/>
-      <c r="N6" s="173"/>
-      <c r="O6" s="172" t="s">
+      <c r="P6" s="212"/>
+      <c r="Q6" s="212"/>
+    </row>
+    <row r="7" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A7" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="P6" s="173"/>
-      <c r="Q6" s="173"/>
-    </row>
-    <row r="7" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -6055,384 +6685,373 @@
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
     </row>
-    <row r="8" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A8" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="O8" s="11"/>
+    </row>
+    <row r="9" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A9" s="11" t="s">
         <v>138</v>
-      </c>
-      <c r="O8" s="11"/>
-    </row>
-    <row r="9" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="11" t="s">
-        <v>139</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="O9" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="O9" s="11" t="s">
+    </row>
+    <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A10" s="11" t="s">
         <v>141</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="11" t="s">
-        <v>142</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="4"/>
-      <c r="J10" s="174" t="s">
+      <c r="J10" s="204" t="s">
+        <v>142</v>
+      </c>
+      <c r="K10" s="205"/>
+      <c r="L10" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="O10" s="11"/>
+    </row>
+    <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A11" s="11" t="s">
         <v>143</v>
-      </c>
-      <c r="K10" s="175"/>
-      <c r="L10" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="O10" s="11"/>
-    </row>
-    <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="11" t="s">
-        <v>144</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="4"/>
       <c r="J11" s="21" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K11" s="22"/>
       <c r="L11" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O11" s="11"/>
     </row>
-    <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A12" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="4"/>
       <c r="J12" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K12" s="22"/>
       <c r="L12" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O12" s="11"/>
     </row>
-    <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A13" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="4"/>
       <c r="J13" s="21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K13" s="22"/>
       <c r="L13" s="23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O13" s="11"/>
     </row>
-    <row r="14" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A14" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="H14" s="11"/>
       <c r="I14" s="4"/>
       <c r="J14" s="21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K14" s="22"/>
       <c r="L14" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O14" s="11"/>
     </row>
-    <row r="15" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A15" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H15" s="11"/>
       <c r="J15" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K15" s="22"/>
       <c r="L15" s="23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O15" s="11"/>
     </row>
-    <row r="16" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A16" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
       <c r="H16" s="11"/>
       <c r="J16" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K16" s="22"/>
       <c r="L16" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O16" s="11"/>
     </row>
-    <row r="17" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A17" s="92" t="s">
+        <v>239</v>
+      </c>
       <c r="H17" s="11"/>
+      <c r="J17" s="93" t="s">
+        <v>240</v>
+      </c>
+      <c r="K17" s="94"/>
+      <c r="L17" s="95" t="s">
+        <v>241</v>
+      </c>
       <c r="O17" s="11"/>
     </row>
-    <row r="18" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="11" t="s">
-        <v>141</v>
-      </c>
+    <row r="18" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="H18" s="11"/>
-      <c r="I18" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="O18" s="11"/>
     </row>
-    <row r="19" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="11"/>
+    <row r="19" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A19" s="11" t="s">
+        <v>140</v>
+      </c>
       <c r="H19" s="11"/>
-      <c r="J19" s="3" t="s">
-        <v>156</v>
+      <c r="I19" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="O19" s="11"/>
     </row>
-    <row r="20" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A20" s="11"/>
       <c r="H20" s="11"/>
       <c r="J20" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="O20" s="11"/>
+    </row>
+    <row r="21" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="J21" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="O21" s="11"/>
+    </row>
+    <row r="22" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A22" s="11"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="11"/>
+      <c r="J22" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="O20" s="11"/>
-    </row>
-    <row r="21" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="11"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="11"/>
-      <c r="J21" s="24" t="s">
+      <c r="K22" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="K21" s="24" t="s">
+      <c r="L22" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="L21" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="M21" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="O21" s="11"/>
-    </row>
-    <row r="22" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="J22" s="176" t="s">
-        <v>161</v>
-      </c>
-      <c r="K22" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="L22" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="M22" s="27" t="s">
-        <v>163</v>
+      <c r="M22" s="24" t="s">
+        <v>114</v>
       </c>
       <c r="O22" s="11"/>
     </row>
-    <row r="23" spans="1:15" s="3" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A23" s="11"/>
       <c r="H23" s="11"/>
-      <c r="J23" s="176"/>
-      <c r="K23" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="L23" s="28" t="s">
-        <v>165</v>
+      <c r="J23" s="206" t="s">
+        <v>160</v>
+      </c>
+      <c r="K23" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="25" t="s">
+        <v>161</v>
       </c>
       <c r="M23" s="27" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="O23" s="11"/>
     </row>
-    <row r="24" spans="1:15" s="3" customFormat="1" ht="47.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:15" s="3" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A24" s="11"/>
       <c r="H24" s="11"/>
-      <c r="J24" s="176"/>
-      <c r="K24" s="75" t="s">
-        <v>193</v>
+      <c r="J24" s="207"/>
+      <c r="K24" s="27" t="s">
+        <v>163</v>
       </c>
       <c r="L24" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="M24" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="M24" s="27" t="s">
-        <v>167</v>
-      </c>
       <c r="O24" s="11"/>
     </row>
-    <row r="25" spans="1:15" s="3" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:15" s="3" customFormat="1" ht="47.1" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A25" s="11"/>
       <c r="H25" s="11"/>
-      <c r="J25" s="176"/>
+      <c r="J25" s="207"/>
       <c r="K25" s="75" t="s">
-        <v>191</v>
-      </c>
-      <c r="L25" s="74" t="s">
         <v>192</v>
       </c>
+      <c r="L25" s="28" t="s">
+        <v>164</v>
+      </c>
       <c r="M25" s="27" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="O25" s="11"/>
     </row>
-    <row r="26" spans="1:15" s="3" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:15" s="3" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A26" s="11"/>
       <c r="H26" s="11"/>
-      <c r="J26" s="176"/>
+      <c r="J26" s="207"/>
       <c r="K26" s="75" t="s">
+        <v>190</v>
+      </c>
+      <c r="L26" s="74" t="s">
+        <v>191</v>
+      </c>
+      <c r="M26" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="O26" s="11"/>
+    </row>
+    <row r="27" spans="1:15" s="3" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="J27" s="207"/>
+      <c r="K27" s="75" t="s">
+        <v>188</v>
+      </c>
+      <c r="L27" s="74" t="s">
         <v>189</v>
       </c>
-      <c r="L26" s="74" t="s">
-        <v>190</v>
-      </c>
-      <c r="M26" s="27" t="s">
+      <c r="M27" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="O27" s="11"/>
+    </row>
+    <row r="28" spans="1:15" s="3" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="J28" s="208"/>
+      <c r="K28" s="98" t="s">
+        <v>242</v>
+      </c>
+      <c r="L28" s="91" t="s">
+        <v>243</v>
+      </c>
+      <c r="M28" s="99" t="s">
+        <v>244</v>
+      </c>
+      <c r="O28" s="11"/>
+    </row>
+    <row r="29" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="101" t="s">
+        <v>91</v>
+      </c>
+      <c r="K29" s="102"/>
+      <c r="L29" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="O26" s="11"/>
-    </row>
-    <row r="27" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="83" t="s">
-        <v>92</v>
-      </c>
-      <c r="K27" s="84"/>
-      <c r="L27" s="25" t="s">
+      <c r="M29" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="M27" s="27" t="s">
+      <c r="N29" s="3"/>
+      <c r="O29" s="10"/>
+    </row>
+    <row r="30" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A30" s="13"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="10"/>
+      <c r="O30" s="10"/>
+    </row>
+    <row r="31" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A31" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="H31" s="10"/>
+      <c r="I31" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="N27" s="3"/>
-      <c r="O27" s="10"/>
-    </row>
-    <row r="28" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="10"/>
-      <c r="O28" s="10"/>
-    </row>
-    <row r="29" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="H29" s="10"/>
-      <c r="I29" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="J29" s="3"/>
-      <c r="O29" s="10" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="77" t="s">
-        <v>194</v>
-      </c>
-      <c r="O30" s="10"/>
-    </row>
-    <row r="31" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="77"/>
-      <c r="O31" s="10"/>
-    </row>
-    <row r="32" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="O31" s="10" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A32" s="10"/>
       <c r="H32" s="10"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3" t="s">
-        <v>173</v>
+      <c r="I32" s="4"/>
+      <c r="J32" s="77" t="s">
+        <v>193</v>
       </c>
       <c r="O32" s="10"/>
     </row>
-    <row r="33" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
+    <row r="33" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A33" s="10"/>
       <c r="H33" s="10"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="179" t="s">
-        <v>220</v>
-      </c>
-      <c r="K33" s="180"/>
-      <c r="L33" s="179" t="s">
-        <v>219</v>
-      </c>
-      <c r="M33" s="180"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="77"/>
       <c r="O33" s="10"/>
     </row>
-    <row r="34" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
+    <row r="34" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
       <c r="H34" s="10"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="177" t="s">
-        <v>58</v>
-      </c>
-      <c r="K34" s="178"/>
-      <c r="L34" s="181" t="s">
-        <v>226</v>
-      </c>
-      <c r="M34" s="182"/>
+      <c r="J34" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="O34" s="10"/>
     </row>
-    <row r="35" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
@@ -6442,17 +7061,17 @@
       <c r="G35" s="14"/>
       <c r="H35" s="10"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="177" t="s">
-        <v>216</v>
-      </c>
-      <c r="K35" s="178"/>
-      <c r="L35" s="181" t="s">
-        <v>227</v>
-      </c>
-      <c r="M35" s="182"/>
+      <c r="J35" s="198" t="s">
+        <v>219</v>
+      </c>
+      <c r="K35" s="199"/>
+      <c r="L35" s="198" t="s">
+        <v>218</v>
+      </c>
+      <c r="M35" s="199"/>
       <c r="O35" s="10"/>
     </row>
-    <row r="36" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A36" s="13"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -6462,17 +7081,17 @@
       <c r="G36" s="14"/>
       <c r="H36" s="10"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="177" t="s">
-        <v>102</v>
-      </c>
-      <c r="K36" s="178"/>
-      <c r="L36" s="181" t="s">
-        <v>228</v>
-      </c>
-      <c r="M36" s="182"/>
+      <c r="J36" s="202" t="s">
+        <v>57</v>
+      </c>
+      <c r="K36" s="203"/>
+      <c r="L36" s="200" t="s">
+        <v>225</v>
+      </c>
+      <c r="M36" s="201"/>
       <c r="O36" s="10"/>
     </row>
-    <row r="37" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A37" s="13"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
@@ -6482,17 +7101,17 @@
       <c r="G37" s="14"/>
       <c r="H37" s="10"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="177" t="s">
-        <v>68</v>
-      </c>
-      <c r="K37" s="178"/>
-      <c r="L37" s="177" t="s">
-        <v>229</v>
-      </c>
-      <c r="M37" s="178"/>
+      <c r="J37" s="202" t="s">
+        <v>215</v>
+      </c>
+      <c r="K37" s="203"/>
+      <c r="L37" s="200" t="s">
+        <v>226</v>
+      </c>
+      <c r="M37" s="201"/>
       <c r="O37" s="10"/>
     </row>
-    <row r="38" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A38" s="13"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -6502,18 +7121,18 @@
       <c r="G38" s="14"/>
       <c r="H38" s="10"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="177" t="s">
-        <v>217</v>
-      </c>
-      <c r="K38" s="178"/>
-      <c r="L38" s="177" t="s">
-        <v>230</v>
-      </c>
-      <c r="M38" s="178"/>
+      <c r="J38" s="202" t="s">
+        <v>101</v>
+      </c>
+      <c r="K38" s="203"/>
+      <c r="L38" s="200" t="s">
+        <v>227</v>
+      </c>
+      <c r="M38" s="201"/>
       <c r="O38" s="10"/>
     </row>
-    <row r="39" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="15"/>
+    <row r="39" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A39" s="13"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
       <c r="D39" s="14"/>
@@ -6522,83 +7141,117 @@
       <c r="G39" s="14"/>
       <c r="H39" s="10"/>
       <c r="I39" s="3"/>
-      <c r="J39" s="177" t="s">
-        <v>218</v>
-      </c>
-      <c r="K39" s="178"/>
-      <c r="L39" s="177" t="s">
-        <v>231</v>
-      </c>
-      <c r="M39" s="178"/>
+      <c r="J39" s="202" t="s">
+        <v>67</v>
+      </c>
+      <c r="K39" s="203"/>
+      <c r="L39" s="202" t="s">
+        <v>228</v>
+      </c>
+      <c r="M39" s="203"/>
       <c r="O39" s="10"/>
     </row>
-    <row r="40" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
+    <row r="40" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A40" s="13"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
       <c r="H40" s="10"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="76"/>
+      <c r="J40" s="202" t="s">
+        <v>216</v>
+      </c>
+      <c r="K40" s="203"/>
+      <c r="L40" s="202" t="s">
+        <v>229</v>
+      </c>
+      <c r="M40" s="203"/>
       <c r="O40" s="10"/>
     </row>
-    <row r="41" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
+    <row r="41" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A41" s="13"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
       <c r="H41" s="10"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="76" t="s">
-        <v>222</v>
-      </c>
+      <c r="J41" s="96" t="s">
+        <v>245</v>
+      </c>
+      <c r="K41" s="97"/>
+      <c r="L41" s="96" t="s">
+        <v>246</v>
+      </c>
+      <c r="M41" s="84"/>
       <c r="O41" s="10"/>
     </row>
-    <row r="42" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
+    <row r="42" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A42" s="13"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
       <c r="H42" s="10"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="76" t="s">
-        <v>223</v>
-      </c>
+      <c r="J42" s="96" t="s">
+        <v>247</v>
+      </c>
+      <c r="K42" s="97"/>
+      <c r="L42" s="96" t="s">
+        <v>248</v>
+      </c>
+      <c r="M42" s="84"/>
       <c r="O42" s="10"/>
     </row>
-    <row r="43" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
+    <row r="43" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A43" s="13"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
       <c r="H43" s="10"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="76" t="s">
-        <v>224</v>
-      </c>
+      <c r="J43" s="196" t="s">
+        <v>249</v>
+      </c>
+      <c r="K43" s="197"/>
+      <c r="L43" s="96" t="s">
+        <v>250</v>
+      </c>
+      <c r="M43" s="84"/>
       <c r="O43" s="10"/>
     </row>
-    <row r="44" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
+    <row r="44" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A44" s="15"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
       <c r="H44" s="10"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="76"/>
+      <c r="J44" s="202" t="s">
+        <v>217</v>
+      </c>
+      <c r="K44" s="203"/>
+      <c r="L44" s="202" t="s">
+        <v>230</v>
+      </c>
+      <c r="M44" s="203"/>
       <c r="O44" s="10"/>
     </row>
-    <row r="45" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
@@ -6607,12 +7260,10 @@
       <c r="G45" s="3"/>
       <c r="H45" s="10"/>
       <c r="I45" s="3"/>
-      <c r="J45" s="76" t="s">
-        <v>198</v>
-      </c>
+      <c r="J45" s="76"/>
       <c r="O45" s="10"/>
     </row>
-    <row r="46" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
@@ -6621,19 +7272,12 @@
       <c r="G46" s="3"/>
       <c r="H46" s="10"/>
       <c r="I46" s="3"/>
-      <c r="J46" s="73" t="s">
-        <v>203</v>
-      </c>
-      <c r="K46" s="170" t="s">
-        <v>211</v>
-      </c>
-      <c r="L46" s="170"/>
-      <c r="M46" s="82" t="s">
-        <v>215</v>
+      <c r="J46" s="76" t="s">
+        <v>221</v>
       </c>
       <c r="O46" s="10"/>
     </row>
-    <row r="47" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
@@ -6642,19 +7286,12 @@
       <c r="G47" s="3"/>
       <c r="H47" s="10"/>
       <c r="I47" s="3"/>
-      <c r="J47" s="80" t="s">
-        <v>63</v>
-      </c>
-      <c r="K47" s="168" t="s">
-        <v>204</v>
-      </c>
-      <c r="L47" s="168"/>
-      <c r="M47" s="81" t="s">
-        <v>212</v>
+      <c r="J47" s="76" t="s">
+        <v>222</v>
       </c>
       <c r="O47" s="10"/>
     </row>
-    <row r="48" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
@@ -6663,19 +7300,12 @@
       <c r="G48" s="3"/>
       <c r="H48" s="10"/>
       <c r="I48" s="3"/>
-      <c r="J48" s="80" t="s">
-        <v>65</v>
-      </c>
-      <c r="K48" s="168" t="s">
-        <v>205</v>
-      </c>
-      <c r="L48" s="168"/>
-      <c r="M48" s="81" t="s">
-        <v>212</v>
+      <c r="J48" s="76" t="s">
+        <v>223</v>
       </c>
       <c r="O48" s="10"/>
     </row>
-    <row r="49" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
@@ -6684,19 +7314,10 @@
       <c r="G49" s="3"/>
       <c r="H49" s="10"/>
       <c r="I49" s="3"/>
-      <c r="J49" s="80" t="s">
-        <v>58</v>
-      </c>
-      <c r="K49" s="168" t="s">
-        <v>206</v>
-      </c>
-      <c r="L49" s="169"/>
-      <c r="M49" s="81" t="s">
-        <v>212</v>
-      </c>
+      <c r="J49" s="76"/>
       <c r="O49" s="10"/>
     </row>
-    <row r="50" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
@@ -6705,19 +7326,12 @@
       <c r="G50" s="3"/>
       <c r="H50" s="10"/>
       <c r="I50" s="3"/>
-      <c r="J50" s="80" t="s">
-        <v>199</v>
-      </c>
-      <c r="K50" s="168" t="s">
-        <v>207</v>
-      </c>
-      <c r="L50" s="169"/>
-      <c r="M50" s="81" t="s">
-        <v>213</v>
+      <c r="J50" s="76" t="s">
+        <v>197</v>
       </c>
       <c r="O50" s="10"/>
     </row>
-    <row r="51" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
@@ -6726,19 +7340,19 @@
       <c r="G51" s="3"/>
       <c r="H51" s="10"/>
       <c r="I51" s="3"/>
-      <c r="J51" s="80" t="s">
-        <v>200</v>
-      </c>
-      <c r="K51" s="168" t="s">
-        <v>208</v>
-      </c>
-      <c r="L51" s="169"/>
-      <c r="M51" s="81" t="s">
+      <c r="J51" s="73" t="s">
+        <v>202</v>
+      </c>
+      <c r="K51" s="214" t="s">
+        <v>210</v>
+      </c>
+      <c r="L51" s="214"/>
+      <c r="M51" s="82" t="s">
         <v>214</v>
       </c>
       <c r="O51" s="10"/>
     </row>
-    <row r="52" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
@@ -6748,18 +7362,18 @@
       <c r="H52" s="10"/>
       <c r="I52" s="3"/>
       <c r="J52" s="80" t="s">
-        <v>201</v>
-      </c>
-      <c r="K52" s="168" t="s">
-        <v>209</v>
-      </c>
-      <c r="L52" s="169"/>
+        <v>62</v>
+      </c>
+      <c r="K52" s="209" t="s">
+        <v>203</v>
+      </c>
+      <c r="L52" s="209"/>
       <c r="M52" s="81" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="O52" s="10"/>
     </row>
-    <row r="53" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
@@ -6769,16 +7383,18 @@
       <c r="H53" s="10"/>
       <c r="I53" s="3"/>
       <c r="J53" s="80" t="s">
-        <v>202</v>
-      </c>
-      <c r="K53" s="168" t="s">
-        <v>210</v>
-      </c>
-      <c r="L53" s="169"/>
-      <c r="M53" s="81"/>
+        <v>64</v>
+      </c>
+      <c r="K53" s="209" t="s">
+        <v>204</v>
+      </c>
+      <c r="L53" s="209"/>
+      <c r="M53" s="81" t="s">
+        <v>211</v>
+      </c>
       <c r="O53" s="10"/>
     </row>
-    <row r="54" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
@@ -6787,300 +7403,486 @@
       <c r="G54" s="3"/>
       <c r="H54" s="10"/>
       <c r="I54" s="3"/>
-      <c r="J54" s="30"/>
-      <c r="K54" s="30"/>
-      <c r="L54" s="79"/>
-      <c r="M54" s="79"/>
+      <c r="J54" s="80" t="s">
+        <v>57</v>
+      </c>
+      <c r="K54" s="209" t="s">
+        <v>205</v>
+      </c>
+      <c r="L54" s="213"/>
+      <c r="M54" s="81" t="s">
+        <v>211</v>
+      </c>
       <c r="O54" s="10"/>
     </row>
-    <row r="55" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
+    <row r="55" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
       <c r="H55" s="10"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="3" t="s">
-        <v>174</v>
+      <c r="I55" s="3"/>
+      <c r="J55" s="80" t="s">
+        <v>198</v>
+      </c>
+      <c r="K55" s="209" t="s">
+        <v>206</v>
+      </c>
+      <c r="L55" s="213"/>
+      <c r="M55" s="81" t="s">
+        <v>212</v>
       </c>
       <c r="O55" s="10"/>
     </row>
-    <row r="56" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
+    <row r="56" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
       <c r="H56" s="10"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="76" t="s">
-        <v>225</v>
+      <c r="I56" s="3"/>
+      <c r="J56" s="80" t="s">
+        <v>199</v>
+      </c>
+      <c r="K56" s="209" t="s">
+        <v>207</v>
+      </c>
+      <c r="L56" s="213"/>
+      <c r="M56" s="81" t="s">
+        <v>213</v>
       </c>
       <c r="O56" s="10"/>
     </row>
-    <row r="57" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="15"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
+    <row r="57" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
       <c r="H57" s="10"/>
       <c r="I57" s="3"/>
-      <c r="J57" s="30"/>
-      <c r="K57" s="30"/>
-      <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2"/>
-      <c r="O57" s="31"/>
-      <c r="P57" s="2"/>
-      <c r="Q57" s="2"/>
-    </row>
-    <row r="58" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="H58" s="11"/>
-      <c r="I58" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="O58" s="11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
+      <c r="J57" s="80" t="s">
+        <v>200</v>
+      </c>
+      <c r="K57" s="209" t="s">
+        <v>208</v>
+      </c>
+      <c r="L57" s="213"/>
+      <c r="M57" s="81" t="s">
+        <v>213</v>
+      </c>
+      <c r="O57" s="10"/>
+    </row>
+    <row r="58" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="100" t="s">
+        <v>245</v>
+      </c>
+      <c r="K58" s="93" t="s">
+        <v>251</v>
+      </c>
+      <c r="L58" s="94"/>
+      <c r="M58" s="81"/>
+      <c r="O58" s="10"/>
+    </row>
+    <row r="59" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
       <c r="H59" s="10"/>
       <c r="I59" s="3"/>
-      <c r="J59" s="76" t="s">
-        <v>232</v>
-      </c>
-      <c r="K59" s="3"/>
-      <c r="L59" s="3"/>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
-      <c r="O59" s="11"/>
-    </row>
-    <row r="60" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="11"/>
-      <c r="H60" s="11"/>
-      <c r="J60" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="K60" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="L60" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="O60" s="11"/>
-    </row>
-    <row r="61" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="11"/>
-      <c r="H61" s="11"/>
-      <c r="J61" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="K61" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="L61" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="O61" s="11"/>
-    </row>
-    <row r="62" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="11"/>
-      <c r="H62" s="11"/>
-      <c r="J62" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="K62" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="L62" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="O62" s="11"/>
-    </row>
-    <row r="63" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="H63" s="11"/>
-      <c r="J63" s="168" t="s">
-        <v>89</v>
-      </c>
-      <c r="K63" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="L63" s="23" t="s">
-        <v>182</v>
-      </c>
-      <c r="O63" s="11" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="11"/>
-      <c r="H64" s="11"/>
-      <c r="J64" s="168"/>
-      <c r="K64" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="L64" s="23" t="s">
-        <v>185</v>
-      </c>
-      <c r="O64" s="11"/>
-    </row>
-    <row r="65" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="11"/>
-      <c r="H65" s="11"/>
-      <c r="O65" s="11"/>
-    </row>
-    <row r="66" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="11"/>
+      <c r="J59" s="96" t="s">
+        <v>247</v>
+      </c>
+      <c r="K59" s="93" t="s">
+        <v>252</v>
+      </c>
+      <c r="L59" s="94"/>
+      <c r="M59" s="81"/>
+      <c r="O59" s="10"/>
+    </row>
+    <row r="60" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="10"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="100" t="s">
+        <v>249</v>
+      </c>
+      <c r="K60" s="215" t="s">
+        <v>253</v>
+      </c>
+      <c r="L60" s="216"/>
+      <c r="M60" s="81"/>
+      <c r="O60" s="10"/>
+    </row>
+    <row r="61" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="80" t="s">
+        <v>201</v>
+      </c>
+      <c r="K61" s="209" t="s">
+        <v>209</v>
+      </c>
+      <c r="L61" s="213"/>
+      <c r="M61" s="81"/>
+      <c r="O61" s="10"/>
+    </row>
+    <row r="62" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="10"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="30"/>
+      <c r="K62" s="30"/>
+      <c r="L62" s="79"/>
+      <c r="M62" s="79"/>
+      <c r="O62" s="10"/>
+    </row>
+    <row r="63" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A63" s="13"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="10"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="O63" s="10"/>
+    </row>
+    <row r="64" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A64" s="13"/>
+      <c r="B64" s="14"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="10"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="76" t="s">
+        <v>224</v>
+      </c>
+      <c r="O64" s="10"/>
+    </row>
+    <row r="65" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A65" s="15"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="10"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="30"/>
+      <c r="K65" s="30"/>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="31"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+    </row>
+    <row r="66" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A66" s="11" t="s">
+        <v>174</v>
+      </c>
       <c r="H66" s="11"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="77" t="s">
-        <v>221</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="O66" s="11"/>
-    </row>
-    <row r="67" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="11"/>
-      <c r="H67" s="11"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="K67" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="L67" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="M67" s="2"/>
-      <c r="N67" s="2"/>
+      <c r="I66" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="O66" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A67" s="13"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="10"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="76" t="s">
+        <v>231</v>
+      </c>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
       <c r="O67" s="11"/>
     </row>
-    <row r="68" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A68" s="11"/>
       <c r="H68" s="11"/>
-      <c r="J68" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="K68" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="L68" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2"/>
+      <c r="J68" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="K68" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="L68" s="20" t="s">
+        <v>46</v>
+      </c>
       <c r="O68" s="11"/>
     </row>
-    <row r="69" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A69" s="11"/>
       <c r="H69" s="11"/>
       <c r="J69" s="21" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K69" s="23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L69" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="M69" s="2"/>
-      <c r="N69" s="2"/>
+        <v>84</v>
+      </c>
       <c r="O69" s="11"/>
     </row>
-    <row r="70" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A70" s="11"/>
       <c r="H70" s="11"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="168" t="s">
-        <v>89</v>
+      <c r="J70" s="21" t="s">
+        <v>85</v>
       </c>
       <c r="K70" s="23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L70" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="M70" s="2"/>
-      <c r="N70" s="2"/>
+        <v>179</v>
+      </c>
       <c r="O70" s="11"/>
     </row>
-    <row r="71" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="11"/>
+    <row r="71" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="H71" s="11"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="168"/>
+      <c r="J71" s="209" t="s">
+        <v>88</v>
+      </c>
       <c r="K71" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="L71" s="29">
-        <v>0</v>
-      </c>
-      <c r="M71" s="2"/>
-      <c r="N71" s="2"/>
-      <c r="O71" s="11"/>
-    </row>
-    <row r="72" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+        <v>180</v>
+      </c>
+      <c r="L71" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="O71" s="11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A72" s="11"/>
       <c r="H72" s="11"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
+      <c r="J72" s="209"/>
+      <c r="K72" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="L72" s="23" t="s">
+        <v>184</v>
+      </c>
       <c r="O72" s="11"/>
     </row>
-    <row r="73" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="I73" s="2"/>
-      <c r="K73" s="2"/>
-      <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
-    </row>
-    <row r="74" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="I74" s="2"/>
-      <c r="K74" s="2"/>
-      <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
-      <c r="N74" s="2"/>
-    </row>
-    <row r="75" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="I75" s="3"/>
-      <c r="J75" s="3"/>
-      <c r="K75" s="3"/>
-      <c r="L75" s="3"/>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3"/>
+    <row r="73" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A73" s="11"/>
+      <c r="H73" s="11"/>
+      <c r="O73" s="11"/>
+    </row>
+    <row r="74" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A74" s="11"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="77" t="s">
+        <v>220</v>
+      </c>
+      <c r="N74" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="O74" s="11"/>
+    </row>
+    <row r="75" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A75" s="11"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="K75" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="L75" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M75" s="2"/>
+      <c r="N75" s="2"/>
+      <c r="O75" s="11"/>
+    </row>
+    <row r="76" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="J76" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="K76" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="L76" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2"/>
+      <c r="O76" s="11"/>
+    </row>
+    <row r="77" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A77" s="11"/>
+      <c r="H77" s="11"/>
+      <c r="J77" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="K77" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="L77" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="M77" s="2"/>
+      <c r="N77" s="2"/>
+      <c r="O77" s="11"/>
+    </row>
+    <row r="78" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A78" s="11"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="209" t="s">
+        <v>88</v>
+      </c>
+      <c r="K78" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="L78" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="M78" s="2"/>
+      <c r="N78" s="2"/>
+      <c r="O78" s="11"/>
+    </row>
+    <row r="79" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A79" s="11"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="209"/>
+      <c r="K79" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="L79" s="29">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2"/>
+      <c r="N79" s="2"/>
+      <c r="O79" s="11"/>
+    </row>
+    <row r="80" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="2"/>
+      <c r="L80" s="2"/>
+      <c r="M80" s="2"/>
+      <c r="N80" s="2"/>
+      <c r="O80" s="11"/>
+    </row>
+    <row r="81" spans="9:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="I81" s="2"/>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
+      <c r="M81" s="2"/>
+      <c r="N81" s="2"/>
+    </row>
+    <row r="82" spans="9:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="I82" s="2"/>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2"/>
+      <c r="N82" s="2"/>
+    </row>
+    <row r="83" spans="9:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3"/>
+      <c r="L83" s="3"/>
+      <c r="M83" s="3"/>
+      <c r="N83" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="J33:K33"/>
+  <mergeCells count="49">
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="K61:L61"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="J71:J72"/>
+    <mergeCell ref="J78:J79"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="J36:K36"/>
     <mergeCell ref="L36:M36"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="L37:M37"/>
     <mergeCell ref="A1:H4"/>
     <mergeCell ref="N3:O4"/>
     <mergeCell ref="P3:Q4"/>
@@ -7088,40 +7890,16 @@
     <mergeCell ref="P1:Q2"/>
     <mergeCell ref="I3:J4"/>
     <mergeCell ref="I1:J2"/>
-    <mergeCell ref="J63:J64"/>
-    <mergeCell ref="J70:J71"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J23:J28"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="L38:M38"/>
     <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J22:J26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="K53:L53"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="K50:L50"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/設計/部品在庫管理/機能仕様書_部品在庫照会API.xlsx
+++ b/docs/設計/部品在庫管理/機能仕様書_部品在庫照会API.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usaposu\git\Java-apiCourse-staffservice\docs\設計\部品在庫管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A204A9D-3B21-45FF-9AE2-5B6FBB5C790A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A809E2-4458-46CA-8F17-D5CE8DA154B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="9766" windowHeight="10882" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="19" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="263">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -1180,6 +1180,14 @@
       <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>2025/10/5</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>2025/10/5</t>
+    <phoneticPr fontId="11"/>
   </si>
 </sst>
 </file>
@@ -1508,7 +1516,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="217">
+  <cellXfs count="218">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1821,132 +1829,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1980,6 +1862,192 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2001,68 +2069,32 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2073,29 +2105,56 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2109,56 +2168,8 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3428,452 +3439,452 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="113" t="s">
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="119" t="s">
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="130"/>
+      <c r="Q1" s="134" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
-      <c r="V1" s="123" t="s">
+      <c r="R1" s="135"/>
+      <c r="S1" s="135"/>
+      <c r="T1" s="135"/>
+      <c r="U1" s="135"/>
+      <c r="V1" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="123"/>
-      <c r="X1" s="123"/>
-      <c r="Y1" s="134" t="s">
+      <c r="W1" s="138"/>
+      <c r="X1" s="138"/>
+      <c r="Y1" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="135"/>
-      <c r="AA1" s="135"/>
-      <c r="AB1" s="136"/>
-      <c r="AC1" s="128" t="s">
+      <c r="Z1" s="150"/>
+      <c r="AA1" s="150"/>
+      <c r="AB1" s="151"/>
+      <c r="AC1" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="AD1" s="129"/>
-      <c r="AE1" s="130"/>
-      <c r="AF1" s="124" t="s">
+      <c r="AD1" s="144"/>
+      <c r="AE1" s="145"/>
+      <c r="AF1" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="125"/>
-      <c r="AH1" s="125"/>
+      <c r="AG1" s="140"/>
+      <c r="AH1" s="140"/>
     </row>
     <row r="2" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="107"/>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="108"/>
-      <c r="K2" s="109"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="117"/>
-      <c r="N2" s="117"/>
-      <c r="O2" s="117"/>
-      <c r="P2" s="118"/>
-      <c r="Q2" s="121"/>
-      <c r="R2" s="122"/>
-      <c r="S2" s="122"/>
-      <c r="T2" s="122"/>
-      <c r="U2" s="122"/>
-      <c r="V2" s="123"/>
-      <c r="W2" s="123"/>
-      <c r="X2" s="123"/>
-      <c r="Y2" s="137"/>
-      <c r="Z2" s="138"/>
-      <c r="AA2" s="138"/>
-      <c r="AB2" s="139"/>
-      <c r="AC2" s="131"/>
-      <c r="AD2" s="132"/>
-      <c r="AE2" s="133"/>
-      <c r="AF2" s="126"/>
-      <c r="AG2" s="127"/>
-      <c r="AH2" s="127"/>
+      <c r="A2" s="122"/>
+      <c r="B2" s="123"/>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="131"/>
+      <c r="M2" s="132"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="132"/>
+      <c r="P2" s="133"/>
+      <c r="Q2" s="136"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
+      <c r="U2" s="137"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="138"/>
+      <c r="Y2" s="152"/>
+      <c r="Z2" s="153"/>
+      <c r="AA2" s="153"/>
+      <c r="AB2" s="154"/>
+      <c r="AC2" s="146"/>
+      <c r="AD2" s="147"/>
+      <c r="AE2" s="148"/>
+      <c r="AF2" s="141"/>
+      <c r="AG2" s="142"/>
+      <c r="AH2" s="142"/>
     </row>
     <row r="3" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A3" s="107"/>
-      <c r="B3" s="108"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="108"/>
-      <c r="K3" s="109"/>
-      <c r="L3" s="113" t="s">
+      <c r="A3" s="122"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="124"/>
+      <c r="L3" s="128" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="114"/>
-      <c r="N3" s="114"/>
-      <c r="O3" s="114"/>
-      <c r="P3" s="115"/>
-      <c r="Q3" s="119" t="s">
+      <c r="M3" s="129"/>
+      <c r="N3" s="129"/>
+      <c r="O3" s="129"/>
+      <c r="P3" s="130"/>
+      <c r="Q3" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="120"/>
-      <c r="S3" s="120"/>
-      <c r="T3" s="120"/>
-      <c r="U3" s="120"/>
-      <c r="V3" s="123" t="s">
+      <c r="R3" s="135"/>
+      <c r="S3" s="135"/>
+      <c r="T3" s="135"/>
+      <c r="U3" s="135"/>
+      <c r="V3" s="138" t="s">
         <v>15</v>
       </c>
-      <c r="W3" s="123"/>
-      <c r="X3" s="123"/>
-      <c r="Y3" s="134" t="s">
+      <c r="W3" s="138"/>
+      <c r="X3" s="138"/>
+      <c r="Y3" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="Z3" s="135"/>
-      <c r="AA3" s="135"/>
-      <c r="AB3" s="136"/>
-      <c r="AC3" s="123" t="s">
+      <c r="Z3" s="150"/>
+      <c r="AA3" s="150"/>
+      <c r="AB3" s="151"/>
+      <c r="AC3" s="138" t="s">
         <v>16</v>
       </c>
-      <c r="AD3" s="123"/>
-      <c r="AE3" s="123"/>
-      <c r="AF3" s="124" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG3" s="125"/>
-      <c r="AH3" s="125"/>
+      <c r="AD3" s="138"/>
+      <c r="AE3" s="138"/>
+      <c r="AF3" s="217" t="s">
+        <v>261</v>
+      </c>
+      <c r="AG3" s="140"/>
+      <c r="AH3" s="140"/>
     </row>
     <row r="4" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A4" s="110"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="117"/>
-      <c r="N4" s="117"/>
-      <c r="O4" s="117"/>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="122"/>
-      <c r="S4" s="122"/>
-      <c r="T4" s="122"/>
-      <c r="U4" s="122"/>
-      <c r="V4" s="123"/>
-      <c r="W4" s="123"/>
-      <c r="X4" s="123"/>
-      <c r="Y4" s="137"/>
-      <c r="Z4" s="138"/>
-      <c r="AA4" s="138"/>
-      <c r="AB4" s="139"/>
-      <c r="AC4" s="123"/>
-      <c r="AD4" s="123"/>
-      <c r="AE4" s="123"/>
-      <c r="AF4" s="126"/>
-      <c r="AG4" s="127"/>
-      <c r="AH4" s="127"/>
+      <c r="A4" s="125"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="126"/>
+      <c r="J4" s="126"/>
+      <c r="K4" s="127"/>
+      <c r="L4" s="131"/>
+      <c r="M4" s="132"/>
+      <c r="N4" s="132"/>
+      <c r="O4" s="132"/>
+      <c r="P4" s="133"/>
+      <c r="Q4" s="136"/>
+      <c r="R4" s="137"/>
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137"/>
+      <c r="V4" s="138"/>
+      <c r="W4" s="138"/>
+      <c r="X4" s="138"/>
+      <c r="Y4" s="152"/>
+      <c r="Z4" s="153"/>
+      <c r="AA4" s="153"/>
+      <c r="AB4" s="154"/>
+      <c r="AC4" s="138"/>
+      <c r="AD4" s="138"/>
+      <c r="AE4" s="138"/>
+      <c r="AF4" s="141"/>
+      <c r="AG4" s="142"/>
+      <c r="AH4" s="142"/>
     </row>
     <row r="5" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A5" s="146" t="s">
+      <c r="A5" s="104" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="147"/>
-      <c r="C5" s="147"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="148"/>
-      <c r="H5" s="149" t="s">
+      <c r="B5" s="105"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="150"/>
-      <c r="J5" s="150"/>
-      <c r="K5" s="150"/>
-      <c r="L5" s="150"/>
-      <c r="M5" s="150"/>
-      <c r="N5" s="150"/>
-      <c r="O5" s="150"/>
-      <c r="P5" s="150"/>
-      <c r="Q5" s="150"/>
-      <c r="R5" s="150"/>
-      <c r="S5" s="150"/>
-      <c r="T5" s="150"/>
-      <c r="U5" s="150"/>
-      <c r="V5" s="150"/>
-      <c r="W5" s="150"/>
-      <c r="X5" s="150"/>
-      <c r="Y5" s="150"/>
-      <c r="Z5" s="150"/>
-      <c r="AA5" s="150"/>
-      <c r="AB5" s="150"/>
-      <c r="AC5" s="150"/>
-      <c r="AD5" s="150"/>
-      <c r="AE5" s="150"/>
-      <c r="AF5" s="150"/>
-      <c r="AG5" s="150"/>
-      <c r="AH5" s="150"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="108"/>
+      <c r="M5" s="108"/>
+      <c r="N5" s="108"/>
+      <c r="O5" s="108"/>
+      <c r="P5" s="108"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="108"/>
+      <c r="S5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="108"/>
+      <c r="V5" s="108"/>
+      <c r="W5" s="108"/>
+      <c r="X5" s="108"/>
+      <c r="Y5" s="108"/>
+      <c r="Z5" s="108"/>
+      <c r="AA5" s="108"/>
+      <c r="AB5" s="108"/>
+      <c r="AC5" s="108"/>
+      <c r="AD5" s="108"/>
+      <c r="AE5" s="108"/>
+      <c r="AF5" s="108"/>
+      <c r="AG5" s="108"/>
+      <c r="AH5" s="108"/>
     </row>
     <row r="6" spans="1:34" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A6" s="146" t="s">
+      <c r="A6" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="147"/>
-      <c r="C6" s="147"/>
-      <c r="D6" s="147"/>
-      <c r="E6" s="147"/>
-      <c r="F6" s="147"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="151" t="s">
+      <c r="B6" s="105"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="106"/>
+      <c r="H6" s="109" t="s">
         <v>196</v>
       </c>
-      <c r="I6" s="150"/>
-      <c r="J6" s="150"/>
-      <c r="K6" s="150"/>
-      <c r="L6" s="150"/>
-      <c r="M6" s="150"/>
-      <c r="N6" s="150"/>
-      <c r="O6" s="150"/>
-      <c r="P6" s="150"/>
-      <c r="Q6" s="150"/>
-      <c r="R6" s="150"/>
-      <c r="S6" s="150"/>
-      <c r="T6" s="150"/>
-      <c r="U6" s="150"/>
-      <c r="V6" s="150"/>
-      <c r="W6" s="150"/>
-      <c r="X6" s="150"/>
-      <c r="Y6" s="150"/>
-      <c r="Z6" s="150"/>
-      <c r="AA6" s="150"/>
-      <c r="AB6" s="150"/>
-      <c r="AC6" s="150"/>
-      <c r="AD6" s="150"/>
-      <c r="AE6" s="150"/>
-      <c r="AF6" s="150"/>
-      <c r="AG6" s="150"/>
-      <c r="AH6" s="150"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="108"/>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
+      <c r="N6" s="108"/>
+      <c r="O6" s="108"/>
+      <c r="P6" s="108"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="108"/>
+      <c r="S6" s="108"/>
+      <c r="T6" s="108"/>
+      <c r="U6" s="108"/>
+      <c r="V6" s="108"/>
+      <c r="W6" s="108"/>
+      <c r="X6" s="108"/>
+      <c r="Y6" s="108"/>
+      <c r="Z6" s="108"/>
+      <c r="AA6" s="108"/>
+      <c r="AB6" s="108"/>
+      <c r="AC6" s="108"/>
+      <c r="AD6" s="108"/>
+      <c r="AE6" s="108"/>
+      <c r="AF6" s="108"/>
+      <c r="AG6" s="108"/>
+      <c r="AH6" s="108"/>
     </row>
     <row r="7" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A7" s="146" t="s">
+      <c r="A7" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="147"/>
-      <c r="C7" s="147"/>
-      <c r="D7" s="147"/>
-      <c r="E7" s="147"/>
-      <c r="F7" s="147"/>
-      <c r="G7" s="148"/>
-      <c r="H7" s="149" t="s">
+      <c r="B7" s="105"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="150"/>
-      <c r="J7" s="150"/>
-      <c r="K7" s="150"/>
-      <c r="L7" s="150"/>
-      <c r="M7" s="150"/>
-      <c r="N7" s="150"/>
-      <c r="O7" s="150"/>
-      <c r="P7" s="150"/>
-      <c r="Q7" s="150"/>
-      <c r="R7" s="150"/>
-      <c r="S7" s="150"/>
-      <c r="T7" s="150"/>
-      <c r="U7" s="150"/>
-      <c r="V7" s="150"/>
-      <c r="W7" s="150"/>
-      <c r="X7" s="150"/>
-      <c r="Y7" s="150"/>
-      <c r="Z7" s="150"/>
-      <c r="AA7" s="150"/>
-      <c r="AB7" s="150"/>
-      <c r="AC7" s="150"/>
-      <c r="AD7" s="150"/>
-      <c r="AE7" s="150"/>
-      <c r="AF7" s="150"/>
-      <c r="AG7" s="150"/>
-      <c r="AH7" s="150"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="108"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="108"/>
+      <c r="M7" s="108"/>
+      <c r="N7" s="108"/>
+      <c r="O7" s="108"/>
+      <c r="P7" s="108"/>
+      <c r="Q7" s="108"/>
+      <c r="R7" s="108"/>
+      <c r="S7" s="108"/>
+      <c r="T7" s="108"/>
+      <c r="U7" s="108"/>
+      <c r="V7" s="108"/>
+      <c r="W7" s="108"/>
+      <c r="X7" s="108"/>
+      <c r="Y7" s="108"/>
+      <c r="Z7" s="108"/>
+      <c r="AA7" s="108"/>
+      <c r="AB7" s="108"/>
+      <c r="AC7" s="108"/>
+      <c r="AD7" s="108"/>
+      <c r="AE7" s="108"/>
+      <c r="AF7" s="108"/>
+      <c r="AG7" s="108"/>
+      <c r="AH7" s="108"/>
     </row>
     <row r="8" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A8" s="146" t="s">
+      <c r="A8" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="147"/>
-      <c r="C8" s="147"/>
-      <c r="D8" s="147"/>
-      <c r="E8" s="147"/>
-      <c r="F8" s="147"/>
-      <c r="G8" s="148"/>
-      <c r="H8" s="149" t="s">
+      <c r="B8" s="105"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="106"/>
+      <c r="H8" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="150"/>
-      <c r="J8" s="150"/>
-      <c r="K8" s="150"/>
-      <c r="L8" s="150"/>
-      <c r="M8" s="150"/>
-      <c r="N8" s="150"/>
-      <c r="O8" s="150"/>
-      <c r="P8" s="150"/>
-      <c r="Q8" s="150"/>
-      <c r="R8" s="150"/>
-      <c r="S8" s="150"/>
-      <c r="T8" s="150"/>
-      <c r="U8" s="150"/>
-      <c r="V8" s="150"/>
-      <c r="W8" s="150"/>
-      <c r="X8" s="150"/>
-      <c r="Y8" s="150"/>
-      <c r="Z8" s="150"/>
-      <c r="AA8" s="150"/>
-      <c r="AB8" s="150"/>
-      <c r="AC8" s="150"/>
-      <c r="AD8" s="150"/>
-      <c r="AE8" s="150"/>
-      <c r="AF8" s="150"/>
-      <c r="AG8" s="150"/>
-      <c r="AH8" s="150"/>
+      <c r="I8" s="108"/>
+      <c r="J8" s="108"/>
+      <c r="K8" s="108"/>
+      <c r="L8" s="108"/>
+      <c r="M8" s="108"/>
+      <c r="N8" s="108"/>
+      <c r="O8" s="108"/>
+      <c r="P8" s="108"/>
+      <c r="Q8" s="108"/>
+      <c r="R8" s="108"/>
+      <c r="S8" s="108"/>
+      <c r="T8" s="108"/>
+      <c r="U8" s="108"/>
+      <c r="V8" s="108"/>
+      <c r="W8" s="108"/>
+      <c r="X8" s="108"/>
+      <c r="Y8" s="108"/>
+      <c r="Z8" s="108"/>
+      <c r="AA8" s="108"/>
+      <c r="AB8" s="108"/>
+      <c r="AC8" s="108"/>
+      <c r="AD8" s="108"/>
+      <c r="AE8" s="108"/>
+      <c r="AF8" s="108"/>
+      <c r="AG8" s="108"/>
+      <c r="AH8" s="108"/>
     </row>
     <row r="9" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A9" s="146" t="s">
+      <c r="A9" s="104" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="147"/>
-      <c r="C9" s="147"/>
-      <c r="D9" s="147"/>
-      <c r="E9" s="147"/>
-      <c r="F9" s="147"/>
-      <c r="G9" s="148"/>
-      <c r="H9" s="149" t="s">
+      <c r="B9" s="105"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="106"/>
+      <c r="H9" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="150"/>
-      <c r="J9" s="150"/>
-      <c r="K9" s="150"/>
-      <c r="L9" s="150"/>
-      <c r="M9" s="150"/>
-      <c r="N9" s="150"/>
-      <c r="O9" s="150"/>
-      <c r="P9" s="150"/>
-      <c r="Q9" s="150"/>
-      <c r="R9" s="150"/>
-      <c r="S9" s="150"/>
-      <c r="T9" s="150"/>
-      <c r="U9" s="150"/>
-      <c r="V9" s="150"/>
-      <c r="W9" s="150"/>
-      <c r="X9" s="150"/>
-      <c r="Y9" s="150"/>
-      <c r="Z9" s="150"/>
-      <c r="AA9" s="150"/>
-      <c r="AB9" s="150"/>
-      <c r="AC9" s="150"/>
-      <c r="AD9" s="150"/>
-      <c r="AE9" s="150"/>
-      <c r="AF9" s="150"/>
-      <c r="AG9" s="150"/>
-      <c r="AH9" s="150"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="108"/>
+      <c r="K9" s="108"/>
+      <c r="L9" s="108"/>
+      <c r="M9" s="108"/>
+      <c r="N9" s="108"/>
+      <c r="O9" s="108"/>
+      <c r="P9" s="108"/>
+      <c r="Q9" s="108"/>
+      <c r="R9" s="108"/>
+      <c r="S9" s="108"/>
+      <c r="T9" s="108"/>
+      <c r="U9" s="108"/>
+      <c r="V9" s="108"/>
+      <c r="W9" s="108"/>
+      <c r="X9" s="108"/>
+      <c r="Y9" s="108"/>
+      <c r="Z9" s="108"/>
+      <c r="AA9" s="108"/>
+      <c r="AB9" s="108"/>
+      <c r="AC9" s="108"/>
+      <c r="AD9" s="108"/>
+      <c r="AE9" s="108"/>
+      <c r="AF9" s="108"/>
+      <c r="AG9" s="108"/>
+      <c r="AH9" s="108"/>
     </row>
     <row r="10" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A10" s="152" t="s">
+      <c r="A10" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="153"/>
-      <c r="C10" s="153"/>
-      <c r="D10" s="153"/>
-      <c r="E10" s="153"/>
-      <c r="F10" s="153"/>
-      <c r="G10" s="154"/>
-      <c r="H10" s="155" t="s">
+      <c r="B10" s="111"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="111"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="I10" s="156"/>
-      <c r="J10" s="156"/>
-      <c r="K10" s="156"/>
-      <c r="L10" s="156"/>
-      <c r="M10" s="156"/>
-      <c r="N10" s="156"/>
-      <c r="O10" s="156"/>
-      <c r="P10" s="156"/>
-      <c r="Q10" s="156"/>
-      <c r="R10" s="156"/>
-      <c r="S10" s="156"/>
-      <c r="T10" s="156"/>
-      <c r="U10" s="156"/>
-      <c r="V10" s="156"/>
-      <c r="W10" s="156"/>
-      <c r="X10" s="156"/>
-      <c r="Y10" s="156"/>
-      <c r="Z10" s="156"/>
-      <c r="AA10" s="156"/>
-      <c r="AB10" s="156"/>
-      <c r="AC10" s="156"/>
-      <c r="AD10" s="156"/>
-      <c r="AE10" s="156"/>
-      <c r="AF10" s="156"/>
-      <c r="AG10" s="156"/>
-      <c r="AH10" s="156"/>
+      <c r="I10" s="114"/>
+      <c r="J10" s="114"/>
+      <c r="K10" s="114"/>
+      <c r="L10" s="114"/>
+      <c r="M10" s="114"/>
+      <c r="N10" s="114"/>
+      <c r="O10" s="114"/>
+      <c r="P10" s="114"/>
+      <c r="Q10" s="114"/>
+      <c r="R10" s="114"/>
+      <c r="S10" s="114"/>
+      <c r="T10" s="114"/>
+      <c r="U10" s="114"/>
+      <c r="V10" s="114"/>
+      <c r="W10" s="114"/>
+      <c r="X10" s="114"/>
+      <c r="Y10" s="114"/>
+      <c r="Z10" s="114"/>
+      <c r="AA10" s="114"/>
+      <c r="AB10" s="114"/>
+      <c r="AC10" s="114"/>
+      <c r="AD10" s="114"/>
+      <c r="AE10" s="114"/>
+      <c r="AF10" s="114"/>
+      <c r="AG10" s="114"/>
+      <c r="AH10" s="114"/>
     </row>
     <row r="11" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A11" s="140" t="s">
+      <c r="A11" s="155" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="141"/>
-      <c r="C11" s="141"/>
-      <c r="D11" s="141"/>
-      <c r="E11" s="141"/>
-      <c r="F11" s="141"/>
-      <c r="G11" s="141"/>
-      <c r="H11" s="141"/>
-      <c r="I11" s="141"/>
-      <c r="J11" s="141"/>
-      <c r="K11" s="141"/>
-      <c r="L11" s="141"/>
-      <c r="M11" s="141"/>
-      <c r="N11" s="141"/>
-      <c r="O11" s="141"/>
-      <c r="P11" s="141"/>
-      <c r="Q11" s="141"/>
-      <c r="R11" s="141"/>
-      <c r="S11" s="141"/>
-      <c r="T11" s="141"/>
-      <c r="U11" s="141"/>
-      <c r="V11" s="141"/>
-      <c r="W11" s="141"/>
-      <c r="X11" s="141"/>
-      <c r="Y11" s="141"/>
-      <c r="Z11" s="141"/>
-      <c r="AA11" s="141"/>
-      <c r="AB11" s="141"/>
-      <c r="AC11" s="141"/>
-      <c r="AD11" s="141"/>
-      <c r="AE11" s="141"/>
-      <c r="AF11" s="141"/>
-      <c r="AG11" s="141"/>
-      <c r="AH11" s="141"/>
+      <c r="B11" s="156"/>
+      <c r="C11" s="156"/>
+      <c r="D11" s="156"/>
+      <c r="E11" s="156"/>
+      <c r="F11" s="156"/>
+      <c r="G11" s="156"/>
+      <c r="H11" s="156"/>
+      <c r="I11" s="156"/>
+      <c r="J11" s="156"/>
+      <c r="K11" s="156"/>
+      <c r="L11" s="156"/>
+      <c r="M11" s="156"/>
+      <c r="N11" s="156"/>
+      <c r="O11" s="156"/>
+      <c r="P11" s="156"/>
+      <c r="Q11" s="156"/>
+      <c r="R11" s="156"/>
+      <c r="S11" s="156"/>
+      <c r="T11" s="156"/>
+      <c r="U11" s="156"/>
+      <c r="V11" s="156"/>
+      <c r="W11" s="156"/>
+      <c r="X11" s="156"/>
+      <c r="Y11" s="156"/>
+      <c r="Z11" s="156"/>
+      <c r="AA11" s="156"/>
+      <c r="AB11" s="156"/>
+      <c r="AC11" s="156"/>
+      <c r="AD11" s="156"/>
+      <c r="AE11" s="156"/>
+      <c r="AF11" s="156"/>
+      <c r="AG11" s="156"/>
+      <c r="AH11" s="156"/>
     </row>
     <row r="12" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A12" s="61"/>
@@ -3945,20 +3956,20 @@
       <c r="AH23" s="58"/>
     </row>
     <row r="24" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A24" s="142" t="s">
+      <c r="A24" s="115" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="143"/>
-      <c r="C24" s="142" t="s">
+      <c r="B24" s="116"/>
+      <c r="C24" s="115" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="144"/>
-      <c r="E24" s="144"/>
-      <c r="F24" s="144"/>
-      <c r="G24" s="144"/>
-      <c r="H24" s="144"/>
-      <c r="I24" s="144"/>
-      <c r="J24" s="143"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="117"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="117"/>
+      <c r="I24" s="117"/>
+      <c r="J24" s="116"/>
       <c r="K24" s="66" t="s">
         <v>30</v>
       </c>
@@ -3971,28 +3982,28 @@
       <c r="N24" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="O24" s="145" t="s">
+      <c r="O24" s="118" t="s">
         <v>34</v>
       </c>
-      <c r="P24" s="145"/>
-      <c r="Q24" s="145"/>
-      <c r="R24" s="145"/>
-      <c r="S24" s="145"/>
-      <c r="T24" s="145"/>
-      <c r="U24" s="145"/>
-      <c r="V24" s="145"/>
-      <c r="W24" s="145"/>
-      <c r="X24" s="145"/>
-      <c r="Y24" s="145"/>
-      <c r="Z24" s="145"/>
-      <c r="AA24" s="145"/>
-      <c r="AB24" s="145"/>
-      <c r="AC24" s="145"/>
-      <c r="AD24" s="145"/>
-      <c r="AE24" s="145"/>
-      <c r="AF24" s="145"/>
-      <c r="AG24" s="145"/>
-      <c r="AH24" s="145"/>
+      <c r="P24" s="118"/>
+      <c r="Q24" s="118"/>
+      <c r="R24" s="118"/>
+      <c r="S24" s="118"/>
+      <c r="T24" s="118"/>
+      <c r="U24" s="118"/>
+      <c r="V24" s="118"/>
+      <c r="W24" s="118"/>
+      <c r="X24" s="118"/>
+      <c r="Y24" s="118"/>
+      <c r="Z24" s="118"/>
+      <c r="AA24" s="118"/>
+      <c r="AB24" s="118"/>
+      <c r="AC24" s="118"/>
+      <c r="AD24" s="118"/>
+      <c r="AE24" s="118"/>
+      <c r="AF24" s="118"/>
+      <c r="AG24" s="118"/>
+      <c r="AH24" s="118"/>
     </row>
     <row r="25" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A25" s="101">
@@ -4164,6 +4175,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="O28:AH28"/>
+    <mergeCell ref="A1:K4"/>
+    <mergeCell ref="L1:P2"/>
+    <mergeCell ref="Q1:U2"/>
+    <mergeCell ref="L3:P4"/>
+    <mergeCell ref="Q3:U4"/>
+    <mergeCell ref="V3:X4"/>
+    <mergeCell ref="AC3:AE4"/>
+    <mergeCell ref="AF3:AH4"/>
+    <mergeCell ref="V1:X2"/>
+    <mergeCell ref="AC1:AE2"/>
+    <mergeCell ref="AF1:AH2"/>
+    <mergeCell ref="Y1:AB2"/>
+    <mergeCell ref="Y3:AB4"/>
+    <mergeCell ref="A11:AH11"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="O24:AH24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="O25:AH25"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="O27:AH27"/>
     <mergeCell ref="A26:B26"/>
@@ -4180,27 +4212,6 @@
     <mergeCell ref="H9:AH9"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="H10:AH10"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:J24"/>
-    <mergeCell ref="O24:AH24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="O25:AH25"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="O28:AH28"/>
-    <mergeCell ref="A1:K4"/>
-    <mergeCell ref="L1:P2"/>
-    <mergeCell ref="Q1:U2"/>
-    <mergeCell ref="L3:P4"/>
-    <mergeCell ref="Q3:U4"/>
-    <mergeCell ref="V3:X4"/>
-    <mergeCell ref="AC3:AE4"/>
-    <mergeCell ref="AF3:AH4"/>
-    <mergeCell ref="V1:X2"/>
-    <mergeCell ref="AC1:AE2"/>
-    <mergeCell ref="AF1:AH2"/>
-    <mergeCell ref="Y1:AB2"/>
-    <mergeCell ref="Y3:AB4"/>
-    <mergeCell ref="A11:AH11"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4230,177 +4241,177 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="176" t="s">
         <v>235</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="113" t="s">
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="119" t="s">
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="130"/>
+      <c r="O1" s="134" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="123" t="s">
+      <c r="P1" s="135"/>
+      <c r="Q1" s="135"/>
+      <c r="R1" s="135"/>
+      <c r="S1" s="135"/>
+      <c r="T1" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="U1" s="134" t="s">
+      <c r="U1" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="135"/>
-      <c r="W1" s="128" t="s">
+      <c r="V1" s="150"/>
+      <c r="W1" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="124" t="s">
+      <c r="X1" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="125"/>
+      <c r="Y1" s="140"/>
     </row>
     <row r="2" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="107"/>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="117"/>
-      <c r="N2" s="118"/>
-      <c r="O2" s="121"/>
-      <c r="P2" s="122"/>
-      <c r="Q2" s="122"/>
-      <c r="R2" s="122"/>
-      <c r="S2" s="122"/>
-      <c r="T2" s="123"/>
-      <c r="U2" s="137"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="131"/>
-      <c r="X2" s="126"/>
-      <c r="Y2" s="127"/>
+      <c r="A2" s="122"/>
+      <c r="B2" s="123"/>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="131"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="132"/>
+      <c r="N2" s="133"/>
+      <c r="O2" s="136"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="137"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="152"/>
+      <c r="V2" s="153"/>
+      <c r="W2" s="146"/>
+      <c r="X2" s="141"/>
+      <c r="Y2" s="142"/>
     </row>
     <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A3" s="107"/>
-      <c r="B3" s="108"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="113" t="s">
+      <c r="A3" s="122"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="128" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="114"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="114"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="119" t="s">
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="N3" s="130"/>
+      <c r="O3" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="120"/>
-      <c r="Q3" s="120"/>
-      <c r="R3" s="120"/>
-      <c r="S3" s="120"/>
-      <c r="T3" s="123" t="s">
+      <c r="P3" s="135"/>
+      <c r="Q3" s="135"/>
+      <c r="R3" s="135"/>
+      <c r="S3" s="135"/>
+      <c r="T3" s="138" t="s">
         <v>15</v>
       </c>
-      <c r="U3" s="134" t="s">
+      <c r="U3" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="V3" s="135"/>
-      <c r="W3" s="123" t="s">
+      <c r="V3" s="150"/>
+      <c r="W3" s="138" t="s">
         <v>16</v>
       </c>
-      <c r="X3" s="124" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y3" s="125"/>
+      <c r="X3" s="139">
+        <v>45935</v>
+      </c>
+      <c r="Y3" s="140"/>
     </row>
     <row r="4" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A4" s="110"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="121"/>
-      <c r="P4" s="122"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="122"/>
-      <c r="S4" s="122"/>
-      <c r="T4" s="123"/>
-      <c r="U4" s="137"/>
-      <c r="V4" s="138"/>
-      <c r="W4" s="123"/>
-      <c r="X4" s="126"/>
-      <c r="Y4" s="127"/>
+      <c r="A4" s="125"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="126"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="132"/>
+      <c r="L4" s="132"/>
+      <c r="M4" s="132"/>
+      <c r="N4" s="133"/>
+      <c r="O4" s="136"/>
+      <c r="P4" s="137"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137"/>
+      <c r="S4" s="137"/>
+      <c r="T4" s="138"/>
+      <c r="U4" s="152"/>
+      <c r="V4" s="153"/>
+      <c r="W4" s="138"/>
+      <c r="X4" s="141"/>
+      <c r="Y4" s="142"/>
     </row>
     <row r="5" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A5" s="182" t="s">
+      <c r="A5" s="157" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="182"/>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="182"/>
-      <c r="F5" s="183" t="s">
+      <c r="B5" s="157"/>
+      <c r="C5" s="157"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
+      <c r="F5" s="158" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="183"/>
-      <c r="H5" s="183"/>
-      <c r="I5" s="183"/>
-      <c r="J5" s="182" t="s">
+      <c r="G5" s="158"/>
+      <c r="H5" s="158"/>
+      <c r="I5" s="158"/>
+      <c r="J5" s="157" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="182"/>
-      <c r="L5" s="182"/>
-      <c r="M5" s="182"/>
-      <c r="N5" s="182"/>
-      <c r="O5" s="183" t="s">
+      <c r="K5" s="157"/>
+      <c r="L5" s="157"/>
+      <c r="M5" s="157"/>
+      <c r="N5" s="157"/>
+      <c r="O5" s="158" t="s">
         <v>20</v>
       </c>
-      <c r="P5" s="183"/>
-      <c r="Q5" s="183"/>
-      <c r="R5" s="183"/>
-      <c r="S5" s="183"/>
+      <c r="P5" s="158"/>
+      <c r="Q5" s="158"/>
+      <c r="R5" s="158"/>
+      <c r="S5" s="158"/>
       <c r="T5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="U5" s="183" t="s">
+      <c r="U5" s="158" t="s">
         <v>26</v>
       </c>
-      <c r="V5" s="183"/>
-      <c r="W5" s="183"/>
-      <c r="X5" s="183"/>
-      <c r="Y5" s="183"/>
+      <c r="V5" s="158"/>
+      <c r="W5" s="158"/>
+      <c r="X5" s="158"/>
+      <c r="Y5" s="158"/>
     </row>
     <row r="6" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A6" s="35" t="s">
@@ -4411,83 +4422,83 @@
       <c r="A7" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="123" t="s">
+      <c r="B7" s="138" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="123"/>
-      <c r="H7" s="123"/>
-      <c r="I7" s="123"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
       <c r="J7" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="175" t="s">
+      <c r="K7" s="159" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="176"/>
-      <c r="M7" s="176"/>
-      <c r="N7" s="181"/>
-      <c r="O7" s="123" t="s">
+      <c r="L7" s="160"/>
+      <c r="M7" s="160"/>
+      <c r="N7" s="161"/>
+      <c r="O7" s="138" t="s">
         <v>44</v>
       </c>
-      <c r="P7" s="123"/>
-      <c r="Q7" s="123"/>
-      <c r="R7" s="123"/>
-      <c r="S7" s="123" t="s">
+      <c r="P7" s="138"/>
+      <c r="Q7" s="138"/>
+      <c r="R7" s="138"/>
+      <c r="S7" s="138" t="s">
         <v>45</v>
       </c>
-      <c r="T7" s="123"/>
-      <c r="U7" s="175" t="s">
+      <c r="T7" s="138"/>
+      <c r="U7" s="159" t="s">
         <v>46</v>
       </c>
-      <c r="V7" s="176"/>
-      <c r="W7" s="176"/>
-      <c r="X7" s="176"/>
-      <c r="Y7" s="176"/>
+      <c r="V7" s="160"/>
+      <c r="W7" s="160"/>
+      <c r="X7" s="160"/>
+      <c r="Y7" s="160"/>
     </row>
     <row r="8" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A8" s="44">
         <v>1</v>
       </c>
-      <c r="B8" s="180" t="s">
+      <c r="B8" s="162" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="180"/>
-      <c r="D8" s="180"/>
-      <c r="E8" s="180"/>
-      <c r="F8" s="180"/>
-      <c r="G8" s="180"/>
-      <c r="H8" s="180"/>
-      <c r="I8" s="180"/>
+      <c r="C8" s="162"/>
+      <c r="D8" s="162"/>
+      <c r="E8" s="162"/>
+      <c r="F8" s="162"/>
+      <c r="G8" s="162"/>
+      <c r="H8" s="162"/>
+      <c r="I8" s="162"/>
       <c r="J8" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="166" t="s">
+      <c r="K8" s="163" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="169"/>
-      <c r="M8" s="169"/>
-      <c r="N8" s="167"/>
-      <c r="O8" s="165">
+      <c r="L8" s="164"/>
+      <c r="M8" s="164"/>
+      <c r="N8" s="165"/>
+      <c r="O8" s="166">
         <v>4000</v>
       </c>
-      <c r="P8" s="165"/>
-      <c r="Q8" s="165"/>
-      <c r="R8" s="165"/>
-      <c r="S8" s="165" t="s">
+      <c r="P8" s="166"/>
+      <c r="Q8" s="166"/>
+      <c r="R8" s="166"/>
+      <c r="S8" s="166" t="s">
         <v>50</v>
       </c>
-      <c r="T8" s="165"/>
-      <c r="U8" s="166" t="s">
+      <c r="T8" s="166"/>
+      <c r="U8" s="163" t="s">
         <v>51</v>
       </c>
-      <c r="V8" s="169"/>
-      <c r="W8" s="169"/>
-      <c r="X8" s="169"/>
-      <c r="Y8" s="169"/>
+      <c r="V8" s="164"/>
+      <c r="W8" s="164"/>
+      <c r="X8" s="164"/>
+      <c r="Y8" s="164"/>
     </row>
     <row r="9" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A9" s="35"/>
@@ -4501,335 +4512,335 @@
       <c r="A11" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="123" t="s">
+      <c r="B11" s="138" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="123"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="123"/>
-      <c r="F11" s="123" t="s">
+      <c r="C11" s="138"/>
+      <c r="D11" s="138"/>
+      <c r="E11" s="138"/>
+      <c r="F11" s="138" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="123"/>
-      <c r="H11" s="123"/>
-      <c r="I11" s="123"/>
-      <c r="J11" s="123"/>
-      <c r="K11" s="123" t="s">
+      <c r="G11" s="138"/>
+      <c r="H11" s="138"/>
+      <c r="I11" s="138"/>
+      <c r="J11" s="138"/>
+      <c r="K11" s="138" t="s">
         <v>54</v>
       </c>
-      <c r="L11" s="123"/>
-      <c r="M11" s="123"/>
-      <c r="N11" s="123"/>
-      <c r="O11" s="123" t="s">
+      <c r="L11" s="138"/>
+      <c r="M11" s="138"/>
+      <c r="N11" s="138"/>
+      <c r="O11" s="138" t="s">
         <v>42</v>
       </c>
-      <c r="P11" s="123"/>
-      <c r="Q11" s="179" t="s">
+      <c r="P11" s="138"/>
+      <c r="Q11" s="173" t="s">
         <v>45</v>
       </c>
-      <c r="R11" s="179"/>
-      <c r="S11" s="179"/>
-      <c r="T11" s="179"/>
-      <c r="U11" s="123" t="s">
+      <c r="R11" s="173"/>
+      <c r="S11" s="173"/>
+      <c r="T11" s="173"/>
+      <c r="U11" s="138" t="s">
         <v>55</v>
       </c>
-      <c r="V11" s="123"/>
-      <c r="W11" s="123"/>
-      <c r="X11" s="175" t="s">
+      <c r="V11" s="138"/>
+      <c r="W11" s="138"/>
+      <c r="X11" s="159" t="s">
         <v>56</v>
       </c>
-      <c r="Y11" s="176"/>
+      <c r="Y11" s="160"/>
     </row>
     <row r="12" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A12" s="44">
         <v>1</v>
       </c>
-      <c r="B12" s="165" t="s">
+      <c r="B12" s="166" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="165"/>
-      <c r="D12" s="165"/>
-      <c r="E12" s="165"/>
-      <c r="F12" s="165" t="s">
+      <c r="C12" s="166"/>
+      <c r="D12" s="166"/>
+      <c r="E12" s="166"/>
+      <c r="F12" s="166" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="165"/>
-      <c r="H12" s="165"/>
-      <c r="I12" s="165"/>
-      <c r="J12" s="165"/>
-      <c r="K12" s="166" t="s">
+      <c r="G12" s="166"/>
+      <c r="H12" s="166"/>
+      <c r="I12" s="166"/>
+      <c r="J12" s="166"/>
+      <c r="K12" s="163" t="s">
         <v>59</v>
       </c>
-      <c r="L12" s="169"/>
-      <c r="M12" s="169"/>
-      <c r="N12" s="167"/>
-      <c r="O12" s="170" t="s">
+      <c r="L12" s="164"/>
+      <c r="M12" s="164"/>
+      <c r="N12" s="165"/>
+      <c r="O12" s="167" t="s">
         <v>48</v>
       </c>
-      <c r="P12" s="171"/>
-      <c r="Q12" s="172" t="s">
+      <c r="P12" s="168"/>
+      <c r="Q12" s="169" t="s">
         <v>57</v>
       </c>
-      <c r="R12" s="165"/>
-      <c r="S12" s="165"/>
-      <c r="T12" s="165"/>
-      <c r="U12" s="168" t="s">
+      <c r="R12" s="166"/>
+      <c r="S12" s="166"/>
+      <c r="T12" s="166"/>
+      <c r="U12" s="170" t="s">
         <v>60</v>
       </c>
-      <c r="V12" s="165"/>
-      <c r="W12" s="165"/>
-      <c r="X12" s="177" t="s">
+      <c r="V12" s="166"/>
+      <c r="W12" s="166"/>
+      <c r="X12" s="171" t="s">
         <v>61</v>
       </c>
-      <c r="Y12" s="178"/>
+      <c r="Y12" s="172"/>
     </row>
     <row r="13" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A13" s="44">
         <v>2</v>
       </c>
-      <c r="B13" s="165" t="s">
+      <c r="B13" s="166" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="165"/>
-      <c r="D13" s="165"/>
-      <c r="E13" s="165"/>
-      <c r="F13" s="165" t="s">
+      <c r="C13" s="166"/>
+      <c r="D13" s="166"/>
+      <c r="E13" s="166"/>
+      <c r="F13" s="166" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="165"/>
-      <c r="H13" s="165"/>
-      <c r="I13" s="165"/>
-      <c r="J13" s="165"/>
-      <c r="K13" s="166" t="s">
+      <c r="G13" s="166"/>
+      <c r="H13" s="166"/>
+      <c r="I13" s="166"/>
+      <c r="J13" s="166"/>
+      <c r="K13" s="163" t="s">
         <v>59</v>
       </c>
-      <c r="L13" s="169"/>
-      <c r="M13" s="169"/>
-      <c r="N13" s="167"/>
-      <c r="O13" s="170"/>
-      <c r="P13" s="171"/>
-      <c r="Q13" s="172" t="s">
+      <c r="L13" s="164"/>
+      <c r="M13" s="164"/>
+      <c r="N13" s="165"/>
+      <c r="O13" s="167"/>
+      <c r="P13" s="168"/>
+      <c r="Q13" s="169" t="s">
         <v>64</v>
       </c>
-      <c r="R13" s="165"/>
-      <c r="S13" s="165"/>
-      <c r="T13" s="165"/>
-      <c r="U13" s="168" t="s">
+      <c r="R13" s="166"/>
+      <c r="S13" s="166"/>
+      <c r="T13" s="166"/>
+      <c r="U13" s="170" t="s">
         <v>60</v>
       </c>
-      <c r="V13" s="165"/>
-      <c r="W13" s="165"/>
-      <c r="X13" s="165" t="s">
+      <c r="V13" s="166"/>
+      <c r="W13" s="166"/>
+      <c r="X13" s="166" t="s">
         <v>65</v>
       </c>
-      <c r="Y13" s="165"/>
+      <c r="Y13" s="166"/>
     </row>
     <row r="14" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A14" s="44">
         <v>3</v>
       </c>
-      <c r="B14" s="165" t="s">
+      <c r="B14" s="166" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="165"/>
-      <c r="D14" s="165"/>
-      <c r="E14" s="165"/>
-      <c r="F14" s="165" t="s">
+      <c r="C14" s="166"/>
+      <c r="D14" s="166"/>
+      <c r="E14" s="166"/>
+      <c r="F14" s="166" t="s">
         <v>66</v>
       </c>
-      <c r="G14" s="165"/>
-      <c r="H14" s="165"/>
-      <c r="I14" s="165"/>
-      <c r="J14" s="165"/>
-      <c r="K14" s="166" t="s">
+      <c r="G14" s="166"/>
+      <c r="H14" s="166"/>
+      <c r="I14" s="166"/>
+      <c r="J14" s="166"/>
+      <c r="K14" s="163" t="s">
         <v>59</v>
       </c>
-      <c r="L14" s="169"/>
-      <c r="M14" s="169"/>
-      <c r="N14" s="167"/>
-      <c r="O14" s="170"/>
-      <c r="P14" s="171"/>
-      <c r="Q14" s="172" t="s">
+      <c r="L14" s="164"/>
+      <c r="M14" s="164"/>
+      <c r="N14" s="165"/>
+      <c r="O14" s="167"/>
+      <c r="P14" s="168"/>
+      <c r="Q14" s="169" t="s">
         <v>64</v>
       </c>
-      <c r="R14" s="165"/>
-      <c r="S14" s="165"/>
-      <c r="T14" s="165"/>
-      <c r="U14" s="168" t="s">
+      <c r="R14" s="166"/>
+      <c r="S14" s="166"/>
+      <c r="T14" s="166"/>
+      <c r="U14" s="170" t="s">
         <v>60</v>
       </c>
-      <c r="V14" s="165"/>
-      <c r="W14" s="165"/>
-      <c r="X14" s="173">
+      <c r="V14" s="166"/>
+      <c r="W14" s="166"/>
+      <c r="X14" s="174">
         <v>1</v>
       </c>
-      <c r="Y14" s="174"/>
+      <c r="Y14" s="175"/>
     </row>
     <row r="15" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A15" s="44">
         <v>4</v>
       </c>
-      <c r="B15" s="165" t="s">
+      <c r="B15" s="166" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="165"/>
-      <c r="D15" s="165"/>
-      <c r="E15" s="165"/>
-      <c r="F15" s="165" t="s">
+      <c r="C15" s="166"/>
+      <c r="D15" s="166"/>
+      <c r="E15" s="166"/>
+      <c r="F15" s="166" t="s">
         <v>68</v>
       </c>
-      <c r="G15" s="165"/>
-      <c r="H15" s="165"/>
-      <c r="I15" s="165"/>
-      <c r="J15" s="165"/>
-      <c r="K15" s="166" t="s">
+      <c r="G15" s="166"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="166"/>
+      <c r="J15" s="166"/>
+      <c r="K15" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="L15" s="169"/>
-      <c r="M15" s="169"/>
-      <c r="N15" s="167"/>
-      <c r="O15" s="170"/>
-      <c r="P15" s="171"/>
-      <c r="Q15" s="172" t="s">
+      <c r="L15" s="164"/>
+      <c r="M15" s="164"/>
+      <c r="N15" s="165"/>
+      <c r="O15" s="167"/>
+      <c r="P15" s="168"/>
+      <c r="Q15" s="169" t="s">
         <v>67</v>
       </c>
-      <c r="R15" s="165"/>
-      <c r="S15" s="165"/>
-      <c r="T15" s="165"/>
-      <c r="U15" s="165" t="s">
+      <c r="R15" s="166"/>
+      <c r="S15" s="166"/>
+      <c r="T15" s="166"/>
+      <c r="U15" s="166" t="s">
         <v>70</v>
       </c>
-      <c r="V15" s="165"/>
-      <c r="W15" s="165"/>
-      <c r="X15" s="166" t="s">
+      <c r="V15" s="166"/>
+      <c r="W15" s="166"/>
+      <c r="X15" s="163" t="s">
         <v>71</v>
       </c>
-      <c r="Y15" s="167"/>
+      <c r="Y15" s="165"/>
     </row>
     <row r="16" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A16" s="44">
         <v>5</v>
       </c>
-      <c r="B16" s="165" t="s">
+      <c r="B16" s="166" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="165"/>
-      <c r="D16" s="165"/>
-      <c r="E16" s="165"/>
-      <c r="F16" s="165" t="s">
+      <c r="C16" s="166"/>
+      <c r="D16" s="166"/>
+      <c r="E16" s="166"/>
+      <c r="F16" s="166" t="s">
         <v>73</v>
       </c>
-      <c r="G16" s="165"/>
-      <c r="H16" s="165"/>
-      <c r="I16" s="165"/>
-      <c r="J16" s="165"/>
-      <c r="K16" s="166" t="s">
+      <c r="G16" s="166"/>
+      <c r="H16" s="166"/>
+      <c r="I16" s="166"/>
+      <c r="J16" s="166"/>
+      <c r="K16" s="163" t="s">
         <v>59</v>
       </c>
-      <c r="L16" s="169"/>
-      <c r="M16" s="169"/>
-      <c r="N16" s="167"/>
-      <c r="O16" s="170"/>
-      <c r="P16" s="171"/>
-      <c r="Q16" s="172" t="s">
+      <c r="L16" s="164"/>
+      <c r="M16" s="164"/>
+      <c r="N16" s="165"/>
+      <c r="O16" s="167"/>
+      <c r="P16" s="168"/>
+      <c r="Q16" s="169" t="s">
         <v>74</v>
       </c>
-      <c r="R16" s="165"/>
-      <c r="S16" s="165"/>
-      <c r="T16" s="165"/>
-      <c r="U16" s="165" t="s">
+      <c r="R16" s="166"/>
+      <c r="S16" s="166"/>
+      <c r="T16" s="166"/>
+      <c r="U16" s="166" t="s">
         <v>75</v>
       </c>
-      <c r="V16" s="165"/>
-      <c r="W16" s="165"/>
-      <c r="X16" s="166">
+      <c r="V16" s="166"/>
+      <c r="W16" s="166"/>
+      <c r="X16" s="163">
         <v>10</v>
       </c>
-      <c r="Y16" s="167"/>
+      <c r="Y16" s="165"/>
     </row>
     <row r="17" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A17" s="44">
         <v>6</v>
       </c>
-      <c r="B17" s="165" t="s">
+      <c r="B17" s="166" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="165"/>
-      <c r="D17" s="165"/>
-      <c r="E17" s="165"/>
-      <c r="F17" s="165" t="s">
+      <c r="C17" s="166"/>
+      <c r="D17" s="166"/>
+      <c r="E17" s="166"/>
+      <c r="F17" s="166" t="s">
         <v>77</v>
       </c>
-      <c r="G17" s="165"/>
-      <c r="H17" s="165"/>
-      <c r="I17" s="165"/>
-      <c r="J17" s="165"/>
-      <c r="K17" s="166" t="s">
+      <c r="G17" s="166"/>
+      <c r="H17" s="166"/>
+      <c r="I17" s="166"/>
+      <c r="J17" s="166"/>
+      <c r="K17" s="163" t="s">
         <v>59</v>
       </c>
-      <c r="L17" s="169"/>
-      <c r="M17" s="169"/>
-      <c r="N17" s="167"/>
-      <c r="O17" s="170"/>
-      <c r="P17" s="171"/>
-      <c r="Q17" s="172" t="s">
+      <c r="L17" s="164"/>
+      <c r="M17" s="164"/>
+      <c r="N17" s="165"/>
+      <c r="O17" s="167"/>
+      <c r="P17" s="168"/>
+      <c r="Q17" s="169" t="s">
         <v>78</v>
       </c>
-      <c r="R17" s="165"/>
-      <c r="S17" s="165"/>
-      <c r="T17" s="165"/>
-      <c r="U17" s="165" t="s">
+      <c r="R17" s="166"/>
+      <c r="S17" s="166"/>
+      <c r="T17" s="166"/>
+      <c r="U17" s="166" t="s">
         <v>75</v>
       </c>
-      <c r="V17" s="165"/>
-      <c r="W17" s="165"/>
-      <c r="X17" s="166">
+      <c r="V17" s="166"/>
+      <c r="W17" s="166"/>
+      <c r="X17" s="163">
         <v>100</v>
       </c>
-      <c r="Y17" s="167"/>
+      <c r="Y17" s="165"/>
     </row>
     <row r="18" spans="1:25" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A18" s="89">
         <v>7</v>
       </c>
-      <c r="B18" s="157" t="s">
+      <c r="B18" s="177" t="s">
         <v>236</v>
       </c>
-      <c r="C18" s="157"/>
-      <c r="D18" s="157"/>
-      <c r="E18" s="157"/>
-      <c r="F18" s="157" t="s">
+      <c r="C18" s="177"/>
+      <c r="D18" s="177"/>
+      <c r="E18" s="177"/>
+      <c r="F18" s="177" t="s">
         <v>254</v>
       </c>
-      <c r="G18" s="157"/>
-      <c r="H18" s="157"/>
-      <c r="I18" s="157"/>
-      <c r="J18" s="157"/>
-      <c r="K18" s="158" t="s">
+      <c r="G18" s="177"/>
+      <c r="H18" s="177"/>
+      <c r="I18" s="177"/>
+      <c r="J18" s="177"/>
+      <c r="K18" s="178" t="s">
         <v>69</v>
       </c>
-      <c r="L18" s="160"/>
-      <c r="M18" s="160"/>
-      <c r="N18" s="159"/>
-      <c r="O18" s="161" t="s">
+      <c r="L18" s="180"/>
+      <c r="M18" s="180"/>
+      <c r="N18" s="179"/>
+      <c r="O18" s="181" t="s">
         <v>48</v>
       </c>
-      <c r="P18" s="162"/>
-      <c r="Q18" s="163" t="s">
+      <c r="P18" s="182"/>
+      <c r="Q18" s="183" t="s">
         <v>236</v>
       </c>
-      <c r="R18" s="157"/>
-      <c r="S18" s="157"/>
-      <c r="T18" s="157"/>
-      <c r="U18" s="157" t="s">
+      <c r="R18" s="177"/>
+      <c r="S18" s="177"/>
+      <c r="T18" s="177"/>
+      <c r="U18" s="177" t="s">
         <v>237</v>
       </c>
-      <c r="V18" s="157"/>
-      <c r="W18" s="157"/>
-      <c r="X18" s="158" t="s">
+      <c r="V18" s="177"/>
+      <c r="W18" s="177"/>
+      <c r="X18" s="178" t="s">
         <v>238</v>
       </c>
-      <c r="Y18" s="159"/>
+      <c r="Y18" s="179"/>
     </row>
     <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A19" s="58"/>
@@ -4860,62 +4871,18 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="U5:Y5"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="U7:Y7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="S8:T8"/>
-    <mergeCell ref="U8:Y8"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="Q12:T12"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="Q11:T11"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="K13:N13"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="Q15:T15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="K16:N16"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:T16"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:T17"/>
+    <mergeCell ref="U18:W18"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="J1:N2"/>
+    <mergeCell ref="O1:S2"/>
+    <mergeCell ref="A1:I4"/>
+    <mergeCell ref="J3:N4"/>
+    <mergeCell ref="O3:S4"/>
     <mergeCell ref="U17:W17"/>
     <mergeCell ref="X17:Y17"/>
     <mergeCell ref="T1:T2"/>
@@ -4932,18 +4899,62 @@
     <mergeCell ref="X16:Y16"/>
     <mergeCell ref="U13:W13"/>
     <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="J1:N2"/>
-    <mergeCell ref="O1:S2"/>
-    <mergeCell ref="A1:I4"/>
-    <mergeCell ref="J3:N4"/>
-    <mergeCell ref="O3:S4"/>
-    <mergeCell ref="U18:W18"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="F18:J18"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:T17"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="Q15:T15"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="K13:N13"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="Q14:T14"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="Q12:T12"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="U8:Y8"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="U7:Y7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="U5:Y5"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4974,162 +4985,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="119" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="113" t="s">
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="119" t="s">
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="134" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="123" t="s">
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
+      <c r="P1" s="135"/>
+      <c r="Q1" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="134" t="s">
+      <c r="R1" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="135"/>
-      <c r="T1" s="128" t="s">
+      <c r="S1" s="150"/>
+      <c r="T1" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="124" t="s">
+      <c r="U1" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="186"/>
+      <c r="V1" s="194"/>
     </row>
     <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="107"/>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="122"/>
-      <c r="O2" s="122"/>
-      <c r="P2" s="122"/>
-      <c r="Q2" s="123"/>
-      <c r="R2" s="137"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="131"/>
-      <c r="U2" s="126"/>
-      <c r="V2" s="187"/>
+      <c r="A2" s="122"/>
+      <c r="B2" s="123"/>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="136"/>
+      <c r="N2" s="137"/>
+      <c r="O2" s="137"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="152"/>
+      <c r="S2" s="153"/>
+      <c r="T2" s="146"/>
+      <c r="U2" s="141"/>
+      <c r="V2" s="195"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A3" s="107"/>
-      <c r="B3" s="108"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="113" t="s">
+      <c r="A3" s="122"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="128" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="114"/>
-      <c r="K3" s="114"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="119" t="s">
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="120"/>
-      <c r="O3" s="120"/>
-      <c r="P3" s="120"/>
-      <c r="Q3" s="123" t="s">
+      <c r="N3" s="135"/>
+      <c r="O3" s="135"/>
+      <c r="P3" s="135"/>
+      <c r="Q3" s="138" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="134" t="s">
+      <c r="R3" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="135"/>
-      <c r="T3" s="123" t="s">
+      <c r="S3" s="150"/>
+      <c r="T3" s="138" t="s">
         <v>16</v>
       </c>
-      <c r="U3" s="124" t="s">
-        <v>12</v>
-      </c>
-      <c r="V3" s="186"/>
+      <c r="U3" s="217" t="s">
+        <v>261</v>
+      </c>
+      <c r="V3" s="194"/>
     </row>
     <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A4" s="110"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="121"/>
-      <c r="N4" s="122"/>
-      <c r="O4" s="122"/>
-      <c r="P4" s="122"/>
-      <c r="Q4" s="123"/>
-      <c r="R4" s="137"/>
-      <c r="S4" s="138"/>
-      <c r="T4" s="123"/>
-      <c r="U4" s="126"/>
-      <c r="V4" s="187"/>
+      <c r="A4" s="125"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="132"/>
+      <c r="K4" s="132"/>
+      <c r="L4" s="132"/>
+      <c r="M4" s="136"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137"/>
+      <c r="P4" s="137"/>
+      <c r="Q4" s="138"/>
+      <c r="R4" s="152"/>
+      <c r="S4" s="153"/>
+      <c r="T4" s="138"/>
+      <c r="U4" s="141"/>
+      <c r="V4" s="195"/>
     </row>
     <row r="5" spans="1:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A5" s="182" t="s">
+      <c r="A5" s="157" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="182"/>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="183" t="s">
+      <c r="B5" s="157"/>
+      <c r="C5" s="157"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="158" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="183"/>
-      <c r="G5" s="183"/>
-      <c r="H5" s="183"/>
-      <c r="I5" s="182" t="s">
+      <c r="F5" s="158"/>
+      <c r="G5" s="158"/>
+      <c r="H5" s="158"/>
+      <c r="I5" s="157" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="182"/>
-      <c r="K5" s="182"/>
-      <c r="L5" s="182"/>
-      <c r="M5" s="183" t="s">
+      <c r="J5" s="157"/>
+      <c r="K5" s="157"/>
+      <c r="L5" s="157"/>
+      <c r="M5" s="158" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="183"/>
-      <c r="O5" s="183"/>
-      <c r="P5" s="183"/>
+      <c r="N5" s="158"/>
+      <c r="O5" s="158"/>
+      <c r="P5" s="158"/>
       <c r="Q5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="R5" s="183" t="s">
+      <c r="R5" s="158" t="s">
         <v>26</v>
       </c>
-      <c r="S5" s="183"/>
-      <c r="T5" s="183"/>
-      <c r="U5" s="183"/>
-      <c r="V5" s="183"/>
+      <c r="S5" s="158"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="158"/>
+      <c r="V5" s="158"/>
     </row>
     <row r="6" spans="1:22" s="32" customFormat="1" ht="18.75" x14ac:dyDescent="0.8">
       <c r="A6" s="39"/>
@@ -5185,73 +5196,73 @@
       <c r="A8" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="188" t="s">
+      <c r="B8" s="184" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="188"/>
-      <c r="D8" s="188"/>
-      <c r="E8" s="188"/>
-      <c r="F8" s="188"/>
-      <c r="G8" s="188"/>
-      <c r="H8" s="188"/>
-      <c r="I8" s="188" t="s">
+      <c r="C8" s="184"/>
+      <c r="D8" s="184"/>
+      <c r="E8" s="184"/>
+      <c r="F8" s="184"/>
+      <c r="G8" s="184"/>
+      <c r="H8" s="184"/>
+      <c r="I8" s="184" t="s">
         <v>54</v>
       </c>
-      <c r="J8" s="188"/>
-      <c r="K8" s="188"/>
-      <c r="L8" s="188"/>
-      <c r="M8" s="188" t="s">
+      <c r="J8" s="184"/>
+      <c r="K8" s="184"/>
+      <c r="L8" s="184"/>
+      <c r="M8" s="184" t="s">
         <v>42</v>
       </c>
-      <c r="N8" s="188"/>
-      <c r="O8" s="188"/>
-      <c r="P8" s="189" t="s">
+      <c r="N8" s="184"/>
+      <c r="O8" s="184"/>
+      <c r="P8" s="185" t="s">
         <v>45</v>
       </c>
-      <c r="Q8" s="189"/>
-      <c r="R8" s="189"/>
-      <c r="S8" s="189"/>
-      <c r="T8" s="131" t="s">
+      <c r="Q8" s="185"/>
+      <c r="R8" s="185"/>
+      <c r="S8" s="185"/>
+      <c r="T8" s="146" t="s">
         <v>81</v>
       </c>
-      <c r="U8" s="132"/>
-      <c r="V8" s="133"/>
+      <c r="U8" s="147"/>
+      <c r="V8" s="148"/>
     </row>
     <row r="9" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A9" s="44">
         <v>1</v>
       </c>
-      <c r="B9" s="190" t="s">
+      <c r="B9" s="186" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="191"/>
-      <c r="D9" s="191"/>
-      <c r="E9" s="191"/>
-      <c r="F9" s="191"/>
-      <c r="G9" s="191"/>
-      <c r="H9" s="191"/>
-      <c r="I9" s="166" t="s">
+      <c r="C9" s="187"/>
+      <c r="D9" s="187"/>
+      <c r="E9" s="187"/>
+      <c r="F9" s="187"/>
+      <c r="G9" s="187"/>
+      <c r="H9" s="187"/>
+      <c r="I9" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
-      <c r="L9" s="167"/>
-      <c r="M9" s="184" t="s">
+      <c r="J9" s="164"/>
+      <c r="K9" s="164"/>
+      <c r="L9" s="165"/>
+      <c r="M9" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="N9" s="180"/>
-      <c r="O9" s="180"/>
-      <c r="P9" s="172" t="s">
+      <c r="N9" s="162"/>
+      <c r="O9" s="162"/>
+      <c r="P9" s="169" t="s">
         <v>83</v>
       </c>
-      <c r="Q9" s="165"/>
-      <c r="R9" s="165"/>
-      <c r="S9" s="165"/>
-      <c r="T9" s="165" t="s">
+      <c r="Q9" s="166"/>
+      <c r="R9" s="166"/>
+      <c r="S9" s="166"/>
+      <c r="T9" s="166" t="s">
         <v>84</v>
       </c>
-      <c r="U9" s="165"/>
-      <c r="V9" s="165"/>
+      <c r="U9" s="166"/>
+      <c r="V9" s="166"/>
     </row>
     <row r="10" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A10" s="44">
@@ -5266,34 +5277,34 @@
       <c r="F10" s="46"/>
       <c r="G10" s="46"/>
       <c r="H10" s="46"/>
-      <c r="I10" s="166" t="s">
+      <c r="I10" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="J10" s="169"/>
-      <c r="K10" s="169"/>
-      <c r="L10" s="167"/>
-      <c r="M10" s="184" t="s">
+      <c r="J10" s="164"/>
+      <c r="K10" s="164"/>
+      <c r="L10" s="165"/>
+      <c r="M10" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="N10" s="180"/>
-      <c r="O10" s="180"/>
-      <c r="P10" s="172" t="s">
+      <c r="N10" s="162"/>
+      <c r="O10" s="162"/>
+      <c r="P10" s="169" t="s">
         <v>86</v>
       </c>
-      <c r="Q10" s="165"/>
-      <c r="R10" s="165"/>
-      <c r="S10" s="165"/>
-      <c r="T10" s="165" t="s">
+      <c r="Q10" s="166"/>
+      <c r="R10" s="166"/>
+      <c r="S10" s="166"/>
+      <c r="T10" s="166" t="s">
         <v>87</v>
       </c>
-      <c r="U10" s="165"/>
-      <c r="V10" s="165"/>
+      <c r="U10" s="166"/>
+      <c r="V10" s="166"/>
     </row>
     <row r="11" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A11" s="44">
         <v>3</v>
       </c>
-      <c r="B11" s="185"/>
+      <c r="B11" s="193"/>
       <c r="C11" s="48" t="s">
         <v>88</v>
       </c>
@@ -5302,35 +5313,35 @@
       <c r="F11" s="50"/>
       <c r="G11" s="50"/>
       <c r="H11" s="50"/>
-      <c r="I11" s="165" t="s">
+      <c r="I11" s="166" t="s">
         <v>89</v>
       </c>
-      <c r="J11" s="165"/>
-      <c r="K11" s="165"/>
-      <c r="L11" s="165"/>
-      <c r="M11" s="184" t="s">
+      <c r="J11" s="166"/>
+      <c r="K11" s="166"/>
+      <c r="L11" s="166"/>
+      <c r="M11" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="N11" s="180"/>
-      <c r="O11" s="180"/>
-      <c r="P11" s="172" t="s">
+      <c r="N11" s="162"/>
+      <c r="O11" s="162"/>
+      <c r="P11" s="169" t="s">
         <v>90</v>
       </c>
-      <c r="Q11" s="165"/>
-      <c r="R11" s="165"/>
-      <c r="S11" s="165"/>
-      <c r="T11" s="172" t="s">
+      <c r="Q11" s="166"/>
+      <c r="R11" s="166"/>
+      <c r="S11" s="166"/>
+      <c r="T11" s="169" t="s">
         <v>91</v>
       </c>
-      <c r="U11" s="165"/>
-      <c r="V11" s="165"/>
+      <c r="U11" s="166"/>
+      <c r="V11" s="166"/>
     </row>
     <row r="12" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A12" s="44">
         <v>4</v>
       </c>
-      <c r="B12" s="185"/>
-      <c r="C12" s="185"/>
+      <c r="B12" s="193"/>
+      <c r="C12" s="193"/>
       <c r="D12" s="48" t="s">
         <v>92</v>
       </c>
@@ -5338,241 +5349,241 @@
       <c r="F12" s="50"/>
       <c r="G12" s="50"/>
       <c r="H12" s="50"/>
-      <c r="I12" s="165" t="s">
+      <c r="I12" s="166" t="s">
         <v>93</v>
       </c>
-      <c r="J12" s="165"/>
-      <c r="K12" s="165"/>
-      <c r="L12" s="165"/>
-      <c r="M12" s="184" t="s">
+      <c r="J12" s="166"/>
+      <c r="K12" s="166"/>
+      <c r="L12" s="166"/>
+      <c r="M12" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="N12" s="180"/>
-      <c r="O12" s="180"/>
-      <c r="P12" s="172" t="s">
+      <c r="N12" s="162"/>
+      <c r="O12" s="162"/>
+      <c r="P12" s="169" t="s">
         <v>94</v>
       </c>
-      <c r="Q12" s="165"/>
-      <c r="R12" s="165"/>
-      <c r="S12" s="165"/>
-      <c r="T12" s="172" t="s">
+      <c r="Q12" s="166"/>
+      <c r="R12" s="166"/>
+      <c r="S12" s="166"/>
+      <c r="T12" s="169" t="s">
         <v>91</v>
       </c>
-      <c r="U12" s="165"/>
-      <c r="V12" s="165"/>
+      <c r="U12" s="166"/>
+      <c r="V12" s="166"/>
     </row>
     <row r="13" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A13" s="44">
         <v>5</v>
       </c>
-      <c r="B13" s="185"/>
-      <c r="C13" s="185"/>
-      <c r="D13" s="185"/>
+      <c r="B13" s="193"/>
+      <c r="C13" s="193"/>
+      <c r="D13" s="193"/>
       <c r="E13" s="44" t="s">
         <v>95</v>
       </c>
       <c r="F13" s="51"/>
       <c r="G13" s="50"/>
       <c r="H13" s="50"/>
-      <c r="I13" s="166" t="s">
+      <c r="I13" s="163" t="s">
         <v>59</v>
       </c>
-      <c r="J13" s="169"/>
-      <c r="K13" s="169"/>
-      <c r="L13" s="167"/>
-      <c r="M13" s="184" t="s">
+      <c r="J13" s="164"/>
+      <c r="K13" s="164"/>
+      <c r="L13" s="165"/>
+      <c r="M13" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="N13" s="180"/>
-      <c r="O13" s="180"/>
-      <c r="P13" s="172" t="s">
+      <c r="N13" s="162"/>
+      <c r="O13" s="162"/>
+      <c r="P13" s="169" t="s">
         <v>96</v>
       </c>
-      <c r="Q13" s="165"/>
-      <c r="R13" s="165"/>
-      <c r="S13" s="165"/>
-      <c r="T13" s="165">
+      <c r="Q13" s="166"/>
+      <c r="R13" s="166"/>
+      <c r="S13" s="166"/>
+      <c r="T13" s="166">
         <v>1</v>
       </c>
-      <c r="U13" s="165"/>
-      <c r="V13" s="165"/>
+      <c r="U13" s="166"/>
+      <c r="V13" s="166"/>
     </row>
     <row r="14" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A14" s="44">
         <v>6</v>
       </c>
-      <c r="B14" s="185"/>
-      <c r="C14" s="185"/>
-      <c r="D14" s="185"/>
+      <c r="B14" s="193"/>
+      <c r="C14" s="193"/>
+      <c r="D14" s="193"/>
       <c r="E14" s="44" t="s">
         <v>97</v>
       </c>
       <c r="F14" s="51"/>
       <c r="G14" s="50"/>
       <c r="H14" s="50"/>
-      <c r="I14" s="166" t="s">
+      <c r="I14" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="169"/>
-      <c r="K14" s="169"/>
-      <c r="L14" s="167"/>
-      <c r="M14" s="180"/>
-      <c r="N14" s="180"/>
-      <c r="O14" s="180"/>
-      <c r="P14" s="172" t="s">
+      <c r="J14" s="164"/>
+      <c r="K14" s="164"/>
+      <c r="L14" s="165"/>
+      <c r="M14" s="162"/>
+      <c r="N14" s="162"/>
+      <c r="O14" s="162"/>
+      <c r="P14" s="169" t="s">
         <v>98</v>
       </c>
-      <c r="Q14" s="165"/>
-      <c r="R14" s="165"/>
-      <c r="S14" s="165"/>
-      <c r="T14" s="165" t="s">
+      <c r="Q14" s="166"/>
+      <c r="R14" s="166"/>
+      <c r="S14" s="166"/>
+      <c r="T14" s="166" t="s">
         <v>99</v>
       </c>
-      <c r="U14" s="165"/>
-      <c r="V14" s="165"/>
+      <c r="U14" s="166"/>
+      <c r="V14" s="166"/>
     </row>
     <row r="15" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A15" s="44">
         <v>7</v>
       </c>
-      <c r="B15" s="185"/>
-      <c r="C15" s="185"/>
-      <c r="D15" s="185"/>
+      <c r="B15" s="193"/>
+      <c r="C15" s="193"/>
+      <c r="D15" s="193"/>
       <c r="E15" s="44" t="s">
         <v>100</v>
       </c>
       <c r="F15" s="51"/>
       <c r="G15" s="50"/>
       <c r="H15" s="50"/>
-      <c r="I15" s="166" t="s">
+      <c r="I15" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="J15" s="169"/>
-      <c r="K15" s="169"/>
-      <c r="L15" s="167"/>
-      <c r="M15" s="180"/>
-      <c r="N15" s="180"/>
-      <c r="O15" s="180"/>
-      <c r="P15" s="172" t="s">
+      <c r="J15" s="164"/>
+      <c r="K15" s="164"/>
+      <c r="L15" s="165"/>
+      <c r="M15" s="162"/>
+      <c r="N15" s="162"/>
+      <c r="O15" s="162"/>
+      <c r="P15" s="169" t="s">
         <v>101</v>
       </c>
-      <c r="Q15" s="165"/>
-      <c r="R15" s="165"/>
-      <c r="S15" s="165"/>
-      <c r="T15" s="165" t="s">
+      <c r="Q15" s="166"/>
+      <c r="R15" s="166"/>
+      <c r="S15" s="166"/>
+      <c r="T15" s="166" t="s">
         <v>102</v>
       </c>
-      <c r="U15" s="165"/>
-      <c r="V15" s="165"/>
+      <c r="U15" s="166"/>
+      <c r="V15" s="166"/>
     </row>
     <row r="16" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A16" s="44">
         <v>8</v>
       </c>
-      <c r="B16" s="185"/>
-      <c r="C16" s="185"/>
-      <c r="D16" s="185"/>
+      <c r="B16" s="193"/>
+      <c r="C16" s="193"/>
+      <c r="D16" s="193"/>
       <c r="E16" s="44" t="s">
         <v>103</v>
       </c>
       <c r="F16" s="51"/>
       <c r="G16" s="50"/>
       <c r="H16" s="50"/>
-      <c r="I16" s="166" t="s">
+      <c r="I16" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="J16" s="169"/>
-      <c r="K16" s="169"/>
-      <c r="L16" s="167"/>
-      <c r="M16" s="180"/>
-      <c r="N16" s="180"/>
-      <c r="O16" s="180"/>
-      <c r="P16" s="172" t="s">
+      <c r="J16" s="164"/>
+      <c r="K16" s="164"/>
+      <c r="L16" s="165"/>
+      <c r="M16" s="162"/>
+      <c r="N16" s="162"/>
+      <c r="O16" s="162"/>
+      <c r="P16" s="169" t="s">
         <v>67</v>
       </c>
-      <c r="Q16" s="165"/>
-      <c r="R16" s="165"/>
-      <c r="S16" s="165"/>
-      <c r="T16" s="165" t="s">
+      <c r="Q16" s="166"/>
+      <c r="R16" s="166"/>
+      <c r="S16" s="166"/>
+      <c r="T16" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="U16" s="165"/>
-      <c r="V16" s="165"/>
+      <c r="U16" s="166"/>
+      <c r="V16" s="166"/>
     </row>
     <row r="17" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A17" s="44">
         <v>9</v>
       </c>
-      <c r="B17" s="185"/>
-      <c r="C17" s="185"/>
-      <c r="D17" s="185"/>
+      <c r="B17" s="193"/>
+      <c r="C17" s="193"/>
+      <c r="D17" s="193"/>
       <c r="E17" s="44" t="s">
         <v>105</v>
       </c>
       <c r="F17" s="51"/>
       <c r="G17" s="50"/>
       <c r="H17" s="50"/>
-      <c r="I17" s="166" t="s">
+      <c r="I17" s="163" t="s">
         <v>59</v>
       </c>
-      <c r="J17" s="169"/>
-      <c r="K17" s="169"/>
-      <c r="L17" s="167"/>
-      <c r="M17" s="180"/>
-      <c r="N17" s="180"/>
-      <c r="O17" s="180"/>
-      <c r="P17" s="172" t="s">
+      <c r="J17" s="164"/>
+      <c r="K17" s="164"/>
+      <c r="L17" s="165"/>
+      <c r="M17" s="162"/>
+      <c r="N17" s="162"/>
+      <c r="O17" s="162"/>
+      <c r="P17" s="169" t="s">
         <v>106</v>
       </c>
-      <c r="Q17" s="165"/>
-      <c r="R17" s="165"/>
-      <c r="S17" s="165"/>
-      <c r="T17" s="165">
+      <c r="Q17" s="166"/>
+      <c r="R17" s="166"/>
+      <c r="S17" s="166"/>
+      <c r="T17" s="166">
         <v>75</v>
       </c>
-      <c r="U17" s="165"/>
-      <c r="V17" s="165"/>
+      <c r="U17" s="166"/>
+      <c r="V17" s="166"/>
     </row>
     <row r="18" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A18" s="44">
         <v>10</v>
       </c>
-      <c r="B18" s="185"/>
-      <c r="C18" s="185"/>
-      <c r="D18" s="185"/>
+      <c r="B18" s="193"/>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
       <c r="E18" s="44" t="s">
         <v>107</v>
       </c>
       <c r="F18" s="51"/>
       <c r="G18" s="50"/>
       <c r="H18" s="50"/>
-      <c r="I18" s="166" t="s">
+      <c r="I18" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="J18" s="169"/>
-      <c r="K18" s="169"/>
-      <c r="L18" s="167"/>
-      <c r="M18" s="180"/>
-      <c r="N18" s="180"/>
-      <c r="O18" s="180"/>
-      <c r="P18" s="172" t="s">
+      <c r="J18" s="164"/>
+      <c r="K18" s="164"/>
+      <c r="L18" s="165"/>
+      <c r="M18" s="162"/>
+      <c r="N18" s="162"/>
+      <c r="O18" s="162"/>
+      <c r="P18" s="169" t="s">
         <v>108</v>
       </c>
-      <c r="Q18" s="165"/>
-      <c r="R18" s="165"/>
-      <c r="S18" s="165"/>
-      <c r="T18" s="165" t="s">
+      <c r="Q18" s="166"/>
+      <c r="R18" s="166"/>
+      <c r="S18" s="166"/>
+      <c r="T18" s="166" t="s">
         <v>109</v>
       </c>
-      <c r="U18" s="165"/>
-      <c r="V18" s="165"/>
+      <c r="U18" s="166"/>
+      <c r="V18" s="166"/>
     </row>
     <row r="19" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A19" s="44">
         <v>11</v>
       </c>
-      <c r="B19" s="185"/>
-      <c r="C19" s="185"/>
+      <c r="B19" s="193"/>
+      <c r="C19" s="193"/>
       <c r="D19" s="83"/>
       <c r="E19" s="89" t="s">
         <v>254</v>
@@ -5580,35 +5591,35 @@
       <c r="F19" s="88"/>
       <c r="G19" s="90"/>
       <c r="H19" s="90"/>
-      <c r="I19" s="158" t="s">
+      <c r="I19" s="178" t="s">
         <v>69</v>
       </c>
-      <c r="J19" s="160"/>
-      <c r="K19" s="160"/>
-      <c r="L19" s="159"/>
-      <c r="M19" s="194" t="s">
+      <c r="J19" s="180"/>
+      <c r="K19" s="180"/>
+      <c r="L19" s="179"/>
+      <c r="M19" s="189" t="s">
         <v>48</v>
       </c>
-      <c r="N19" s="194"/>
-      <c r="O19" s="194"/>
-      <c r="P19" s="163" t="s">
+      <c r="N19" s="189"/>
+      <c r="O19" s="189"/>
+      <c r="P19" s="183" t="s">
         <v>236</v>
       </c>
-      <c r="Q19" s="157"/>
-      <c r="R19" s="157"/>
-      <c r="S19" s="157"/>
-      <c r="T19" s="195" t="s">
+      <c r="Q19" s="177"/>
+      <c r="R19" s="177"/>
+      <c r="S19" s="177"/>
+      <c r="T19" s="190" t="s">
         <v>255</v>
       </c>
-      <c r="U19" s="157"/>
-      <c r="V19" s="157"/>
+      <c r="U19" s="177"/>
+      <c r="V19" s="177"/>
     </row>
     <row r="20" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A20" s="44">
         <v>12</v>
       </c>
-      <c r="B20" s="173"/>
-      <c r="C20" s="173"/>
+      <c r="B20" s="174"/>
+      <c r="C20" s="174"/>
       <c r="D20" s="44" t="s">
         <v>110</v>
       </c>
@@ -5616,28 +5627,28 @@
       <c r="F20" s="51"/>
       <c r="G20" s="50"/>
       <c r="H20" s="50"/>
-      <c r="I20" s="166" t="s">
+      <c r="I20" s="163" t="s">
         <v>59</v>
       </c>
-      <c r="J20" s="169"/>
-      <c r="K20" s="169"/>
-      <c r="L20" s="167"/>
-      <c r="M20" s="184" t="s">
+      <c r="J20" s="164"/>
+      <c r="K20" s="164"/>
+      <c r="L20" s="165"/>
+      <c r="M20" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="N20" s="180"/>
-      <c r="O20" s="180"/>
-      <c r="P20" s="172" t="s">
+      <c r="N20" s="162"/>
+      <c r="O20" s="162"/>
+      <c r="P20" s="169" t="s">
         <v>111</v>
       </c>
-      <c r="Q20" s="165"/>
-      <c r="R20" s="165"/>
-      <c r="S20" s="165"/>
-      <c r="T20" s="165">
+      <c r="Q20" s="166"/>
+      <c r="R20" s="166"/>
+      <c r="S20" s="166"/>
+      <c r="T20" s="166">
         <v>3</v>
       </c>
-      <c r="U20" s="165"/>
-      <c r="V20" s="165"/>
+      <c r="U20" s="166"/>
+      <c r="V20" s="166"/>
     </row>
     <row r="21" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A21" s="39"/>
@@ -5693,145 +5704,145 @@
       <c r="A23" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="188" t="s">
+      <c r="B23" s="184" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="188"/>
-      <c r="D23" s="188"/>
-      <c r="E23" s="188"/>
-      <c r="F23" s="188"/>
-      <c r="G23" s="188"/>
-      <c r="H23" s="188"/>
-      <c r="I23" s="188" t="s">
+      <c r="C23" s="184"/>
+      <c r="D23" s="184"/>
+      <c r="E23" s="184"/>
+      <c r="F23" s="184"/>
+      <c r="G23" s="184"/>
+      <c r="H23" s="184"/>
+      <c r="I23" s="184" t="s">
         <v>54</v>
       </c>
-      <c r="J23" s="188"/>
-      <c r="K23" s="188"/>
-      <c r="L23" s="188"/>
-      <c r="M23" s="188" t="s">
+      <c r="J23" s="184"/>
+      <c r="K23" s="184"/>
+      <c r="L23" s="184"/>
+      <c r="M23" s="184" t="s">
         <v>42</v>
       </c>
-      <c r="N23" s="188"/>
-      <c r="O23" s="188"/>
-      <c r="P23" s="189" t="s">
+      <c r="N23" s="184"/>
+      <c r="O23" s="184"/>
+      <c r="P23" s="185" t="s">
         <v>45</v>
       </c>
-      <c r="Q23" s="189"/>
-      <c r="R23" s="189"/>
-      <c r="S23" s="189"/>
-      <c r="T23" s="131" t="s">
+      <c r="Q23" s="185"/>
+      <c r="R23" s="185"/>
+      <c r="S23" s="185"/>
+      <c r="T23" s="146" t="s">
         <v>81</v>
       </c>
-      <c r="U23" s="132"/>
-      <c r="V23" s="133"/>
+      <c r="U23" s="147"/>
+      <c r="V23" s="148"/>
     </row>
     <row r="24" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A24" s="44">
         <v>1</v>
       </c>
-      <c r="B24" s="190" t="s">
+      <c r="B24" s="186" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="191"/>
-      <c r="D24" s="191"/>
-      <c r="E24" s="191"/>
-      <c r="F24" s="191"/>
-      <c r="G24" s="191"/>
-      <c r="H24" s="191"/>
-      <c r="I24" s="166" t="s">
+      <c r="C24" s="187"/>
+      <c r="D24" s="187"/>
+      <c r="E24" s="187"/>
+      <c r="F24" s="187"/>
+      <c r="G24" s="187"/>
+      <c r="H24" s="187"/>
+      <c r="I24" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="J24" s="169"/>
-      <c r="K24" s="169"/>
-      <c r="L24" s="167"/>
-      <c r="M24" s="184" t="s">
+      <c r="J24" s="164"/>
+      <c r="K24" s="164"/>
+      <c r="L24" s="165"/>
+      <c r="M24" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="N24" s="180"/>
-      <c r="O24" s="180"/>
-      <c r="P24" s="172" t="s">
+      <c r="N24" s="162"/>
+      <c r="O24" s="162"/>
+      <c r="P24" s="169" t="s">
         <v>83</v>
       </c>
-      <c r="Q24" s="165"/>
-      <c r="R24" s="165"/>
-      <c r="S24" s="165"/>
-      <c r="T24" s="165" t="s">
+      <c r="Q24" s="166"/>
+      <c r="R24" s="166"/>
+      <c r="S24" s="166"/>
+      <c r="T24" s="166" t="s">
         <v>113</v>
       </c>
-      <c r="U24" s="165"/>
-      <c r="V24" s="165"/>
+      <c r="U24" s="166"/>
+      <c r="V24" s="166"/>
     </row>
     <row r="25" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A25" s="44">
         <v>2</v>
       </c>
-      <c r="B25" s="190" t="s">
+      <c r="B25" s="186" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="191"/>
-      <c r="D25" s="191"/>
-      <c r="E25" s="191"/>
-      <c r="F25" s="191"/>
-      <c r="G25" s="191"/>
-      <c r="H25" s="191"/>
-      <c r="I25" s="166" t="s">
+      <c r="C25" s="187"/>
+      <c r="D25" s="187"/>
+      <c r="E25" s="187"/>
+      <c r="F25" s="187"/>
+      <c r="G25" s="187"/>
+      <c r="H25" s="187"/>
+      <c r="I25" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="J25" s="169"/>
-      <c r="K25" s="169"/>
-      <c r="L25" s="167"/>
-      <c r="M25" s="184" t="s">
+      <c r="J25" s="164"/>
+      <c r="K25" s="164"/>
+      <c r="L25" s="165"/>
+      <c r="M25" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="N25" s="180"/>
-      <c r="O25" s="180"/>
-      <c r="P25" s="172" t="s">
+      <c r="N25" s="162"/>
+      <c r="O25" s="162"/>
+      <c r="P25" s="169" t="s">
         <v>114</v>
       </c>
-      <c r="Q25" s="165"/>
-      <c r="R25" s="165"/>
-      <c r="S25" s="165"/>
-      <c r="T25" s="165" t="s">
+      <c r="Q25" s="166"/>
+      <c r="R25" s="166"/>
+      <c r="S25" s="166"/>
+      <c r="T25" s="166" t="s">
         <v>115</v>
       </c>
-      <c r="U25" s="165"/>
-      <c r="V25" s="165"/>
+      <c r="U25" s="166"/>
+      <c r="V25" s="166"/>
     </row>
     <row r="26" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A26" s="44">
         <v>3</v>
       </c>
-      <c r="B26" s="192" t="s">
+      <c r="B26" s="191" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="191"/>
-      <c r="D26" s="191"/>
-      <c r="E26" s="191"/>
-      <c r="F26" s="191"/>
-      <c r="G26" s="191"/>
-      <c r="H26" s="193"/>
-      <c r="I26" s="166" t="s">
+      <c r="C26" s="187"/>
+      <c r="D26" s="187"/>
+      <c r="E26" s="187"/>
+      <c r="F26" s="187"/>
+      <c r="G26" s="187"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="J26" s="169"/>
-      <c r="K26" s="169"/>
-      <c r="L26" s="167"/>
-      <c r="M26" s="184" t="s">
+      <c r="J26" s="164"/>
+      <c r="K26" s="164"/>
+      <c r="L26" s="165"/>
+      <c r="M26" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="N26" s="180"/>
-      <c r="O26" s="180"/>
-      <c r="P26" s="165" t="s">
+      <c r="N26" s="162"/>
+      <c r="O26" s="162"/>
+      <c r="P26" s="166" t="s">
         <v>117</v>
       </c>
-      <c r="Q26" s="165"/>
-      <c r="R26" s="165"/>
-      <c r="S26" s="165"/>
-      <c r="T26" s="165" t="s">
+      <c r="Q26" s="166"/>
+      <c r="R26" s="166"/>
+      <c r="S26" s="166"/>
+      <c r="T26" s="166" t="s">
         <v>118</v>
       </c>
-      <c r="U26" s="165"/>
-      <c r="V26" s="165"/>
+      <c r="U26" s="166"/>
+      <c r="V26" s="166"/>
     </row>
     <row r="27" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="M27" s="1"/>
@@ -5868,73 +5879,73 @@
       <c r="A29" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="188" t="s">
+      <c r="B29" s="184" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="188"/>
-      <c r="D29" s="188"/>
-      <c r="E29" s="188"/>
-      <c r="F29" s="188"/>
-      <c r="G29" s="188"/>
-      <c r="H29" s="188"/>
-      <c r="I29" s="188" t="s">
+      <c r="C29" s="184"/>
+      <c r="D29" s="184"/>
+      <c r="E29" s="184"/>
+      <c r="F29" s="184"/>
+      <c r="G29" s="184"/>
+      <c r="H29" s="184"/>
+      <c r="I29" s="184" t="s">
         <v>54</v>
       </c>
-      <c r="J29" s="188"/>
-      <c r="K29" s="188"/>
-      <c r="L29" s="188"/>
-      <c r="M29" s="188" t="s">
+      <c r="J29" s="184"/>
+      <c r="K29" s="184"/>
+      <c r="L29" s="184"/>
+      <c r="M29" s="184" t="s">
         <v>42</v>
       </c>
-      <c r="N29" s="188"/>
-      <c r="O29" s="188"/>
-      <c r="P29" s="189" t="s">
+      <c r="N29" s="184"/>
+      <c r="O29" s="184"/>
+      <c r="P29" s="185" t="s">
         <v>45</v>
       </c>
-      <c r="Q29" s="189"/>
-      <c r="R29" s="189"/>
-      <c r="S29" s="189"/>
-      <c r="T29" s="131" t="s">
+      <c r="Q29" s="185"/>
+      <c r="R29" s="185"/>
+      <c r="S29" s="185"/>
+      <c r="T29" s="146" t="s">
         <v>81</v>
       </c>
-      <c r="U29" s="132"/>
-      <c r="V29" s="133"/>
+      <c r="U29" s="147"/>
+      <c r="V29" s="148"/>
     </row>
     <row r="30" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A30" s="44">
         <v>1</v>
       </c>
-      <c r="B30" s="190" t="s">
+      <c r="B30" s="186" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="191"/>
-      <c r="D30" s="191"/>
-      <c r="E30" s="191"/>
-      <c r="F30" s="191"/>
-      <c r="G30" s="191"/>
-      <c r="H30" s="191"/>
-      <c r="I30" s="166" t="s">
+      <c r="C30" s="187"/>
+      <c r="D30" s="187"/>
+      <c r="E30" s="187"/>
+      <c r="F30" s="187"/>
+      <c r="G30" s="187"/>
+      <c r="H30" s="187"/>
+      <c r="I30" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="J30" s="169"/>
-      <c r="K30" s="169"/>
-      <c r="L30" s="167"/>
-      <c r="M30" s="184" t="s">
+      <c r="J30" s="164"/>
+      <c r="K30" s="164"/>
+      <c r="L30" s="165"/>
+      <c r="M30" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="N30" s="180"/>
-      <c r="O30" s="180"/>
-      <c r="P30" s="172" t="s">
+      <c r="N30" s="162"/>
+      <c r="O30" s="162"/>
+      <c r="P30" s="169" t="s">
         <v>83</v>
       </c>
-      <c r="Q30" s="165"/>
-      <c r="R30" s="165"/>
-      <c r="S30" s="165"/>
-      <c r="T30" s="165" t="s">
+      <c r="Q30" s="166"/>
+      <c r="R30" s="166"/>
+      <c r="S30" s="166"/>
+      <c r="T30" s="166" t="s">
         <v>113</v>
       </c>
-      <c r="U30" s="165"/>
-      <c r="V30" s="165"/>
+      <c r="U30" s="166"/>
+      <c r="V30" s="166"/>
     </row>
     <row r="31" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A31" s="44">
@@ -5949,28 +5960,28 @@
       <c r="F31" s="47"/>
       <c r="G31" s="47"/>
       <c r="H31" s="47"/>
-      <c r="I31" s="166" t="s">
+      <c r="I31" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="J31" s="169"/>
-      <c r="K31" s="169"/>
-      <c r="L31" s="167"/>
-      <c r="M31" s="184" t="s">
+      <c r="J31" s="164"/>
+      <c r="K31" s="164"/>
+      <c r="L31" s="165"/>
+      <c r="M31" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="N31" s="180"/>
-      <c r="O31" s="180"/>
-      <c r="P31" s="172" t="s">
+      <c r="N31" s="162"/>
+      <c r="O31" s="162"/>
+      <c r="P31" s="169" t="s">
         <v>114</v>
       </c>
-      <c r="Q31" s="165"/>
-      <c r="R31" s="165"/>
-      <c r="S31" s="165"/>
-      <c r="T31" s="165" t="s">
+      <c r="Q31" s="166"/>
+      <c r="R31" s="166"/>
+      <c r="S31" s="166"/>
+      <c r="T31" s="166" t="s">
         <v>120</v>
       </c>
-      <c r="U31" s="165"/>
-      <c r="V31" s="165"/>
+      <c r="U31" s="166"/>
+      <c r="V31" s="166"/>
     </row>
     <row r="32" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A32" s="44">
@@ -5985,28 +5996,28 @@
       <c r="F32" s="50"/>
       <c r="G32" s="50"/>
       <c r="H32" s="54"/>
-      <c r="I32" s="166" t="s">
+      <c r="I32" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="J32" s="169"/>
-      <c r="K32" s="169"/>
-      <c r="L32" s="167"/>
-      <c r="M32" s="184" t="s">
+      <c r="J32" s="164"/>
+      <c r="K32" s="164"/>
+      <c r="L32" s="165"/>
+      <c r="M32" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="N32" s="180"/>
-      <c r="O32" s="180"/>
-      <c r="P32" s="165" t="s">
+      <c r="N32" s="162"/>
+      <c r="O32" s="162"/>
+      <c r="P32" s="166" t="s">
         <v>117</v>
       </c>
-      <c r="Q32" s="165"/>
-      <c r="R32" s="165"/>
-      <c r="S32" s="165"/>
-      <c r="T32" s="172" t="s">
+      <c r="Q32" s="166"/>
+      <c r="R32" s="166"/>
+      <c r="S32" s="166"/>
+      <c r="T32" s="169" t="s">
         <v>122</v>
       </c>
-      <c r="U32" s="165"/>
-      <c r="V32" s="165"/>
+      <c r="U32" s="166"/>
+      <c r="V32" s="166"/>
     </row>
     <row r="33" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A33" s="44">
@@ -6021,28 +6032,28 @@
       <c r="F33" s="50"/>
       <c r="G33" s="50"/>
       <c r="H33" s="54"/>
-      <c r="I33" s="166" t="s">
+      <c r="I33" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="J33" s="169"/>
-      <c r="K33" s="169"/>
-      <c r="L33" s="167"/>
-      <c r="M33" s="184" t="s">
+      <c r="J33" s="164"/>
+      <c r="K33" s="164"/>
+      <c r="L33" s="165"/>
+      <c r="M33" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="N33" s="180"/>
-      <c r="O33" s="180"/>
-      <c r="P33" s="165" t="s">
+      <c r="N33" s="162"/>
+      <c r="O33" s="162"/>
+      <c r="P33" s="166" t="s">
         <v>124</v>
       </c>
-      <c r="Q33" s="165"/>
-      <c r="R33" s="165"/>
-      <c r="S33" s="165"/>
-      <c r="T33" s="165" t="s">
+      <c r="Q33" s="166"/>
+      <c r="R33" s="166"/>
+      <c r="S33" s="166"/>
+      <c r="T33" s="166" t="s">
         <v>125</v>
       </c>
-      <c r="U33" s="165"/>
-      <c r="V33" s="165"/>
+      <c r="U33" s="166"/>
+      <c r="V33" s="166"/>
     </row>
     <row r="34" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A34" s="44">
@@ -6057,128 +6068,31 @@
       <c r="F34" s="50"/>
       <c r="G34" s="50"/>
       <c r="H34" s="54"/>
-      <c r="I34" s="166" t="s">
+      <c r="I34" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="J34" s="169"/>
-      <c r="K34" s="169"/>
-      <c r="L34" s="167"/>
-      <c r="M34" s="184" t="s">
+      <c r="J34" s="164"/>
+      <c r="K34" s="164"/>
+      <c r="L34" s="165"/>
+      <c r="M34" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="N34" s="180"/>
-      <c r="O34" s="180"/>
-      <c r="P34" s="165" t="s">
+      <c r="N34" s="162"/>
+      <c r="O34" s="162"/>
+      <c r="P34" s="166" t="s">
         <v>127</v>
       </c>
-      <c r="Q34" s="165"/>
-      <c r="R34" s="165"/>
-      <c r="S34" s="165"/>
-      <c r="T34" s="165" t="s">
+      <c r="Q34" s="166"/>
+      <c r="R34" s="166"/>
+      <c r="S34" s="166"/>
+      <c r="T34" s="166" t="s">
         <v>128</v>
       </c>
-      <c r="U34" s="165"/>
-      <c r="V34" s="165"/>
+      <c r="U34" s="166"/>
+      <c r="V34" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="121">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="R5:V5"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="P8:S8"/>
-    <mergeCell ref="T8:V8"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="T9:V9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="P10:S10"/>
-    <mergeCell ref="T10:V10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="P11:S11"/>
-    <mergeCell ref="T11:V11"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="P12:S12"/>
-    <mergeCell ref="T12:V12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="P13:S13"/>
-    <mergeCell ref="T13:V13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="P14:S14"/>
-    <mergeCell ref="T14:V14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="P15:S15"/>
-    <mergeCell ref="T15:V15"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="P16:S16"/>
-    <mergeCell ref="T16:V16"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="P17:S17"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="P18:S18"/>
-    <mergeCell ref="T18:V18"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="M20:O20"/>
-    <mergeCell ref="P20:S20"/>
-    <mergeCell ref="T20:V20"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="P19:S19"/>
-    <mergeCell ref="T19:V19"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="P23:S23"/>
-    <mergeCell ref="T23:V23"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P24:S24"/>
-    <mergeCell ref="T24:V24"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="P25:S25"/>
-    <mergeCell ref="T25:V25"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="P26:S26"/>
-    <mergeCell ref="T26:V26"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="M32:O32"/>
-    <mergeCell ref="P32:S32"/>
-    <mergeCell ref="T32:V32"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="P33:S33"/>
-    <mergeCell ref="T33:V33"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="P29:S29"/>
-    <mergeCell ref="T29:V29"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="P30:S30"/>
-    <mergeCell ref="T30:V30"/>
     <mergeCell ref="I34:L34"/>
     <mergeCell ref="M34:O34"/>
     <mergeCell ref="P34:S34"/>
@@ -6203,6 +6117,103 @@
     <mergeCell ref="M31:O31"/>
     <mergeCell ref="P31:S31"/>
     <mergeCell ref="T31:V31"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="P32:S32"/>
+    <mergeCell ref="T32:V32"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="P33:S33"/>
+    <mergeCell ref="T33:V33"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="P29:S29"/>
+    <mergeCell ref="T29:V29"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="P30:S30"/>
+    <mergeCell ref="T30:V30"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="P25:S25"/>
+    <mergeCell ref="T25:V25"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="P26:S26"/>
+    <mergeCell ref="T26:V26"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="P23:S23"/>
+    <mergeCell ref="T23:V23"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P24:S24"/>
+    <mergeCell ref="T24:V24"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="P17:S17"/>
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="P18:S18"/>
+    <mergeCell ref="T18:V18"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="P20:S20"/>
+    <mergeCell ref="T20:V20"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="P19:S19"/>
+    <mergeCell ref="T19:V19"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="P14:S14"/>
+    <mergeCell ref="T14:V14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="P15:S15"/>
+    <mergeCell ref="T15:V15"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="P16:S16"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="P11:S11"/>
+    <mergeCell ref="T11:V11"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="P12:S12"/>
+    <mergeCell ref="T12:V12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="P13:S13"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="T9:V9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="P10:S10"/>
+    <mergeCell ref="T10:V10"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="P8:S8"/>
+    <mergeCell ref="T8:V8"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6229,162 +6240,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="119" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="113" t="s">
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="119" t="s">
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="134" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="123" t="s">
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
+      <c r="P1" s="135"/>
+      <c r="Q1" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="134" t="s">
+      <c r="R1" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="135"/>
-      <c r="T1" s="128" t="s">
+      <c r="S1" s="150"/>
+      <c r="T1" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="124" t="s">
+      <c r="U1" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="125"/>
+      <c r="V1" s="140"/>
     </row>
     <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="107"/>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="122"/>
-      <c r="O2" s="122"/>
-      <c r="P2" s="122"/>
-      <c r="Q2" s="123"/>
-      <c r="R2" s="137"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="131"/>
-      <c r="U2" s="126"/>
-      <c r="V2" s="127"/>
+      <c r="A2" s="122"/>
+      <c r="B2" s="123"/>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="136"/>
+      <c r="N2" s="137"/>
+      <c r="O2" s="137"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="152"/>
+      <c r="S2" s="153"/>
+      <c r="T2" s="146"/>
+      <c r="U2" s="141"/>
+      <c r="V2" s="142"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A3" s="107"/>
-      <c r="B3" s="108"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="113" t="s">
+      <c r="A3" s="122"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="128" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="114"/>
-      <c r="K3" s="114"/>
-      <c r="L3" s="114"/>
-      <c r="M3" s="119" t="s">
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="120"/>
-      <c r="O3" s="120"/>
-      <c r="P3" s="120"/>
-      <c r="Q3" s="123" t="s">
+      <c r="N3" s="135"/>
+      <c r="O3" s="135"/>
+      <c r="P3" s="135"/>
+      <c r="Q3" s="138" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="134" t="s">
+      <c r="R3" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="135"/>
-      <c r="T3" s="123" t="s">
+      <c r="S3" s="150"/>
+      <c r="T3" s="138" t="s">
         <v>16</v>
       </c>
-      <c r="U3" s="124" t="s">
-        <v>12</v>
-      </c>
-      <c r="V3" s="125"/>
+      <c r="U3" s="217" t="s">
+        <v>261</v>
+      </c>
+      <c r="V3" s="140"/>
     </row>
     <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A4" s="110"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="121"/>
-      <c r="N4" s="122"/>
-      <c r="O4" s="122"/>
-      <c r="P4" s="122"/>
-      <c r="Q4" s="123"/>
-      <c r="R4" s="137"/>
-      <c r="S4" s="138"/>
-      <c r="T4" s="123"/>
-      <c r="U4" s="126"/>
-      <c r="V4" s="127"/>
+      <c r="A4" s="125"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="132"/>
+      <c r="K4" s="132"/>
+      <c r="L4" s="132"/>
+      <c r="M4" s="136"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137"/>
+      <c r="P4" s="137"/>
+      <c r="Q4" s="138"/>
+      <c r="R4" s="152"/>
+      <c r="S4" s="153"/>
+      <c r="T4" s="138"/>
+      <c r="U4" s="141"/>
+      <c r="V4" s="142"/>
     </row>
     <row r="5" spans="1:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A5" s="182" t="s">
+      <c r="A5" s="157" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="182"/>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="183" t="s">
+      <c r="B5" s="157"/>
+      <c r="C5" s="157"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="158" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="183"/>
-      <c r="G5" s="183"/>
-      <c r="H5" s="183"/>
-      <c r="I5" s="182" t="s">
+      <c r="F5" s="158"/>
+      <c r="G5" s="158"/>
+      <c r="H5" s="158"/>
+      <c r="I5" s="157" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="182"/>
-      <c r="K5" s="182"/>
-      <c r="L5" s="182"/>
-      <c r="M5" s="183" t="s">
+      <c r="J5" s="157"/>
+      <c r="K5" s="157"/>
+      <c r="L5" s="157"/>
+      <c r="M5" s="158" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="183"/>
-      <c r="O5" s="183"/>
-      <c r="P5" s="183"/>
+      <c r="N5" s="158"/>
+      <c r="O5" s="158"/>
+      <c r="P5" s="158"/>
       <c r="Q5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="R5" s="183" t="s">
+      <c r="R5" s="158" t="s">
         <v>26</v>
       </c>
-      <c r="S5" s="183"/>
-      <c r="T5" s="183"/>
-      <c r="U5" s="183"/>
-      <c r="V5" s="183"/>
+      <c r="S5" s="158"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="158"/>
+      <c r="V5" s="158"/>
     </row>
     <row r="6" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A6" s="35"/>
@@ -6466,16 +6477,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="R5:V5"/>
-    <mergeCell ref="A1:H4"/>
-    <mergeCell ref="I1:L2"/>
-    <mergeCell ref="M1:P2"/>
-    <mergeCell ref="I3:L4"/>
-    <mergeCell ref="M3:P4"/>
     <mergeCell ref="U1:V2"/>
     <mergeCell ref="U3:V4"/>
     <mergeCell ref="Q1:Q2"/>
@@ -6484,6 +6485,16 @@
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="R1:S2"/>
     <mergeCell ref="R3:S4"/>
+    <mergeCell ref="A1:H4"/>
+    <mergeCell ref="I1:L2"/>
+    <mergeCell ref="M1:P2"/>
+    <mergeCell ref="I3:L4"/>
+    <mergeCell ref="M3:P4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="R5:V5"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6513,162 +6524,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="113" t="s">
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="119" t="s">
+      <c r="J1" s="129"/>
+      <c r="K1" s="134" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="128" t="s">
+      <c r="L1" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="134" t="s">
+      <c r="M1" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="123" t="s">
+      <c r="N1" s="138" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="123"/>
-      <c r="P1" s="124" t="s">
+      <c r="O1" s="138"/>
+      <c r="P1" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="125"/>
+      <c r="Q1" s="140"/>
     </row>
     <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="107"/>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="131"/>
-      <c r="M2" s="137"/>
-      <c r="N2" s="123"/>
-      <c r="O2" s="123"/>
-      <c r="P2" s="126"/>
-      <c r="Q2" s="127"/>
+      <c r="A2" s="122"/>
+      <c r="B2" s="123"/>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="136"/>
+      <c r="L2" s="146"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="141"/>
+      <c r="Q2" s="142"/>
     </row>
     <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A3" s="107"/>
-      <c r="B3" s="108"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="113" t="s">
+      <c r="A3" s="122"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="128" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="114"/>
-      <c r="K3" s="119" t="s">
+      <c r="J3" s="129"/>
+      <c r="K3" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="128" t="s">
+      <c r="L3" s="143" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="134" t="s">
+      <c r="M3" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="123" t="s">
+      <c r="N3" s="138" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="123"/>
-      <c r="P3" s="124" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q3" s="125"/>
+      <c r="O3" s="138"/>
+      <c r="P3" s="217" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q3" s="140"/>
     </row>
     <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A4" s="110"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="131"/>
-      <c r="M4" s="137"/>
-      <c r="N4" s="123"/>
-      <c r="O4" s="123"/>
-      <c r="P4" s="126"/>
-      <c r="Q4" s="127"/>
+      <c r="A4" s="125"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="132"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="146"/>
+      <c r="M4" s="152"/>
+      <c r="N4" s="138"/>
+      <c r="O4" s="138"/>
+      <c r="P4" s="141"/>
+      <c r="Q4" s="142"/>
     </row>
     <row r="5" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A5" s="182" t="s">
+      <c r="A5" s="157" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="182"/>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="183" t="s">
+      <c r="B5" s="157"/>
+      <c r="C5" s="157"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="158" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="183"/>
-      <c r="G5" s="183"/>
-      <c r="H5" s="183"/>
-      <c r="I5" s="182" t="s">
+      <c r="F5" s="158"/>
+      <c r="G5" s="158"/>
+      <c r="H5" s="158"/>
+      <c r="I5" s="157" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="182"/>
+      <c r="J5" s="157"/>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="M5" s="183" t="s">
+      <c r="M5" s="158" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="183"/>
-      <c r="O5" s="183"/>
-      <c r="P5" s="183"/>
-      <c r="Q5" s="183"/>
+      <c r="N5" s="158"/>
+      <c r="O5" s="158"/>
+      <c r="P5" s="158"/>
+      <c r="Q5" s="158"/>
     </row>
     <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A6" s="210" t="s">
+      <c r="A6" s="201" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="210"/>
-      <c r="C6" s="210"/>
-      <c r="D6" s="210"/>
-      <c r="E6" s="210"/>
-      <c r="F6" s="210"/>
-      <c r="G6" s="210"/>
-      <c r="H6" s="211" t="s">
+      <c r="B6" s="201"/>
+      <c r="C6" s="201"/>
+      <c r="D6" s="201"/>
+      <c r="E6" s="201"/>
+      <c r="F6" s="201"/>
+      <c r="G6" s="201"/>
+      <c r="H6" s="202" t="s">
         <v>133</v>
       </c>
-      <c r="I6" s="212"/>
-      <c r="J6" s="212"/>
-      <c r="K6" s="212"/>
-      <c r="L6" s="212"/>
-      <c r="M6" s="212"/>
-      <c r="N6" s="212"/>
-      <c r="O6" s="211" t="s">
+      <c r="I6" s="203"/>
+      <c r="J6" s="203"/>
+      <c r="K6" s="203"/>
+      <c r="L6" s="203"/>
+      <c r="M6" s="203"/>
+      <c r="N6" s="203"/>
+      <c r="O6" s="202" t="s">
         <v>134</v>
       </c>
-      <c r="P6" s="212"/>
-      <c r="Q6" s="212"/>
+      <c r="P6" s="203"/>
+      <c r="Q6" s="203"/>
     </row>
     <row r="7" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A7" s="8" t="s">
@@ -6719,10 +6730,10 @@
       <c r="C10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="4"/>
-      <c r="J10" s="204" t="s">
+      <c r="J10" s="208" t="s">
         <v>142</v>
       </c>
-      <c r="K10" s="205"/>
+      <c r="K10" s="209"/>
       <c r="L10" s="73" t="s">
         <v>187</v>
       </c>
@@ -6891,7 +6902,7 @@
     <row r="23" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A23" s="11"/>
       <c r="H23" s="11"/>
-      <c r="J23" s="206" t="s">
+      <c r="J23" s="210" t="s">
         <v>160</v>
       </c>
       <c r="K23" s="26" t="s">
@@ -6908,7 +6919,7 @@
     <row r="24" spans="1:15" s="3" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A24" s="11"/>
       <c r="H24" s="11"/>
-      <c r="J24" s="207"/>
+      <c r="J24" s="211"/>
       <c r="K24" s="27" t="s">
         <v>163</v>
       </c>
@@ -6923,7 +6934,7 @@
     <row r="25" spans="1:15" s="3" customFormat="1" ht="47.1" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A25" s="11"/>
       <c r="H25" s="11"/>
-      <c r="J25" s="207"/>
+      <c r="J25" s="211"/>
       <c r="K25" s="75" t="s">
         <v>192</v>
       </c>
@@ -6938,7 +6949,7 @@
     <row r="26" spans="1:15" s="3" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A26" s="11"/>
       <c r="H26" s="11"/>
-      <c r="J26" s="207"/>
+      <c r="J26" s="211"/>
       <c r="K26" s="75" t="s">
         <v>190</v>
       </c>
@@ -6953,7 +6964,7 @@
     <row r="27" spans="1:15" s="3" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A27" s="11"/>
       <c r="H27" s="11"/>
-      <c r="J27" s="207"/>
+      <c r="J27" s="211"/>
       <c r="K27" s="75" t="s">
         <v>188</v>
       </c>
@@ -6968,7 +6979,7 @@
     <row r="28" spans="1:15" s="3" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A28" s="11"/>
       <c r="H28" s="11"/>
-      <c r="J28" s="208"/>
+      <c r="J28" s="212"/>
       <c r="K28" s="98" t="s">
         <v>242</v>
       </c>
@@ -7061,14 +7072,14 @@
       <c r="G35" s="14"/>
       <c r="H35" s="10"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="198" t="s">
+      <c r="J35" s="215" t="s">
         <v>219</v>
       </c>
-      <c r="K35" s="199"/>
-      <c r="L35" s="198" t="s">
+      <c r="K35" s="216"/>
+      <c r="L35" s="215" t="s">
         <v>218</v>
       </c>
-      <c r="M35" s="199"/>
+      <c r="M35" s="216"/>
       <c r="O35" s="10"/>
     </row>
     <row r="36" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7081,14 +7092,14 @@
       <c r="G36" s="14"/>
       <c r="H36" s="10"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="202" t="s">
+      <c r="J36" s="204" t="s">
         <v>57</v>
       </c>
-      <c r="K36" s="203"/>
-      <c r="L36" s="200" t="s">
+      <c r="K36" s="205"/>
+      <c r="L36" s="206" t="s">
         <v>225</v>
       </c>
-      <c r="M36" s="201"/>
+      <c r="M36" s="207"/>
       <c r="O36" s="10"/>
     </row>
     <row r="37" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7101,14 +7112,14 @@
       <c r="G37" s="14"/>
       <c r="H37" s="10"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="202" t="s">
+      <c r="J37" s="204" t="s">
         <v>215</v>
       </c>
-      <c r="K37" s="203"/>
-      <c r="L37" s="200" t="s">
+      <c r="K37" s="205"/>
+      <c r="L37" s="206" t="s">
         <v>226</v>
       </c>
-      <c r="M37" s="201"/>
+      <c r="M37" s="207"/>
       <c r="O37" s="10"/>
     </row>
     <row r="38" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7121,14 +7132,14 @@
       <c r="G38" s="14"/>
       <c r="H38" s="10"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="202" t="s">
+      <c r="J38" s="204" t="s">
         <v>101</v>
       </c>
-      <c r="K38" s="203"/>
-      <c r="L38" s="200" t="s">
+      <c r="K38" s="205"/>
+      <c r="L38" s="206" t="s">
         <v>227</v>
       </c>
-      <c r="M38" s="201"/>
+      <c r="M38" s="207"/>
       <c r="O38" s="10"/>
     </row>
     <row r="39" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7141,14 +7152,14 @@
       <c r="G39" s="14"/>
       <c r="H39" s="10"/>
       <c r="I39" s="3"/>
-      <c r="J39" s="202" t="s">
+      <c r="J39" s="204" t="s">
         <v>67</v>
       </c>
-      <c r="K39" s="203"/>
-      <c r="L39" s="202" t="s">
+      <c r="K39" s="205"/>
+      <c r="L39" s="204" t="s">
         <v>228</v>
       </c>
-      <c r="M39" s="203"/>
+      <c r="M39" s="205"/>
       <c r="O39" s="10"/>
     </row>
     <row r="40" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7161,14 +7172,14 @@
       <c r="G40" s="14"/>
       <c r="H40" s="10"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="202" t="s">
+      <c r="J40" s="204" t="s">
         <v>216</v>
       </c>
-      <c r="K40" s="203"/>
-      <c r="L40" s="202" t="s">
+      <c r="K40" s="205"/>
+      <c r="L40" s="204" t="s">
         <v>229</v>
       </c>
-      <c r="M40" s="203"/>
+      <c r="M40" s="205"/>
       <c r="O40" s="10"/>
     </row>
     <row r="41" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7221,10 +7232,10 @@
       <c r="G43" s="14"/>
       <c r="H43" s="10"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="196" t="s">
+      <c r="J43" s="213" t="s">
         <v>249</v>
       </c>
-      <c r="K43" s="197"/>
+      <c r="K43" s="214"/>
       <c r="L43" s="96" t="s">
         <v>250</v>
       </c>
@@ -7241,14 +7252,14 @@
       <c r="G44" s="14"/>
       <c r="H44" s="10"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="202" t="s">
+      <c r="J44" s="204" t="s">
         <v>217</v>
       </c>
-      <c r="K44" s="203"/>
-      <c r="L44" s="202" t="s">
+      <c r="K44" s="205"/>
+      <c r="L44" s="204" t="s">
         <v>230</v>
       </c>
-      <c r="M44" s="203"/>
+      <c r="M44" s="205"/>
       <c r="O44" s="10"/>
     </row>
     <row r="45" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7343,10 +7354,10 @@
       <c r="J51" s="73" t="s">
         <v>202</v>
       </c>
-      <c r="K51" s="214" t="s">
+      <c r="K51" s="198" t="s">
         <v>210</v>
       </c>
-      <c r="L51" s="214"/>
+      <c r="L51" s="198"/>
       <c r="M51" s="82" t="s">
         <v>214</v>
       </c>
@@ -7364,10 +7375,10 @@
       <c r="J52" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="K52" s="209" t="s">
+      <c r="K52" s="196" t="s">
         <v>203</v>
       </c>
-      <c r="L52" s="209"/>
+      <c r="L52" s="196"/>
       <c r="M52" s="81" t="s">
         <v>211</v>
       </c>
@@ -7385,10 +7396,10 @@
       <c r="J53" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="K53" s="209" t="s">
+      <c r="K53" s="196" t="s">
         <v>204</v>
       </c>
-      <c r="L53" s="209"/>
+      <c r="L53" s="196"/>
       <c r="M53" s="81" t="s">
         <v>211</v>
       </c>
@@ -7406,10 +7417,10 @@
       <c r="J54" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="K54" s="209" t="s">
+      <c r="K54" s="196" t="s">
         <v>205</v>
       </c>
-      <c r="L54" s="213"/>
+      <c r="L54" s="197"/>
       <c r="M54" s="81" t="s">
         <v>211</v>
       </c>
@@ -7427,10 +7438,10 @@
       <c r="J55" s="80" t="s">
         <v>198</v>
       </c>
-      <c r="K55" s="209" t="s">
+      <c r="K55" s="196" t="s">
         <v>206</v>
       </c>
-      <c r="L55" s="213"/>
+      <c r="L55" s="197"/>
       <c r="M55" s="81" t="s">
         <v>212</v>
       </c>
@@ -7448,10 +7459,10 @@
       <c r="J56" s="80" t="s">
         <v>199</v>
       </c>
-      <c r="K56" s="209" t="s">
+      <c r="K56" s="196" t="s">
         <v>207</v>
       </c>
-      <c r="L56" s="213"/>
+      <c r="L56" s="197"/>
       <c r="M56" s="81" t="s">
         <v>213</v>
       </c>
@@ -7469,10 +7480,10 @@
       <c r="J57" s="80" t="s">
         <v>200</v>
       </c>
-      <c r="K57" s="209" t="s">
+      <c r="K57" s="196" t="s">
         <v>208</v>
       </c>
-      <c r="L57" s="213"/>
+      <c r="L57" s="197"/>
       <c r="M57" s="81" t="s">
         <v>213</v>
       </c>
@@ -7528,10 +7539,10 @@
       <c r="J60" s="100" t="s">
         <v>249</v>
       </c>
-      <c r="K60" s="215" t="s">
+      <c r="K60" s="199" t="s">
         <v>253</v>
       </c>
-      <c r="L60" s="216"/>
+      <c r="L60" s="200"/>
       <c r="M60" s="81"/>
       <c r="O60" s="10"/>
     </row>
@@ -7547,10 +7558,10 @@
       <c r="J61" s="80" t="s">
         <v>201</v>
       </c>
-      <c r="K61" s="209" t="s">
+      <c r="K61" s="196" t="s">
         <v>209</v>
       </c>
-      <c r="L61" s="213"/>
+      <c r="L61" s="197"/>
       <c r="M61" s="81"/>
       <c r="O61" s="10"/>
     </row>
@@ -7693,7 +7704,7 @@
     </row>
     <row r="71" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="H71" s="11"/>
-      <c r="J71" s="209" t="s">
+      <c r="J71" s="196" t="s">
         <v>88</v>
       </c>
       <c r="K71" s="23" t="s">
@@ -7709,7 +7720,7 @@
     <row r="72" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A72" s="11"/>
       <c r="H72" s="11"/>
-      <c r="J72" s="209"/>
+      <c r="J72" s="196"/>
       <c r="K72" s="23" t="s">
         <v>183</v>
       </c>
@@ -7788,7 +7799,7 @@
       <c r="A78" s="11"/>
       <c r="H78" s="11"/>
       <c r="I78" s="2"/>
-      <c r="J78" s="209" t="s">
+      <c r="J78" s="196" t="s">
         <v>88</v>
       </c>
       <c r="K78" s="23" t="s">
@@ -7805,7 +7816,7 @@
       <c r="A79" s="11"/>
       <c r="H79" s="11"/>
       <c r="I79" s="2"/>
-      <c r="J79" s="209"/>
+      <c r="J79" s="196"/>
       <c r="K79" s="23" t="s">
         <v>110</v>
       </c>
@@ -7851,22 +7862,23 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="K53:L53"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J23:J28"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="A1:H4"/>
+    <mergeCell ref="N3:O4"/>
+    <mergeCell ref="P3:Q4"/>
+    <mergeCell ref="N1:O2"/>
+    <mergeCell ref="P1:Q2"/>
+    <mergeCell ref="I3:J4"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="M3:M4"/>
     <mergeCell ref="J71:J72"/>
     <mergeCell ref="J78:J79"/>
     <mergeCell ref="K1:K2"/>
@@ -7883,23 +7895,22 @@
     <mergeCell ref="L36:M36"/>
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="L37:M37"/>
-    <mergeCell ref="A1:H4"/>
-    <mergeCell ref="N3:O4"/>
-    <mergeCell ref="P3:Q4"/>
-    <mergeCell ref="N1:O2"/>
-    <mergeCell ref="P1:Q2"/>
-    <mergeCell ref="I3:J4"/>
-    <mergeCell ref="I1:J2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J23:J28"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="K61:L61"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="K60:L60"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/設計/部品在庫管理/機能仕様書_部品在庫照会API.xlsx
+++ b/docs/設計/部品在庫管理/機能仕様書_部品在庫照会API.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usaposu\git\Java-apiCourse-staffservice\docs\設計\部品在庫管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A809E2-4458-46CA-8F17-D5CE8DA154B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDF4E12-2A3D-4766-B596-D1C2C192131B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,14 +25,14 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">リクエスト!$A$1:$AA$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">レスポンス!$A$1:$V$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">機能概要!$A$1:$AH$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">処理詳細!$A$1:$Q$80</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">処理詳細!$A$1:$Q$74</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="253">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -899,179 +899,10 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>トランザクションID</t>
-  </si>
-  <si>
-    <t>UUID v4 形式</t>
-  </si>
-  <si>
-    <t>123e4567-e89b-12d3-a456-426614174000</t>
-  </si>
-  <si>
     <t>　リクエストトレーシング（必須）</t>
     <rPh sb="13" eb="15">
       <t>ヒッス</t>
     </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>TransactionId</t>
-  </si>
-  <si>
-    <t>トランザクションID</t>
-    <phoneticPr fontId="11"/>
-  </si>
-  <si>
-    <t>Transaction_id</t>
-  </si>
-  <si>
-    <t>Transaction_id = NULL</t>
-  </si>
-  <si>
-    <t>Transaction_idは必須項目です。</t>
-    <rPh sb="15" eb="17">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>コウモク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>管理者ID</t>
-    <rPh sb="0" eb="3">
-      <t>カンリシャ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>管理者情報テーブル.管理者ID</t>
-    <rPh sb="0" eb="3">
-      <t>カンリシャ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>カンリシャ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>管理者名</t>
-    <rPh sb="0" eb="3">
-      <t>カンリシャ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>管理者情報テーブル.管理者名</t>
-    <rPh sb="0" eb="3">
-      <t>カンリシャ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>カンリシャ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>管理者メアド</t>
-    <rPh sb="0" eb="3">
-      <t>カンリシャ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>管理者情報テーブル.メールアドレス</t>
-    <rPh sb="0" eb="3">
-      <t>カンリシャ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジョウホウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>管理者IDが指定リストに含まれる場合に絞り込み</t>
-    <rPh sb="0" eb="3">
-      <t>カンリシャ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>シボ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>コ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>管理者名が指定リストに含まれる場合に絞り込み</t>
-    <rPh sb="0" eb="4">
-      <t>カンリシャメイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>シボ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>コ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>管理者メールアドレスが指定リストに含まれる場合に絞り込み</t>
-    <rPh sb="0" eb="3">
-      <t>カンリシャ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>シボ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>コ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>Transaction-id</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>"id": 123,"name": "Taro Yamada","email": "taro@example.com"</t>
     <phoneticPr fontId="13"/>
   </si>
   <si>
@@ -1117,49 +948,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>【処理詳細シート】パラメータ設定にTransactionIDを追加/入力チェックにTransaction_idを追加/部品在庫検索に管理者ID,管理者名、管理者メアドを追加</t>
-    <rPh sb="1" eb="3">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>ブヒン</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>ザイコ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="66" eb="69">
-      <t>カンリシャ</t>
-    </rPh>
-    <rPh sb="72" eb="75">
-      <t>カンリシャ</t>
-    </rPh>
-    <rPh sb="75" eb="76">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="77" eb="80">
-      <t>カンリシャ</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>【シーケンスシート】シーケンス図に管理者情報検索/管理者データを追加</t>
     <rPh sb="15" eb="16">
       <t>ズ</t>
@@ -1188,6 +976,57 @@
   <si>
     <t>2025/10/5</t>
     <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>Transaction-id</t>
+  </si>
+  <si>
+    <t>UUID v4 形式</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>固定長</t>
+    <rPh sb="0" eb="3">
+      <t>コテイチョウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>Transaction-id</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>○</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>トランザクションID</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>"123e4567-e89b-12d3-a456-426614174000"</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>　TransactionId</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>【処理詳細シート】ヘッダーにTransactionIDを追加</t>
+    <rPh sb="1" eb="3">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
   </si>
 </sst>
 </file>
@@ -1338,7 +1177,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1504,6 +1343,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1516,7 +1366,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="218">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1769,372 +1619,351 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2153,22 +1982,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2985,73 +2802,65 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.8">
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="90" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="87">
+      <c r="C4" s="85">
         <v>45935</v>
       </c>
       <c r="D4" s="75" t="s">
         <v>233</v>
       </c>
-      <c r="E4" s="85" t="s">
-        <v>256</v>
+      <c r="E4" s="84" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.8">
-      <c r="B5" s="86" t="s">
-        <v>232</v>
-      </c>
-      <c r="C5" s="87">
+      <c r="B5" s="91"/>
+      <c r="C5" s="85">
         <v>45935</v>
       </c>
       <c r="D5" s="75" t="s">
         <v>233</v>
       </c>
-      <c r="E5" s="85" t="s">
-        <v>257</v>
+      <c r="E5" s="84" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.8">
-      <c r="B6" s="86" t="s">
-        <v>232</v>
-      </c>
-      <c r="C6" s="87">
+      <c r="B6" s="91"/>
+      <c r="C6" s="85">
         <v>45935</v>
       </c>
       <c r="D6" s="75" t="s">
         <v>233</v>
       </c>
-      <c r="E6" s="85" t="s">
-        <v>258</v>
+      <c r="E6" s="84" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.8">
-      <c r="B7" s="86" t="s">
-        <v>232</v>
-      </c>
-      <c r="C7" s="87">
+      <c r="B7" s="91"/>
+      <c r="C7" s="85">
         <v>45935</v>
       </c>
       <c r="D7" s="75" t="s">
         <v>233</v>
       </c>
-      <c r="E7" s="85" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="33" x14ac:dyDescent="0.8">
-      <c r="B8" s="86" t="s">
-        <v>232</v>
-      </c>
-      <c r="C8" s="87">
+      <c r="E7" s="84" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.8">
+      <c r="B8" s="92"/>
+      <c r="C8" s="85">
         <v>45935</v>
       </c>
       <c r="D8" s="75" t="s">
         <v>233</v>
       </c>
-      <c r="E8" s="85" t="s">
-        <v>259</v>
+      <c r="E8" s="84" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.8">
@@ -3421,6 +3230,9 @@
       <c r="E69" s="26"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B4:B8"/>
+  </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3439,452 +3251,452 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="128" t="s">
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="129"/>
-      <c r="N1" s="129"/>
-      <c r="O1" s="129"/>
-      <c r="P1" s="130"/>
-      <c r="Q1" s="134" t="s">
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="135"/>
-      <c r="S1" s="135"/>
-      <c r="T1" s="135"/>
-      <c r="U1" s="135"/>
-      <c r="V1" s="138" t="s">
+      <c r="R1" s="127"/>
+      <c r="S1" s="127"/>
+      <c r="T1" s="127"/>
+      <c r="U1" s="127"/>
+      <c r="V1" s="130" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="138"/>
-      <c r="X1" s="138"/>
-      <c r="Y1" s="149" t="s">
+      <c r="W1" s="130"/>
+      <c r="X1" s="130"/>
+      <c r="Y1" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="150"/>
-      <c r="AA1" s="150"/>
-      <c r="AB1" s="151"/>
-      <c r="AC1" s="143" t="s">
+      <c r="Z1" s="143"/>
+      <c r="AA1" s="143"/>
+      <c r="AB1" s="144"/>
+      <c r="AC1" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="AD1" s="144"/>
-      <c r="AE1" s="145"/>
-      <c r="AF1" s="139" t="s">
+      <c r="AD1" s="136"/>
+      <c r="AE1" s="137"/>
+      <c r="AF1" s="141" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="140"/>
-      <c r="AH1" s="140"/>
+      <c r="AG1" s="132"/>
+      <c r="AH1" s="132"/>
     </row>
     <row r="2" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="122"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="123"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="131"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
-      <c r="P2" s="133"/>
-      <c r="Q2" s="136"/>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
-      <c r="U2" s="137"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="138"/>
-      <c r="Y2" s="152"/>
-      <c r="Z2" s="153"/>
-      <c r="AA2" s="153"/>
-      <c r="AB2" s="154"/>
-      <c r="AC2" s="146"/>
-      <c r="AD2" s="147"/>
-      <c r="AE2" s="148"/>
-      <c r="AF2" s="141"/>
-      <c r="AG2" s="142"/>
-      <c r="AH2" s="142"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="124"/>
+      <c r="N2" s="124"/>
+      <c r="O2" s="124"/>
+      <c r="P2" s="125"/>
+      <c r="Q2" s="128"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="130"/>
+      <c r="W2" s="130"/>
+      <c r="X2" s="130"/>
+      <c r="Y2" s="145"/>
+      <c r="Z2" s="146"/>
+      <c r="AA2" s="146"/>
+      <c r="AB2" s="147"/>
+      <c r="AC2" s="138"/>
+      <c r="AD2" s="139"/>
+      <c r="AE2" s="140"/>
+      <c r="AF2" s="133"/>
+      <c r="AG2" s="134"/>
+      <c r="AH2" s="134"/>
     </row>
     <row r="3" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A3" s="122"/>
-      <c r="B3" s="123"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="123"/>
-      <c r="F3" s="123"/>
-      <c r="G3" s="123"/>
-      <c r="H3" s="123"/>
-      <c r="I3" s="123"/>
-      <c r="J3" s="123"/>
-      <c r="K3" s="124"/>
-      <c r="L3" s="128" t="s">
+      <c r="A3" s="114"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="116"/>
+      <c r="L3" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="129"/>
-      <c r="N3" s="129"/>
-      <c r="O3" s="129"/>
-      <c r="P3" s="130"/>
-      <c r="Q3" s="134" t="s">
+      <c r="M3" s="121"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="121"/>
+      <c r="P3" s="122"/>
+      <c r="Q3" s="126" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="135"/>
-      <c r="S3" s="135"/>
-      <c r="T3" s="135"/>
-      <c r="U3" s="135"/>
-      <c r="V3" s="138" t="s">
+      <c r="R3" s="127"/>
+      <c r="S3" s="127"/>
+      <c r="T3" s="127"/>
+      <c r="U3" s="127"/>
+      <c r="V3" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="W3" s="138"/>
-      <c r="X3" s="138"/>
-      <c r="Y3" s="149" t="s">
+      <c r="W3" s="130"/>
+      <c r="X3" s="130"/>
+      <c r="Y3" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="Z3" s="150"/>
-      <c r="AA3" s="150"/>
-      <c r="AB3" s="151"/>
-      <c r="AC3" s="138" t="s">
+      <c r="Z3" s="143"/>
+      <c r="AA3" s="143"/>
+      <c r="AB3" s="144"/>
+      <c r="AC3" s="130" t="s">
         <v>16</v>
       </c>
-      <c r="AD3" s="138"/>
-      <c r="AE3" s="138"/>
-      <c r="AF3" s="217" t="s">
-        <v>261</v>
-      </c>
-      <c r="AG3" s="140"/>
-      <c r="AH3" s="140"/>
+      <c r="AD3" s="130"/>
+      <c r="AE3" s="130"/>
+      <c r="AF3" s="131" t="s">
+        <v>241</v>
+      </c>
+      <c r="AG3" s="132"/>
+      <c r="AH3" s="132"/>
     </row>
     <row r="4" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A4" s="125"/>
-      <c r="B4" s="126"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="126"/>
-      <c r="I4" s="126"/>
-      <c r="J4" s="126"/>
-      <c r="K4" s="127"/>
-      <c r="L4" s="131"/>
-      <c r="M4" s="132"/>
-      <c r="N4" s="132"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="133"/>
-      <c r="Q4" s="136"/>
-      <c r="R4" s="137"/>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137"/>
-      <c r="V4" s="138"/>
-      <c r="W4" s="138"/>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="152"/>
-      <c r="Z4" s="153"/>
-      <c r="AA4" s="153"/>
-      <c r="AB4" s="154"/>
-      <c r="AC4" s="138"/>
-      <c r="AD4" s="138"/>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="141"/>
-      <c r="AG4" s="142"/>
-      <c r="AH4" s="142"/>
+      <c r="A4" s="117"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
+      <c r="L4" s="123"/>
+      <c r="M4" s="124"/>
+      <c r="N4" s="124"/>
+      <c r="O4" s="124"/>
+      <c r="P4" s="125"/>
+      <c r="Q4" s="128"/>
+      <c r="R4" s="129"/>
+      <c r="S4" s="129"/>
+      <c r="T4" s="129"/>
+      <c r="U4" s="129"/>
+      <c r="V4" s="130"/>
+      <c r="W4" s="130"/>
+      <c r="X4" s="130"/>
+      <c r="Y4" s="145"/>
+      <c r="Z4" s="146"/>
+      <c r="AA4" s="146"/>
+      <c r="AB4" s="147"/>
+      <c r="AC4" s="130"/>
+      <c r="AD4" s="130"/>
+      <c r="AE4" s="130"/>
+      <c r="AF4" s="133"/>
+      <c r="AG4" s="134"/>
+      <c r="AH4" s="134"/>
     </row>
     <row r="5" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A5" s="104" t="s">
+      <c r="A5" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="105"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="107" t="s">
+      <c r="B5" s="97"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
-      <c r="L5" s="108"/>
-      <c r="M5" s="108"/>
-      <c r="N5" s="108"/>
-      <c r="O5" s="108"/>
-      <c r="P5" s="108"/>
-      <c r="Q5" s="108"/>
-      <c r="R5" s="108"/>
-      <c r="S5" s="108"/>
-      <c r="T5" s="108"/>
-      <c r="U5" s="108"/>
-      <c r="V5" s="108"/>
-      <c r="W5" s="108"/>
-      <c r="X5" s="108"/>
-      <c r="Y5" s="108"/>
-      <c r="Z5" s="108"/>
-      <c r="AA5" s="108"/>
-      <c r="AB5" s="108"/>
-      <c r="AC5" s="108"/>
-      <c r="AD5" s="108"/>
-      <c r="AE5" s="108"/>
-      <c r="AF5" s="108"/>
-      <c r="AG5" s="108"/>
-      <c r="AH5" s="108"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="100"/>
+      <c r="K5" s="100"/>
+      <c r="L5" s="100"/>
+      <c r="M5" s="100"/>
+      <c r="N5" s="100"/>
+      <c r="O5" s="100"/>
+      <c r="P5" s="100"/>
+      <c r="Q5" s="100"/>
+      <c r="R5" s="100"/>
+      <c r="S5" s="100"/>
+      <c r="T5" s="100"/>
+      <c r="U5" s="100"/>
+      <c r="V5" s="100"/>
+      <c r="W5" s="100"/>
+      <c r="X5" s="100"/>
+      <c r="Y5" s="100"/>
+      <c r="Z5" s="100"/>
+      <c r="AA5" s="100"/>
+      <c r="AB5" s="100"/>
+      <c r="AC5" s="100"/>
+      <c r="AD5" s="100"/>
+      <c r="AE5" s="100"/>
+      <c r="AF5" s="100"/>
+      <c r="AG5" s="100"/>
+      <c r="AH5" s="100"/>
     </row>
     <row r="6" spans="1:34" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A6" s="104" t="s">
+      <c r="A6" s="96" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="105"/>
-      <c r="C6" s="105"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="109" t="s">
+      <c r="B6" s="97"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="101" t="s">
         <v>196</v>
       </c>
-      <c r="I6" s="108"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="108"/>
-      <c r="L6" s="108"/>
-      <c r="M6" s="108"/>
-      <c r="N6" s="108"/>
-      <c r="O6" s="108"/>
-      <c r="P6" s="108"/>
-      <c r="Q6" s="108"/>
-      <c r="R6" s="108"/>
-      <c r="S6" s="108"/>
-      <c r="T6" s="108"/>
-      <c r="U6" s="108"/>
-      <c r="V6" s="108"/>
-      <c r="W6" s="108"/>
-      <c r="X6" s="108"/>
-      <c r="Y6" s="108"/>
-      <c r="Z6" s="108"/>
-      <c r="AA6" s="108"/>
-      <c r="AB6" s="108"/>
-      <c r="AC6" s="108"/>
-      <c r="AD6" s="108"/>
-      <c r="AE6" s="108"/>
-      <c r="AF6" s="108"/>
-      <c r="AG6" s="108"/>
-      <c r="AH6" s="108"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="100"/>
+      <c r="L6" s="100"/>
+      <c r="M6" s="100"/>
+      <c r="N6" s="100"/>
+      <c r="O6" s="100"/>
+      <c r="P6" s="100"/>
+      <c r="Q6" s="100"/>
+      <c r="R6" s="100"/>
+      <c r="S6" s="100"/>
+      <c r="T6" s="100"/>
+      <c r="U6" s="100"/>
+      <c r="V6" s="100"/>
+      <c r="W6" s="100"/>
+      <c r="X6" s="100"/>
+      <c r="Y6" s="100"/>
+      <c r="Z6" s="100"/>
+      <c r="AA6" s="100"/>
+      <c r="AB6" s="100"/>
+      <c r="AC6" s="100"/>
+      <c r="AD6" s="100"/>
+      <c r="AE6" s="100"/>
+      <c r="AF6" s="100"/>
+      <c r="AG6" s="100"/>
+      <c r="AH6" s="100"/>
     </row>
     <row r="7" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A7" s="104" t="s">
+      <c r="A7" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="105"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="107" t="s">
+      <c r="B7" s="97"/>
+      <c r="C7" s="97"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="108"/>
-      <c r="J7" s="108"/>
-      <c r="K7" s="108"/>
-      <c r="L7" s="108"/>
-      <c r="M7" s="108"/>
-      <c r="N7" s="108"/>
-      <c r="O7" s="108"/>
-      <c r="P7" s="108"/>
-      <c r="Q7" s="108"/>
-      <c r="R7" s="108"/>
-      <c r="S7" s="108"/>
-      <c r="T7" s="108"/>
-      <c r="U7" s="108"/>
-      <c r="V7" s="108"/>
-      <c r="W7" s="108"/>
-      <c r="X7" s="108"/>
-      <c r="Y7" s="108"/>
-      <c r="Z7" s="108"/>
-      <c r="AA7" s="108"/>
-      <c r="AB7" s="108"/>
-      <c r="AC7" s="108"/>
-      <c r="AD7" s="108"/>
-      <c r="AE7" s="108"/>
-      <c r="AF7" s="108"/>
-      <c r="AG7" s="108"/>
-      <c r="AH7" s="108"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
+      <c r="L7" s="100"/>
+      <c r="M7" s="100"/>
+      <c r="N7" s="100"/>
+      <c r="O7" s="100"/>
+      <c r="P7" s="100"/>
+      <c r="Q7" s="100"/>
+      <c r="R7" s="100"/>
+      <c r="S7" s="100"/>
+      <c r="T7" s="100"/>
+      <c r="U7" s="100"/>
+      <c r="V7" s="100"/>
+      <c r="W7" s="100"/>
+      <c r="X7" s="100"/>
+      <c r="Y7" s="100"/>
+      <c r="Z7" s="100"/>
+      <c r="AA7" s="100"/>
+      <c r="AB7" s="100"/>
+      <c r="AC7" s="100"/>
+      <c r="AD7" s="100"/>
+      <c r="AE7" s="100"/>
+      <c r="AF7" s="100"/>
+      <c r="AG7" s="100"/>
+      <c r="AH7" s="100"/>
     </row>
     <row r="8" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A8" s="104" t="s">
+      <c r="A8" s="96" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="105"/>
-      <c r="C8" s="105"/>
-      <c r="D8" s="105"/>
-      <c r="E8" s="105"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="107" t="s">
+      <c r="B8" s="97"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="108"/>
-      <c r="J8" s="108"/>
-      <c r="K8" s="108"/>
-      <c r="L8" s="108"/>
-      <c r="M8" s="108"/>
-      <c r="N8" s="108"/>
-      <c r="O8" s="108"/>
-      <c r="P8" s="108"/>
-      <c r="Q8" s="108"/>
-      <c r="R8" s="108"/>
-      <c r="S8" s="108"/>
-      <c r="T8" s="108"/>
-      <c r="U8" s="108"/>
-      <c r="V8" s="108"/>
-      <c r="W8" s="108"/>
-      <c r="X8" s="108"/>
-      <c r="Y8" s="108"/>
-      <c r="Z8" s="108"/>
-      <c r="AA8" s="108"/>
-      <c r="AB8" s="108"/>
-      <c r="AC8" s="108"/>
-      <c r="AD8" s="108"/>
-      <c r="AE8" s="108"/>
-      <c r="AF8" s="108"/>
-      <c r="AG8" s="108"/>
-      <c r="AH8" s="108"/>
+      <c r="I8" s="100"/>
+      <c r="J8" s="100"/>
+      <c r="K8" s="100"/>
+      <c r="L8" s="100"/>
+      <c r="M8" s="100"/>
+      <c r="N8" s="100"/>
+      <c r="O8" s="100"/>
+      <c r="P8" s="100"/>
+      <c r="Q8" s="100"/>
+      <c r="R8" s="100"/>
+      <c r="S8" s="100"/>
+      <c r="T8" s="100"/>
+      <c r="U8" s="100"/>
+      <c r="V8" s="100"/>
+      <c r="W8" s="100"/>
+      <c r="X8" s="100"/>
+      <c r="Y8" s="100"/>
+      <c r="Z8" s="100"/>
+      <c r="AA8" s="100"/>
+      <c r="AB8" s="100"/>
+      <c r="AC8" s="100"/>
+      <c r="AD8" s="100"/>
+      <c r="AE8" s="100"/>
+      <c r="AF8" s="100"/>
+      <c r="AG8" s="100"/>
+      <c r="AH8" s="100"/>
     </row>
     <row r="9" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A9" s="104" t="s">
+      <c r="A9" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="105"/>
-      <c r="C9" s="105"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="107" t="s">
+      <c r="B9" s="97"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="108"/>
-      <c r="J9" s="108"/>
-      <c r="K9" s="108"/>
-      <c r="L9" s="108"/>
-      <c r="M9" s="108"/>
-      <c r="N9" s="108"/>
-      <c r="O9" s="108"/>
-      <c r="P9" s="108"/>
-      <c r="Q9" s="108"/>
-      <c r="R9" s="108"/>
-      <c r="S9" s="108"/>
-      <c r="T9" s="108"/>
-      <c r="U9" s="108"/>
-      <c r="V9" s="108"/>
-      <c r="W9" s="108"/>
-      <c r="X9" s="108"/>
-      <c r="Y9" s="108"/>
-      <c r="Z9" s="108"/>
-      <c r="AA9" s="108"/>
-      <c r="AB9" s="108"/>
-      <c r="AC9" s="108"/>
-      <c r="AD9" s="108"/>
-      <c r="AE9" s="108"/>
-      <c r="AF9" s="108"/>
-      <c r="AG9" s="108"/>
-      <c r="AH9" s="108"/>
+      <c r="I9" s="100"/>
+      <c r="J9" s="100"/>
+      <c r="K9" s="100"/>
+      <c r="L9" s="100"/>
+      <c r="M9" s="100"/>
+      <c r="N9" s="100"/>
+      <c r="O9" s="100"/>
+      <c r="P9" s="100"/>
+      <c r="Q9" s="100"/>
+      <c r="R9" s="100"/>
+      <c r="S9" s="100"/>
+      <c r="T9" s="100"/>
+      <c r="U9" s="100"/>
+      <c r="V9" s="100"/>
+      <c r="W9" s="100"/>
+      <c r="X9" s="100"/>
+      <c r="Y9" s="100"/>
+      <c r="Z9" s="100"/>
+      <c r="AA9" s="100"/>
+      <c r="AB9" s="100"/>
+      <c r="AC9" s="100"/>
+      <c r="AD9" s="100"/>
+      <c r="AE9" s="100"/>
+      <c r="AF9" s="100"/>
+      <c r="AG9" s="100"/>
+      <c r="AH9" s="100"/>
     </row>
     <row r="10" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A10" s="110" t="s">
+      <c r="A10" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="111"/>
-      <c r="C10" s="111"/>
-      <c r="D10" s="111"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="111"/>
-      <c r="G10" s="112"/>
-      <c r="H10" s="113" t="s">
+      <c r="B10" s="103"/>
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="I10" s="114"/>
-      <c r="J10" s="114"/>
-      <c r="K10" s="114"/>
-      <c r="L10" s="114"/>
-      <c r="M10" s="114"/>
-      <c r="N10" s="114"/>
-      <c r="O10" s="114"/>
-      <c r="P10" s="114"/>
-      <c r="Q10" s="114"/>
-      <c r="R10" s="114"/>
-      <c r="S10" s="114"/>
-      <c r="T10" s="114"/>
-      <c r="U10" s="114"/>
-      <c r="V10" s="114"/>
-      <c r="W10" s="114"/>
-      <c r="X10" s="114"/>
-      <c r="Y10" s="114"/>
-      <c r="Z10" s="114"/>
-      <c r="AA10" s="114"/>
-      <c r="AB10" s="114"/>
-      <c r="AC10" s="114"/>
-      <c r="AD10" s="114"/>
-      <c r="AE10" s="114"/>
-      <c r="AF10" s="114"/>
-      <c r="AG10" s="114"/>
-      <c r="AH10" s="114"/>
+      <c r="I10" s="106"/>
+      <c r="J10" s="106"/>
+      <c r="K10" s="106"/>
+      <c r="L10" s="106"/>
+      <c r="M10" s="106"/>
+      <c r="N10" s="106"/>
+      <c r="O10" s="106"/>
+      <c r="P10" s="106"/>
+      <c r="Q10" s="106"/>
+      <c r="R10" s="106"/>
+      <c r="S10" s="106"/>
+      <c r="T10" s="106"/>
+      <c r="U10" s="106"/>
+      <c r="V10" s="106"/>
+      <c r="W10" s="106"/>
+      <c r="X10" s="106"/>
+      <c r="Y10" s="106"/>
+      <c r="Z10" s="106"/>
+      <c r="AA10" s="106"/>
+      <c r="AB10" s="106"/>
+      <c r="AC10" s="106"/>
+      <c r="AD10" s="106"/>
+      <c r="AE10" s="106"/>
+      <c r="AF10" s="106"/>
+      <c r="AG10" s="106"/>
+      <c r="AH10" s="106"/>
     </row>
     <row r="11" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A11" s="155" t="s">
+      <c r="A11" s="148" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="156"/>
-      <c r="C11" s="156"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
-      <c r="F11" s="156"/>
-      <c r="G11" s="156"/>
-      <c r="H11" s="156"/>
-      <c r="I11" s="156"/>
-      <c r="J11" s="156"/>
-      <c r="K11" s="156"/>
-      <c r="L11" s="156"/>
-      <c r="M11" s="156"/>
-      <c r="N11" s="156"/>
-      <c r="O11" s="156"/>
-      <c r="P11" s="156"/>
-      <c r="Q11" s="156"/>
-      <c r="R11" s="156"/>
-      <c r="S11" s="156"/>
-      <c r="T11" s="156"/>
-      <c r="U11" s="156"/>
-      <c r="V11" s="156"/>
-      <c r="W11" s="156"/>
-      <c r="X11" s="156"/>
-      <c r="Y11" s="156"/>
-      <c r="Z11" s="156"/>
-      <c r="AA11" s="156"/>
-      <c r="AB11" s="156"/>
-      <c r="AC11" s="156"/>
-      <c r="AD11" s="156"/>
-      <c r="AE11" s="156"/>
-      <c r="AF11" s="156"/>
-      <c r="AG11" s="156"/>
-      <c r="AH11" s="156"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="149"/>
+      <c r="D11" s="149"/>
+      <c r="E11" s="149"/>
+      <c r="F11" s="149"/>
+      <c r="G11" s="149"/>
+      <c r="H11" s="149"/>
+      <c r="I11" s="149"/>
+      <c r="J11" s="149"/>
+      <c r="K11" s="149"/>
+      <c r="L11" s="149"/>
+      <c r="M11" s="149"/>
+      <c r="N11" s="149"/>
+      <c r="O11" s="149"/>
+      <c r="P11" s="149"/>
+      <c r="Q11" s="149"/>
+      <c r="R11" s="149"/>
+      <c r="S11" s="149"/>
+      <c r="T11" s="149"/>
+      <c r="U11" s="149"/>
+      <c r="V11" s="149"/>
+      <c r="W11" s="149"/>
+      <c r="X11" s="149"/>
+      <c r="Y11" s="149"/>
+      <c r="Z11" s="149"/>
+      <c r="AA11" s="149"/>
+      <c r="AB11" s="149"/>
+      <c r="AC11" s="149"/>
+      <c r="AD11" s="149"/>
+      <c r="AE11" s="149"/>
+      <c r="AF11" s="149"/>
+      <c r="AG11" s="149"/>
+      <c r="AH11" s="149"/>
     </row>
     <row r="12" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A12" s="61"/>
@@ -3956,20 +3768,20 @@
       <c r="AH23" s="58"/>
     </row>
     <row r="24" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A24" s="115" t="s">
+      <c r="A24" s="107" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="116"/>
-      <c r="C24" s="115" t="s">
+      <c r="B24" s="108"/>
+      <c r="C24" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="117"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="117"/>
-      <c r="G24" s="117"/>
-      <c r="H24" s="117"/>
-      <c r="I24" s="117"/>
-      <c r="J24" s="116"/>
+      <c r="D24" s="109"/>
+      <c r="E24" s="109"/>
+      <c r="F24" s="109"/>
+      <c r="G24" s="109"/>
+      <c r="H24" s="109"/>
+      <c r="I24" s="109"/>
+      <c r="J24" s="108"/>
       <c r="K24" s="66" t="s">
         <v>30</v>
       </c>
@@ -3982,34 +3794,34 @@
       <c r="N24" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="O24" s="118" t="s">
+      <c r="O24" s="110" t="s">
         <v>34</v>
       </c>
-      <c r="P24" s="118"/>
-      <c r="Q24" s="118"/>
-      <c r="R24" s="118"/>
-      <c r="S24" s="118"/>
-      <c r="T24" s="118"/>
-      <c r="U24" s="118"/>
-      <c r="V24" s="118"/>
-      <c r="W24" s="118"/>
-      <c r="X24" s="118"/>
-      <c r="Y24" s="118"/>
-      <c r="Z24" s="118"/>
-      <c r="AA24" s="118"/>
-      <c r="AB24" s="118"/>
-      <c r="AC24" s="118"/>
-      <c r="AD24" s="118"/>
-      <c r="AE24" s="118"/>
-      <c r="AF24" s="118"/>
-      <c r="AG24" s="118"/>
-      <c r="AH24" s="118"/>
+      <c r="P24" s="110"/>
+      <c r="Q24" s="110"/>
+      <c r="R24" s="110"/>
+      <c r="S24" s="110"/>
+      <c r="T24" s="110"/>
+      <c r="U24" s="110"/>
+      <c r="V24" s="110"/>
+      <c r="W24" s="110"/>
+      <c r="X24" s="110"/>
+      <c r="Y24" s="110"/>
+      <c r="Z24" s="110"/>
+      <c r="AA24" s="110"/>
+      <c r="AB24" s="110"/>
+      <c r="AC24" s="110"/>
+      <c r="AD24" s="110"/>
+      <c r="AE24" s="110"/>
+      <c r="AF24" s="110"/>
+      <c r="AG24" s="110"/>
+      <c r="AH24" s="110"/>
     </row>
     <row r="25" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A25" s="101">
+      <c r="A25" s="93">
         <v>1</v>
       </c>
-      <c r="B25" s="102"/>
+      <c r="B25" s="94"/>
       <c r="C25" s="64" t="s">
         <v>35</v>
       </c>
@@ -4026,32 +3838,32 @@
       <c r="L25" s="67"/>
       <c r="M25" s="67"/>
       <c r="N25" s="64"/>
-      <c r="O25" s="103"/>
-      <c r="P25" s="103"/>
-      <c r="Q25" s="103"/>
-      <c r="R25" s="103"/>
-      <c r="S25" s="103"/>
-      <c r="T25" s="103"/>
-      <c r="U25" s="103"/>
-      <c r="V25" s="103"/>
-      <c r="W25" s="103"/>
-      <c r="X25" s="103"/>
-      <c r="Y25" s="103"/>
-      <c r="Z25" s="103"/>
-      <c r="AA25" s="103"/>
-      <c r="AB25" s="103"/>
-      <c r="AC25" s="103"/>
-      <c r="AD25" s="103"/>
-      <c r="AE25" s="103"/>
-      <c r="AF25" s="103"/>
-      <c r="AG25" s="103"/>
-      <c r="AH25" s="103"/>
+      <c r="O25" s="95"/>
+      <c r="P25" s="95"/>
+      <c r="Q25" s="95"/>
+      <c r="R25" s="95"/>
+      <c r="S25" s="95"/>
+      <c r="T25" s="95"/>
+      <c r="U25" s="95"/>
+      <c r="V25" s="95"/>
+      <c r="W25" s="95"/>
+      <c r="X25" s="95"/>
+      <c r="Y25" s="95"/>
+      <c r="Z25" s="95"/>
+      <c r="AA25" s="95"/>
+      <c r="AB25" s="95"/>
+      <c r="AC25" s="95"/>
+      <c r="AD25" s="95"/>
+      <c r="AE25" s="95"/>
+      <c r="AF25" s="95"/>
+      <c r="AG25" s="95"/>
+      <c r="AH25" s="95"/>
     </row>
     <row r="26" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A26" s="101">
+      <c r="A26" s="93">
         <v>2</v>
       </c>
-      <c r="B26" s="102"/>
+      <c r="B26" s="94"/>
       <c r="C26" s="78" t="s">
         <v>194</v>
       </c>
@@ -4068,32 +3880,32 @@
       <c r="L26" s="67"/>
       <c r="M26" s="67"/>
       <c r="N26" s="64"/>
-      <c r="O26" s="103"/>
-      <c r="P26" s="103"/>
-      <c r="Q26" s="103"/>
-      <c r="R26" s="103"/>
-      <c r="S26" s="103"/>
-      <c r="T26" s="103"/>
-      <c r="U26" s="103"/>
-      <c r="V26" s="103"/>
-      <c r="W26" s="103"/>
-      <c r="X26" s="103"/>
-      <c r="Y26" s="103"/>
-      <c r="Z26" s="103"/>
-      <c r="AA26" s="103"/>
-      <c r="AB26" s="103"/>
-      <c r="AC26" s="103"/>
-      <c r="AD26" s="103"/>
-      <c r="AE26" s="103"/>
-      <c r="AF26" s="103"/>
-      <c r="AG26" s="103"/>
-      <c r="AH26" s="103"/>
+      <c r="O26" s="95"/>
+      <c r="P26" s="95"/>
+      <c r="Q26" s="95"/>
+      <c r="R26" s="95"/>
+      <c r="S26" s="95"/>
+      <c r="T26" s="95"/>
+      <c r="U26" s="95"/>
+      <c r="V26" s="95"/>
+      <c r="W26" s="95"/>
+      <c r="X26" s="95"/>
+      <c r="Y26" s="95"/>
+      <c r="Z26" s="95"/>
+      <c r="AA26" s="95"/>
+      <c r="AB26" s="95"/>
+      <c r="AC26" s="95"/>
+      <c r="AD26" s="95"/>
+      <c r="AE26" s="95"/>
+      <c r="AF26" s="95"/>
+      <c r="AG26" s="95"/>
+      <c r="AH26" s="95"/>
     </row>
     <row r="27" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A27" s="101">
+      <c r="A27" s="93">
         <v>3</v>
       </c>
-      <c r="B27" s="102"/>
+      <c r="B27" s="94"/>
       <c r="C27" s="78" t="s">
         <v>195</v>
       </c>
@@ -4110,32 +3922,32 @@
       <c r="L27" s="67"/>
       <c r="M27" s="67"/>
       <c r="N27" s="64"/>
-      <c r="O27" s="103"/>
-      <c r="P27" s="103"/>
-      <c r="Q27" s="103"/>
-      <c r="R27" s="103"/>
-      <c r="S27" s="103"/>
-      <c r="T27" s="103"/>
-      <c r="U27" s="103"/>
-      <c r="V27" s="103"/>
-      <c r="W27" s="103"/>
-      <c r="X27" s="103"/>
-      <c r="Y27" s="103"/>
-      <c r="Z27" s="103"/>
-      <c r="AA27" s="103"/>
-      <c r="AB27" s="103"/>
-      <c r="AC27" s="103"/>
-      <c r="AD27" s="103"/>
-      <c r="AE27" s="103"/>
-      <c r="AF27" s="103"/>
-      <c r="AG27" s="103"/>
-      <c r="AH27" s="103"/>
+      <c r="O27" s="95"/>
+      <c r="P27" s="95"/>
+      <c r="Q27" s="95"/>
+      <c r="R27" s="95"/>
+      <c r="S27" s="95"/>
+      <c r="T27" s="95"/>
+      <c r="U27" s="95"/>
+      <c r="V27" s="95"/>
+      <c r="W27" s="95"/>
+      <c r="X27" s="95"/>
+      <c r="Y27" s="95"/>
+      <c r="Z27" s="95"/>
+      <c r="AA27" s="95"/>
+      <c r="AB27" s="95"/>
+      <c r="AC27" s="95"/>
+      <c r="AD27" s="95"/>
+      <c r="AE27" s="95"/>
+      <c r="AF27" s="95"/>
+      <c r="AG27" s="95"/>
+      <c r="AH27" s="95"/>
     </row>
     <row r="28" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A28" s="101">
+      <c r="A28" s="93">
         <v>4</v>
       </c>
-      <c r="B28" s="102"/>
+      <c r="B28" s="94"/>
       <c r="C28" s="78" t="s">
         <v>234</v>
       </c>
@@ -4152,26 +3964,26 @@
       <c r="L28" s="67"/>
       <c r="M28" s="67"/>
       <c r="N28" s="64"/>
-      <c r="O28" s="103"/>
-      <c r="P28" s="103"/>
-      <c r="Q28" s="103"/>
-      <c r="R28" s="103"/>
-      <c r="S28" s="103"/>
-      <c r="T28" s="103"/>
-      <c r="U28" s="103"/>
-      <c r="V28" s="103"/>
-      <c r="W28" s="103"/>
-      <c r="X28" s="103"/>
-      <c r="Y28" s="103"/>
-      <c r="Z28" s="103"/>
-      <c r="AA28" s="103"/>
-      <c r="AB28" s="103"/>
-      <c r="AC28" s="103"/>
-      <c r="AD28" s="103"/>
-      <c r="AE28" s="103"/>
-      <c r="AF28" s="103"/>
-      <c r="AG28" s="103"/>
-      <c r="AH28" s="103"/>
+      <c r="O28" s="95"/>
+      <c r="P28" s="95"/>
+      <c r="Q28" s="95"/>
+      <c r="R28" s="95"/>
+      <c r="S28" s="95"/>
+      <c r="T28" s="95"/>
+      <c r="U28" s="95"/>
+      <c r="V28" s="95"/>
+      <c r="W28" s="95"/>
+      <c r="X28" s="95"/>
+      <c r="Y28" s="95"/>
+      <c r="Z28" s="95"/>
+      <c r="AA28" s="95"/>
+      <c r="AB28" s="95"/>
+      <c r="AC28" s="95"/>
+      <c r="AD28" s="95"/>
+      <c r="AE28" s="95"/>
+      <c r="AF28" s="95"/>
+      <c r="AG28" s="95"/>
+      <c r="AH28" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="37">
@@ -4241,138 +4053,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="171" t="s">
         <v>235</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="128" t="s">
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="129"/>
-      <c r="L1" s="129"/>
-      <c r="M1" s="129"/>
-      <c r="N1" s="130"/>
-      <c r="O1" s="134" t="s">
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
-      <c r="S1" s="135"/>
-      <c r="T1" s="138" t="s">
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="127"/>
+      <c r="S1" s="127"/>
+      <c r="T1" s="130" t="s">
         <v>3</v>
       </c>
-      <c r="U1" s="149" t="s">
+      <c r="U1" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="150"/>
-      <c r="W1" s="143" t="s">
+      <c r="V1" s="143"/>
+      <c r="W1" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="139" t="s">
+      <c r="X1" s="141" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="140"/>
+      <c r="Y1" s="132"/>
     </row>
     <row r="2" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="122"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="131"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="133"/>
-      <c r="O2" s="136"/>
-      <c r="P2" s="137"/>
-      <c r="Q2" s="137"/>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="152"/>
-      <c r="V2" s="153"/>
-      <c r="W2" s="146"/>
-      <c r="X2" s="141"/>
-      <c r="Y2" s="142"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="124"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="130"/>
+      <c r="U2" s="145"/>
+      <c r="V2" s="146"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="133"/>
+      <c r="Y2" s="134"/>
     </row>
     <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A3" s="122"/>
-      <c r="B3" s="123"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="123"/>
-      <c r="F3" s="123"/>
-      <c r="G3" s="123"/>
-      <c r="H3" s="123"/>
-      <c r="I3" s="123"/>
-      <c r="J3" s="128" t="s">
+      <c r="A3" s="114"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="130"/>
-      <c r="O3" s="134" t="s">
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="121"/>
+      <c r="N3" s="122"/>
+      <c r="O3" s="126" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="135"/>
-      <c r="Q3" s="135"/>
-      <c r="R3" s="135"/>
-      <c r="S3" s="135"/>
-      <c r="T3" s="138" t="s">
+      <c r="P3" s="127"/>
+      <c r="Q3" s="127"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="127"/>
+      <c r="T3" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="U3" s="149" t="s">
+      <c r="U3" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="V3" s="150"/>
-      <c r="W3" s="138" t="s">
+      <c r="V3" s="143"/>
+      <c r="W3" s="130" t="s">
         <v>16</v>
       </c>
-      <c r="X3" s="139">
+      <c r="X3" s="141">
         <v>45935</v>
       </c>
-      <c r="Y3" s="140"/>
+      <c r="Y3" s="132"/>
     </row>
     <row r="4" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A4" s="125"/>
-      <c r="B4" s="126"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="126"/>
-      <c r="I4" s="126"/>
-      <c r="J4" s="131"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="132"/>
-      <c r="N4" s="133"/>
-      <c r="O4" s="136"/>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137"/>
-      <c r="S4" s="137"/>
-      <c r="T4" s="138"/>
-      <c r="U4" s="152"/>
-      <c r="V4" s="153"/>
-      <c r="W4" s="138"/>
-      <c r="X4" s="141"/>
-      <c r="Y4" s="142"/>
+      <c r="A4" s="117"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="124"/>
+      <c r="N4" s="125"/>
+      <c r="O4" s="128"/>
+      <c r="P4" s="129"/>
+      <c r="Q4" s="129"/>
+      <c r="R4" s="129"/>
+      <c r="S4" s="129"/>
+      <c r="T4" s="130"/>
+      <c r="U4" s="145"/>
+      <c r="V4" s="146"/>
+      <c r="W4" s="130"/>
+      <c r="X4" s="133"/>
+      <c r="Y4" s="134"/>
     </row>
     <row r="5" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A5" s="157" t="s">
@@ -4422,16 +4234,16 @@
       <c r="A7" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="138" t="s">
+      <c r="B7" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="138"/>
-      <c r="D7" s="138"/>
-      <c r="E7" s="138"/>
-      <c r="F7" s="138"/>
-      <c r="G7" s="138"/>
-      <c r="H7" s="138"/>
-      <c r="I7" s="138"/>
+      <c r="C7" s="130"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="130"/>
+      <c r="G7" s="130"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="130"/>
       <c r="J7" s="59" t="s">
         <v>42</v>
       </c>
@@ -4441,16 +4253,16 @@
       <c r="L7" s="160"/>
       <c r="M7" s="160"/>
       <c r="N7" s="161"/>
-      <c r="O7" s="138" t="s">
+      <c r="O7" s="130" t="s">
         <v>44</v>
       </c>
-      <c r="P7" s="138"/>
-      <c r="Q7" s="138"/>
-      <c r="R7" s="138"/>
-      <c r="S7" s="138" t="s">
+      <c r="P7" s="130"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="130"/>
+      <c r="S7" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="T7" s="138"/>
+      <c r="T7" s="130"/>
       <c r="U7" s="159" t="s">
         <v>46</v>
       </c>
@@ -4463,384 +4275,382 @@
       <c r="A8" s="44">
         <v>1</v>
       </c>
-      <c r="B8" s="162" t="s">
+      <c r="B8" s="150" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="162"/>
-      <c r="D8" s="162"/>
-      <c r="E8" s="162"/>
-      <c r="F8" s="162"/>
-      <c r="G8" s="162"/>
-      <c r="H8" s="162"/>
-      <c r="I8" s="162"/>
+      <c r="C8" s="150"/>
+      <c r="D8" s="150"/>
+      <c r="E8" s="150"/>
+      <c r="F8" s="150"/>
+      <c r="G8" s="150"/>
+      <c r="H8" s="150"/>
+      <c r="I8" s="150"/>
       <c r="J8" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="163" t="s">
+      <c r="K8" s="156" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="164"/>
-      <c r="M8" s="164"/>
-      <c r="N8" s="165"/>
-      <c r="O8" s="166">
+      <c r="L8" s="152"/>
+      <c r="M8" s="152"/>
+      <c r="N8" s="153"/>
+      <c r="O8" s="154">
         <v>4000</v>
       </c>
-      <c r="P8" s="166"/>
-      <c r="Q8" s="166"/>
-      <c r="R8" s="166"/>
-      <c r="S8" s="166" t="s">
+      <c r="P8" s="154"/>
+      <c r="Q8" s="154"/>
+      <c r="R8" s="154"/>
+      <c r="S8" s="154" t="s">
         <v>50</v>
       </c>
-      <c r="T8" s="166"/>
-      <c r="U8" s="163" t="s">
+      <c r="T8" s="154"/>
+      <c r="U8" s="156" t="s">
         <v>51</v>
       </c>
-      <c r="V8" s="164"/>
-      <c r="W8" s="164"/>
-      <c r="X8" s="164"/>
-      <c r="Y8" s="164"/>
+      <c r="V8" s="152"/>
+      <c r="W8" s="152"/>
+      <c r="X8" s="152"/>
+      <c r="Y8" s="152"/>
     </row>
     <row r="9" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A9" s="35"/>
+      <c r="A9" s="44">
+        <v>2</v>
+      </c>
+      <c r="B9" s="150" t="s">
+        <v>243</v>
+      </c>
+      <c r="C9" s="150"/>
+      <c r="D9" s="150"/>
+      <c r="E9" s="150"/>
+      <c r="F9" s="150"/>
+      <c r="G9" s="150"/>
+      <c r="H9" s="150"/>
+      <c r="I9" s="150"/>
+      <c r="J9" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9" s="151" t="s">
+        <v>245</v>
+      </c>
+      <c r="L9" s="152"/>
+      <c r="M9" s="152"/>
+      <c r="N9" s="153"/>
+      <c r="O9" s="154">
+        <v>16</v>
+      </c>
+      <c r="P9" s="154"/>
+      <c r="Q9" s="154"/>
+      <c r="R9" s="154"/>
+      <c r="S9" s="155" t="s">
+        <v>244</v>
+      </c>
+      <c r="T9" s="154"/>
+      <c r="U9" s="156" t="s">
+        <v>51</v>
+      </c>
+      <c r="V9" s="152"/>
+      <c r="W9" s="152"/>
+      <c r="X9" s="152"/>
+      <c r="Y9" s="152"/>
     </row>
     <row r="10" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="35"/>
+    </row>
+    <row r="11" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A11" s="35" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:25" s="32" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A11" s="16" t="s">
+    <row r="12" spans="1:25" s="32" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A12" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="138" t="s">
+      <c r="B12" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="138"/>
-      <c r="D11" s="138"/>
-      <c r="E11" s="138"/>
-      <c r="F11" s="138" t="s">
+      <c r="C12" s="130"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="138"/>
-      <c r="H11" s="138"/>
-      <c r="I11" s="138"/>
-      <c r="J11" s="138"/>
-      <c r="K11" s="138" t="s">
+      <c r="G12" s="130"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="130"/>
+      <c r="K12" s="130" t="s">
         <v>54</v>
       </c>
-      <c r="L11" s="138"/>
-      <c r="M11" s="138"/>
-      <c r="N11" s="138"/>
-      <c r="O11" s="138" t="s">
+      <c r="L12" s="130"/>
+      <c r="M12" s="130"/>
+      <c r="N12" s="130"/>
+      <c r="O12" s="130" t="s">
         <v>42</v>
       </c>
-      <c r="P11" s="138"/>
-      <c r="Q11" s="173" t="s">
+      <c r="P12" s="130"/>
+      <c r="Q12" s="168" t="s">
         <v>45</v>
       </c>
-      <c r="R11" s="173"/>
-      <c r="S11" s="173"/>
-      <c r="T11" s="173"/>
-      <c r="U11" s="138" t="s">
+      <c r="R12" s="168"/>
+      <c r="S12" s="168"/>
+      <c r="T12" s="168"/>
+      <c r="U12" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="V11" s="138"/>
-      <c r="W11" s="138"/>
-      <c r="X11" s="159" t="s">
+      <c r="V12" s="130"/>
+      <c r="W12" s="130"/>
+      <c r="X12" s="159" t="s">
         <v>56</v>
       </c>
-      <c r="Y11" s="160"/>
-    </row>
-    <row r="12" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
-      <c r="A12" s="44">
-        <v>1</v>
-      </c>
-      <c r="B12" s="166" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="166"/>
-      <c r="D12" s="166"/>
-      <c r="E12" s="166"/>
-      <c r="F12" s="166" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" s="166"/>
-      <c r="H12" s="166"/>
-      <c r="I12" s="166"/>
-      <c r="J12" s="166"/>
-      <c r="K12" s="163" t="s">
-        <v>59</v>
-      </c>
-      <c r="L12" s="164"/>
-      <c r="M12" s="164"/>
-      <c r="N12" s="165"/>
-      <c r="O12" s="167" t="s">
-        <v>48</v>
-      </c>
-      <c r="P12" s="168"/>
-      <c r="Q12" s="169" t="s">
-        <v>57</v>
-      </c>
-      <c r="R12" s="166"/>
-      <c r="S12" s="166"/>
-      <c r="T12" s="166"/>
-      <c r="U12" s="170" t="s">
-        <v>60</v>
-      </c>
-      <c r="V12" s="166"/>
-      <c r="W12" s="166"/>
-      <c r="X12" s="171" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y12" s="172"/>
+      <c r="Y12" s="160"/>
     </row>
     <row r="13" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A13" s="44">
-        <v>2</v>
-      </c>
-      <c r="B13" s="166" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="166"/>
-      <c r="D13" s="166"/>
-      <c r="E13" s="166"/>
-      <c r="F13" s="166" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="166"/>
-      <c r="H13" s="166"/>
-      <c r="I13" s="166"/>
-      <c r="J13" s="166"/>
-      <c r="K13" s="163" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="154" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="154"/>
+      <c r="D13" s="154"/>
+      <c r="E13" s="154"/>
+      <c r="F13" s="154" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="154"/>
+      <c r="H13" s="154"/>
+      <c r="I13" s="154"/>
+      <c r="J13" s="154"/>
+      <c r="K13" s="156" t="s">
         <v>59</v>
       </c>
-      <c r="L13" s="164"/>
-      <c r="M13" s="164"/>
-      <c r="N13" s="165"/>
-      <c r="O13" s="167"/>
-      <c r="P13" s="168"/>
-      <c r="Q13" s="169" t="s">
-        <v>64</v>
-      </c>
-      <c r="R13" s="166"/>
-      <c r="S13" s="166"/>
-      <c r="T13" s="166"/>
-      <c r="U13" s="170" t="s">
+      <c r="L13" s="152"/>
+      <c r="M13" s="152"/>
+      <c r="N13" s="153"/>
+      <c r="O13" s="162" t="s">
+        <v>48</v>
+      </c>
+      <c r="P13" s="163"/>
+      <c r="Q13" s="164" t="s">
+        <v>57</v>
+      </c>
+      <c r="R13" s="154"/>
+      <c r="S13" s="154"/>
+      <c r="T13" s="154"/>
+      <c r="U13" s="165" t="s">
         <v>60</v>
       </c>
-      <c r="V13" s="166"/>
-      <c r="W13" s="166"/>
+      <c r="V13" s="154"/>
+      <c r="W13" s="154"/>
       <c r="X13" s="166" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y13" s="166"/>
+        <v>61</v>
+      </c>
+      <c r="Y13" s="167"/>
     </row>
     <row r="14" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A14" s="44">
-        <v>3</v>
-      </c>
-      <c r="B14" s="166" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="154" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="154"/>
+      <c r="D14" s="154"/>
+      <c r="E14" s="154"/>
+      <c r="F14" s="154" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="154"/>
+      <c r="H14" s="154"/>
+      <c r="I14" s="154"/>
+      <c r="J14" s="154"/>
+      <c r="K14" s="156" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="152"/>
+      <c r="M14" s="152"/>
+      <c r="N14" s="153"/>
+      <c r="O14" s="162"/>
+      <c r="P14" s="163"/>
+      <c r="Q14" s="164" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="166"/>
-      <c r="D14" s="166"/>
-      <c r="E14" s="166"/>
-      <c r="F14" s="166" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14" s="166"/>
-      <c r="H14" s="166"/>
-      <c r="I14" s="166"/>
-      <c r="J14" s="166"/>
-      <c r="K14" s="163" t="s">
-        <v>59</v>
-      </c>
-      <c r="L14" s="164"/>
-      <c r="M14" s="164"/>
-      <c r="N14" s="165"/>
-      <c r="O14" s="167"/>
-      <c r="P14" s="168"/>
-      <c r="Q14" s="169" t="s">
-        <v>64</v>
-      </c>
-      <c r="R14" s="166"/>
-      <c r="S14" s="166"/>
-      <c r="T14" s="166"/>
-      <c r="U14" s="170" t="s">
+      <c r="R14" s="154"/>
+      <c r="S14" s="154"/>
+      <c r="T14" s="154"/>
+      <c r="U14" s="165" t="s">
         <v>60</v>
       </c>
-      <c r="V14" s="166"/>
-      <c r="W14" s="166"/>
-      <c r="X14" s="174">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="175"/>
+      <c r="V14" s="154"/>
+      <c r="W14" s="154"/>
+      <c r="X14" s="154" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y14" s="154"/>
     </row>
     <row r="15" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A15" s="44">
-        <v>4</v>
-      </c>
-      <c r="B15" s="166" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="166"/>
-      <c r="D15" s="166"/>
-      <c r="E15" s="166"/>
-      <c r="F15" s="166" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="166"/>
-      <c r="H15" s="166"/>
-      <c r="I15" s="166"/>
-      <c r="J15" s="166"/>
-      <c r="K15" s="163" t="s">
-        <v>69</v>
-      </c>
-      <c r="L15" s="164"/>
-      <c r="M15" s="164"/>
-      <c r="N15" s="165"/>
-      <c r="O15" s="167"/>
-      <c r="P15" s="168"/>
-      <c r="Q15" s="169" t="s">
-        <v>67</v>
-      </c>
-      <c r="R15" s="166"/>
-      <c r="S15" s="166"/>
-      <c r="T15" s="166"/>
-      <c r="U15" s="166" t="s">
-        <v>70</v>
-      </c>
-      <c r="V15" s="166"/>
-      <c r="W15" s="166"/>
-      <c r="X15" s="163" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y15" s="165"/>
+        <v>3</v>
+      </c>
+      <c r="B15" s="154" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="154"/>
+      <c r="D15" s="154"/>
+      <c r="E15" s="154"/>
+      <c r="F15" s="154" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" s="154"/>
+      <c r="H15" s="154"/>
+      <c r="I15" s="154"/>
+      <c r="J15" s="154"/>
+      <c r="K15" s="156" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="152"/>
+      <c r="M15" s="152"/>
+      <c r="N15" s="153"/>
+      <c r="O15" s="162"/>
+      <c r="P15" s="163"/>
+      <c r="Q15" s="164" t="s">
+        <v>64</v>
+      </c>
+      <c r="R15" s="154"/>
+      <c r="S15" s="154"/>
+      <c r="T15" s="154"/>
+      <c r="U15" s="165" t="s">
+        <v>60</v>
+      </c>
+      <c r="V15" s="154"/>
+      <c r="W15" s="154"/>
+      <c r="X15" s="169">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="170"/>
     </row>
     <row r="16" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A16" s="44">
-        <v>5</v>
-      </c>
-      <c r="B16" s="166" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="166"/>
-      <c r="D16" s="166"/>
-      <c r="E16" s="166"/>
-      <c r="F16" s="166" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" s="166"/>
-      <c r="H16" s="166"/>
-      <c r="I16" s="166"/>
-      <c r="J16" s="166"/>
-      <c r="K16" s="163" t="s">
-        <v>59</v>
-      </c>
-      <c r="L16" s="164"/>
-      <c r="M16" s="164"/>
-      <c r="N16" s="165"/>
-      <c r="O16" s="167"/>
-      <c r="P16" s="168"/>
-      <c r="Q16" s="169" t="s">
-        <v>74</v>
-      </c>
-      <c r="R16" s="166"/>
-      <c r="S16" s="166"/>
-      <c r="T16" s="166"/>
-      <c r="U16" s="166" t="s">
-        <v>75</v>
-      </c>
-      <c r="V16" s="166"/>
-      <c r="W16" s="166"/>
-      <c r="X16" s="163">
-        <v>10</v>
-      </c>
-      <c r="Y16" s="165"/>
+        <v>4</v>
+      </c>
+      <c r="B16" s="154" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="154"/>
+      <c r="D16" s="154"/>
+      <c r="E16" s="154"/>
+      <c r="F16" s="154" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="154"/>
+      <c r="H16" s="154"/>
+      <c r="I16" s="154"/>
+      <c r="J16" s="154"/>
+      <c r="K16" s="156" t="s">
+        <v>69</v>
+      </c>
+      <c r="L16" s="152"/>
+      <c r="M16" s="152"/>
+      <c r="N16" s="153"/>
+      <c r="O16" s="162"/>
+      <c r="P16" s="163"/>
+      <c r="Q16" s="164" t="s">
+        <v>67</v>
+      </c>
+      <c r="R16" s="154"/>
+      <c r="S16" s="154"/>
+      <c r="T16" s="154"/>
+      <c r="U16" s="154" t="s">
+        <v>70</v>
+      </c>
+      <c r="V16" s="154"/>
+      <c r="W16" s="154"/>
+      <c r="X16" s="156" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y16" s="153"/>
     </row>
     <row r="17" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A17" s="44">
+        <v>5</v>
+      </c>
+      <c r="B17" s="154" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="154"/>
+      <c r="D17" s="154"/>
+      <c r="E17" s="154"/>
+      <c r="F17" s="154" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="154"/>
+      <c r="H17" s="154"/>
+      <c r="I17" s="154"/>
+      <c r="J17" s="154"/>
+      <c r="K17" s="156" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="152"/>
+      <c r="M17" s="152"/>
+      <c r="N17" s="153"/>
+      <c r="O17" s="162"/>
+      <c r="P17" s="163"/>
+      <c r="Q17" s="164" t="s">
+        <v>74</v>
+      </c>
+      <c r="R17" s="154"/>
+      <c r="S17" s="154"/>
+      <c r="T17" s="154"/>
+      <c r="U17" s="154" t="s">
+        <v>75</v>
+      </c>
+      <c r="V17" s="154"/>
+      <c r="W17" s="154"/>
+      <c r="X17" s="156">
+        <v>10</v>
+      </c>
+      <c r="Y17" s="153"/>
+    </row>
+    <row r="18" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
+      <c r="A18" s="44">
         <v>6</v>
       </c>
-      <c r="B17" s="166" t="s">
+      <c r="B18" s="154" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="166"/>
-      <c r="D17" s="166"/>
-      <c r="E17" s="166"/>
-      <c r="F17" s="166" t="s">
+      <c r="C18" s="154"/>
+      <c r="D18" s="154"/>
+      <c r="E18" s="154"/>
+      <c r="F18" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="G17" s="166"/>
-      <c r="H17" s="166"/>
-      <c r="I17" s="166"/>
-      <c r="J17" s="166"/>
-      <c r="K17" s="163" t="s">
+      <c r="G18" s="154"/>
+      <c r="H18" s="154"/>
+      <c r="I18" s="154"/>
+      <c r="J18" s="154"/>
+      <c r="K18" s="156" t="s">
         <v>59</v>
       </c>
-      <c r="L17" s="164"/>
-      <c r="M17" s="164"/>
-      <c r="N17" s="165"/>
-      <c r="O17" s="167"/>
-      <c r="P17" s="168"/>
-      <c r="Q17" s="169" t="s">
+      <c r="L18" s="152"/>
+      <c r="M18" s="152"/>
+      <c r="N18" s="153"/>
+      <c r="O18" s="162"/>
+      <c r="P18" s="163"/>
+      <c r="Q18" s="164" t="s">
         <v>78</v>
       </c>
-      <c r="R17" s="166"/>
-      <c r="S17" s="166"/>
-      <c r="T17" s="166"/>
-      <c r="U17" s="166" t="s">
+      <c r="R18" s="154"/>
+      <c r="S18" s="154"/>
+      <c r="T18" s="154"/>
+      <c r="U18" s="154" t="s">
         <v>75</v>
       </c>
-      <c r="V17" s="166"/>
-      <c r="W17" s="166"/>
-      <c r="X17" s="163">
+      <c r="V18" s="154"/>
+      <c r="W18" s="154"/>
+      <c r="X18" s="156">
         <v>100</v>
       </c>
-      <c r="Y17" s="165"/>
-    </row>
-    <row r="18" spans="1:25" s="33" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A18" s="89">
-        <v>7</v>
-      </c>
-      <c r="B18" s="177" t="s">
-        <v>236</v>
-      </c>
-      <c r="C18" s="177"/>
-      <c r="D18" s="177"/>
-      <c r="E18" s="177"/>
-      <c r="F18" s="177" t="s">
-        <v>254</v>
-      </c>
-      <c r="G18" s="177"/>
-      <c r="H18" s="177"/>
-      <c r="I18" s="177"/>
-      <c r="J18" s="177"/>
-      <c r="K18" s="178" t="s">
-        <v>69</v>
-      </c>
-      <c r="L18" s="180"/>
-      <c r="M18" s="180"/>
-      <c r="N18" s="179"/>
-      <c r="O18" s="181" t="s">
-        <v>48</v>
-      </c>
-      <c r="P18" s="182"/>
-      <c r="Q18" s="183" t="s">
-        <v>236</v>
-      </c>
-      <c r="R18" s="177"/>
-      <c r="S18" s="177"/>
-      <c r="T18" s="177"/>
-      <c r="U18" s="177" t="s">
-        <v>237</v>
-      </c>
-      <c r="V18" s="177"/>
-      <c r="W18" s="177"/>
-      <c r="X18" s="178" t="s">
-        <v>238</v>
-      </c>
-      <c r="Y18" s="179"/>
+      <c r="Y18" s="153"/>
     </row>
     <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A19" s="58"/>
@@ -4870,21 +4680,14 @@
       <c r="Y19" s="58"/>
     </row>
   </sheetData>
-  <mergeCells count="84">
-    <mergeCell ref="U18:W18"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="F18:J18"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:T18"/>
+  <mergeCells count="82">
     <mergeCell ref="J1:N2"/>
     <mergeCell ref="O1:S2"/>
     <mergeCell ref="A1:I4"/>
     <mergeCell ref="J3:N4"/>
     <mergeCell ref="O3:S4"/>
-    <mergeCell ref="U17:W17"/>
-    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="U18:W18"/>
+    <mergeCell ref="X18:Y18"/>
     <mergeCell ref="T1:T2"/>
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="W1:W2"/>
@@ -4893,12 +4696,17 @@
     <mergeCell ref="X1:Y2"/>
     <mergeCell ref="U3:V4"/>
     <mergeCell ref="U1:V2"/>
-    <mergeCell ref="U15:W15"/>
-    <mergeCell ref="X15:Y15"/>
     <mergeCell ref="U16:W16"/>
     <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="U13:W13"/>
-    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="U17:W17"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:T18"/>
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="F17:J17"/>
     <mergeCell ref="K17:N17"/>
@@ -4909,37 +4717,32 @@
     <mergeCell ref="K16:N16"/>
     <mergeCell ref="O16:P16"/>
     <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="U15:W15"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="Q14:T14"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="F15:J15"/>
     <mergeCell ref="K15:N15"/>
     <mergeCell ref="O15:P15"/>
     <mergeCell ref="Q15:T15"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="X12:Y12"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="F13:J13"/>
     <mergeCell ref="K13:N13"/>
     <mergeCell ref="O13:P13"/>
     <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="X13:Y13"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="F12:J12"/>
     <mergeCell ref="K12:N12"/>
     <mergeCell ref="O12:P12"/>
     <mergeCell ref="Q12:T12"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="Q11:T11"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="K8:N8"/>
     <mergeCell ref="O8:R8"/>
@@ -4955,6 +4758,11 @@
     <mergeCell ref="J5:N5"/>
     <mergeCell ref="O5:S5"/>
     <mergeCell ref="U5:Y5"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="U9:Y9"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4985,126 +4793,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="111" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="128" t="s">
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="129"/>
-      <c r="M1" s="134" t="s">
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="138" t="s">
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="130" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="149" t="s">
+      <c r="R1" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="150"/>
-      <c r="T1" s="143" t="s">
+      <c r="S1" s="143"/>
+      <c r="T1" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="139" t="s">
+      <c r="U1" s="141" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="194"/>
+      <c r="V1" s="187"/>
     </row>
     <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="122"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="136"/>
-      <c r="N2" s="137"/>
-      <c r="O2" s="137"/>
-      <c r="P2" s="137"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="152"/>
-      <c r="S2" s="153"/>
-      <c r="T2" s="146"/>
-      <c r="U2" s="141"/>
-      <c r="V2" s="195"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="130"/>
+      <c r="R2" s="145"/>
+      <c r="S2" s="146"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="133"/>
+      <c r="V2" s="188"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A3" s="122"/>
-      <c r="B3" s="123"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="123"/>
-      <c r="F3" s="123"/>
-      <c r="G3" s="123"/>
-      <c r="H3" s="123"/>
-      <c r="I3" s="128" t="s">
+      <c r="A3" s="114"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="134" t="s">
+      <c r="J3" s="121"/>
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="126" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="135"/>
-      <c r="O3" s="135"/>
-      <c r="P3" s="135"/>
-      <c r="Q3" s="138" t="s">
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="149" t="s">
+      <c r="R3" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="150"/>
-      <c r="T3" s="138" t="s">
+      <c r="S3" s="143"/>
+      <c r="T3" s="130" t="s">
         <v>16</v>
       </c>
-      <c r="U3" s="217" t="s">
-        <v>261</v>
-      </c>
-      <c r="V3" s="194"/>
+      <c r="U3" s="131" t="s">
+        <v>241</v>
+      </c>
+      <c r="V3" s="187"/>
     </row>
     <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A4" s="125"/>
-      <c r="B4" s="126"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="126"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="136"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137"/>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="138"/>
-      <c r="R4" s="152"/>
-      <c r="S4" s="153"/>
-      <c r="T4" s="138"/>
-      <c r="U4" s="141"/>
-      <c r="V4" s="195"/>
+      <c r="A4" s="117"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="128"/>
+      <c r="N4" s="129"/>
+      <c r="O4" s="129"/>
+      <c r="P4" s="129"/>
+      <c r="Q4" s="130"/>
+      <c r="R4" s="145"/>
+      <c r="S4" s="146"/>
+      <c r="T4" s="130"/>
+      <c r="U4" s="133"/>
+      <c r="V4" s="188"/>
     </row>
     <row r="5" spans="1:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A5" s="157" t="s">
@@ -5196,73 +5004,73 @@
       <c r="A8" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="184" t="s">
+      <c r="B8" s="178" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="184"/>
-      <c r="D8" s="184"/>
-      <c r="E8" s="184"/>
-      <c r="F8" s="184"/>
-      <c r="G8" s="184"/>
-      <c r="H8" s="184"/>
-      <c r="I8" s="184" t="s">
+      <c r="C8" s="178"/>
+      <c r="D8" s="178"/>
+      <c r="E8" s="178"/>
+      <c r="F8" s="178"/>
+      <c r="G8" s="178"/>
+      <c r="H8" s="178"/>
+      <c r="I8" s="178" t="s">
         <v>54</v>
       </c>
-      <c r="J8" s="184"/>
-      <c r="K8" s="184"/>
-      <c r="L8" s="184"/>
-      <c r="M8" s="184" t="s">
+      <c r="J8" s="178"/>
+      <c r="K8" s="178"/>
+      <c r="L8" s="178"/>
+      <c r="M8" s="178" t="s">
         <v>42</v>
       </c>
-      <c r="N8" s="184"/>
-      <c r="O8" s="184"/>
-      <c r="P8" s="185" t="s">
+      <c r="N8" s="178"/>
+      <c r="O8" s="178"/>
+      <c r="P8" s="179" t="s">
         <v>45</v>
       </c>
-      <c r="Q8" s="185"/>
-      <c r="R8" s="185"/>
-      <c r="S8" s="185"/>
-      <c r="T8" s="146" t="s">
+      <c r="Q8" s="179"/>
+      <c r="R8" s="179"/>
+      <c r="S8" s="179"/>
+      <c r="T8" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="U8" s="147"/>
-      <c r="V8" s="148"/>
+      <c r="U8" s="139"/>
+      <c r="V8" s="140"/>
     </row>
     <row r="9" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A9" s="44">
         <v>1</v>
       </c>
-      <c r="B9" s="186" t="s">
+      <c r="B9" s="180" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="187"/>
-      <c r="D9" s="187"/>
-      <c r="E9" s="187"/>
-      <c r="F9" s="187"/>
-      <c r="G9" s="187"/>
-      <c r="H9" s="187"/>
-      <c r="I9" s="163" t="s">
+      <c r="C9" s="181"/>
+      <c r="D9" s="181"/>
+      <c r="E9" s="181"/>
+      <c r="F9" s="181"/>
+      <c r="G9" s="181"/>
+      <c r="H9" s="181"/>
+      <c r="I9" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="J9" s="164"/>
-      <c r="K9" s="164"/>
-      <c r="L9" s="165"/>
-      <c r="M9" s="188" t="s">
+      <c r="J9" s="152"/>
+      <c r="K9" s="152"/>
+      <c r="L9" s="153"/>
+      <c r="M9" s="182" t="s">
         <v>48</v>
       </c>
-      <c r="N9" s="162"/>
-      <c r="O9" s="162"/>
-      <c r="P9" s="169" t="s">
+      <c r="N9" s="150"/>
+      <c r="O9" s="150"/>
+      <c r="P9" s="164" t="s">
         <v>83</v>
       </c>
-      <c r="Q9" s="166"/>
-      <c r="R9" s="166"/>
-      <c r="S9" s="166"/>
-      <c r="T9" s="166" t="s">
+      <c r="Q9" s="154"/>
+      <c r="R9" s="154"/>
+      <c r="S9" s="154"/>
+      <c r="T9" s="154" t="s">
         <v>84</v>
       </c>
-      <c r="U9" s="166"/>
-      <c r="V9" s="166"/>
+      <c r="U9" s="154"/>
+      <c r="V9" s="154"/>
     </row>
     <row r="10" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A10" s="44">
@@ -5277,378 +5085,378 @@
       <c r="F10" s="46"/>
       <c r="G10" s="46"/>
       <c r="H10" s="46"/>
-      <c r="I10" s="163" t="s">
+      <c r="I10" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="J10" s="164"/>
-      <c r="K10" s="164"/>
-      <c r="L10" s="165"/>
-      <c r="M10" s="188" t="s">
+      <c r="J10" s="152"/>
+      <c r="K10" s="152"/>
+      <c r="L10" s="153"/>
+      <c r="M10" s="182" t="s">
         <v>48</v>
       </c>
-      <c r="N10" s="162"/>
-      <c r="O10" s="162"/>
-      <c r="P10" s="169" t="s">
+      <c r="N10" s="150"/>
+      <c r="O10" s="150"/>
+      <c r="P10" s="164" t="s">
         <v>86</v>
       </c>
-      <c r="Q10" s="166"/>
-      <c r="R10" s="166"/>
-      <c r="S10" s="166"/>
-      <c r="T10" s="166" t="s">
+      <c r="Q10" s="154"/>
+      <c r="R10" s="154"/>
+      <c r="S10" s="154"/>
+      <c r="T10" s="154" t="s">
         <v>87</v>
       </c>
-      <c r="U10" s="166"/>
-      <c r="V10" s="166"/>
+      <c r="U10" s="154"/>
+      <c r="V10" s="154"/>
     </row>
     <row r="11" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A11" s="44">
         <v>3</v>
       </c>
-      <c r="B11" s="193"/>
-      <c r="C11" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="166" t="s">
-        <v>89</v>
-      </c>
-      <c r="J11" s="166"/>
-      <c r="K11" s="166"/>
-      <c r="L11" s="166"/>
-      <c r="M11" s="188" t="s">
-        <v>48</v>
-      </c>
-      <c r="N11" s="162"/>
-      <c r="O11" s="162"/>
-      <c r="P11" s="169" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q11" s="166"/>
-      <c r="R11" s="166"/>
-      <c r="S11" s="166"/>
-      <c r="T11" s="169" t="s">
-        <v>91</v>
-      </c>
-      <c r="U11" s="166"/>
-      <c r="V11" s="166"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="89" t="s">
+        <v>246</v>
+      </c>
+      <c r="D11" s="47"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="172" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" s="173"/>
+      <c r="K11" s="173"/>
+      <c r="L11" s="174"/>
+      <c r="M11" s="175" t="s">
+        <v>247</v>
+      </c>
+      <c r="N11" s="163"/>
+      <c r="O11" s="176"/>
+      <c r="P11" s="177" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q11" s="152"/>
+      <c r="R11" s="152"/>
+      <c r="S11" s="153"/>
+      <c r="T11" s="151" t="s">
+        <v>250</v>
+      </c>
+      <c r="U11" s="152"/>
+      <c r="V11" s="152"/>
     </row>
     <row r="12" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A12" s="44">
         <v>4</v>
       </c>
-      <c r="B12" s="193"/>
-      <c r="C12" s="193"/>
+      <c r="B12" s="186"/>
+      <c r="C12" s="83"/>
       <c r="D12" s="48" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" s="50"/>
+        <v>88</v>
+      </c>
+      <c r="E12" s="49"/>
       <c r="F12" s="50"/>
       <c r="G12" s="50"/>
       <c r="H12" s="50"/>
-      <c r="I12" s="166" t="s">
-        <v>93</v>
-      </c>
-      <c r="J12" s="166"/>
-      <c r="K12" s="166"/>
-      <c r="L12" s="166"/>
-      <c r="M12" s="188" t="s">
+      <c r="I12" s="154" t="s">
+        <v>89</v>
+      </c>
+      <c r="J12" s="154"/>
+      <c r="K12" s="154"/>
+      <c r="L12" s="154"/>
+      <c r="M12" s="182" t="s">
         <v>48</v>
       </c>
-      <c r="N12" s="162"/>
-      <c r="O12" s="162"/>
-      <c r="P12" s="169" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q12" s="166"/>
-      <c r="R12" s="166"/>
-      <c r="S12" s="166"/>
-      <c r="T12" s="169" t="s">
-        <v>91</v>
-      </c>
-      <c r="U12" s="166"/>
-      <c r="V12" s="166"/>
+      <c r="N12" s="150"/>
+      <c r="O12" s="150"/>
+      <c r="P12" s="164" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q12" s="154"/>
+      <c r="R12" s="154"/>
+      <c r="S12" s="154"/>
+      <c r="T12" s="183" t="s">
+        <v>249</v>
+      </c>
+      <c r="U12" s="154"/>
+      <c r="V12" s="154"/>
     </row>
     <row r="13" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A13" s="44">
         <v>5</v>
       </c>
-      <c r="B13" s="193"/>
-      <c r="C13" s="193"/>
-      <c r="D13" s="193"/>
-      <c r="E13" s="44" t="s">
-        <v>95</v>
-      </c>
-      <c r="F13" s="51"/>
+      <c r="B13" s="186"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="186"/>
+      <c r="E13" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="50"/>
       <c r="G13" s="50"/>
       <c r="H13" s="50"/>
-      <c r="I13" s="163" t="s">
-        <v>59</v>
-      </c>
-      <c r="J13" s="164"/>
-      <c r="K13" s="164"/>
-      <c r="L13" s="165"/>
-      <c r="M13" s="188" t="s">
+      <c r="I13" s="154" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" s="154"/>
+      <c r="K13" s="154"/>
+      <c r="L13" s="154"/>
+      <c r="M13" s="182" t="s">
         <v>48</v>
       </c>
-      <c r="N13" s="162"/>
-      <c r="O13" s="162"/>
-      <c r="P13" s="169" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q13" s="166"/>
-      <c r="R13" s="166"/>
-      <c r="S13" s="166"/>
-      <c r="T13" s="166">
-        <v>1</v>
-      </c>
-      <c r="U13" s="166"/>
-      <c r="V13" s="166"/>
+      <c r="N13" s="150"/>
+      <c r="O13" s="150"/>
+      <c r="P13" s="164" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q13" s="154"/>
+      <c r="R13" s="154"/>
+      <c r="S13" s="154"/>
+      <c r="T13" s="164" t="s">
+        <v>91</v>
+      </c>
+      <c r="U13" s="154"/>
+      <c r="V13" s="154"/>
     </row>
     <row r="14" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A14" s="44">
         <v>6</v>
       </c>
-      <c r="B14" s="193"/>
-      <c r="C14" s="193"/>
-      <c r="D14" s="193"/>
-      <c r="E14" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="F14" s="51"/>
-      <c r="G14" s="50"/>
+      <c r="B14" s="186"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="186"/>
+      <c r="E14" s="186"/>
+      <c r="F14" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14" s="51"/>
       <c r="H14" s="50"/>
-      <c r="I14" s="163" t="s">
-        <v>69</v>
-      </c>
-      <c r="J14" s="164"/>
-      <c r="K14" s="164"/>
-      <c r="L14" s="165"/>
-      <c r="M14" s="162"/>
-      <c r="N14" s="162"/>
-      <c r="O14" s="162"/>
-      <c r="P14" s="169" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q14" s="166"/>
-      <c r="R14" s="166"/>
-      <c r="S14" s="166"/>
-      <c r="T14" s="166" t="s">
-        <v>99</v>
-      </c>
-      <c r="U14" s="166"/>
-      <c r="V14" s="166"/>
+      <c r="I14" s="156" t="s">
+        <v>59</v>
+      </c>
+      <c r="J14" s="152"/>
+      <c r="K14" s="152"/>
+      <c r="L14" s="153"/>
+      <c r="M14" s="182" t="s">
+        <v>48</v>
+      </c>
+      <c r="N14" s="150"/>
+      <c r="O14" s="150"/>
+      <c r="P14" s="164" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q14" s="154"/>
+      <c r="R14" s="154"/>
+      <c r="S14" s="154"/>
+      <c r="T14" s="154">
+        <v>1</v>
+      </c>
+      <c r="U14" s="154"/>
+      <c r="V14" s="154"/>
     </row>
     <row r="15" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A15" s="44">
         <v>7</v>
       </c>
-      <c r="B15" s="193"/>
-      <c r="C15" s="193"/>
-      <c r="D15" s="193"/>
-      <c r="E15" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="F15" s="51"/>
-      <c r="G15" s="50"/>
+      <c r="B15" s="186"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="186"/>
+      <c r="E15" s="186"/>
+      <c r="F15" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="51"/>
       <c r="H15" s="50"/>
-      <c r="I15" s="163" t="s">
+      <c r="I15" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="J15" s="164"/>
-      <c r="K15" s="164"/>
-      <c r="L15" s="165"/>
-      <c r="M15" s="162"/>
-      <c r="N15" s="162"/>
-      <c r="O15" s="162"/>
-      <c r="P15" s="169" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q15" s="166"/>
-      <c r="R15" s="166"/>
-      <c r="S15" s="166"/>
-      <c r="T15" s="166" t="s">
-        <v>102</v>
-      </c>
-      <c r="U15" s="166"/>
-      <c r="V15" s="166"/>
+      <c r="J15" s="152"/>
+      <c r="K15" s="152"/>
+      <c r="L15" s="153"/>
+      <c r="M15" s="150"/>
+      <c r="N15" s="150"/>
+      <c r="O15" s="150"/>
+      <c r="P15" s="164" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q15" s="154"/>
+      <c r="R15" s="154"/>
+      <c r="S15" s="154"/>
+      <c r="T15" s="154" t="s">
+        <v>99</v>
+      </c>
+      <c r="U15" s="154"/>
+      <c r="V15" s="154"/>
     </row>
     <row r="16" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A16" s="44">
         <v>8</v>
       </c>
-      <c r="B16" s="193"/>
-      <c r="C16" s="193"/>
-      <c r="D16" s="193"/>
-      <c r="E16" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="F16" s="51"/>
-      <c r="G16" s="50"/>
+      <c r="B16" s="186"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="186"/>
+      <c r="E16" s="186"/>
+      <c r="F16" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="51"/>
       <c r="H16" s="50"/>
-      <c r="I16" s="163" t="s">
+      <c r="I16" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="J16" s="164"/>
-      <c r="K16" s="164"/>
-      <c r="L16" s="165"/>
-      <c r="M16" s="162"/>
-      <c r="N16" s="162"/>
-      <c r="O16" s="162"/>
-      <c r="P16" s="169" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q16" s="166"/>
-      <c r="R16" s="166"/>
-      <c r="S16" s="166"/>
-      <c r="T16" s="166" t="s">
-        <v>104</v>
-      </c>
-      <c r="U16" s="166"/>
-      <c r="V16" s="166"/>
+      <c r="J16" s="152"/>
+      <c r="K16" s="152"/>
+      <c r="L16" s="153"/>
+      <c r="M16" s="150"/>
+      <c r="N16" s="150"/>
+      <c r="O16" s="150"/>
+      <c r="P16" s="164" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q16" s="154"/>
+      <c r="R16" s="154"/>
+      <c r="S16" s="154"/>
+      <c r="T16" s="154" t="s">
+        <v>102</v>
+      </c>
+      <c r="U16" s="154"/>
+      <c r="V16" s="154"/>
     </row>
     <row r="17" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A17" s="44">
         <v>9</v>
       </c>
-      <c r="B17" s="193"/>
-      <c r="C17" s="193"/>
-      <c r="D17" s="193"/>
-      <c r="E17" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="F17" s="51"/>
-      <c r="G17" s="50"/>
+      <c r="B17" s="186"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="186"/>
+      <c r="E17" s="186"/>
+      <c r="F17" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" s="51"/>
       <c r="H17" s="50"/>
-      <c r="I17" s="163" t="s">
-        <v>59</v>
-      </c>
-      <c r="J17" s="164"/>
-      <c r="K17" s="164"/>
-      <c r="L17" s="165"/>
-      <c r="M17" s="162"/>
-      <c r="N17" s="162"/>
-      <c r="O17" s="162"/>
-      <c r="P17" s="169" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q17" s="166"/>
-      <c r="R17" s="166"/>
-      <c r="S17" s="166"/>
-      <c r="T17" s="166">
-        <v>75</v>
-      </c>
-      <c r="U17" s="166"/>
-      <c r="V17" s="166"/>
+      <c r="I17" s="156" t="s">
+        <v>69</v>
+      </c>
+      <c r="J17" s="152"/>
+      <c r="K17" s="152"/>
+      <c r="L17" s="153"/>
+      <c r="M17" s="150"/>
+      <c r="N17" s="150"/>
+      <c r="O17" s="150"/>
+      <c r="P17" s="164" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q17" s="154"/>
+      <c r="R17" s="154"/>
+      <c r="S17" s="154"/>
+      <c r="T17" s="154" t="s">
+        <v>104</v>
+      </c>
+      <c r="U17" s="154"/>
+      <c r="V17" s="154"/>
     </row>
     <row r="18" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A18" s="44">
         <v>10</v>
       </c>
-      <c r="B18" s="193"/>
-      <c r="C18" s="193"/>
-      <c r="D18" s="193"/>
-      <c r="E18" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="F18" s="51"/>
-      <c r="G18" s="50"/>
+      <c r="B18" s="186"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="186"/>
+      <c r="E18" s="186"/>
+      <c r="F18" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" s="51"/>
       <c r="H18" s="50"/>
-      <c r="I18" s="163" t="s">
-        <v>69</v>
-      </c>
-      <c r="J18" s="164"/>
-      <c r="K18" s="164"/>
-      <c r="L18" s="165"/>
-      <c r="M18" s="162"/>
-      <c r="N18" s="162"/>
-      <c r="O18" s="162"/>
-      <c r="P18" s="169" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q18" s="166"/>
-      <c r="R18" s="166"/>
-      <c r="S18" s="166"/>
-      <c r="T18" s="166" t="s">
-        <v>109</v>
-      </c>
-      <c r="U18" s="166"/>
-      <c r="V18" s="166"/>
+      <c r="I18" s="156" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="152"/>
+      <c r="K18" s="152"/>
+      <c r="L18" s="153"/>
+      <c r="M18" s="150"/>
+      <c r="N18" s="150"/>
+      <c r="O18" s="150"/>
+      <c r="P18" s="164" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q18" s="154"/>
+      <c r="R18" s="154"/>
+      <c r="S18" s="154"/>
+      <c r="T18" s="154">
+        <v>75</v>
+      </c>
+      <c r="U18" s="154"/>
+      <c r="V18" s="154"/>
     </row>
     <row r="19" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A19" s="44">
         <v>11</v>
       </c>
-      <c r="B19" s="193"/>
-      <c r="C19" s="193"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="89" t="s">
-        <v>254</v>
-      </c>
-      <c r="F19" s="88"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="178" t="s">
+      <c r="B19" s="186"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="186"/>
+      <c r="E19" s="186"/>
+      <c r="F19" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="51"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="J19" s="180"/>
-      <c r="K19" s="180"/>
-      <c r="L19" s="179"/>
-      <c r="M19" s="189" t="s">
-        <v>48</v>
-      </c>
-      <c r="N19" s="189"/>
-      <c r="O19" s="189"/>
-      <c r="P19" s="183" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q19" s="177"/>
-      <c r="R19" s="177"/>
-      <c r="S19" s="177"/>
-      <c r="T19" s="190" t="s">
-        <v>255</v>
-      </c>
-      <c r="U19" s="177"/>
-      <c r="V19" s="177"/>
+      <c r="J19" s="152"/>
+      <c r="K19" s="152"/>
+      <c r="L19" s="153"/>
+      <c r="M19" s="150"/>
+      <c r="N19" s="150"/>
+      <c r="O19" s="150"/>
+      <c r="P19" s="164" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q19" s="154"/>
+      <c r="R19" s="154"/>
+      <c r="S19" s="154"/>
+      <c r="T19" s="154" t="s">
+        <v>109</v>
+      </c>
+      <c r="U19" s="154"/>
+      <c r="V19" s="154"/>
     </row>
     <row r="20" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A20" s="44">
         <v>12</v>
       </c>
-      <c r="B20" s="174"/>
-      <c r="C20" s="174"/>
-      <c r="D20" s="44" t="s">
+      <c r="B20" s="169"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="169"/>
+      <c r="E20" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="E20" s="44"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="50"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="51"/>
       <c r="H20" s="50"/>
-      <c r="I20" s="163" t="s">
+      <c r="I20" s="156" t="s">
         <v>59</v>
       </c>
-      <c r="J20" s="164"/>
-      <c r="K20" s="164"/>
-      <c r="L20" s="165"/>
-      <c r="M20" s="188" t="s">
+      <c r="J20" s="152"/>
+      <c r="K20" s="152"/>
+      <c r="L20" s="153"/>
+      <c r="M20" s="182" t="s">
         <v>48</v>
       </c>
-      <c r="N20" s="162"/>
-      <c r="O20" s="162"/>
-      <c r="P20" s="169" t="s">
+      <c r="N20" s="150"/>
+      <c r="O20" s="150"/>
+      <c r="P20" s="164" t="s">
         <v>111</v>
       </c>
-      <c r="Q20" s="166"/>
-      <c r="R20" s="166"/>
-      <c r="S20" s="166"/>
-      <c r="T20" s="166">
+      <c r="Q20" s="154"/>
+      <c r="R20" s="154"/>
+      <c r="S20" s="154"/>
+      <c r="T20" s="154">
         <v>3</v>
       </c>
-      <c r="U20" s="166"/>
-      <c r="V20" s="166"/>
+      <c r="U20" s="154"/>
+      <c r="V20" s="154"/>
     </row>
     <row r="21" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A21" s="39"/>
@@ -5704,145 +5512,145 @@
       <c r="A23" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="184" t="s">
+      <c r="B23" s="178" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="184"/>
-      <c r="D23" s="184"/>
-      <c r="E23" s="184"/>
-      <c r="F23" s="184"/>
-      <c r="G23" s="184"/>
-      <c r="H23" s="184"/>
-      <c r="I23" s="184" t="s">
+      <c r="C23" s="178"/>
+      <c r="D23" s="178"/>
+      <c r="E23" s="178"/>
+      <c r="F23" s="178"/>
+      <c r="G23" s="178"/>
+      <c r="H23" s="178"/>
+      <c r="I23" s="178" t="s">
         <v>54</v>
       </c>
-      <c r="J23" s="184"/>
-      <c r="K23" s="184"/>
-      <c r="L23" s="184"/>
-      <c r="M23" s="184" t="s">
+      <c r="J23" s="178"/>
+      <c r="K23" s="178"/>
+      <c r="L23" s="178"/>
+      <c r="M23" s="178" t="s">
         <v>42</v>
       </c>
-      <c r="N23" s="184"/>
-      <c r="O23" s="184"/>
-      <c r="P23" s="185" t="s">
+      <c r="N23" s="178"/>
+      <c r="O23" s="178"/>
+      <c r="P23" s="179" t="s">
         <v>45</v>
       </c>
-      <c r="Q23" s="185"/>
-      <c r="R23" s="185"/>
-      <c r="S23" s="185"/>
-      <c r="T23" s="146" t="s">
+      <c r="Q23" s="179"/>
+      <c r="R23" s="179"/>
+      <c r="S23" s="179"/>
+      <c r="T23" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="U23" s="147"/>
-      <c r="V23" s="148"/>
+      <c r="U23" s="139"/>
+      <c r="V23" s="140"/>
     </row>
     <row r="24" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A24" s="44">
         <v>1</v>
       </c>
-      <c r="B24" s="186" t="s">
+      <c r="B24" s="180" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="187"/>
-      <c r="D24" s="187"/>
-      <c r="E24" s="187"/>
-      <c r="F24" s="187"/>
-      <c r="G24" s="187"/>
-      <c r="H24" s="187"/>
-      <c r="I24" s="163" t="s">
+      <c r="C24" s="181"/>
+      <c r="D24" s="181"/>
+      <c r="E24" s="181"/>
+      <c r="F24" s="181"/>
+      <c r="G24" s="181"/>
+      <c r="H24" s="181"/>
+      <c r="I24" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="J24" s="164"/>
-      <c r="K24" s="164"/>
-      <c r="L24" s="165"/>
-      <c r="M24" s="188" t="s">
+      <c r="J24" s="152"/>
+      <c r="K24" s="152"/>
+      <c r="L24" s="153"/>
+      <c r="M24" s="182" t="s">
         <v>48</v>
       </c>
-      <c r="N24" s="162"/>
-      <c r="O24" s="162"/>
-      <c r="P24" s="169" t="s">
+      <c r="N24" s="150"/>
+      <c r="O24" s="150"/>
+      <c r="P24" s="164" t="s">
         <v>83</v>
       </c>
-      <c r="Q24" s="166"/>
-      <c r="R24" s="166"/>
-      <c r="S24" s="166"/>
-      <c r="T24" s="166" t="s">
+      <c r="Q24" s="154"/>
+      <c r="R24" s="154"/>
+      <c r="S24" s="154"/>
+      <c r="T24" s="154" t="s">
         <v>113</v>
       </c>
-      <c r="U24" s="166"/>
-      <c r="V24" s="166"/>
+      <c r="U24" s="154"/>
+      <c r="V24" s="154"/>
     </row>
     <row r="25" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A25" s="44">
         <v>2</v>
       </c>
-      <c r="B25" s="186" t="s">
+      <c r="B25" s="180" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="187"/>
-      <c r="D25" s="187"/>
-      <c r="E25" s="187"/>
-      <c r="F25" s="187"/>
-      <c r="G25" s="187"/>
-      <c r="H25" s="187"/>
-      <c r="I25" s="163" t="s">
+      <c r="C25" s="181"/>
+      <c r="D25" s="181"/>
+      <c r="E25" s="181"/>
+      <c r="F25" s="181"/>
+      <c r="G25" s="181"/>
+      <c r="H25" s="181"/>
+      <c r="I25" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="J25" s="164"/>
-      <c r="K25" s="164"/>
-      <c r="L25" s="165"/>
-      <c r="M25" s="188" t="s">
+      <c r="J25" s="152"/>
+      <c r="K25" s="152"/>
+      <c r="L25" s="153"/>
+      <c r="M25" s="182" t="s">
         <v>48</v>
       </c>
-      <c r="N25" s="162"/>
-      <c r="O25" s="162"/>
-      <c r="P25" s="169" t="s">
+      <c r="N25" s="150"/>
+      <c r="O25" s="150"/>
+      <c r="P25" s="164" t="s">
         <v>114</v>
       </c>
-      <c r="Q25" s="166"/>
-      <c r="R25" s="166"/>
-      <c r="S25" s="166"/>
-      <c r="T25" s="166" t="s">
+      <c r="Q25" s="154"/>
+      <c r="R25" s="154"/>
+      <c r="S25" s="154"/>
+      <c r="T25" s="154" t="s">
         <v>115</v>
       </c>
-      <c r="U25" s="166"/>
-      <c r="V25" s="166"/>
+      <c r="U25" s="154"/>
+      <c r="V25" s="154"/>
     </row>
     <row r="26" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A26" s="44">
         <v>3</v>
       </c>
-      <c r="B26" s="191" t="s">
+      <c r="B26" s="184" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="187"/>
-      <c r="D26" s="187"/>
-      <c r="E26" s="187"/>
-      <c r="F26" s="187"/>
-      <c r="G26" s="187"/>
-      <c r="H26" s="192"/>
-      <c r="I26" s="163" t="s">
+      <c r="C26" s="181"/>
+      <c r="D26" s="181"/>
+      <c r="E26" s="181"/>
+      <c r="F26" s="181"/>
+      <c r="G26" s="181"/>
+      <c r="H26" s="185"/>
+      <c r="I26" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="J26" s="164"/>
-      <c r="K26" s="164"/>
-      <c r="L26" s="165"/>
-      <c r="M26" s="188" t="s">
+      <c r="J26" s="152"/>
+      <c r="K26" s="152"/>
+      <c r="L26" s="153"/>
+      <c r="M26" s="182" t="s">
         <v>48</v>
       </c>
-      <c r="N26" s="162"/>
-      <c r="O26" s="162"/>
-      <c r="P26" s="166" t="s">
+      <c r="N26" s="150"/>
+      <c r="O26" s="150"/>
+      <c r="P26" s="154" t="s">
         <v>117</v>
       </c>
-      <c r="Q26" s="166"/>
-      <c r="R26" s="166"/>
-      <c r="S26" s="166"/>
-      <c r="T26" s="166" t="s">
+      <c r="Q26" s="154"/>
+      <c r="R26" s="154"/>
+      <c r="S26" s="154"/>
+      <c r="T26" s="154" t="s">
         <v>118</v>
       </c>
-      <c r="U26" s="166"/>
-      <c r="V26" s="166"/>
+      <c r="U26" s="154"/>
+      <c r="V26" s="154"/>
     </row>
     <row r="27" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="M27" s="1"/>
@@ -5879,73 +5687,73 @@
       <c r="A29" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="184" t="s">
+      <c r="B29" s="178" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="184"/>
-      <c r="D29" s="184"/>
-      <c r="E29" s="184"/>
-      <c r="F29" s="184"/>
-      <c r="G29" s="184"/>
-      <c r="H29" s="184"/>
-      <c r="I29" s="184" t="s">
+      <c r="C29" s="178"/>
+      <c r="D29" s="178"/>
+      <c r="E29" s="178"/>
+      <c r="F29" s="178"/>
+      <c r="G29" s="178"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="178" t="s">
         <v>54</v>
       </c>
-      <c r="J29" s="184"/>
-      <c r="K29" s="184"/>
-      <c r="L29" s="184"/>
-      <c r="M29" s="184" t="s">
+      <c r="J29" s="178"/>
+      <c r="K29" s="178"/>
+      <c r="L29" s="178"/>
+      <c r="M29" s="178" t="s">
         <v>42</v>
       </c>
-      <c r="N29" s="184"/>
-      <c r="O29" s="184"/>
-      <c r="P29" s="185" t="s">
+      <c r="N29" s="178"/>
+      <c r="O29" s="178"/>
+      <c r="P29" s="179" t="s">
         <v>45</v>
       </c>
-      <c r="Q29" s="185"/>
-      <c r="R29" s="185"/>
-      <c r="S29" s="185"/>
-      <c r="T29" s="146" t="s">
+      <c r="Q29" s="179"/>
+      <c r="R29" s="179"/>
+      <c r="S29" s="179"/>
+      <c r="T29" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="U29" s="147"/>
-      <c r="V29" s="148"/>
+      <c r="U29" s="139"/>
+      <c r="V29" s="140"/>
     </row>
     <row r="30" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A30" s="44">
         <v>1</v>
       </c>
-      <c r="B30" s="186" t="s">
+      <c r="B30" s="180" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="187"/>
-      <c r="D30" s="187"/>
-      <c r="E30" s="187"/>
-      <c r="F30" s="187"/>
-      <c r="G30" s="187"/>
-      <c r="H30" s="187"/>
-      <c r="I30" s="163" t="s">
+      <c r="C30" s="181"/>
+      <c r="D30" s="181"/>
+      <c r="E30" s="181"/>
+      <c r="F30" s="181"/>
+      <c r="G30" s="181"/>
+      <c r="H30" s="181"/>
+      <c r="I30" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="J30" s="164"/>
-      <c r="K30" s="164"/>
-      <c r="L30" s="165"/>
-      <c r="M30" s="188" t="s">
+      <c r="J30" s="152"/>
+      <c r="K30" s="152"/>
+      <c r="L30" s="153"/>
+      <c r="M30" s="182" t="s">
         <v>48</v>
       </c>
-      <c r="N30" s="162"/>
-      <c r="O30" s="162"/>
-      <c r="P30" s="169" t="s">
+      <c r="N30" s="150"/>
+      <c r="O30" s="150"/>
+      <c r="P30" s="164" t="s">
         <v>83</v>
       </c>
-      <c r="Q30" s="166"/>
-      <c r="R30" s="166"/>
-      <c r="S30" s="166"/>
-      <c r="T30" s="166" t="s">
+      <c r="Q30" s="154"/>
+      <c r="R30" s="154"/>
+      <c r="S30" s="154"/>
+      <c r="T30" s="154" t="s">
         <v>113</v>
       </c>
-      <c r="U30" s="166"/>
-      <c r="V30" s="166"/>
+      <c r="U30" s="154"/>
+      <c r="V30" s="154"/>
     </row>
     <row r="31" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A31" s="44">
@@ -5960,28 +5768,28 @@
       <c r="F31" s="47"/>
       <c r="G31" s="47"/>
       <c r="H31" s="47"/>
-      <c r="I31" s="163" t="s">
+      <c r="I31" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="J31" s="164"/>
-      <c r="K31" s="164"/>
-      <c r="L31" s="165"/>
-      <c r="M31" s="188" t="s">
+      <c r="J31" s="152"/>
+      <c r="K31" s="152"/>
+      <c r="L31" s="153"/>
+      <c r="M31" s="182" t="s">
         <v>48</v>
       </c>
-      <c r="N31" s="162"/>
-      <c r="O31" s="162"/>
-      <c r="P31" s="169" t="s">
+      <c r="N31" s="150"/>
+      <c r="O31" s="150"/>
+      <c r="P31" s="164" t="s">
         <v>114</v>
       </c>
-      <c r="Q31" s="166"/>
-      <c r="R31" s="166"/>
-      <c r="S31" s="166"/>
-      <c r="T31" s="166" t="s">
+      <c r="Q31" s="154"/>
+      <c r="R31" s="154"/>
+      <c r="S31" s="154"/>
+      <c r="T31" s="154" t="s">
         <v>120</v>
       </c>
-      <c r="U31" s="166"/>
-      <c r="V31" s="166"/>
+      <c r="U31" s="154"/>
+      <c r="V31" s="154"/>
     </row>
     <row r="32" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A32" s="44">
@@ -5996,28 +5804,28 @@
       <c r="F32" s="50"/>
       <c r="G32" s="50"/>
       <c r="H32" s="54"/>
-      <c r="I32" s="163" t="s">
+      <c r="I32" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="J32" s="164"/>
-      <c r="K32" s="164"/>
-      <c r="L32" s="165"/>
-      <c r="M32" s="188" t="s">
+      <c r="J32" s="152"/>
+      <c r="K32" s="152"/>
+      <c r="L32" s="153"/>
+      <c r="M32" s="182" t="s">
         <v>48</v>
       </c>
-      <c r="N32" s="162"/>
-      <c r="O32" s="162"/>
-      <c r="P32" s="166" t="s">
+      <c r="N32" s="150"/>
+      <c r="O32" s="150"/>
+      <c r="P32" s="154" t="s">
         <v>117</v>
       </c>
-      <c r="Q32" s="166"/>
-      <c r="R32" s="166"/>
-      <c r="S32" s="166"/>
-      <c r="T32" s="169" t="s">
+      <c r="Q32" s="154"/>
+      <c r="R32" s="154"/>
+      <c r="S32" s="154"/>
+      <c r="T32" s="164" t="s">
         <v>122</v>
       </c>
-      <c r="U32" s="166"/>
-      <c r="V32" s="166"/>
+      <c r="U32" s="154"/>
+      <c r="V32" s="154"/>
     </row>
     <row r="33" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A33" s="44">
@@ -6032,28 +5840,28 @@
       <c r="F33" s="50"/>
       <c r="G33" s="50"/>
       <c r="H33" s="54"/>
-      <c r="I33" s="163" t="s">
+      <c r="I33" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="J33" s="164"/>
-      <c r="K33" s="164"/>
-      <c r="L33" s="165"/>
-      <c r="M33" s="188" t="s">
+      <c r="J33" s="152"/>
+      <c r="K33" s="152"/>
+      <c r="L33" s="153"/>
+      <c r="M33" s="182" t="s">
         <v>48</v>
       </c>
-      <c r="N33" s="162"/>
-      <c r="O33" s="162"/>
-      <c r="P33" s="166" t="s">
+      <c r="N33" s="150"/>
+      <c r="O33" s="150"/>
+      <c r="P33" s="154" t="s">
         <v>124</v>
       </c>
-      <c r="Q33" s="166"/>
-      <c r="R33" s="166"/>
-      <c r="S33" s="166"/>
-      <c r="T33" s="166" t="s">
+      <c r="Q33" s="154"/>
+      <c r="R33" s="154"/>
+      <c r="S33" s="154"/>
+      <c r="T33" s="154" t="s">
         <v>125</v>
       </c>
-      <c r="U33" s="166"/>
-      <c r="V33" s="166"/>
+      <c r="U33" s="154"/>
+      <c r="V33" s="154"/>
     </row>
     <row r="34" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A34" s="44">
@@ -6068,28 +5876,28 @@
       <c r="F34" s="50"/>
       <c r="G34" s="50"/>
       <c r="H34" s="54"/>
-      <c r="I34" s="163" t="s">
+      <c r="I34" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="J34" s="164"/>
-      <c r="K34" s="164"/>
-      <c r="L34" s="165"/>
-      <c r="M34" s="188" t="s">
+      <c r="J34" s="152"/>
+      <c r="K34" s="152"/>
+      <c r="L34" s="153"/>
+      <c r="M34" s="182" t="s">
         <v>48</v>
       </c>
-      <c r="N34" s="162"/>
-      <c r="O34" s="162"/>
-      <c r="P34" s="166" t="s">
+      <c r="N34" s="150"/>
+      <c r="O34" s="150"/>
+      <c r="P34" s="154" t="s">
         <v>127</v>
       </c>
-      <c r="Q34" s="166"/>
-      <c r="R34" s="166"/>
-      <c r="S34" s="166"/>
-      <c r="T34" s="166" t="s">
+      <c r="Q34" s="154"/>
+      <c r="R34" s="154"/>
+      <c r="S34" s="154"/>
+      <c r="T34" s="154" t="s">
         <v>128</v>
       </c>
-      <c r="U34" s="166"/>
-      <c r="V34" s="166"/>
+      <c r="U34" s="154"/>
+      <c r="V34" s="154"/>
     </row>
   </sheetData>
   <mergeCells count="121">
@@ -6097,9 +5905,9 @@
     <mergeCell ref="M34:O34"/>
     <mergeCell ref="P34:S34"/>
     <mergeCell ref="T34:V34"/>
-    <mergeCell ref="B11:B20"/>
-    <mergeCell ref="C12:C20"/>
-    <mergeCell ref="D13:D18"/>
+    <mergeCell ref="B12:B20"/>
+    <mergeCell ref="D13:D20"/>
+    <mergeCell ref="E14:E19"/>
     <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="T1:T2"/>
@@ -6155,26 +5963,18 @@
     <mergeCell ref="M24:O24"/>
     <mergeCell ref="P24:S24"/>
     <mergeCell ref="T24:V24"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="P17:S17"/>
-    <mergeCell ref="T17:V17"/>
     <mergeCell ref="I18:L18"/>
     <mergeCell ref="M18:O18"/>
     <mergeCell ref="P18:S18"/>
     <mergeCell ref="T18:V18"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="P19:S19"/>
+    <mergeCell ref="T19:V19"/>
     <mergeCell ref="I20:L20"/>
     <mergeCell ref="M20:O20"/>
     <mergeCell ref="P20:S20"/>
     <mergeCell ref="T20:V20"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="P19:S19"/>
-    <mergeCell ref="T19:V19"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="P14:S14"/>
-    <mergeCell ref="T14:V14"/>
     <mergeCell ref="I15:L15"/>
     <mergeCell ref="M15:O15"/>
     <mergeCell ref="P15:S15"/>
@@ -6183,10 +5983,10 @@
     <mergeCell ref="M16:O16"/>
     <mergeCell ref="P16:S16"/>
     <mergeCell ref="T16:V16"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="P11:S11"/>
-    <mergeCell ref="T11:V11"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="P17:S17"/>
+    <mergeCell ref="T17:V17"/>
     <mergeCell ref="I12:L12"/>
     <mergeCell ref="M12:O12"/>
     <mergeCell ref="P12:S12"/>
@@ -6195,15 +5995,14 @@
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="P13:S13"/>
     <mergeCell ref="T13:V13"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="T9:V9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="P10:S10"/>
-    <mergeCell ref="T10:V10"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="P14:S14"/>
+    <mergeCell ref="T14:V14"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="P11:S11"/>
+    <mergeCell ref="T11:V11"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="E5:H5"/>
     <mergeCell ref="I5:L5"/>
@@ -6214,6 +6013,15 @@
     <mergeCell ref="M8:O8"/>
     <mergeCell ref="P8:S8"/>
     <mergeCell ref="T8:V8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="T9:V9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="P10:S10"/>
+    <mergeCell ref="T10:V10"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6240,126 +6048,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="111" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="128" t="s">
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="129"/>
-      <c r="M1" s="134" t="s">
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="138" t="s">
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="130" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="149" t="s">
+      <c r="R1" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="150"/>
-      <c r="T1" s="143" t="s">
+      <c r="S1" s="143"/>
+      <c r="T1" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="139" t="s">
+      <c r="U1" s="141" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="140"/>
+      <c r="V1" s="132"/>
     </row>
     <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="122"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="136"/>
-      <c r="N2" s="137"/>
-      <c r="O2" s="137"/>
-      <c r="P2" s="137"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="152"/>
-      <c r="S2" s="153"/>
-      <c r="T2" s="146"/>
-      <c r="U2" s="141"/>
-      <c r="V2" s="142"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="130"/>
+      <c r="R2" s="145"/>
+      <c r="S2" s="146"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="133"/>
+      <c r="V2" s="134"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A3" s="122"/>
-      <c r="B3" s="123"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="123"/>
-      <c r="F3" s="123"/>
-      <c r="G3" s="123"/>
-      <c r="H3" s="123"/>
-      <c r="I3" s="128" t="s">
+      <c r="A3" s="114"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="134" t="s">
+      <c r="J3" s="121"/>
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="126" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="135"/>
-      <c r="O3" s="135"/>
-      <c r="P3" s="135"/>
-      <c r="Q3" s="138" t="s">
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="149" t="s">
+      <c r="R3" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="150"/>
-      <c r="T3" s="138" t="s">
+      <c r="S3" s="143"/>
+      <c r="T3" s="130" t="s">
         <v>16</v>
       </c>
-      <c r="U3" s="217" t="s">
-        <v>261</v>
-      </c>
-      <c r="V3" s="140"/>
+      <c r="U3" s="131" t="s">
+        <v>241</v>
+      </c>
+      <c r="V3" s="132"/>
     </row>
     <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A4" s="125"/>
-      <c r="B4" s="126"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="126"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="136"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137"/>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="138"/>
-      <c r="R4" s="152"/>
-      <c r="S4" s="153"/>
-      <c r="T4" s="138"/>
-      <c r="U4" s="141"/>
-      <c r="V4" s="142"/>
+      <c r="A4" s="117"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="128"/>
+      <c r="N4" s="129"/>
+      <c r="O4" s="129"/>
+      <c r="P4" s="129"/>
+      <c r="Q4" s="130"/>
+      <c r="R4" s="145"/>
+      <c r="S4" s="146"/>
+      <c r="T4" s="130"/>
+      <c r="U4" s="133"/>
+      <c r="V4" s="134"/>
     </row>
     <row r="5" spans="1:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A5" s="157" t="s">
@@ -6505,7 +6313,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="6" width="3.6640625" style="5"/>
@@ -6524,106 +6332,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="111" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="128" t="s">
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="129"/>
-      <c r="K1" s="134" t="s">
+      <c r="J1" s="121"/>
+      <c r="K1" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="143" t="s">
+      <c r="L1" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="149" t="s">
+      <c r="M1" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="138" t="s">
+      <c r="N1" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="138"/>
-      <c r="P1" s="139" t="s">
+      <c r="O1" s="130"/>
+      <c r="P1" s="141" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="140"/>
+      <c r="Q1" s="132"/>
     </row>
     <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="122"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="146"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="141"/>
-      <c r="Q2" s="142"/>
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="145"/>
+      <c r="N2" s="130"/>
+      <c r="O2" s="130"/>
+      <c r="P2" s="133"/>
+      <c r="Q2" s="134"/>
     </row>
     <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A3" s="122"/>
-      <c r="B3" s="123"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="123"/>
-      <c r="F3" s="123"/>
-      <c r="G3" s="123"/>
-      <c r="H3" s="123"/>
-      <c r="I3" s="128" t="s">
+      <c r="A3" s="114"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="129"/>
-      <c r="K3" s="134" t="s">
+      <c r="J3" s="121"/>
+      <c r="K3" s="126" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="143" t="s">
+      <c r="L3" s="135" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="149" t="s">
+      <c r="M3" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="138" t="s">
+      <c r="N3" s="130" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="138"/>
-      <c r="P3" s="217" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q3" s="140"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="131" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q3" s="132"/>
     </row>
     <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A4" s="125"/>
-      <c r="B4" s="126"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="126"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="136"/>
-      <c r="L4" s="146"/>
-      <c r="M4" s="152"/>
-      <c r="N4" s="138"/>
-      <c r="O4" s="138"/>
-      <c r="P4" s="141"/>
-      <c r="Q4" s="142"/>
+      <c r="A4" s="117"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="128"/>
+      <c r="L4" s="138"/>
+      <c r="M4" s="145"/>
+      <c r="N4" s="130"/>
+      <c r="O4" s="130"/>
+      <c r="P4" s="133"/>
+      <c r="Q4" s="134"/>
     </row>
     <row r="5" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A5" s="157" t="s">
@@ -6657,29 +6465,29 @@
       <c r="Q5" s="158"/>
     </row>
     <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A6" s="201" t="s">
+      <c r="A6" s="194" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="201"/>
-      <c r="C6" s="201"/>
-      <c r="D6" s="201"/>
-      <c r="E6" s="201"/>
-      <c r="F6" s="201"/>
-      <c r="G6" s="201"/>
-      <c r="H6" s="202" t="s">
+      <c r="B6" s="194"/>
+      <c r="C6" s="194"/>
+      <c r="D6" s="194"/>
+      <c r="E6" s="194"/>
+      <c r="F6" s="194"/>
+      <c r="G6" s="194"/>
+      <c r="H6" s="195" t="s">
         <v>133</v>
       </c>
-      <c r="I6" s="203"/>
-      <c r="J6" s="203"/>
-      <c r="K6" s="203"/>
-      <c r="L6" s="203"/>
-      <c r="M6" s="203"/>
-      <c r="N6" s="203"/>
-      <c r="O6" s="202" t="s">
+      <c r="I6" s="196"/>
+      <c r="J6" s="196"/>
+      <c r="K6" s="196"/>
+      <c r="L6" s="196"/>
+      <c r="M6" s="196"/>
+      <c r="N6" s="196"/>
+      <c r="O6" s="195" t="s">
         <v>134</v>
       </c>
-      <c r="P6" s="203"/>
-      <c r="Q6" s="203"/>
+      <c r="P6" s="196"/>
+      <c r="Q6" s="196"/>
     </row>
     <row r="7" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A7" s="8" t="s">
@@ -6723,153 +6531,153 @@
       </c>
     </row>
     <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A10" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
+      <c r="A10" s="189" t="s">
+        <v>251</v>
+      </c>
+      <c r="B10" s="190"/>
+      <c r="C10" s="190"/>
+      <c r="D10" s="190"/>
+      <c r="E10" s="190"/>
       <c r="H10" s="11"/>
       <c r="I10" s="4"/>
-      <c r="J10" s="208" t="s">
-        <v>142</v>
-      </c>
-      <c r="K10" s="209"/>
-      <c r="L10" s="73" t="s">
-        <v>187</v>
-      </c>
       <c r="O10" s="11"/>
     </row>
     <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A11" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="4"/>
-      <c r="J11" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="K11" s="22"/>
-      <c r="L11" s="23" t="s">
-        <v>57</v>
+      <c r="J11" s="201" t="s">
+        <v>142</v>
+      </c>
+      <c r="K11" s="202"/>
+      <c r="L11" s="73" t="s">
+        <v>187</v>
       </c>
       <c r="O11" s="11"/>
     </row>
     <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A12" s="11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="4"/>
       <c r="J12" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K12" s="22"/>
       <c r="L12" s="23" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="O12" s="11"/>
     </row>
     <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A13" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="4"/>
       <c r="J13" s="21" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="K13" s="22"/>
       <c r="L13" s="23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O13" s="11"/>
     </row>
     <row r="14" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A14" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="H14" s="11"/>
       <c r="I14" s="4"/>
       <c r="J14" s="21" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="K14" s="22"/>
       <c r="L14" s="23" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O14" s="11"/>
     </row>
     <row r="15" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A15" s="11" t="s">
-        <v>150</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
       <c r="H15" s="11"/>
+      <c r="I15" s="4"/>
       <c r="J15" s="21" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K15" s="22"/>
       <c r="L15" s="23" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="O15" s="11"/>
     </row>
     <row r="16" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A16" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
+        <v>150</v>
+      </c>
       <c r="H16" s="11"/>
       <c r="J16" s="21" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K16" s="22"/>
       <c r="L16" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="O16" s="11"/>
+    </row>
+    <row r="17" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A17" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="J17" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="K17" s="22"/>
+      <c r="L17" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="O16" s="11"/>
-    </row>
-    <row r="17" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A17" s="92" t="s">
-        <v>239</v>
-      </c>
-      <c r="H17" s="11"/>
-      <c r="J17" s="93" t="s">
-        <v>240</v>
-      </c>
-      <c r="K17" s="94"/>
-      <c r="L17" s="95" t="s">
-        <v>241</v>
-      </c>
       <c r="O17" s="11"/>
     </row>
     <row r="18" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A18" s="86" t="s">
+        <v>236</v>
+      </c>
       <c r="H18" s="11"/>
+      <c r="J18" s="86"/>
+      <c r="K18" s="86"/>
+      <c r="L18" s="86"/>
       <c r="O18" s="11"/>
     </row>
     <row r="19" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A19" s="11" t="s">
+      <c r="H19" s="11"/>
+      <c r="O19" s="11"/>
+    </row>
+    <row r="20" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A20" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="H19" s="11"/>
-      <c r="I19" s="3" t="s">
+      <c r="H20" s="11"/>
+      <c r="I20" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="O19" s="11"/>
-    </row>
-    <row r="20" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="J20" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="O20" s="11"/>
     </row>
@@ -6877,117 +6685,110 @@
       <c r="A21" s="11"/>
       <c r="H21" s="11"/>
       <c r="J21" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O21" s="11"/>
     </row>
     <row r="22" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A22" s="11"/>
-      <c r="G22" s="12"/>
       <c r="H22" s="11"/>
-      <c r="J22" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="K22" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="L22" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="M22" s="24" t="s">
-        <v>114</v>
+      <c r="J22" s="3" t="s">
+        <v>156</v>
       </c>
       <c r="O22" s="11"/>
     </row>
     <row r="23" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A23" s="11"/>
+      <c r="G23" s="12"/>
       <c r="H23" s="11"/>
-      <c r="J23" s="210" t="s">
-        <v>160</v>
-      </c>
-      <c r="K23" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="L23" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="M23" s="27" t="s">
-        <v>162</v>
+      <c r="J23" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="K23" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="L23" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="M23" s="24" t="s">
+        <v>114</v>
       </c>
       <c r="O23" s="11"/>
     </row>
-    <row r="24" spans="1:15" s="3" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="24" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A24" s="11"/>
       <c r="H24" s="11"/>
-      <c r="J24" s="211"/>
-      <c r="K24" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="L24" s="28" t="s">
-        <v>164</v>
+      <c r="J24" s="203" t="s">
+        <v>160</v>
+      </c>
+      <c r="K24" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="L24" s="25" t="s">
+        <v>161</v>
       </c>
       <c r="M24" s="27" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O24" s="11"/>
     </row>
-    <row r="25" spans="1:15" s="3" customFormat="1" ht="47.1" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="25" spans="1:15" s="3" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A25" s="11"/>
       <c r="H25" s="11"/>
-      <c r="J25" s="211"/>
-      <c r="K25" s="75" t="s">
-        <v>192</v>
+      <c r="J25" s="204"/>
+      <c r="K25" s="27" t="s">
+        <v>163</v>
       </c>
       <c r="L25" s="28" t="s">
         <v>164</v>
       </c>
       <c r="M25" s="27" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O25" s="11"/>
     </row>
-    <row r="26" spans="1:15" s="3" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="26" spans="1:15" s="3" customFormat="1" ht="47.1" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A26" s="11"/>
       <c r="H26" s="11"/>
-      <c r="J26" s="211"/>
+      <c r="J26" s="204"/>
       <c r="K26" s="75" t="s">
-        <v>190</v>
-      </c>
-      <c r="L26" s="74" t="s">
-        <v>191</v>
+        <v>192</v>
+      </c>
+      <c r="L26" s="28" t="s">
+        <v>164</v>
       </c>
       <c r="M26" s="27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O26" s="11"/>
     </row>
-    <row r="27" spans="1:15" s="3" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="27" spans="1:15" s="3" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A27" s="11"/>
       <c r="H27" s="11"/>
-      <c r="J27" s="211"/>
+      <c r="J27" s="204"/>
       <c r="K27" s="75" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L27" s="74" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="M27" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O27" s="11"/>
     </row>
     <row r="28" spans="1:15" s="3" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A28" s="11"/>
       <c r="H28" s="11"/>
-      <c r="J28" s="212"/>
-      <c r="K28" s="98" t="s">
-        <v>242</v>
-      </c>
-      <c r="L28" s="91" t="s">
-        <v>243</v>
-      </c>
-      <c r="M28" s="99" t="s">
-        <v>244</v>
+      <c r="J28" s="204"/>
+      <c r="K28" s="75" t="s">
+        <v>188</v>
+      </c>
+      <c r="L28" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="M28" s="27" t="s">
+        <v>168</v>
       </c>
       <c r="O28" s="11"/>
     </row>
@@ -6995,10 +6796,10 @@
       <c r="A29" s="10"/>
       <c r="H29" s="10"/>
       <c r="I29" s="3"/>
-      <c r="J29" s="101" t="s">
+      <c r="J29" s="93" t="s">
         <v>91</v>
       </c>
-      <c r="K29" s="102"/>
+      <c r="K29" s="94"/>
       <c r="L29" s="25" t="s">
         <v>169</v>
       </c>
@@ -7072,14 +6873,14 @@
       <c r="G35" s="14"/>
       <c r="H35" s="10"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="215" t="s">
+      <c r="J35" s="205" t="s">
         <v>219</v>
       </c>
-      <c r="K35" s="216"/>
-      <c r="L35" s="215" t="s">
+      <c r="K35" s="206"/>
+      <c r="L35" s="205" t="s">
         <v>218</v>
       </c>
-      <c r="M35" s="216"/>
+      <c r="M35" s="206"/>
       <c r="O35" s="10"/>
     </row>
     <row r="36" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7092,14 +6893,14 @@
       <c r="G36" s="14"/>
       <c r="H36" s="10"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="204" t="s">
+      <c r="J36" s="197" t="s">
         <v>57</v>
       </c>
-      <c r="K36" s="205"/>
-      <c r="L36" s="206" t="s">
+      <c r="K36" s="198"/>
+      <c r="L36" s="199" t="s">
         <v>225</v>
       </c>
-      <c r="M36" s="207"/>
+      <c r="M36" s="200"/>
       <c r="O36" s="10"/>
     </row>
     <row r="37" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7112,14 +6913,14 @@
       <c r="G37" s="14"/>
       <c r="H37" s="10"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="204" t="s">
+      <c r="J37" s="197" t="s">
         <v>215</v>
       </c>
-      <c r="K37" s="205"/>
-      <c r="L37" s="206" t="s">
+      <c r="K37" s="198"/>
+      <c r="L37" s="199" t="s">
         <v>226</v>
       </c>
-      <c r="M37" s="207"/>
+      <c r="M37" s="200"/>
       <c r="O37" s="10"/>
     </row>
     <row r="38" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7132,14 +6933,14 @@
       <c r="G38" s="14"/>
       <c r="H38" s="10"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="204" t="s">
+      <c r="J38" s="197" t="s">
         <v>101</v>
       </c>
-      <c r="K38" s="205"/>
-      <c r="L38" s="206" t="s">
+      <c r="K38" s="198"/>
+      <c r="L38" s="199" t="s">
         <v>227</v>
       </c>
-      <c r="M38" s="207"/>
+      <c r="M38" s="200"/>
       <c r="O38" s="10"/>
     </row>
     <row r="39" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7152,14 +6953,14 @@
       <c r="G39" s="14"/>
       <c r="H39" s="10"/>
       <c r="I39" s="3"/>
-      <c r="J39" s="204" t="s">
+      <c r="J39" s="197" t="s">
         <v>67</v>
       </c>
-      <c r="K39" s="205"/>
-      <c r="L39" s="204" t="s">
+      <c r="K39" s="198"/>
+      <c r="L39" s="197" t="s">
         <v>228</v>
       </c>
-      <c r="M39" s="205"/>
+      <c r="M39" s="198"/>
       <c r="O39" s="10"/>
     </row>
     <row r="40" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7172,18 +6973,18 @@
       <c r="G40" s="14"/>
       <c r="H40" s="10"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="204" t="s">
+      <c r="J40" s="197" t="s">
         <v>216</v>
       </c>
-      <c r="K40" s="205"/>
-      <c r="L40" s="204" t="s">
+      <c r="K40" s="198"/>
+      <c r="L40" s="197" t="s">
         <v>229</v>
       </c>
-      <c r="M40" s="205"/>
+      <c r="M40" s="198"/>
       <c r="O40" s="10"/>
     </row>
     <row r="41" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A41" s="13"/>
+      <c r="A41" s="15"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
       <c r="D41" s="14"/>
@@ -7192,74 +6993,54 @@
       <c r="G41" s="14"/>
       <c r="H41" s="10"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="96" t="s">
-        <v>245</v>
-      </c>
-      <c r="K41" s="97"/>
-      <c r="L41" s="96" t="s">
-        <v>246</v>
-      </c>
-      <c r="M41" s="84"/>
+      <c r="J41" s="197" t="s">
+        <v>217</v>
+      </c>
+      <c r="K41" s="198"/>
+      <c r="L41" s="197" t="s">
+        <v>230</v>
+      </c>
+      <c r="M41" s="198"/>
       <c r="O41" s="10"/>
     </row>
     <row r="42" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
       <c r="H42" s="10"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="96" t="s">
-        <v>247</v>
-      </c>
-      <c r="K42" s="97"/>
-      <c r="L42" s="96" t="s">
-        <v>248</v>
-      </c>
-      <c r="M42" s="84"/>
+      <c r="J42" s="76"/>
       <c r="O42" s="10"/>
     </row>
     <row r="43" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
       <c r="H43" s="10"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="213" t="s">
-        <v>249</v>
-      </c>
-      <c r="K43" s="214"/>
-      <c r="L43" s="96" t="s">
-        <v>250</v>
-      </c>
-      <c r="M43" s="84"/>
+      <c r="J43" s="76" t="s">
+        <v>221</v>
+      </c>
       <c r="O43" s="10"/>
     </row>
     <row r="44" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A44" s="15"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
       <c r="H44" s="10"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="204" t="s">
-        <v>217</v>
-      </c>
-      <c r="K44" s="205"/>
-      <c r="L44" s="204" t="s">
-        <v>230</v>
-      </c>
-      <c r="M44" s="205"/>
+      <c r="J44" s="76" t="s">
+        <v>222</v>
+      </c>
       <c r="O44" s="10"/>
     </row>
     <row r="45" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7271,7 +7052,9 @@
       <c r="G45" s="3"/>
       <c r="H45" s="10"/>
       <c r="I45" s="3"/>
-      <c r="J45" s="76"/>
+      <c r="J45" s="76" t="s">
+        <v>223</v>
+      </c>
       <c r="O45" s="10"/>
     </row>
     <row r="46" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7283,9 +7066,7 @@
       <c r="G46" s="3"/>
       <c r="H46" s="10"/>
       <c r="I46" s="3"/>
-      <c r="J46" s="76" t="s">
-        <v>221</v>
-      </c>
+      <c r="J46" s="76"/>
       <c r="O46" s="10"/>
     </row>
     <row r="47" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7298,7 +7079,7 @@
       <c r="H47" s="10"/>
       <c r="I47" s="3"/>
       <c r="J47" s="76" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="O47" s="10"/>
     </row>
@@ -7311,12 +7092,19 @@
       <c r="G48" s="3"/>
       <c r="H48" s="10"/>
       <c r="I48" s="3"/>
-      <c r="J48" s="76" t="s">
-        <v>223</v>
+      <c r="J48" s="73" t="s">
+        <v>202</v>
+      </c>
+      <c r="K48" s="193" t="s">
+        <v>210</v>
+      </c>
+      <c r="L48" s="193"/>
+      <c r="M48" s="82" t="s">
+        <v>214</v>
       </c>
       <c r="O48" s="10"/>
     </row>
-    <row r="49" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="49" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
@@ -7325,10 +7113,19 @@
       <c r="G49" s="3"/>
       <c r="H49" s="10"/>
       <c r="I49" s="3"/>
-      <c r="J49" s="76"/>
+      <c r="J49" s="80" t="s">
+        <v>62</v>
+      </c>
+      <c r="K49" s="191" t="s">
+        <v>203</v>
+      </c>
+      <c r="L49" s="191"/>
+      <c r="M49" s="81" t="s">
+        <v>211</v>
+      </c>
       <c r="O49" s="10"/>
     </row>
-    <row r="50" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="50" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
@@ -7337,12 +7134,19 @@
       <c r="G50" s="3"/>
       <c r="H50" s="10"/>
       <c r="I50" s="3"/>
-      <c r="J50" s="76" t="s">
-        <v>197</v>
+      <c r="J50" s="80" t="s">
+        <v>64</v>
+      </c>
+      <c r="K50" s="191" t="s">
+        <v>204</v>
+      </c>
+      <c r="L50" s="191"/>
+      <c r="M50" s="81" t="s">
+        <v>211</v>
       </c>
       <c r="O50" s="10"/>
     </row>
-    <row r="51" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="51" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
@@ -7351,19 +7155,19 @@
       <c r="G51" s="3"/>
       <c r="H51" s="10"/>
       <c r="I51" s="3"/>
-      <c r="J51" s="73" t="s">
-        <v>202</v>
-      </c>
-      <c r="K51" s="198" t="s">
-        <v>210</v>
-      </c>
-      <c r="L51" s="198"/>
-      <c r="M51" s="82" t="s">
-        <v>214</v>
+      <c r="J51" s="80" t="s">
+        <v>57</v>
+      </c>
+      <c r="K51" s="191" t="s">
+        <v>205</v>
+      </c>
+      <c r="L51" s="192"/>
+      <c r="M51" s="81" t="s">
+        <v>211</v>
       </c>
       <c r="O51" s="10"/>
     </row>
-    <row r="52" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="52" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
@@ -7373,18 +7177,18 @@
       <c r="H52" s="10"/>
       <c r="I52" s="3"/>
       <c r="J52" s="80" t="s">
-        <v>62</v>
-      </c>
-      <c r="K52" s="196" t="s">
-        <v>203</v>
-      </c>
-      <c r="L52" s="196"/>
+        <v>198</v>
+      </c>
+      <c r="K52" s="191" t="s">
+        <v>206</v>
+      </c>
+      <c r="L52" s="192"/>
       <c r="M52" s="81" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O52" s="10"/>
     </row>
-    <row r="53" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="53" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
@@ -7394,18 +7198,18 @@
       <c r="H53" s="10"/>
       <c r="I53" s="3"/>
       <c r="J53" s="80" t="s">
-        <v>64</v>
-      </c>
-      <c r="K53" s="196" t="s">
-        <v>204</v>
-      </c>
-      <c r="L53" s="196"/>
+        <v>199</v>
+      </c>
+      <c r="K53" s="191" t="s">
+        <v>207</v>
+      </c>
+      <c r="L53" s="192"/>
       <c r="M53" s="81" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="O53" s="10"/>
     </row>
-    <row r="54" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="54" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
@@ -7415,18 +7219,18 @@
       <c r="H54" s="10"/>
       <c r="I54" s="3"/>
       <c r="J54" s="80" t="s">
-        <v>57</v>
-      </c>
-      <c r="K54" s="196" t="s">
-        <v>205</v>
-      </c>
-      <c r="L54" s="197"/>
+        <v>200</v>
+      </c>
+      <c r="K54" s="191" t="s">
+        <v>208</v>
+      </c>
+      <c r="L54" s="192"/>
       <c r="M54" s="81" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="O54" s="10"/>
     </row>
-    <row r="55" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="55" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
@@ -7436,18 +7240,16 @@
       <c r="H55" s="10"/>
       <c r="I55" s="3"/>
       <c r="J55" s="80" t="s">
-        <v>198</v>
-      </c>
-      <c r="K55" s="196" t="s">
-        <v>206</v>
-      </c>
-      <c r="L55" s="197"/>
-      <c r="M55" s="81" t="s">
-        <v>212</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="K55" s="191" t="s">
+        <v>209</v>
+      </c>
+      <c r="L55" s="192"/>
+      <c r="M55" s="81"/>
       <c r="O55" s="10"/>
     </row>
-    <row r="56" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="56" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -7456,420 +7258,294 @@
       <c r="G56" s="3"/>
       <c r="H56" s="10"/>
       <c r="I56" s="3"/>
-      <c r="J56" s="80" t="s">
-        <v>199</v>
-      </c>
-      <c r="K56" s="196" t="s">
-        <v>207</v>
-      </c>
-      <c r="L56" s="197"/>
-      <c r="M56" s="81" t="s">
-        <v>213</v>
-      </c>
+      <c r="J56" s="30"/>
+      <c r="K56" s="30"/>
+      <c r="L56" s="79"/>
+      <c r="M56" s="79"/>
       <c r="O56" s="10"/>
     </row>
-    <row r="57" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
+    <row r="57" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A57" s="13"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
       <c r="H57" s="10"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="80" t="s">
-        <v>200</v>
-      </c>
-      <c r="K57" s="196" t="s">
-        <v>208</v>
-      </c>
-      <c r="L57" s="197"/>
-      <c r="M57" s="81" t="s">
-        <v>213</v>
+      <c r="I57" s="4"/>
+      <c r="J57" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="O57" s="10"/>
     </row>
-    <row r="58" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
+    <row r="58" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A58" s="13"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
       <c r="H58" s="10"/>
-      <c r="I58" s="3"/>
-      <c r="J58" s="100" t="s">
-        <v>245</v>
-      </c>
-      <c r="K58" s="93" t="s">
-        <v>251</v>
-      </c>
-      <c r="L58" s="94"/>
-      <c r="M58" s="81"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="76" t="s">
+        <v>224</v>
+      </c>
       <c r="O58" s="10"/>
     </row>
-    <row r="59" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
+    <row r="59" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A59" s="15"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
       <c r="H59" s="10"/>
       <c r="I59" s="3"/>
-      <c r="J59" s="96" t="s">
-        <v>247</v>
-      </c>
-      <c r="K59" s="93" t="s">
-        <v>252</v>
-      </c>
-      <c r="L59" s="94"/>
-      <c r="M59" s="81"/>
-      <c r="O59" s="10"/>
-    </row>
-    <row r="60" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="10"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="100" t="s">
-        <v>249</v>
-      </c>
-      <c r="K60" s="199" t="s">
-        <v>253</v>
-      </c>
-      <c r="L60" s="200"/>
-      <c r="M60" s="81"/>
-      <c r="O60" s="10"/>
-    </row>
-    <row r="61" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
+      <c r="J59" s="30"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="31"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2"/>
+    </row>
+    <row r="60" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A60" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="H60" s="11"/>
+      <c r="I60" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="O60" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A61" s="13"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
       <c r="H61" s="10"/>
       <c r="I61" s="3"/>
-      <c r="J61" s="80" t="s">
-        <v>201</v>
-      </c>
-      <c r="K61" s="196" t="s">
-        <v>209</v>
-      </c>
-      <c r="L61" s="197"/>
-      <c r="M61" s="81"/>
-      <c r="O61" s="10"/>
-    </row>
-    <row r="62" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="10"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="30"/>
-      <c r="K62" s="30"/>
-      <c r="L62" s="79"/>
-      <c r="M62" s="79"/>
-      <c r="O62" s="10"/>
-    </row>
-    <row r="63" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="10"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="O63" s="10"/>
-    </row>
-    <row r="64" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="10"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="76" t="s">
-        <v>224</v>
-      </c>
-      <c r="O64" s="10"/>
-    </row>
-    <row r="65" spans="1:17" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A65" s="15"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="10"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="30"/>
-      <c r="K65" s="30"/>
-      <c r="L65" s="2"/>
-      <c r="M65" s="2"/>
-      <c r="N65" s="2"/>
-      <c r="O65" s="31"/>
-      <c r="P65" s="2"/>
-      <c r="Q65" s="2"/>
-    </row>
-    <row r="66" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A66" s="11" t="s">
-        <v>174</v>
-      </c>
+      <c r="J61" s="76" t="s">
+        <v>231</v>
+      </c>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="11"/>
+    </row>
+    <row r="62" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="J62" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="K62" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="L62" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="O62" s="11"/>
+    </row>
+    <row r="63" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A63" s="11"/>
+      <c r="H63" s="11"/>
+      <c r="J63" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="K63" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="L63" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="O63" s="11"/>
+    </row>
+    <row r="64" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A64" s="11"/>
+      <c r="H64" s="11"/>
+      <c r="J64" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="K64" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="L64" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="O64" s="11"/>
+    </row>
+    <row r="65" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="H65" s="11"/>
+      <c r="J65" s="191" t="s">
+        <v>88</v>
+      </c>
+      <c r="K65" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="L65" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="O65" s="11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A66" s="11"/>
       <c r="H66" s="11"/>
-      <c r="I66" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="O66" s="11" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="10"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="76" t="s">
-        <v>231</v>
-      </c>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3"/>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
+      <c r="J66" s="191"/>
+      <c r="K66" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="L66" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="O66" s="11"/>
+    </row>
+    <row r="67" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A67" s="11"/>
+      <c r="H67" s="11"/>
       <c r="O67" s="11"/>
     </row>
-    <row r="68" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="68" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A68" s="11"/>
       <c r="H68" s="11"/>
-      <c r="J68" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="K68" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="L68" s="20" t="s">
-        <v>46</v>
+      <c r="I68" s="4"/>
+      <c r="J68" s="77" t="s">
+        <v>220</v>
+      </c>
+      <c r="N68" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="O68" s="11"/>
     </row>
-    <row r="69" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="69" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A69" s="11"/>
       <c r="H69" s="11"/>
-      <c r="J69" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="K69" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="L69" s="23" t="s">
-        <v>84</v>
-      </c>
+      <c r="I69" s="2"/>
+      <c r="J69" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="K69" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="L69" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
       <c r="O69" s="11"/>
     </row>
-    <row r="70" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="70" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A70" s="11"/>
       <c r="H70" s="11"/>
       <c r="J70" s="21" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K70" s="23" t="s">
         <v>91</v>
       </c>
       <c r="L70" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="11"/>
+    </row>
+    <row r="71" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A71" s="11"/>
+      <c r="H71" s="11"/>
+      <c r="J71" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="K71" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="L71" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="O70" s="11"/>
-    </row>
-    <row r="71" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="H71" s="11"/>
-      <c r="J71" s="196" t="s">
-        <v>88</v>
-      </c>
-      <c r="K71" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="L71" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="O71" s="11" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
+      <c r="O71" s="11"/>
+    </row>
+    <row r="72" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A72" s="11"/>
       <c r="H72" s="11"/>
-      <c r="J72" s="196"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="191" t="s">
+        <v>88</v>
+      </c>
       <c r="K72" s="23" t="s">
-        <v>183</v>
+        <v>92</v>
       </c>
       <c r="L72" s="23" t="s">
-        <v>184</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2"/>
       <c r="O72" s="11"/>
     </row>
-    <row r="73" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="73" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A73" s="11"/>
       <c r="H73" s="11"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="191"/>
+      <c r="K73" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="L73" s="29">
+        <v>0</v>
+      </c>
+      <c r="M73" s="2"/>
+      <c r="N73" s="2"/>
       <c r="O73" s="11"/>
     </row>
-    <row r="74" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="74" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A74" s="11"/>
       <c r="H74" s="11"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="77" t="s">
-        <v>220</v>
-      </c>
-      <c r="N74" s="3" t="s">
-        <v>182</v>
-      </c>
+      <c r="I74" s="2"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
+      <c r="M74" s="2"/>
+      <c r="N74" s="2"/>
       <c r="O74" s="11"/>
     </row>
-    <row r="75" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A75" s="11"/>
-      <c r="H75" s="11"/>
+    <row r="75" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="I75" s="2"/>
-      <c r="J75" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="K75" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="L75" s="20" t="s">
-        <v>46</v>
-      </c>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
-      <c r="O75" s="11"/>
-    </row>
-    <row r="76" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A76" s="11"/>
-      <c r="H76" s="11"/>
-      <c r="J76" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="K76" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="L76" s="23" t="s">
-        <v>84</v>
-      </c>
+    </row>
+    <row r="76" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="I76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
-      <c r="O76" s="11"/>
-    </row>
-    <row r="77" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A77" s="11"/>
-      <c r="H77" s="11"/>
-      <c r="J77" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="K77" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="L77" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
-      <c r="O77" s="11"/>
-    </row>
-    <row r="78" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A78" s="11"/>
-      <c r="H78" s="11"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="196" t="s">
-        <v>88</v>
-      </c>
-      <c r="K78" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="L78" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
-      <c r="O78" s="11"/>
-    </row>
-    <row r="79" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A79" s="11"/>
-      <c r="H79" s="11"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="196"/>
-      <c r="K79" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="L79" s="29">
-        <v>0</v>
-      </c>
-      <c r="M79" s="2"/>
-      <c r="N79" s="2"/>
-      <c r="O79" s="11"/>
-    </row>
-    <row r="80" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A80" s="11"/>
-      <c r="H80" s="11"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="2"/>
-      <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
-      <c r="N80" s="2"/>
-      <c r="O80" s="11"/>
-    </row>
-    <row r="81" spans="9:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="I81" s="2"/>
-      <c r="K81" s="2"/>
-      <c r="L81" s="2"/>
-      <c r="M81" s="2"/>
-      <c r="N81" s="2"/>
-    </row>
-    <row r="82" spans="9:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="I82" s="2"/>
-      <c r="K82" s="2"/>
-      <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
-      <c r="N82" s="2"/>
-    </row>
-    <row r="83" spans="9:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="I83" s="3"/>
-      <c r="J83" s="3"/>
-      <c r="K83" s="3"/>
-      <c r="L83" s="3"/>
-      <c r="M83" s="3"/>
-      <c r="N83" s="3"/>
+    </row>
+    <row r="77" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J23:J28"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="J38:K38"/>
+  <mergeCells count="48">
     <mergeCell ref="A1:H4"/>
     <mergeCell ref="N3:O4"/>
     <mergeCell ref="P3:Q4"/>
@@ -7879,8 +7555,8 @@
     <mergeCell ref="I1:J2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="M3:M4"/>
-    <mergeCell ref="J71:J72"/>
-    <mergeCell ref="J78:J79"/>
+    <mergeCell ref="J65:J66"/>
+    <mergeCell ref="J72:J73"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L1:L2"/>
@@ -7889,8 +7565,8 @@
     <mergeCell ref="L39:M39"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="L40:M40"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="L41:M41"/>
     <mergeCell ref="J36:K36"/>
     <mergeCell ref="L36:M36"/>
     <mergeCell ref="J37:K37"/>
@@ -7902,15 +7578,22 @@
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="H6:N6"/>
     <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="K61:L61"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="K50:L50"/>
     <mergeCell ref="K51:L51"/>
     <mergeCell ref="K52:L52"/>
     <mergeCell ref="K53:L53"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J24:J28"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="J38:K38"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/設計/部品在庫管理/機能仕様書_部品在庫照会API.xlsx
+++ b/docs/設計/部品在庫管理/機能仕様書_部品在庫照会API.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usaposu\git\Java-apiCourse-staffservice\docs\設計\部品在庫管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDF4E12-2A3D-4766-B596-D1C2C192131B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC392425-BA46-4581-91CB-E3E0BF97084F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="19" r:id="rId1"/>
@@ -23,16 +23,16 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="4">シーケンス!$A$1:$V$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">リクエスト!$A$1:$AA$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">レスポンス!$A$1:$V$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">レスポンス!$A$1:$V$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">機能概要!$A$1:$AH$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">処理詳細!$A$1:$Q$74</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">処理詳細!$A$1:$Q$82</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="256">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -173,9 +173,6 @@
   </si>
   <si>
     <t>備考</t>
-  </si>
-  <si>
-    <t>Authorization</t>
   </si>
   <si>
     <t>○</t>
@@ -992,14 +989,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>Transaction-id</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>○</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>トランザクションID</t>
     <phoneticPr fontId="13"/>
   </si>
@@ -1027,6 +1016,30 @@
       <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>Authorization</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>data</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Transaction-Id</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>(3) Transaction-Idがリクエストヘッダーに存在しない/または値が存在しない場合、400 Bad Request を返す。</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>"400 Bad Request"</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>(4) Transaction-Idがが「UUID v4 形式」でない場合、400 Bad Requestを返却する。</t>
+    <phoneticPr fontId="11"/>
   </si>
 </sst>
 </file>
@@ -1366,7 +1379,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1616,322 +1629,349 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1940,35 +1980,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2448,23 +2464,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>141194</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>17929</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>161760</xdr:rowOff>
+      <xdr:rowOff>166196</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0D23A42-D473-7DF2-879E-350535A55D3D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C80FA2AD-EB84-5EA2-7F27-4880FEE53779}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2486,8 +2502,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="627529" y="2017059"/>
-          <a:ext cx="7772400" cy="7221466"/>
+          <a:off x="0" y="2017059"/>
+          <a:ext cx="7772400" cy="7225902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2802,65 +2818,65 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.8">
-      <c r="B4" s="90" t="s">
+      <c r="B4" s="91" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="84">
+        <v>45935</v>
+      </c>
+      <c r="D4" s="75" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="85">
+      <c r="E4" s="83" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.8">
+      <c r="B5" s="92"/>
+      <c r="C5" s="84">
         <v>45935</v>
       </c>
-      <c r="D4" s="75" t="s">
-        <v>233</v>
-      </c>
-      <c r="E4" s="84" t="s">
+      <c r="D5" s="75" t="s">
+        <v>232</v>
+      </c>
+      <c r="E5" s="83" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.8">
-      <c r="B5" s="91"/>
-      <c r="C5" s="85">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.8">
+      <c r="B6" s="92"/>
+      <c r="C6" s="84">
         <v>45935</v>
       </c>
-      <c r="D5" s="75" t="s">
-        <v>233</v>
-      </c>
-      <c r="E5" s="84" t="s">
+      <c r="D6" s="75" t="s">
+        <v>232</v>
+      </c>
+      <c r="E6" s="83" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.8">
-      <c r="B6" s="91"/>
-      <c r="C6" s="85">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.8">
+      <c r="B7" s="92"/>
+      <c r="C7" s="84">
         <v>45935</v>
       </c>
-      <c r="D6" s="75" t="s">
-        <v>233</v>
-      </c>
-      <c r="E6" s="84" t="s">
+      <c r="D7" s="75" t="s">
+        <v>232</v>
+      </c>
+      <c r="E7" s="83" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.8">
-      <c r="B7" s="91"/>
-      <c r="C7" s="85">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.8">
+      <c r="B8" s="93"/>
+      <c r="C8" s="84">
         <v>45935</v>
       </c>
-      <c r="D7" s="75" t="s">
-        <v>233</v>
-      </c>
-      <c r="E7" s="84" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.8">
-      <c r="B8" s="92"/>
-      <c r="C8" s="85">
-        <v>45935</v>
-      </c>
       <c r="D8" s="75" t="s">
-        <v>233</v>
-      </c>
-      <c r="E8" s="84" t="s">
-        <v>252</v>
+        <v>232</v>
+      </c>
+      <c r="E8" s="83" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.8">
@@ -3251,452 +3267,452 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="120" t="s">
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="121"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="126" t="s">
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="127"/>
-      <c r="S1" s="127"/>
-      <c r="T1" s="127"/>
-      <c r="U1" s="127"/>
-      <c r="V1" s="130" t="s">
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="130"/>
-      <c r="X1" s="130"/>
-      <c r="Y1" s="142" t="s">
+      <c r="W1" s="116"/>
+      <c r="X1" s="116"/>
+      <c r="Y1" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="143"/>
-      <c r="AA1" s="143"/>
-      <c r="AB1" s="144"/>
-      <c r="AC1" s="135" t="s">
+      <c r="Z1" s="129"/>
+      <c r="AA1" s="129"/>
+      <c r="AB1" s="130"/>
+      <c r="AC1" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="AD1" s="136"/>
-      <c r="AE1" s="137"/>
-      <c r="AF1" s="141" t="s">
+      <c r="AD1" s="122"/>
+      <c r="AE1" s="123"/>
+      <c r="AF1" s="127" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="132"/>
-      <c r="AH1" s="132"/>
+      <c r="AG1" s="118"/>
+      <c r="AH1" s="118"/>
     </row>
     <row r="2" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="114"/>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="123"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="124"/>
-      <c r="O2" s="124"/>
-      <c r="P2" s="125"/>
-      <c r="Q2" s="128"/>
-      <c r="R2" s="129"/>
-      <c r="S2" s="129"/>
-      <c r="T2" s="129"/>
-      <c r="U2" s="129"/>
-      <c r="V2" s="130"/>
-      <c r="W2" s="130"/>
-      <c r="X2" s="130"/>
-      <c r="Y2" s="145"/>
-      <c r="Z2" s="146"/>
-      <c r="AA2" s="146"/>
-      <c r="AB2" s="147"/>
-      <c r="AC2" s="138"/>
-      <c r="AD2" s="139"/>
-      <c r="AE2" s="140"/>
-      <c r="AF2" s="133"/>
-      <c r="AG2" s="134"/>
-      <c r="AH2" s="134"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="110"/>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="115"/>
+      <c r="S2" s="115"/>
+      <c r="T2" s="115"/>
+      <c r="U2" s="115"/>
+      <c r="V2" s="116"/>
+      <c r="W2" s="116"/>
+      <c r="X2" s="116"/>
+      <c r="Y2" s="131"/>
+      <c r="Z2" s="132"/>
+      <c r="AA2" s="132"/>
+      <c r="AB2" s="133"/>
+      <c r="AC2" s="124"/>
+      <c r="AD2" s="125"/>
+      <c r="AE2" s="126"/>
+      <c r="AF2" s="119"/>
+      <c r="AG2" s="120"/>
+      <c r="AH2" s="120"/>
     </row>
     <row r="3" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A3" s="114"/>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="120" t="s">
+      <c r="A3" s="100"/>
+      <c r="B3" s="101"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="121"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="121"/>
-      <c r="P3" s="122"/>
-      <c r="Q3" s="126" t="s">
+      <c r="M3" s="107"/>
+      <c r="N3" s="107"/>
+      <c r="O3" s="107"/>
+      <c r="P3" s="108"/>
+      <c r="Q3" s="112" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="127"/>
-      <c r="S3" s="127"/>
-      <c r="T3" s="127"/>
-      <c r="U3" s="127"/>
-      <c r="V3" s="130" t="s">
+      <c r="R3" s="113"/>
+      <c r="S3" s="113"/>
+      <c r="T3" s="113"/>
+      <c r="U3" s="113"/>
+      <c r="V3" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="W3" s="130"/>
-      <c r="X3" s="130"/>
-      <c r="Y3" s="142" t="s">
+      <c r="W3" s="116"/>
+      <c r="X3" s="116"/>
+      <c r="Y3" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="Z3" s="143"/>
-      <c r="AA3" s="143"/>
-      <c r="AB3" s="144"/>
-      <c r="AC3" s="130" t="s">
+      <c r="Z3" s="129"/>
+      <c r="AA3" s="129"/>
+      <c r="AB3" s="130"/>
+      <c r="AC3" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="AD3" s="130"/>
-      <c r="AE3" s="130"/>
-      <c r="AF3" s="131" t="s">
-        <v>241</v>
-      </c>
-      <c r="AG3" s="132"/>
-      <c r="AH3" s="132"/>
+      <c r="AD3" s="116"/>
+      <c r="AE3" s="116"/>
+      <c r="AF3" s="117" t="s">
+        <v>240</v>
+      </c>
+      <c r="AG3" s="118"/>
+      <c r="AH3" s="118"/>
     </row>
     <row r="4" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A4" s="117"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="119"/>
-      <c r="L4" s="123"/>
-      <c r="M4" s="124"/>
-      <c r="N4" s="124"/>
-      <c r="O4" s="124"/>
-      <c r="P4" s="125"/>
-      <c r="Q4" s="128"/>
-      <c r="R4" s="129"/>
-      <c r="S4" s="129"/>
-      <c r="T4" s="129"/>
-      <c r="U4" s="129"/>
-      <c r="V4" s="130"/>
-      <c r="W4" s="130"/>
-      <c r="X4" s="130"/>
-      <c r="Y4" s="145"/>
-      <c r="Z4" s="146"/>
-      <c r="AA4" s="146"/>
-      <c r="AB4" s="147"/>
-      <c r="AC4" s="130"/>
-      <c r="AD4" s="130"/>
-      <c r="AE4" s="130"/>
-      <c r="AF4" s="133"/>
-      <c r="AG4" s="134"/>
-      <c r="AH4" s="134"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="105"/>
+      <c r="L4" s="109"/>
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110"/>
+      <c r="P4" s="111"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="115"/>
+      <c r="S4" s="115"/>
+      <c r="T4" s="115"/>
+      <c r="U4" s="115"/>
+      <c r="V4" s="116"/>
+      <c r="W4" s="116"/>
+      <c r="X4" s="116"/>
+      <c r="Y4" s="131"/>
+      <c r="Z4" s="132"/>
+      <c r="AA4" s="132"/>
+      <c r="AB4" s="133"/>
+      <c r="AC4" s="116"/>
+      <c r="AD4" s="116"/>
+      <c r="AE4" s="116"/>
+      <c r="AF4" s="119"/>
+      <c r="AG4" s="120"/>
+      <c r="AH4" s="120"/>
     </row>
     <row r="5" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="140" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="99" t="s">
+      <c r="B5" s="141"/>
+      <c r="C5" s="141"/>
+      <c r="D5" s="141"/>
+      <c r="E5" s="141"/>
+      <c r="F5" s="141"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="143" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="100"/>
-      <c r="J5" s="100"/>
-      <c r="K5" s="100"/>
-      <c r="L5" s="100"/>
-      <c r="M5" s="100"/>
-      <c r="N5" s="100"/>
-      <c r="O5" s="100"/>
-      <c r="P5" s="100"/>
-      <c r="Q5" s="100"/>
-      <c r="R5" s="100"/>
-      <c r="S5" s="100"/>
-      <c r="T5" s="100"/>
-      <c r="U5" s="100"/>
-      <c r="V5" s="100"/>
-      <c r="W5" s="100"/>
-      <c r="X5" s="100"/>
-      <c r="Y5" s="100"/>
-      <c r="Z5" s="100"/>
-      <c r="AA5" s="100"/>
-      <c r="AB5" s="100"/>
-      <c r="AC5" s="100"/>
-      <c r="AD5" s="100"/>
-      <c r="AE5" s="100"/>
-      <c r="AF5" s="100"/>
-      <c r="AG5" s="100"/>
-      <c r="AH5" s="100"/>
+      <c r="I5" s="144"/>
+      <c r="J5" s="144"/>
+      <c r="K5" s="144"/>
+      <c r="L5" s="144"/>
+      <c r="M5" s="144"/>
+      <c r="N5" s="144"/>
+      <c r="O5" s="144"/>
+      <c r="P5" s="144"/>
+      <c r="Q5" s="144"/>
+      <c r="R5" s="144"/>
+      <c r="S5" s="144"/>
+      <c r="T5" s="144"/>
+      <c r="U5" s="144"/>
+      <c r="V5" s="144"/>
+      <c r="W5" s="144"/>
+      <c r="X5" s="144"/>
+      <c r="Y5" s="144"/>
+      <c r="Z5" s="144"/>
+      <c r="AA5" s="144"/>
+      <c r="AB5" s="144"/>
+      <c r="AC5" s="144"/>
+      <c r="AD5" s="144"/>
+      <c r="AE5" s="144"/>
+      <c r="AF5" s="144"/>
+      <c r="AG5" s="144"/>
+      <c r="AH5" s="144"/>
     </row>
     <row r="6" spans="1:34" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A6" s="96" t="s">
+      <c r="A6" s="140" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="97"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="101" t="s">
-        <v>196</v>
-      </c>
-      <c r="I6" s="100"/>
-      <c r="J6" s="100"/>
-      <c r="K6" s="100"/>
-      <c r="L6" s="100"/>
-      <c r="M6" s="100"/>
-      <c r="N6" s="100"/>
-      <c r="O6" s="100"/>
-      <c r="P6" s="100"/>
-      <c r="Q6" s="100"/>
-      <c r="R6" s="100"/>
-      <c r="S6" s="100"/>
-      <c r="T6" s="100"/>
-      <c r="U6" s="100"/>
-      <c r="V6" s="100"/>
-      <c r="W6" s="100"/>
-      <c r="X6" s="100"/>
-      <c r="Y6" s="100"/>
-      <c r="Z6" s="100"/>
-      <c r="AA6" s="100"/>
-      <c r="AB6" s="100"/>
-      <c r="AC6" s="100"/>
-      <c r="AD6" s="100"/>
-      <c r="AE6" s="100"/>
-      <c r="AF6" s="100"/>
-      <c r="AG6" s="100"/>
-      <c r="AH6" s="100"/>
+      <c r="B6" s="141"/>
+      <c r="C6" s="141"/>
+      <c r="D6" s="141"/>
+      <c r="E6" s="141"/>
+      <c r="F6" s="141"/>
+      <c r="G6" s="142"/>
+      <c r="H6" s="145" t="s">
+        <v>195</v>
+      </c>
+      <c r="I6" s="144"/>
+      <c r="J6" s="144"/>
+      <c r="K6" s="144"/>
+      <c r="L6" s="144"/>
+      <c r="M6" s="144"/>
+      <c r="N6" s="144"/>
+      <c r="O6" s="144"/>
+      <c r="P6" s="144"/>
+      <c r="Q6" s="144"/>
+      <c r="R6" s="144"/>
+      <c r="S6" s="144"/>
+      <c r="T6" s="144"/>
+      <c r="U6" s="144"/>
+      <c r="V6" s="144"/>
+      <c r="W6" s="144"/>
+      <c r="X6" s="144"/>
+      <c r="Y6" s="144"/>
+      <c r="Z6" s="144"/>
+      <c r="AA6" s="144"/>
+      <c r="AB6" s="144"/>
+      <c r="AC6" s="144"/>
+      <c r="AD6" s="144"/>
+      <c r="AE6" s="144"/>
+      <c r="AF6" s="144"/>
+      <c r="AG6" s="144"/>
+      <c r="AH6" s="144"/>
     </row>
     <row r="7" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A7" s="96" t="s">
+      <c r="A7" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="97"/>
-      <c r="C7" s="97"/>
-      <c r="D7" s="97"/>
-      <c r="E7" s="97"/>
-      <c r="F7" s="97"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="99" t="s">
+      <c r="B7" s="141"/>
+      <c r="C7" s="141"/>
+      <c r="D7" s="141"/>
+      <c r="E7" s="141"/>
+      <c r="F7" s="141"/>
+      <c r="G7" s="142"/>
+      <c r="H7" s="143" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="100"/>
-      <c r="J7" s="100"/>
-      <c r="K7" s="100"/>
-      <c r="L7" s="100"/>
-      <c r="M7" s="100"/>
-      <c r="N7" s="100"/>
-      <c r="O7" s="100"/>
-      <c r="P7" s="100"/>
-      <c r="Q7" s="100"/>
-      <c r="R7" s="100"/>
-      <c r="S7" s="100"/>
-      <c r="T7" s="100"/>
-      <c r="U7" s="100"/>
-      <c r="V7" s="100"/>
-      <c r="W7" s="100"/>
-      <c r="X7" s="100"/>
-      <c r="Y7" s="100"/>
-      <c r="Z7" s="100"/>
-      <c r="AA7" s="100"/>
-      <c r="AB7" s="100"/>
-      <c r="AC7" s="100"/>
-      <c r="AD7" s="100"/>
-      <c r="AE7" s="100"/>
-      <c r="AF7" s="100"/>
-      <c r="AG7" s="100"/>
-      <c r="AH7" s="100"/>
+      <c r="I7" s="144"/>
+      <c r="J7" s="144"/>
+      <c r="K7" s="144"/>
+      <c r="L7" s="144"/>
+      <c r="M7" s="144"/>
+      <c r="N7" s="144"/>
+      <c r="O7" s="144"/>
+      <c r="P7" s="144"/>
+      <c r="Q7" s="144"/>
+      <c r="R7" s="144"/>
+      <c r="S7" s="144"/>
+      <c r="T7" s="144"/>
+      <c r="U7" s="144"/>
+      <c r="V7" s="144"/>
+      <c r="W7" s="144"/>
+      <c r="X7" s="144"/>
+      <c r="Y7" s="144"/>
+      <c r="Z7" s="144"/>
+      <c r="AA7" s="144"/>
+      <c r="AB7" s="144"/>
+      <c r="AC7" s="144"/>
+      <c r="AD7" s="144"/>
+      <c r="AE7" s="144"/>
+      <c r="AF7" s="144"/>
+      <c r="AG7" s="144"/>
+      <c r="AH7" s="144"/>
     </row>
     <row r="8" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A8" s="96" t="s">
+      <c r="A8" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="97"/>
-      <c r="C8" s="97"/>
-      <c r="D8" s="97"/>
-      <c r="E8" s="97"/>
-      <c r="F8" s="97"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="99" t="s">
+      <c r="B8" s="141"/>
+      <c r="C8" s="141"/>
+      <c r="D8" s="141"/>
+      <c r="E8" s="141"/>
+      <c r="F8" s="141"/>
+      <c r="G8" s="142"/>
+      <c r="H8" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="100"/>
-      <c r="J8" s="100"/>
-      <c r="K8" s="100"/>
-      <c r="L8" s="100"/>
-      <c r="M8" s="100"/>
-      <c r="N8" s="100"/>
-      <c r="O8" s="100"/>
-      <c r="P8" s="100"/>
-      <c r="Q8" s="100"/>
-      <c r="R8" s="100"/>
-      <c r="S8" s="100"/>
-      <c r="T8" s="100"/>
-      <c r="U8" s="100"/>
-      <c r="V8" s="100"/>
-      <c r="W8" s="100"/>
-      <c r="X8" s="100"/>
-      <c r="Y8" s="100"/>
-      <c r="Z8" s="100"/>
-      <c r="AA8" s="100"/>
-      <c r="AB8" s="100"/>
-      <c r="AC8" s="100"/>
-      <c r="AD8" s="100"/>
-      <c r="AE8" s="100"/>
-      <c r="AF8" s="100"/>
-      <c r="AG8" s="100"/>
-      <c r="AH8" s="100"/>
+      <c r="I8" s="144"/>
+      <c r="J8" s="144"/>
+      <c r="K8" s="144"/>
+      <c r="L8" s="144"/>
+      <c r="M8" s="144"/>
+      <c r="N8" s="144"/>
+      <c r="O8" s="144"/>
+      <c r="P8" s="144"/>
+      <c r="Q8" s="144"/>
+      <c r="R8" s="144"/>
+      <c r="S8" s="144"/>
+      <c r="T8" s="144"/>
+      <c r="U8" s="144"/>
+      <c r="V8" s="144"/>
+      <c r="W8" s="144"/>
+      <c r="X8" s="144"/>
+      <c r="Y8" s="144"/>
+      <c r="Z8" s="144"/>
+      <c r="AA8" s="144"/>
+      <c r="AB8" s="144"/>
+      <c r="AC8" s="144"/>
+      <c r="AD8" s="144"/>
+      <c r="AE8" s="144"/>
+      <c r="AF8" s="144"/>
+      <c r="AG8" s="144"/>
+      <c r="AH8" s="144"/>
     </row>
     <row r="9" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A9" s="96" t="s">
+      <c r="A9" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="97"/>
-      <c r="C9" s="97"/>
-      <c r="D9" s="97"/>
-      <c r="E9" s="97"/>
-      <c r="F9" s="97"/>
-      <c r="G9" s="98"/>
-      <c r="H9" s="99" t="s">
+      <c r="B9" s="141"/>
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="141"/>
+      <c r="G9" s="142"/>
+      <c r="H9" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="100"/>
-      <c r="J9" s="100"/>
-      <c r="K9" s="100"/>
-      <c r="L9" s="100"/>
-      <c r="M9" s="100"/>
-      <c r="N9" s="100"/>
-      <c r="O9" s="100"/>
-      <c r="P9" s="100"/>
-      <c r="Q9" s="100"/>
-      <c r="R9" s="100"/>
-      <c r="S9" s="100"/>
-      <c r="T9" s="100"/>
-      <c r="U9" s="100"/>
-      <c r="V9" s="100"/>
-      <c r="W9" s="100"/>
-      <c r="X9" s="100"/>
-      <c r="Y9" s="100"/>
-      <c r="Z9" s="100"/>
-      <c r="AA9" s="100"/>
-      <c r="AB9" s="100"/>
-      <c r="AC9" s="100"/>
-      <c r="AD9" s="100"/>
-      <c r="AE9" s="100"/>
-      <c r="AF9" s="100"/>
-      <c r="AG9" s="100"/>
-      <c r="AH9" s="100"/>
+      <c r="I9" s="144"/>
+      <c r="J9" s="144"/>
+      <c r="K9" s="144"/>
+      <c r="L9" s="144"/>
+      <c r="M9" s="144"/>
+      <c r="N9" s="144"/>
+      <c r="O9" s="144"/>
+      <c r="P9" s="144"/>
+      <c r="Q9" s="144"/>
+      <c r="R9" s="144"/>
+      <c r="S9" s="144"/>
+      <c r="T9" s="144"/>
+      <c r="U9" s="144"/>
+      <c r="V9" s="144"/>
+      <c r="W9" s="144"/>
+      <c r="X9" s="144"/>
+      <c r="Y9" s="144"/>
+      <c r="Z9" s="144"/>
+      <c r="AA9" s="144"/>
+      <c r="AB9" s="144"/>
+      <c r="AC9" s="144"/>
+      <c r="AD9" s="144"/>
+      <c r="AE9" s="144"/>
+      <c r="AF9" s="144"/>
+      <c r="AG9" s="144"/>
+      <c r="AH9" s="144"/>
     </row>
     <row r="10" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A10" s="102" t="s">
+      <c r="A10" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="103"/>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="105" t="s">
+      <c r="B10" s="147"/>
+      <c r="C10" s="147"/>
+      <c r="D10" s="147"/>
+      <c r="E10" s="147"/>
+      <c r="F10" s="147"/>
+      <c r="G10" s="148"/>
+      <c r="H10" s="149" t="s">
         <v>26</v>
       </c>
-      <c r="I10" s="106"/>
-      <c r="J10" s="106"/>
-      <c r="K10" s="106"/>
-      <c r="L10" s="106"/>
-      <c r="M10" s="106"/>
-      <c r="N10" s="106"/>
-      <c r="O10" s="106"/>
-      <c r="P10" s="106"/>
-      <c r="Q10" s="106"/>
-      <c r="R10" s="106"/>
-      <c r="S10" s="106"/>
-      <c r="T10" s="106"/>
-      <c r="U10" s="106"/>
-      <c r="V10" s="106"/>
-      <c r="W10" s="106"/>
-      <c r="X10" s="106"/>
-      <c r="Y10" s="106"/>
-      <c r="Z10" s="106"/>
-      <c r="AA10" s="106"/>
-      <c r="AB10" s="106"/>
-      <c r="AC10" s="106"/>
-      <c r="AD10" s="106"/>
-      <c r="AE10" s="106"/>
-      <c r="AF10" s="106"/>
-      <c r="AG10" s="106"/>
-      <c r="AH10" s="106"/>
+      <c r="I10" s="150"/>
+      <c r="J10" s="150"/>
+      <c r="K10" s="150"/>
+      <c r="L10" s="150"/>
+      <c r="M10" s="150"/>
+      <c r="N10" s="150"/>
+      <c r="O10" s="150"/>
+      <c r="P10" s="150"/>
+      <c r="Q10" s="150"/>
+      <c r="R10" s="150"/>
+      <c r="S10" s="150"/>
+      <c r="T10" s="150"/>
+      <c r="U10" s="150"/>
+      <c r="V10" s="150"/>
+      <c r="W10" s="150"/>
+      <c r="X10" s="150"/>
+      <c r="Y10" s="150"/>
+      <c r="Z10" s="150"/>
+      <c r="AA10" s="150"/>
+      <c r="AB10" s="150"/>
+      <c r="AC10" s="150"/>
+      <c r="AD10" s="150"/>
+      <c r="AE10" s="150"/>
+      <c r="AF10" s="150"/>
+      <c r="AG10" s="150"/>
+      <c r="AH10" s="150"/>
     </row>
     <row r="11" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A11" s="148" t="s">
+      <c r="A11" s="134" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="149"/>
-      <c r="C11" s="149"/>
-      <c r="D11" s="149"/>
-      <c r="E11" s="149"/>
-      <c r="F11" s="149"/>
-      <c r="G11" s="149"/>
-      <c r="H11" s="149"/>
-      <c r="I11" s="149"/>
-      <c r="J11" s="149"/>
-      <c r="K11" s="149"/>
-      <c r="L11" s="149"/>
-      <c r="M11" s="149"/>
-      <c r="N11" s="149"/>
-      <c r="O11" s="149"/>
-      <c r="P11" s="149"/>
-      <c r="Q11" s="149"/>
-      <c r="R11" s="149"/>
-      <c r="S11" s="149"/>
-      <c r="T11" s="149"/>
-      <c r="U11" s="149"/>
-      <c r="V11" s="149"/>
-      <c r="W11" s="149"/>
-      <c r="X11" s="149"/>
-      <c r="Y11" s="149"/>
-      <c r="Z11" s="149"/>
-      <c r="AA11" s="149"/>
-      <c r="AB11" s="149"/>
-      <c r="AC11" s="149"/>
-      <c r="AD11" s="149"/>
-      <c r="AE11" s="149"/>
-      <c r="AF11" s="149"/>
-      <c r="AG11" s="149"/>
-      <c r="AH11" s="149"/>
+      <c r="B11" s="135"/>
+      <c r="C11" s="135"/>
+      <c r="D11" s="135"/>
+      <c r="E11" s="135"/>
+      <c r="F11" s="135"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="135"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="135"/>
+      <c r="K11" s="135"/>
+      <c r="L11" s="135"/>
+      <c r="M11" s="135"/>
+      <c r="N11" s="135"/>
+      <c r="O11" s="135"/>
+      <c r="P11" s="135"/>
+      <c r="Q11" s="135"/>
+      <c r="R11" s="135"/>
+      <c r="S11" s="135"/>
+      <c r="T11" s="135"/>
+      <c r="U11" s="135"/>
+      <c r="V11" s="135"/>
+      <c r="W11" s="135"/>
+      <c r="X11" s="135"/>
+      <c r="Y11" s="135"/>
+      <c r="Z11" s="135"/>
+      <c r="AA11" s="135"/>
+      <c r="AB11" s="135"/>
+      <c r="AC11" s="135"/>
+      <c r="AD11" s="135"/>
+      <c r="AE11" s="135"/>
+      <c r="AF11" s="135"/>
+      <c r="AG11" s="135"/>
+      <c r="AH11" s="135"/>
     </row>
     <row r="12" spans="1:34" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A12" s="61"/>
@@ -3768,20 +3784,20 @@
       <c r="AH23" s="58"/>
     </row>
     <row r="24" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A24" s="107" t="s">
+      <c r="A24" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="108"/>
-      <c r="C24" s="107" t="s">
+      <c r="B24" s="137"/>
+      <c r="C24" s="136" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="109"/>
-      <c r="E24" s="109"/>
-      <c r="F24" s="109"/>
-      <c r="G24" s="109"/>
-      <c r="H24" s="109"/>
-      <c r="I24" s="109"/>
-      <c r="J24" s="108"/>
+      <c r="D24" s="138"/>
+      <c r="E24" s="138"/>
+      <c r="F24" s="138"/>
+      <c r="G24" s="138"/>
+      <c r="H24" s="138"/>
+      <c r="I24" s="138"/>
+      <c r="J24" s="137"/>
       <c r="K24" s="66" t="s">
         <v>30</v>
       </c>
@@ -3794,34 +3810,34 @@
       <c r="N24" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="O24" s="110" t="s">
+      <c r="O24" s="139" t="s">
         <v>34</v>
       </c>
-      <c r="P24" s="110"/>
-      <c r="Q24" s="110"/>
-      <c r="R24" s="110"/>
-      <c r="S24" s="110"/>
-      <c r="T24" s="110"/>
-      <c r="U24" s="110"/>
-      <c r="V24" s="110"/>
-      <c r="W24" s="110"/>
-      <c r="X24" s="110"/>
-      <c r="Y24" s="110"/>
-      <c r="Z24" s="110"/>
-      <c r="AA24" s="110"/>
-      <c r="AB24" s="110"/>
-      <c r="AC24" s="110"/>
-      <c r="AD24" s="110"/>
-      <c r="AE24" s="110"/>
-      <c r="AF24" s="110"/>
-      <c r="AG24" s="110"/>
-      <c r="AH24" s="110"/>
+      <c r="P24" s="139"/>
+      <c r="Q24" s="139"/>
+      <c r="R24" s="139"/>
+      <c r="S24" s="139"/>
+      <c r="T24" s="139"/>
+      <c r="U24" s="139"/>
+      <c r="V24" s="139"/>
+      <c r="W24" s="139"/>
+      <c r="X24" s="139"/>
+      <c r="Y24" s="139"/>
+      <c r="Z24" s="139"/>
+      <c r="AA24" s="139"/>
+      <c r="AB24" s="139"/>
+      <c r="AC24" s="139"/>
+      <c r="AD24" s="139"/>
+      <c r="AE24" s="139"/>
+      <c r="AF24" s="139"/>
+      <c r="AG24" s="139"/>
+      <c r="AH24" s="139"/>
     </row>
     <row r="25" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A25" s="93">
+      <c r="A25" s="94">
         <v>1</v>
       </c>
-      <c r="B25" s="94"/>
+      <c r="B25" s="95"/>
       <c r="C25" s="64" t="s">
         <v>35</v>
       </c>
@@ -3838,34 +3854,34 @@
       <c r="L25" s="67"/>
       <c r="M25" s="67"/>
       <c r="N25" s="64"/>
-      <c r="O25" s="95"/>
-      <c r="P25" s="95"/>
-      <c r="Q25" s="95"/>
-      <c r="R25" s="95"/>
-      <c r="S25" s="95"/>
-      <c r="T25" s="95"/>
-      <c r="U25" s="95"/>
-      <c r="V25" s="95"/>
-      <c r="W25" s="95"/>
-      <c r="X25" s="95"/>
-      <c r="Y25" s="95"/>
-      <c r="Z25" s="95"/>
-      <c r="AA25" s="95"/>
-      <c r="AB25" s="95"/>
-      <c r="AC25" s="95"/>
-      <c r="AD25" s="95"/>
-      <c r="AE25" s="95"/>
-      <c r="AF25" s="95"/>
-      <c r="AG25" s="95"/>
-      <c r="AH25" s="95"/>
+      <c r="O25" s="96"/>
+      <c r="P25" s="96"/>
+      <c r="Q25" s="96"/>
+      <c r="R25" s="96"/>
+      <c r="S25" s="96"/>
+      <c r="T25" s="96"/>
+      <c r="U25" s="96"/>
+      <c r="V25" s="96"/>
+      <c r="W25" s="96"/>
+      <c r="X25" s="96"/>
+      <c r="Y25" s="96"/>
+      <c r="Z25" s="96"/>
+      <c r="AA25" s="96"/>
+      <c r="AB25" s="96"/>
+      <c r="AC25" s="96"/>
+      <c r="AD25" s="96"/>
+      <c r="AE25" s="96"/>
+      <c r="AF25" s="96"/>
+      <c r="AG25" s="96"/>
+      <c r="AH25" s="96"/>
     </row>
     <row r="26" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A26" s="93">
+      <c r="A26" s="94">
         <v>2</v>
       </c>
-      <c r="B26" s="94"/>
+      <c r="B26" s="95"/>
       <c r="C26" s="78" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="65"/>
@@ -3880,34 +3896,34 @@
       <c r="L26" s="67"/>
       <c r="M26" s="67"/>
       <c r="N26" s="64"/>
-      <c r="O26" s="95"/>
-      <c r="P26" s="95"/>
-      <c r="Q26" s="95"/>
-      <c r="R26" s="95"/>
-      <c r="S26" s="95"/>
-      <c r="T26" s="95"/>
-      <c r="U26" s="95"/>
-      <c r="V26" s="95"/>
-      <c r="W26" s="95"/>
-      <c r="X26" s="95"/>
-      <c r="Y26" s="95"/>
-      <c r="Z26" s="95"/>
-      <c r="AA26" s="95"/>
-      <c r="AB26" s="95"/>
-      <c r="AC26" s="95"/>
-      <c r="AD26" s="95"/>
-      <c r="AE26" s="95"/>
-      <c r="AF26" s="95"/>
-      <c r="AG26" s="95"/>
-      <c r="AH26" s="95"/>
+      <c r="O26" s="96"/>
+      <c r="P26" s="96"/>
+      <c r="Q26" s="96"/>
+      <c r="R26" s="96"/>
+      <c r="S26" s="96"/>
+      <c r="T26" s="96"/>
+      <c r="U26" s="96"/>
+      <c r="V26" s="96"/>
+      <c r="W26" s="96"/>
+      <c r="X26" s="96"/>
+      <c r="Y26" s="96"/>
+      <c r="Z26" s="96"/>
+      <c r="AA26" s="96"/>
+      <c r="AB26" s="96"/>
+      <c r="AC26" s="96"/>
+      <c r="AD26" s="96"/>
+      <c r="AE26" s="96"/>
+      <c r="AF26" s="96"/>
+      <c r="AG26" s="96"/>
+      <c r="AH26" s="96"/>
     </row>
     <row r="27" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A27" s="93">
+      <c r="A27" s="94">
         <v>3</v>
       </c>
-      <c r="B27" s="94"/>
+      <c r="B27" s="95"/>
       <c r="C27" s="78" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="65"/>
@@ -3922,34 +3938,34 @@
       <c r="L27" s="67"/>
       <c r="M27" s="67"/>
       <c r="N27" s="64"/>
-      <c r="O27" s="95"/>
-      <c r="P27" s="95"/>
-      <c r="Q27" s="95"/>
-      <c r="R27" s="95"/>
-      <c r="S27" s="95"/>
-      <c r="T27" s="95"/>
-      <c r="U27" s="95"/>
-      <c r="V27" s="95"/>
-      <c r="W27" s="95"/>
-      <c r="X27" s="95"/>
-      <c r="Y27" s="95"/>
-      <c r="Z27" s="95"/>
-      <c r="AA27" s="95"/>
-      <c r="AB27" s="95"/>
-      <c r="AC27" s="95"/>
-      <c r="AD27" s="95"/>
-      <c r="AE27" s="95"/>
-      <c r="AF27" s="95"/>
-      <c r="AG27" s="95"/>
-      <c r="AH27" s="95"/>
+      <c r="O27" s="96"/>
+      <c r="P27" s="96"/>
+      <c r="Q27" s="96"/>
+      <c r="R27" s="96"/>
+      <c r="S27" s="96"/>
+      <c r="T27" s="96"/>
+      <c r="U27" s="96"/>
+      <c r="V27" s="96"/>
+      <c r="W27" s="96"/>
+      <c r="X27" s="96"/>
+      <c r="Y27" s="96"/>
+      <c r="Z27" s="96"/>
+      <c r="AA27" s="96"/>
+      <c r="AB27" s="96"/>
+      <c r="AC27" s="96"/>
+      <c r="AD27" s="96"/>
+      <c r="AE27" s="96"/>
+      <c r="AF27" s="96"/>
+      <c r="AG27" s="96"/>
+      <c r="AH27" s="96"/>
     </row>
     <row r="28" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A28" s="93">
+      <c r="A28" s="94">
         <v>4</v>
       </c>
-      <c r="B28" s="94"/>
+      <c r="B28" s="95"/>
       <c r="C28" s="78" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D28" s="65"/>
       <c r="E28" s="65"/>
@@ -3964,29 +3980,50 @@
       <c r="L28" s="67"/>
       <c r="M28" s="67"/>
       <c r="N28" s="64"/>
-      <c r="O28" s="95"/>
-      <c r="P28" s="95"/>
-      <c r="Q28" s="95"/>
-      <c r="R28" s="95"/>
-      <c r="S28" s="95"/>
-      <c r="T28" s="95"/>
-      <c r="U28" s="95"/>
-      <c r="V28" s="95"/>
-      <c r="W28" s="95"/>
-      <c r="X28" s="95"/>
-      <c r="Y28" s="95"/>
-      <c r="Z28" s="95"/>
-      <c r="AA28" s="95"/>
-      <c r="AB28" s="95"/>
-      <c r="AC28" s="95"/>
-      <c r="AD28" s="95"/>
-      <c r="AE28" s="95"/>
-      <c r="AF28" s="95"/>
-      <c r="AG28" s="95"/>
-      <c r="AH28" s="95"/>
+      <c r="O28" s="96"/>
+      <c r="P28" s="96"/>
+      <c r="Q28" s="96"/>
+      <c r="R28" s="96"/>
+      <c r="S28" s="96"/>
+      <c r="T28" s="96"/>
+      <c r="U28" s="96"/>
+      <c r="V28" s="96"/>
+      <c r="W28" s="96"/>
+      <c r="X28" s="96"/>
+      <c r="Y28" s="96"/>
+      <c r="Z28" s="96"/>
+      <c r="AA28" s="96"/>
+      <c r="AB28" s="96"/>
+      <c r="AC28" s="96"/>
+      <c r="AD28" s="96"/>
+      <c r="AE28" s="96"/>
+      <c r="AF28" s="96"/>
+      <c r="AG28" s="96"/>
+      <c r="AH28" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="O27:AH27"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="O26:AH26"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="H5:AH5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H6:AH6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="H7:AH7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="H8:AH8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="H9:AH9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="H10:AH10"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="O24:AH24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="O25:AH25"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="O28:AH28"/>
     <mergeCell ref="A1:K4"/>
@@ -4003,27 +4040,6 @@
     <mergeCell ref="Y1:AB2"/>
     <mergeCell ref="Y3:AB4"/>
     <mergeCell ref="A11:AH11"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:J24"/>
-    <mergeCell ref="O24:AH24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="O25:AH25"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="O27:AH27"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="O26:AH26"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="H5:AH5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="H6:AH6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="H7:AH7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="H8:AH8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="H9:AH9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="H10:AH10"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4053,177 +4069,177 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="171" t="s">
-        <v>235</v>
-      </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="120" t="s">
+      <c r="A1" s="151" t="s">
+        <v>234</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="126" t="s">
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-      <c r="R1" s="127"/>
-      <c r="S1" s="127"/>
-      <c r="T1" s="130" t="s">
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="U1" s="142" t="s">
+      <c r="U1" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="143"/>
-      <c r="W1" s="135" t="s">
+      <c r="V1" s="129"/>
+      <c r="W1" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="141" t="s">
+      <c r="X1" s="127" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="132"/>
+      <c r="Y1" s="118"/>
     </row>
     <row r="2" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="114"/>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="123"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="125"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="129"/>
-      <c r="Q2" s="129"/>
-      <c r="R2" s="129"/>
-      <c r="S2" s="129"/>
-      <c r="T2" s="130"/>
-      <c r="U2" s="145"/>
-      <c r="V2" s="146"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="133"/>
-      <c r="Y2" s="134"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="111"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="115"/>
+      <c r="Q2" s="115"/>
+      <c r="R2" s="115"/>
+      <c r="S2" s="115"/>
+      <c r="T2" s="116"/>
+      <c r="U2" s="131"/>
+      <c r="V2" s="132"/>
+      <c r="W2" s="124"/>
+      <c r="X2" s="119"/>
+      <c r="Y2" s="120"/>
     </row>
     <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A3" s="114"/>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="120" t="s">
+      <c r="A3" s="100"/>
+      <c r="B3" s="101"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="121"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="121"/>
-      <c r="N3" s="122"/>
-      <c r="O3" s="126" t="s">
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="108"/>
+      <c r="O3" s="112" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="127"/>
-      <c r="Q3" s="127"/>
-      <c r="R3" s="127"/>
-      <c r="S3" s="127"/>
-      <c r="T3" s="130" t="s">
+      <c r="P3" s="113"/>
+      <c r="Q3" s="113"/>
+      <c r="R3" s="113"/>
+      <c r="S3" s="113"/>
+      <c r="T3" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="U3" s="142" t="s">
+      <c r="U3" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="V3" s="143"/>
-      <c r="W3" s="130" t="s">
+      <c r="V3" s="129"/>
+      <c r="W3" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="X3" s="141">
+      <c r="X3" s="127">
         <v>45935</v>
       </c>
-      <c r="Y3" s="132"/>
+      <c r="Y3" s="118"/>
     </row>
     <row r="4" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A4" s="117"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="123"/>
-      <c r="K4" s="124"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="124"/>
-      <c r="N4" s="125"/>
-      <c r="O4" s="128"/>
-      <c r="P4" s="129"/>
-      <c r="Q4" s="129"/>
-      <c r="R4" s="129"/>
-      <c r="S4" s="129"/>
-      <c r="T4" s="130"/>
-      <c r="U4" s="145"/>
-      <c r="V4" s="146"/>
-      <c r="W4" s="130"/>
-      <c r="X4" s="133"/>
-      <c r="Y4" s="134"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110"/>
+      <c r="M4" s="110"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="114"/>
+      <c r="P4" s="115"/>
+      <c r="Q4" s="115"/>
+      <c r="R4" s="115"/>
+      <c r="S4" s="115"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="131"/>
+      <c r="V4" s="132"/>
+      <c r="W4" s="116"/>
+      <c r="X4" s="119"/>
+      <c r="Y4" s="120"/>
     </row>
     <row r="5" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="170" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="157"/>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="158" t="s">
+      <c r="B5" s="170"/>
+      <c r="C5" s="170"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="170"/>
+      <c r="F5" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="158"/>
-      <c r="H5" s="158"/>
-      <c r="I5" s="158"/>
-      <c r="J5" s="157" t="s">
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="171"/>
+      <c r="J5" s="170" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="157"/>
-      <c r="L5" s="157"/>
-      <c r="M5" s="157"/>
-      <c r="N5" s="157"/>
-      <c r="O5" s="158" t="s">
+      <c r="K5" s="170"/>
+      <c r="L5" s="170"/>
+      <c r="M5" s="170"/>
+      <c r="N5" s="170"/>
+      <c r="O5" s="171" t="s">
         <v>20</v>
       </c>
-      <c r="P5" s="158"/>
-      <c r="Q5" s="158"/>
-      <c r="R5" s="158"/>
-      <c r="S5" s="158"/>
+      <c r="P5" s="171"/>
+      <c r="Q5" s="171"/>
+      <c r="R5" s="171"/>
+      <c r="S5" s="171"/>
       <c r="T5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="U5" s="158" t="s">
+      <c r="U5" s="171" t="s">
         <v>26</v>
       </c>
-      <c r="V5" s="158"/>
-      <c r="W5" s="158"/>
-      <c r="X5" s="158"/>
-      <c r="Y5" s="158"/>
+      <c r="V5" s="171"/>
+      <c r="W5" s="171"/>
+      <c r="X5" s="171"/>
+      <c r="Y5" s="171"/>
     </row>
     <row r="6" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A6" s="35" t="s">
@@ -4234,423 +4250,421 @@
       <c r="A7" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="130" t="s">
+      <c r="B7" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
       <c r="J7" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="159" t="s">
+      <c r="K7" s="162" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="160"/>
-      <c r="M7" s="160"/>
-      <c r="N7" s="161"/>
-      <c r="O7" s="130" t="s">
+      <c r="L7" s="163"/>
+      <c r="M7" s="163"/>
+      <c r="N7" s="169"/>
+      <c r="O7" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="P7" s="130"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="130"/>
-      <c r="S7" s="130" t="s">
+      <c r="P7" s="116"/>
+      <c r="Q7" s="116"/>
+      <c r="R7" s="116"/>
+      <c r="S7" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="T7" s="130"/>
-      <c r="U7" s="159" t="s">
+      <c r="T7" s="116"/>
+      <c r="U7" s="162" t="s">
         <v>46</v>
       </c>
-      <c r="V7" s="160"/>
-      <c r="W7" s="160"/>
-      <c r="X7" s="160"/>
-      <c r="Y7" s="160"/>
+      <c r="V7" s="163"/>
+      <c r="W7" s="163"/>
+      <c r="X7" s="163"/>
+      <c r="Y7" s="163"/>
     </row>
     <row r="8" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A8" s="44">
         <v>1</v>
       </c>
-      <c r="B8" s="150" t="s">
+      <c r="B8" s="167" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" s="168"/>
+      <c r="D8" s="168"/>
+      <c r="E8" s="168"/>
+      <c r="F8" s="168"/>
+      <c r="G8" s="168"/>
+      <c r="H8" s="168"/>
+      <c r="I8" s="168"/>
+      <c r="J8" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="150"/>
-      <c r="D8" s="150"/>
-      <c r="E8" s="150"/>
-      <c r="F8" s="150"/>
-      <c r="G8" s="150"/>
-      <c r="H8" s="150"/>
-      <c r="I8" s="150"/>
-      <c r="J8" s="55" t="s">
+      <c r="K8" s="153" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="156" t="s">
+      <c r="L8" s="156"/>
+      <c r="M8" s="156"/>
+      <c r="N8" s="154"/>
+      <c r="O8" s="152">
+        <v>4000</v>
+      </c>
+      <c r="P8" s="152"/>
+      <c r="Q8" s="152"/>
+      <c r="R8" s="152"/>
+      <c r="S8" s="152" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="152"/>
-      <c r="M8" s="152"/>
-      <c r="N8" s="153"/>
-      <c r="O8" s="154">
-        <v>4000</v>
-      </c>
-      <c r="P8" s="154"/>
-      <c r="Q8" s="154"/>
-      <c r="R8" s="154"/>
-      <c r="S8" s="154" t="s">
+      <c r="T8" s="152"/>
+      <c r="U8" s="153" t="s">
         <v>50</v>
       </c>
-      <c r="T8" s="154"/>
-      <c r="U8" s="156" t="s">
-        <v>51</v>
-      </c>
-      <c r="V8" s="152"/>
-      <c r="W8" s="152"/>
-      <c r="X8" s="152"/>
-      <c r="Y8" s="152"/>
+      <c r="V8" s="156"/>
+      <c r="W8" s="156"/>
+      <c r="X8" s="156"/>
+      <c r="Y8" s="156"/>
     </row>
     <row r="9" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A9" s="44">
         <v>2</v>
       </c>
-      <c r="B9" s="150" t="s">
+      <c r="B9" s="168" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" s="168"/>
+      <c r="D9" s="168"/>
+      <c r="E9" s="168"/>
+      <c r="F9" s="168"/>
+      <c r="G9" s="168"/>
+      <c r="H9" s="168"/>
+      <c r="I9" s="168"/>
+      <c r="J9" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="172" t="s">
+        <v>244</v>
+      </c>
+      <c r="L9" s="156"/>
+      <c r="M9" s="156"/>
+      <c r="N9" s="154"/>
+      <c r="O9" s="152">
+        <v>36</v>
+      </c>
+      <c r="P9" s="152"/>
+      <c r="Q9" s="152"/>
+      <c r="R9" s="152"/>
+      <c r="S9" s="173" t="s">
         <v>243</v>
       </c>
-      <c r="C9" s="150"/>
-      <c r="D9" s="150"/>
-      <c r="E9" s="150"/>
-      <c r="F9" s="150"/>
-      <c r="G9" s="150"/>
-      <c r="H9" s="150"/>
-      <c r="I9" s="150"/>
-      <c r="J9" s="55" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" s="151" t="s">
-        <v>245</v>
-      </c>
-      <c r="L9" s="152"/>
-      <c r="M9" s="152"/>
-      <c r="N9" s="153"/>
-      <c r="O9" s="154">
-        <v>16</v>
-      </c>
-      <c r="P9" s="154"/>
-      <c r="Q9" s="154"/>
-      <c r="R9" s="154"/>
-      <c r="S9" s="155" t="s">
-        <v>244</v>
-      </c>
-      <c r="T9" s="154"/>
-      <c r="U9" s="156" t="s">
-        <v>51</v>
-      </c>
-      <c r="V9" s="152"/>
-      <c r="W9" s="152"/>
-      <c r="X9" s="152"/>
-      <c r="Y9" s="152"/>
+      <c r="T9" s="152"/>
+      <c r="U9" s="153"/>
+      <c r="V9" s="156"/>
+      <c r="W9" s="156"/>
+      <c r="X9" s="156"/>
+      <c r="Y9" s="156"/>
     </row>
     <row r="10" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A10" s="35"/>
     </row>
     <row r="11" spans="1:25" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A11" s="35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:25" s="32" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A12" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="130" t="s">
+      <c r="B12" s="116" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="116"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="116"/>
+      <c r="F12" s="116" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="116"/>
+      <c r="H12" s="116"/>
+      <c r="I12" s="116"/>
+      <c r="J12" s="116"/>
+      <c r="K12" s="116" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="130"/>
-      <c r="D12" s="130"/>
-      <c r="E12" s="130"/>
-      <c r="F12" s="130" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="130"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="130"/>
-      <c r="K12" s="130" t="s">
+      <c r="L12" s="116"/>
+      <c r="M12" s="116"/>
+      <c r="N12" s="116"/>
+      <c r="O12" s="116" t="s">
+        <v>42</v>
+      </c>
+      <c r="P12" s="116"/>
+      <c r="Q12" s="166" t="s">
+        <v>45</v>
+      </c>
+      <c r="R12" s="166"/>
+      <c r="S12" s="166"/>
+      <c r="T12" s="166"/>
+      <c r="U12" s="116" t="s">
         <v>54</v>
       </c>
-      <c r="L12" s="130"/>
-      <c r="M12" s="130"/>
-      <c r="N12" s="130"/>
-      <c r="O12" s="130" t="s">
-        <v>42</v>
-      </c>
-      <c r="P12" s="130"/>
-      <c r="Q12" s="168" t="s">
-        <v>45</v>
-      </c>
-      <c r="R12" s="168"/>
-      <c r="S12" s="168"/>
-      <c r="T12" s="168"/>
-      <c r="U12" s="130" t="s">
+      <c r="V12" s="116"/>
+      <c r="W12" s="116"/>
+      <c r="X12" s="162" t="s">
         <v>55</v>
       </c>
-      <c r="V12" s="130"/>
-      <c r="W12" s="130"/>
-      <c r="X12" s="159" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y12" s="160"/>
+      <c r="Y12" s="163"/>
     </row>
     <row r="13" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A13" s="44">
         <v>1</v>
       </c>
-      <c r="B13" s="154" t="s">
+      <c r="B13" s="152" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="152"/>
+      <c r="D13" s="152"/>
+      <c r="E13" s="152"/>
+      <c r="F13" s="152" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="154"/>
-      <c r="D13" s="154"/>
-      <c r="E13" s="154"/>
-      <c r="F13" s="154" t="s">
+      <c r="G13" s="152"/>
+      <c r="H13" s="152"/>
+      <c r="I13" s="152"/>
+      <c r="J13" s="152"/>
+      <c r="K13" s="153" t="s">
         <v>58</v>
       </c>
-      <c r="G13" s="154"/>
-      <c r="H13" s="154"/>
-      <c r="I13" s="154"/>
-      <c r="J13" s="154"/>
-      <c r="K13" s="156" t="s">
+      <c r="L13" s="156"/>
+      <c r="M13" s="156"/>
+      <c r="N13" s="154"/>
+      <c r="O13" s="157" t="s">
+        <v>47</v>
+      </c>
+      <c r="P13" s="158"/>
+      <c r="Q13" s="159" t="s">
+        <v>56</v>
+      </c>
+      <c r="R13" s="152"/>
+      <c r="S13" s="152"/>
+      <c r="T13" s="152"/>
+      <c r="U13" s="155" t="s">
         <v>59</v>
       </c>
-      <c r="L13" s="152"/>
-      <c r="M13" s="152"/>
-      <c r="N13" s="153"/>
-      <c r="O13" s="162" t="s">
-        <v>48</v>
-      </c>
-      <c r="P13" s="163"/>
-      <c r="Q13" s="164" t="s">
-        <v>57</v>
-      </c>
-      <c r="R13" s="154"/>
-      <c r="S13" s="154"/>
-      <c r="T13" s="154"/>
-      <c r="U13" s="165" t="s">
+      <c r="V13" s="152"/>
+      <c r="W13" s="152"/>
+      <c r="X13" s="164" t="s">
         <v>60</v>
       </c>
-      <c r="V13" s="154"/>
-      <c r="W13" s="154"/>
-      <c r="X13" s="166" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y13" s="167"/>
+      <c r="Y13" s="165"/>
     </row>
     <row r="14" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A14" s="44">
         <v>2</v>
       </c>
-      <c r="B14" s="154" t="s">
+      <c r="B14" s="152" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="152"/>
+      <c r="D14" s="152"/>
+      <c r="E14" s="152"/>
+      <c r="F14" s="152" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="154"/>
-      <c r="D14" s="154"/>
-      <c r="E14" s="154"/>
-      <c r="F14" s="154" t="s">
+      <c r="G14" s="152"/>
+      <c r="H14" s="152"/>
+      <c r="I14" s="152"/>
+      <c r="J14" s="152"/>
+      <c r="K14" s="153" t="s">
+        <v>58</v>
+      </c>
+      <c r="L14" s="156"/>
+      <c r="M14" s="156"/>
+      <c r="N14" s="154"/>
+      <c r="O14" s="157"/>
+      <c r="P14" s="158"/>
+      <c r="Q14" s="159" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="154"/>
-      <c r="H14" s="154"/>
-      <c r="I14" s="154"/>
-      <c r="J14" s="154"/>
-      <c r="K14" s="156" t="s">
+      <c r="R14" s="152"/>
+      <c r="S14" s="152"/>
+      <c r="T14" s="152"/>
+      <c r="U14" s="155" t="s">
         <v>59</v>
       </c>
-      <c r="L14" s="152"/>
-      <c r="M14" s="152"/>
-      <c r="N14" s="153"/>
-      <c r="O14" s="162"/>
-      <c r="P14" s="163"/>
-      <c r="Q14" s="164" t="s">
+      <c r="V14" s="152"/>
+      <c r="W14" s="152"/>
+      <c r="X14" s="152" t="s">
         <v>64</v>
       </c>
-      <c r="R14" s="154"/>
-      <c r="S14" s="154"/>
-      <c r="T14" s="154"/>
-      <c r="U14" s="165" t="s">
-        <v>60</v>
-      </c>
-      <c r="V14" s="154"/>
-      <c r="W14" s="154"/>
-      <c r="X14" s="154" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y14" s="154"/>
+      <c r="Y14" s="152"/>
     </row>
     <row r="15" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A15" s="44">
         <v>3</v>
       </c>
-      <c r="B15" s="154" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="154"/>
-      <c r="D15" s="154"/>
-      <c r="E15" s="154"/>
-      <c r="F15" s="154" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15" s="154"/>
-      <c r="H15" s="154"/>
-      <c r="I15" s="154"/>
-      <c r="J15" s="154"/>
-      <c r="K15" s="156" t="s">
+      <c r="B15" s="152" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="152"/>
+      <c r="D15" s="152"/>
+      <c r="E15" s="152"/>
+      <c r="F15" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15" s="152"/>
+      <c r="H15" s="152"/>
+      <c r="I15" s="152"/>
+      <c r="J15" s="152"/>
+      <c r="K15" s="153" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" s="156"/>
+      <c r="M15" s="156"/>
+      <c r="N15" s="154"/>
+      <c r="O15" s="157"/>
+      <c r="P15" s="158"/>
+      <c r="Q15" s="159" t="s">
+        <v>63</v>
+      </c>
+      <c r="R15" s="152"/>
+      <c r="S15" s="152"/>
+      <c r="T15" s="152"/>
+      <c r="U15" s="155" t="s">
         <v>59</v>
       </c>
-      <c r="L15" s="152"/>
-      <c r="M15" s="152"/>
-      <c r="N15" s="153"/>
-      <c r="O15" s="162"/>
-      <c r="P15" s="163"/>
-      <c r="Q15" s="164" t="s">
-        <v>64</v>
-      </c>
-      <c r="R15" s="154"/>
-      <c r="S15" s="154"/>
-      <c r="T15" s="154"/>
-      <c r="U15" s="165" t="s">
-        <v>60</v>
-      </c>
-      <c r="V15" s="154"/>
-      <c r="W15" s="154"/>
-      <c r="X15" s="169">
+      <c r="V15" s="152"/>
+      <c r="W15" s="152"/>
+      <c r="X15" s="160">
         <v>1</v>
       </c>
-      <c r="Y15" s="170"/>
+      <c r="Y15" s="161"/>
     </row>
     <row r="16" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A16" s="44">
         <v>4</v>
       </c>
-      <c r="B16" s="154" t="s">
+      <c r="B16" s="152" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="152"/>
+      <c r="D16" s="152"/>
+      <c r="E16" s="152"/>
+      <c r="F16" s="152" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="154"/>
-      <c r="D16" s="154"/>
-      <c r="E16" s="154"/>
-      <c r="F16" s="154" t="s">
+      <c r="G16" s="152"/>
+      <c r="H16" s="152"/>
+      <c r="I16" s="152"/>
+      <c r="J16" s="152"/>
+      <c r="K16" s="153" t="s">
         <v>68</v>
       </c>
-      <c r="G16" s="154"/>
-      <c r="H16" s="154"/>
-      <c r="I16" s="154"/>
-      <c r="J16" s="154"/>
-      <c r="K16" s="156" t="s">
+      <c r="L16" s="156"/>
+      <c r="M16" s="156"/>
+      <c r="N16" s="154"/>
+      <c r="O16" s="157"/>
+      <c r="P16" s="158"/>
+      <c r="Q16" s="159" t="s">
+        <v>66</v>
+      </c>
+      <c r="R16" s="152"/>
+      <c r="S16" s="152"/>
+      <c r="T16" s="152"/>
+      <c r="U16" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="L16" s="152"/>
-      <c r="M16" s="152"/>
-      <c r="N16" s="153"/>
-      <c r="O16" s="162"/>
-      <c r="P16" s="163"/>
-      <c r="Q16" s="164" t="s">
-        <v>67</v>
-      </c>
-      <c r="R16" s="154"/>
-      <c r="S16" s="154"/>
-      <c r="T16" s="154"/>
-      <c r="U16" s="154" t="s">
+      <c r="V16" s="152"/>
+      <c r="W16" s="152"/>
+      <c r="X16" s="153" t="s">
         <v>70</v>
       </c>
-      <c r="V16" s="154"/>
-      <c r="W16" s="154"/>
-      <c r="X16" s="156" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y16" s="153"/>
+      <c r="Y16" s="154"/>
     </row>
     <row r="17" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A17" s="44">
         <v>5</v>
       </c>
-      <c r="B17" s="154" t="s">
+      <c r="B17" s="152" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="152"/>
+      <c r="D17" s="152"/>
+      <c r="E17" s="152"/>
+      <c r="F17" s="152" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="154"/>
-      <c r="D17" s="154"/>
-      <c r="E17" s="154"/>
-      <c r="F17" s="154" t="s">
+      <c r="G17" s="152"/>
+      <c r="H17" s="152"/>
+      <c r="I17" s="152"/>
+      <c r="J17" s="152"/>
+      <c r="K17" s="153" t="s">
+        <v>58</v>
+      </c>
+      <c r="L17" s="156"/>
+      <c r="M17" s="156"/>
+      <c r="N17" s="154"/>
+      <c r="O17" s="157"/>
+      <c r="P17" s="158"/>
+      <c r="Q17" s="159" t="s">
         <v>73</v>
       </c>
-      <c r="G17" s="154"/>
-      <c r="H17" s="154"/>
-      <c r="I17" s="154"/>
-      <c r="J17" s="154"/>
-      <c r="K17" s="156" t="s">
-        <v>59</v>
-      </c>
-      <c r="L17" s="152"/>
-      <c r="M17" s="152"/>
-      <c r="N17" s="153"/>
-      <c r="O17" s="162"/>
-      <c r="P17" s="163"/>
-      <c r="Q17" s="164" t="s">
+      <c r="R17" s="152"/>
+      <c r="S17" s="152"/>
+      <c r="T17" s="152"/>
+      <c r="U17" s="152" t="s">
         <v>74</v>
       </c>
-      <c r="R17" s="154"/>
-      <c r="S17" s="154"/>
-      <c r="T17" s="154"/>
-      <c r="U17" s="154" t="s">
-        <v>75</v>
-      </c>
-      <c r="V17" s="154"/>
-      <c r="W17" s="154"/>
-      <c r="X17" s="156">
+      <c r="V17" s="152"/>
+      <c r="W17" s="152"/>
+      <c r="X17" s="153">
         <v>10</v>
       </c>
-      <c r="Y17" s="153"/>
+      <c r="Y17" s="154"/>
     </row>
     <row r="18" spans="1:25" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A18" s="44">
         <v>6</v>
       </c>
-      <c r="B18" s="154" t="s">
+      <c r="B18" s="152" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="152"/>
+      <c r="D18" s="152"/>
+      <c r="E18" s="152"/>
+      <c r="F18" s="152" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="154"/>
-      <c r="D18" s="154"/>
-      <c r="E18" s="154"/>
-      <c r="F18" s="154" t="s">
+      <c r="G18" s="152"/>
+      <c r="H18" s="152"/>
+      <c r="I18" s="152"/>
+      <c r="J18" s="152"/>
+      <c r="K18" s="153" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="156"/>
+      <c r="M18" s="156"/>
+      <c r="N18" s="154"/>
+      <c r="O18" s="157"/>
+      <c r="P18" s="158"/>
+      <c r="Q18" s="159" t="s">
         <v>77</v>
       </c>
-      <c r="G18" s="154"/>
-      <c r="H18" s="154"/>
-      <c r="I18" s="154"/>
-      <c r="J18" s="154"/>
-      <c r="K18" s="156" t="s">
-        <v>59</v>
-      </c>
-      <c r="L18" s="152"/>
-      <c r="M18" s="152"/>
-      <c r="N18" s="153"/>
-      <c r="O18" s="162"/>
-      <c r="P18" s="163"/>
-      <c r="Q18" s="164" t="s">
-        <v>78</v>
-      </c>
-      <c r="R18" s="154"/>
-      <c r="S18" s="154"/>
-      <c r="T18" s="154"/>
-      <c r="U18" s="154" t="s">
-        <v>75</v>
-      </c>
-      <c r="V18" s="154"/>
-      <c r="W18" s="154"/>
-      <c r="X18" s="156">
+      <c r="R18" s="152"/>
+      <c r="S18" s="152"/>
+      <c r="T18" s="152"/>
+      <c r="U18" s="152" t="s">
+        <v>74</v>
+      </c>
+      <c r="V18" s="152"/>
+      <c r="W18" s="152"/>
+      <c r="X18" s="153">
         <v>100</v>
       </c>
-      <c r="Y18" s="153"/>
+      <c r="Y18" s="154"/>
     </row>
     <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A19" s="58"/>
@@ -4681,11 +4695,67 @@
     </row>
   </sheetData>
   <mergeCells count="82">
-    <mergeCell ref="J1:N2"/>
-    <mergeCell ref="O1:S2"/>
-    <mergeCell ref="A1:I4"/>
-    <mergeCell ref="J3:N4"/>
-    <mergeCell ref="O3:S4"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="U9:Y9"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="U5:Y5"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="U7:Y7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="U8:Y8"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="K13:N13"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="Q12:T12"/>
+    <mergeCell ref="U15:W15"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="Q14:T14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="Q15:T15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:T17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:T18"/>
     <mergeCell ref="U18:W18"/>
     <mergeCell ref="X18:Y18"/>
     <mergeCell ref="T1:T2"/>
@@ -4702,67 +4772,11 @@
     <mergeCell ref="X17:Y17"/>
     <mergeCell ref="U14:W14"/>
     <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="F18:J18"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:T18"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:T17"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="K16:N16"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:T16"/>
-    <mergeCell ref="U15:W15"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="Q15:T15"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="K13:N13"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="U13:W13"/>
-    <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="Q12:T12"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="S8:T8"/>
-    <mergeCell ref="U8:Y8"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="U7:Y7"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="U5:Y5"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="S9:T9"/>
-    <mergeCell ref="U9:Y9"/>
+    <mergeCell ref="J1:N2"/>
+    <mergeCell ref="O1:S2"/>
+    <mergeCell ref="A1:I4"/>
+    <mergeCell ref="J3:N4"/>
+    <mergeCell ref="O3:S4"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4772,7 +4786,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:V34"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="6.44140625" style="34" customWidth="1"/>
@@ -4793,162 +4807,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="111" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="120" t="s">
+      <c r="A1" s="97" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="126" t="s">
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="130" t="s">
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="142" t="s">
+      <c r="R1" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="143"/>
-      <c r="T1" s="135" t="s">
+      <c r="S1" s="129"/>
+      <c r="T1" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="141" t="s">
+      <c r="U1" s="127" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="187"/>
+      <c r="V1" s="176"/>
     </row>
     <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="114"/>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="129"/>
-      <c r="O2" s="129"/>
-      <c r="P2" s="129"/>
-      <c r="Q2" s="130"/>
-      <c r="R2" s="145"/>
-      <c r="S2" s="146"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="133"/>
-      <c r="V2" s="188"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="115"/>
+      <c r="O2" s="115"/>
+      <c r="P2" s="115"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="131"/>
+      <c r="S2" s="132"/>
+      <c r="T2" s="124"/>
+      <c r="U2" s="119"/>
+      <c r="V2" s="177"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A3" s="114"/>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="120" t="s">
+      <c r="A3" s="100"/>
+      <c r="B3" s="101"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="121"/>
-      <c r="K3" s="121"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="126" t="s">
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="112" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="127"/>
-      <c r="O3" s="127"/>
-      <c r="P3" s="127"/>
-      <c r="Q3" s="130" t="s">
+      <c r="N3" s="113"/>
+      <c r="O3" s="113"/>
+      <c r="P3" s="113"/>
+      <c r="Q3" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="142" t="s">
+      <c r="R3" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="143"/>
-      <c r="T3" s="130" t="s">
+      <c r="S3" s="129"/>
+      <c r="T3" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="U3" s="131" t="s">
-        <v>241</v>
-      </c>
-      <c r="V3" s="187"/>
+      <c r="U3" s="117" t="s">
+        <v>240</v>
+      </c>
+      <c r="V3" s="176"/>
     </row>
     <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A4" s="117"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="123"/>
-      <c r="J4" s="124"/>
-      <c r="K4" s="124"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="128"/>
-      <c r="N4" s="129"/>
-      <c r="O4" s="129"/>
-      <c r="P4" s="129"/>
-      <c r="Q4" s="130"/>
-      <c r="R4" s="145"/>
-      <c r="S4" s="146"/>
-      <c r="T4" s="130"/>
-      <c r="U4" s="133"/>
-      <c r="V4" s="188"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110"/>
+      <c r="M4" s="114"/>
+      <c r="N4" s="115"/>
+      <c r="O4" s="115"/>
+      <c r="P4" s="115"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="131"/>
+      <c r="S4" s="132"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="119"/>
+      <c r="V4" s="177"/>
     </row>
     <row r="5" spans="1:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="170" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="157"/>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="158" t="s">
+      <c r="B5" s="170"/>
+      <c r="C5" s="170"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="158"/>
-      <c r="G5" s="158"/>
-      <c r="H5" s="158"/>
-      <c r="I5" s="157" t="s">
+      <c r="F5" s="171"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="170" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="157"/>
-      <c r="K5" s="157"/>
-      <c r="L5" s="157"/>
-      <c r="M5" s="158" t="s">
+      <c r="J5" s="170"/>
+      <c r="K5" s="170"/>
+      <c r="L5" s="170"/>
+      <c r="M5" s="171" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="158"/>
-      <c r="O5" s="158"/>
-      <c r="P5" s="158"/>
+      <c r="N5" s="171"/>
+      <c r="O5" s="171"/>
+      <c r="P5" s="171"/>
       <c r="Q5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="R5" s="158" t="s">
+      <c r="R5" s="171" t="s">
         <v>26</v>
       </c>
-      <c r="S5" s="158"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="158"/>
-      <c r="V5" s="158"/>
+      <c r="S5" s="171"/>
+      <c r="T5" s="171"/>
+      <c r="U5" s="171"/>
+      <c r="V5" s="171"/>
     </row>
     <row r="6" spans="1:22" s="32" customFormat="1" ht="18.75" x14ac:dyDescent="0.8">
       <c r="A6" s="39"/>
@@ -4976,7 +4990,7 @@
     </row>
     <row r="7" spans="1:22" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
       <c r="A7" s="41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
@@ -5014,7 +5028,7 @@
       <c r="G8" s="178"/>
       <c r="H8" s="178"/>
       <c r="I8" s="178" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J8" s="178"/>
       <c r="K8" s="178"/>
@@ -5030,884 +5044,1216 @@
       <c r="Q8" s="179"/>
       <c r="R8" s="179"/>
       <c r="S8" s="179"/>
-      <c r="T8" s="138" t="s">
-        <v>81</v>
-      </c>
-      <c r="U8" s="139"/>
-      <c r="V8" s="140"/>
+      <c r="T8" s="124" t="s">
+        <v>80</v>
+      </c>
+      <c r="U8" s="125"/>
+      <c r="V8" s="126"/>
     </row>
     <row r="9" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A9" s="44">
         <v>1</v>
       </c>
-      <c r="B9" s="180" t="s">
-        <v>82</v>
+      <c r="B9" s="182" t="s">
+        <v>242</v>
       </c>
       <c r="C9" s="181"/>
       <c r="D9" s="181"/>
       <c r="E9" s="181"/>
       <c r="F9" s="181"/>
       <c r="G9" s="181"/>
-      <c r="H9" s="181"/>
-      <c r="I9" s="156" t="s">
-        <v>69</v>
-      </c>
-      <c r="J9" s="152"/>
-      <c r="K9" s="152"/>
-      <c r="L9" s="153"/>
-      <c r="M9" s="182" t="s">
-        <v>48</v>
-      </c>
-      <c r="N9" s="150"/>
-      <c r="O9" s="150"/>
-      <c r="P9" s="164" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q9" s="154"/>
-      <c r="R9" s="154"/>
+      <c r="H9" s="183"/>
+      <c r="I9" s="153" t="s">
+        <v>68</v>
+      </c>
+      <c r="J9" s="156"/>
+      <c r="K9" s="156"/>
+      <c r="L9" s="154"/>
+      <c r="M9" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="N9" s="168"/>
+      <c r="O9" s="168"/>
+      <c r="P9" s="187" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q9" s="156"/>
+      <c r="R9" s="156"/>
       <c r="S9" s="154"/>
-      <c r="T9" s="154" t="s">
-        <v>84</v>
-      </c>
-      <c r="U9" s="154"/>
-      <c r="V9" s="154"/>
+      <c r="T9" s="172" t="s">
+        <v>247</v>
+      </c>
+      <c r="U9" s="188"/>
+      <c r="V9" s="188"/>
     </row>
     <row r="10" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A10" s="44">
-        <v>2</v>
-      </c>
-      <c r="B10" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="156" t="s">
-        <v>69</v>
-      </c>
-      <c r="J10" s="152"/>
-      <c r="K10" s="152"/>
-      <c r="L10" s="153"/>
-      <c r="M10" s="182" t="s">
-        <v>48</v>
-      </c>
-      <c r="N10" s="150"/>
-      <c r="O10" s="150"/>
-      <c r="P10" s="164" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q10" s="154"/>
-      <c r="R10" s="154"/>
-      <c r="S10" s="154"/>
-      <c r="T10" s="154" t="s">
-        <v>87</v>
-      </c>
-      <c r="U10" s="154"/>
-      <c r="V10" s="154"/>
+      <c r="A10" s="86"/>
+      <c r="B10" s="89"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="89"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="86"/>
+      <c r="J10" s="86"/>
+      <c r="K10" s="86"/>
+      <c r="L10" s="86"/>
+      <c r="M10" s="87"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="88"/>
+      <c r="Q10" s="86"/>
+      <c r="R10" s="86"/>
+      <c r="S10" s="86"/>
+      <c r="T10" s="86"/>
+      <c r="U10" s="86"/>
+      <c r="V10" s="86"/>
     </row>
     <row r="11" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A11" s="44">
-        <v>3</v>
-      </c>
-      <c r="B11" s="88"/>
-      <c r="C11" s="89" t="s">
-        <v>246</v>
-      </c>
-      <c r="D11" s="47"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="172" t="s">
-        <v>69</v>
-      </c>
-      <c r="J11" s="173"/>
-      <c r="K11" s="173"/>
-      <c r="L11" s="174"/>
-      <c r="M11" s="175" t="s">
-        <v>247</v>
-      </c>
-      <c r="N11" s="163"/>
-      <c r="O11" s="176"/>
-      <c r="P11" s="177" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q11" s="152"/>
-      <c r="R11" s="152"/>
-      <c r="S11" s="153"/>
-      <c r="T11" s="151" t="s">
-        <v>250</v>
-      </c>
-      <c r="U11" s="152"/>
-      <c r="V11" s="152"/>
-    </row>
-    <row r="12" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A12" s="44">
-        <v>4</v>
-      </c>
-      <c r="B12" s="186"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="49"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="154" t="s">
-        <v>89</v>
-      </c>
-      <c r="J12" s="154"/>
-      <c r="K12" s="154"/>
-      <c r="L12" s="154"/>
-      <c r="M12" s="182" t="s">
-        <v>48</v>
-      </c>
-      <c r="N12" s="150"/>
-      <c r="O12" s="150"/>
-      <c r="P12" s="164" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q12" s="154"/>
-      <c r="R12" s="154"/>
-      <c r="S12" s="154"/>
-      <c r="T12" s="183" t="s">
-        <v>249</v>
-      </c>
-      <c r="U12" s="154"/>
-      <c r="V12" s="154"/>
-    </row>
-    <row r="13" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A13" s="44">
-        <v>5</v>
-      </c>
-      <c r="B13" s="186"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="186"/>
-      <c r="E13" s="48" t="s">
-        <v>92</v>
-      </c>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="154" t="s">
-        <v>93</v>
-      </c>
-      <c r="J13" s="154"/>
-      <c r="K13" s="154"/>
-      <c r="L13" s="154"/>
-      <c r="M13" s="182" t="s">
-        <v>48</v>
-      </c>
-      <c r="N13" s="150"/>
-      <c r="O13" s="150"/>
-      <c r="P13" s="164" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q13" s="154"/>
-      <c r="R13" s="154"/>
-      <c r="S13" s="154"/>
-      <c r="T13" s="164" t="s">
-        <v>91</v>
-      </c>
-      <c r="U13" s="154"/>
-      <c r="V13" s="154"/>
-    </row>
-    <row r="14" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A14" s="44">
-        <v>6</v>
-      </c>
-      <c r="B14" s="186"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="186"/>
-      <c r="E14" s="186"/>
-      <c r="F14" s="44" t="s">
-        <v>95</v>
-      </c>
-      <c r="G14" s="51"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="156" t="s">
-        <v>59</v>
-      </c>
-      <c r="J14" s="152"/>
-      <c r="K14" s="152"/>
-      <c r="L14" s="153"/>
-      <c r="M14" s="182" t="s">
-        <v>48</v>
-      </c>
-      <c r="N14" s="150"/>
-      <c r="O14" s="150"/>
-      <c r="P14" s="164" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q14" s="154"/>
-      <c r="R14" s="154"/>
-      <c r="S14" s="154"/>
-      <c r="T14" s="154">
-        <v>1</v>
-      </c>
-      <c r="U14" s="154"/>
-      <c r="V14" s="154"/>
+      <c r="A11" s="86"/>
+      <c r="B11" s="89"/>
+      <c r="C11" s="89"/>
+      <c r="D11" s="89"/>
+      <c r="E11" s="89"/>
+      <c r="F11" s="89"/>
+      <c r="G11" s="89"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="86"/>
+      <c r="J11" s="86"/>
+      <c r="K11" s="86"/>
+      <c r="L11" s="86"/>
+      <c r="M11" s="87"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="88"/>
+      <c r="Q11" s="86"/>
+      <c r="R11" s="86"/>
+      <c r="S11" s="86"/>
+      <c r="T11" s="86"/>
+      <c r="U11" s="86"/>
+      <c r="V11" s="86"/>
+    </row>
+    <row r="12" spans="1:22" s="32" customFormat="1" ht="18.75" x14ac:dyDescent="0.8">
+      <c r="A12" s="39"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="40"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="40"/>
+      <c r="S12" s="40"/>
+      <c r="T12" s="40"/>
+      <c r="U12" s="40"/>
+      <c r="V12" s="40"/>
+    </row>
+    <row r="13" spans="1:22" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
+      <c r="A13" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="42"/>
+      <c r="T13" s="42"/>
+      <c r="U13" s="42"/>
+      <c r="V13" s="56"/>
+    </row>
+    <row r="14" spans="1:22" s="32" customFormat="1" ht="16.5" x14ac:dyDescent="0.8">
+      <c r="A14" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="178" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="178"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="178"/>
+      <c r="F14" s="178"/>
+      <c r="G14" s="178"/>
+      <c r="H14" s="178"/>
+      <c r="I14" s="178" t="s">
+        <v>53</v>
+      </c>
+      <c r="J14" s="178"/>
+      <c r="K14" s="178"/>
+      <c r="L14" s="178"/>
+      <c r="M14" s="178" t="s">
+        <v>42</v>
+      </c>
+      <c r="N14" s="178"/>
+      <c r="O14" s="178"/>
+      <c r="P14" s="179" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q14" s="179"/>
+      <c r="R14" s="179"/>
+      <c r="S14" s="179"/>
+      <c r="T14" s="124" t="s">
+        <v>80</v>
+      </c>
+      <c r="U14" s="125"/>
+      <c r="V14" s="126"/>
     </row>
     <row r="15" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A15" s="44">
-        <v>7</v>
-      </c>
-      <c r="B15" s="186"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="186"/>
-      <c r="E15" s="186"/>
-      <c r="F15" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" s="51"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="156" t="s">
-        <v>69</v>
-      </c>
-      <c r="J15" s="152"/>
-      <c r="K15" s="152"/>
-      <c r="L15" s="153"/>
-      <c r="M15" s="150"/>
-      <c r="N15" s="150"/>
-      <c r="O15" s="150"/>
-      <c r="P15" s="164" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q15" s="154"/>
-      <c r="R15" s="154"/>
-      <c r="S15" s="154"/>
-      <c r="T15" s="154" t="s">
-        <v>99</v>
-      </c>
-      <c r="U15" s="154"/>
-      <c r="V15" s="154"/>
+        <v>1</v>
+      </c>
+      <c r="B15" s="180" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="181"/>
+      <c r="D15" s="181"/>
+      <c r="E15" s="181"/>
+      <c r="F15" s="181"/>
+      <c r="G15" s="181"/>
+      <c r="H15" s="181"/>
+      <c r="I15" s="153" t="s">
+        <v>68</v>
+      </c>
+      <c r="J15" s="156"/>
+      <c r="K15" s="156"/>
+      <c r="L15" s="154"/>
+      <c r="M15" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="N15" s="168"/>
+      <c r="O15" s="168"/>
+      <c r="P15" s="159" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q15" s="152"/>
+      <c r="R15" s="152"/>
+      <c r="S15" s="152"/>
+      <c r="T15" s="152" t="s">
+        <v>83</v>
+      </c>
+      <c r="U15" s="152"/>
+      <c r="V15" s="152"/>
     </row>
     <row r="16" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A16" s="44">
-        <v>8</v>
-      </c>
-      <c r="B16" s="186"/>
-      <c r="C16" s="83"/>
-      <c r="D16" s="186"/>
-      <c r="E16" s="186"/>
-      <c r="F16" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="G16" s="51"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="156" t="s">
-        <v>69</v>
-      </c>
-      <c r="J16" s="152"/>
-      <c r="K16" s="152"/>
-      <c r="L16" s="153"/>
-      <c r="M16" s="150"/>
-      <c r="N16" s="150"/>
-      <c r="O16" s="150"/>
-      <c r="P16" s="164" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q16" s="154"/>
-      <c r="R16" s="154"/>
-      <c r="S16" s="154"/>
-      <c r="T16" s="154" t="s">
-        <v>102</v>
-      </c>
-      <c r="U16" s="154"/>
-      <c r="V16" s="154"/>
+        <v>2</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="153" t="s">
+        <v>68</v>
+      </c>
+      <c r="J16" s="156"/>
+      <c r="K16" s="156"/>
+      <c r="L16" s="154"/>
+      <c r="M16" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="N16" s="168"/>
+      <c r="O16" s="168"/>
+      <c r="P16" s="159" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q16" s="152"/>
+      <c r="R16" s="152"/>
+      <c r="S16" s="152"/>
+      <c r="T16" s="152" t="s">
+        <v>86</v>
+      </c>
+      <c r="U16" s="152"/>
+      <c r="V16" s="152"/>
     </row>
     <row r="17" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A17" s="44">
-        <v>9</v>
-      </c>
-      <c r="B17" s="186"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="186"/>
-      <c r="E17" s="186"/>
-      <c r="F17" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="G17" s="51"/>
+        <v>3</v>
+      </c>
+      <c r="B17" s="185"/>
+      <c r="C17" s="186"/>
+      <c r="D17" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" s="49"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
       <c r="H17" s="50"/>
-      <c r="I17" s="156" t="s">
-        <v>69</v>
+      <c r="I17" s="152" t="s">
+        <v>88</v>
       </c>
       <c r="J17" s="152"/>
       <c r="K17" s="152"/>
-      <c r="L17" s="153"/>
-      <c r="M17" s="150"/>
-      <c r="N17" s="150"/>
-      <c r="O17" s="150"/>
-      <c r="P17" s="164" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q17" s="154"/>
-      <c r="R17" s="154"/>
-      <c r="S17" s="154"/>
-      <c r="T17" s="154" t="s">
-        <v>104</v>
-      </c>
-      <c r="U17" s="154"/>
-      <c r="V17" s="154"/>
+      <c r="L17" s="152"/>
+      <c r="M17" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="N17" s="168"/>
+      <c r="O17" s="168"/>
+      <c r="P17" s="159" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q17" s="152"/>
+      <c r="R17" s="152"/>
+      <c r="S17" s="152"/>
+      <c r="T17" s="184" t="s">
+        <v>246</v>
+      </c>
+      <c r="U17" s="152"/>
+      <c r="V17" s="152"/>
     </row>
     <row r="18" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A18" s="44">
-        <v>10</v>
-      </c>
-      <c r="B18" s="186"/>
-      <c r="C18" s="83"/>
-      <c r="D18" s="186"/>
-      <c r="E18" s="186"/>
-      <c r="F18" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="G18" s="51"/>
+        <v>4</v>
+      </c>
+      <c r="B18" s="185"/>
+      <c r="C18" s="186"/>
+      <c r="D18" s="175"/>
+      <c r="E18" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
       <c r="H18" s="50"/>
-      <c r="I18" s="156" t="s">
-        <v>59</v>
+      <c r="I18" s="152" t="s">
+        <v>92</v>
       </c>
       <c r="J18" s="152"/>
       <c r="K18" s="152"/>
-      <c r="L18" s="153"/>
-      <c r="M18" s="150"/>
-      <c r="N18" s="150"/>
-      <c r="O18" s="150"/>
-      <c r="P18" s="164" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q18" s="154"/>
-      <c r="R18" s="154"/>
-      <c r="S18" s="154"/>
-      <c r="T18" s="154">
-        <v>75</v>
-      </c>
-      <c r="U18" s="154"/>
-      <c r="V18" s="154"/>
+      <c r="L18" s="152"/>
+      <c r="M18" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="N18" s="168"/>
+      <c r="O18" s="168"/>
+      <c r="P18" s="159" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q18" s="152"/>
+      <c r="R18" s="152"/>
+      <c r="S18" s="152"/>
+      <c r="T18" s="159" t="s">
+        <v>90</v>
+      </c>
+      <c r="U18" s="152"/>
+      <c r="V18" s="152"/>
     </row>
     <row r="19" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A19" s="44">
-        <v>11</v>
-      </c>
-      <c r="B19" s="186"/>
-      <c r="C19" s="83"/>
-      <c r="D19" s="186"/>
-      <c r="E19" s="186"/>
+        <v>5</v>
+      </c>
+      <c r="B19" s="185"/>
+      <c r="C19" s="186"/>
+      <c r="D19" s="175"/>
+      <c r="E19" s="175"/>
       <c r="F19" s="44" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G19" s="51"/>
       <c r="H19" s="50"/>
-      <c r="I19" s="156" t="s">
-        <v>69</v>
-      </c>
-      <c r="J19" s="152"/>
-      <c r="K19" s="152"/>
-      <c r="L19" s="153"/>
-      <c r="M19" s="150"/>
-      <c r="N19" s="150"/>
-      <c r="O19" s="150"/>
-      <c r="P19" s="164" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q19" s="154"/>
-      <c r="R19" s="154"/>
-      <c r="S19" s="154"/>
-      <c r="T19" s="154" t="s">
-        <v>109</v>
-      </c>
-      <c r="U19" s="154"/>
-      <c r="V19" s="154"/>
+      <c r="I19" s="153" t="s">
+        <v>58</v>
+      </c>
+      <c r="J19" s="156"/>
+      <c r="K19" s="156"/>
+      <c r="L19" s="154"/>
+      <c r="M19" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="N19" s="168"/>
+      <c r="O19" s="168"/>
+      <c r="P19" s="159" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q19" s="152"/>
+      <c r="R19" s="152"/>
+      <c r="S19" s="152"/>
+      <c r="T19" s="152">
+        <v>1</v>
+      </c>
+      <c r="U19" s="152"/>
+      <c r="V19" s="152"/>
     </row>
     <row r="20" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A20" s="44">
-        <v>12</v>
-      </c>
-      <c r="B20" s="169"/>
-      <c r="C20" s="87"/>
-      <c r="D20" s="169"/>
-      <c r="E20" s="44" t="s">
-        <v>110</v>
-      </c>
-      <c r="F20" s="44"/>
+        <v>6</v>
+      </c>
+      <c r="B20" s="185"/>
+      <c r="C20" s="186"/>
+      <c r="D20" s="175"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="44" t="s">
+        <v>96</v>
+      </c>
       <c r="G20" s="51"/>
       <c r="H20" s="50"/>
-      <c r="I20" s="156" t="s">
-        <v>59</v>
-      </c>
-      <c r="J20" s="152"/>
-      <c r="K20" s="152"/>
-      <c r="L20" s="153"/>
-      <c r="M20" s="182" t="s">
-        <v>48</v>
-      </c>
-      <c r="N20" s="150"/>
-      <c r="O20" s="150"/>
-      <c r="P20" s="164" t="s">
+      <c r="I20" s="153" t="s">
+        <v>68</v>
+      </c>
+      <c r="J20" s="156"/>
+      <c r="K20" s="156"/>
+      <c r="L20" s="154"/>
+      <c r="M20" s="168"/>
+      <c r="N20" s="168"/>
+      <c r="O20" s="168"/>
+      <c r="P20" s="159" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q20" s="152"/>
+      <c r="R20" s="152"/>
+      <c r="S20" s="152"/>
+      <c r="T20" s="152" t="s">
+        <v>98</v>
+      </c>
+      <c r="U20" s="152"/>
+      <c r="V20" s="152"/>
+    </row>
+    <row r="21" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A21" s="44">
+        <v>7</v>
+      </c>
+      <c r="B21" s="185"/>
+      <c r="C21" s="186"/>
+      <c r="D21" s="175"/>
+      <c r="E21" s="175"/>
+      <c r="F21" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="G21" s="51"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="153" t="s">
+        <v>68</v>
+      </c>
+      <c r="J21" s="156"/>
+      <c r="K21" s="156"/>
+      <c r="L21" s="154"/>
+      <c r="M21" s="168"/>
+      <c r="N21" s="168"/>
+      <c r="O21" s="168"/>
+      <c r="P21" s="159" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="152"/>
+      <c r="R21" s="152"/>
+      <c r="S21" s="152"/>
+      <c r="T21" s="152" t="s">
+        <v>101</v>
+      </c>
+      <c r="U21" s="152"/>
+      <c r="V21" s="152"/>
+    </row>
+    <row r="22" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A22" s="44">
+        <v>8</v>
+      </c>
+      <c r="B22" s="185"/>
+      <c r="C22" s="186"/>
+      <c r="D22" s="175"/>
+      <c r="E22" s="175"/>
+      <c r="F22" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="G22" s="51"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="153" t="s">
+        <v>68</v>
+      </c>
+      <c r="J22" s="156"/>
+      <c r="K22" s="156"/>
+      <c r="L22" s="154"/>
+      <c r="M22" s="168"/>
+      <c r="N22" s="168"/>
+      <c r="O22" s="168"/>
+      <c r="P22" s="159" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q22" s="152"/>
+      <c r="R22" s="152"/>
+      <c r="S22" s="152"/>
+      <c r="T22" s="152" t="s">
+        <v>103</v>
+      </c>
+      <c r="U22" s="152"/>
+      <c r="V22" s="152"/>
+    </row>
+    <row r="23" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A23" s="44">
+        <v>9</v>
+      </c>
+      <c r="B23" s="185"/>
+      <c r="C23" s="186"/>
+      <c r="D23" s="175"/>
+      <c r="E23" s="175"/>
+      <c r="F23" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G23" s="51"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="153" t="s">
+        <v>58</v>
+      </c>
+      <c r="J23" s="156"/>
+      <c r="K23" s="156"/>
+      <c r="L23" s="154"/>
+      <c r="M23" s="168"/>
+      <c r="N23" s="168"/>
+      <c r="O23" s="168"/>
+      <c r="P23" s="159" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q23" s="152"/>
+      <c r="R23" s="152"/>
+      <c r="S23" s="152"/>
+      <c r="T23" s="152">
+        <v>75</v>
+      </c>
+      <c r="U23" s="152"/>
+      <c r="V23" s="152"/>
+    </row>
+    <row r="24" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A24" s="44">
+        <v>10</v>
+      </c>
+      <c r="B24" s="185"/>
+      <c r="C24" s="186"/>
+      <c r="D24" s="175"/>
+      <c r="E24" s="175"/>
+      <c r="F24" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" s="51"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="153" t="s">
+        <v>68</v>
+      </c>
+      <c r="J24" s="156"/>
+      <c r="K24" s="156"/>
+      <c r="L24" s="154"/>
+      <c r="M24" s="168"/>
+      <c r="N24" s="168"/>
+      <c r="O24" s="168"/>
+      <c r="P24" s="159" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q24" s="152"/>
+      <c r="R24" s="152"/>
+      <c r="S24" s="152"/>
+      <c r="T24" s="152" t="s">
+        <v>108</v>
+      </c>
+      <c r="U24" s="152"/>
+      <c r="V24" s="152"/>
+    </row>
+    <row r="25" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A25" s="44">
+        <v>11</v>
+      </c>
+      <c r="B25" s="131"/>
+      <c r="C25" s="133"/>
+      <c r="D25" s="160"/>
+      <c r="E25" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="F25" s="44"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="153" t="s">
+        <v>58</v>
+      </c>
+      <c r="J25" s="156"/>
+      <c r="K25" s="156"/>
+      <c r="L25" s="154"/>
+      <c r="M25" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="N25" s="168"/>
+      <c r="O25" s="168"/>
+      <c r="P25" s="159" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q25" s="152"/>
+      <c r="R25" s="152"/>
+      <c r="S25" s="152"/>
+      <c r="T25" s="152">
+        <v>3</v>
+      </c>
+      <c r="U25" s="152"/>
+      <c r="V25" s="152"/>
+    </row>
+    <row r="26" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A26" s="86"/>
+      <c r="B26" s="86"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="86"/>
+      <c r="L26" s="86"/>
+      <c r="M26" s="87"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="40"/>
+      <c r="P26" s="88"/>
+      <c r="Q26" s="86"/>
+      <c r="R26" s="86"/>
+      <c r="S26" s="86"/>
+      <c r="T26" s="86"/>
+      <c r="U26" s="86"/>
+      <c r="V26" s="86"/>
+    </row>
+    <row r="27" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A27" s="86"/>
+      <c r="B27" s="86"/>
+      <c r="C27" s="86"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="86"/>
+      <c r="G27" s="86"/>
+      <c r="H27" s="86"/>
+      <c r="I27" s="86"/>
+      <c r="J27" s="86"/>
+      <c r="K27" s="86"/>
+      <c r="L27" s="86"/>
+      <c r="M27" s="87"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="88"/>
+      <c r="Q27" s="86"/>
+      <c r="R27" s="86"/>
+      <c r="S27" s="86"/>
+      <c r="T27" s="86"/>
+      <c r="U27" s="86"/>
+      <c r="V27" s="86"/>
+    </row>
+    <row r="28" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A28" s="86"/>
+      <c r="B28" s="86"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="86"/>
+      <c r="G28" s="86"/>
+      <c r="H28" s="86"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="K28" s="86"/>
+      <c r="L28" s="86"/>
+      <c r="M28" s="87"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="88"/>
+      <c r="Q28" s="86"/>
+      <c r="R28" s="86"/>
+      <c r="S28" s="86"/>
+      <c r="T28" s="86"/>
+      <c r="U28" s="86"/>
+      <c r="V28" s="86"/>
+    </row>
+    <row r="29" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A29" s="86"/>
+      <c r="B29" s="86"/>
+      <c r="C29" s="86"/>
+      <c r="D29" s="86"/>
+      <c r="E29" s="86"/>
+      <c r="F29" s="86"/>
+      <c r="G29" s="86"/>
+      <c r="H29" s="86"/>
+      <c r="I29" s="86"/>
+      <c r="J29" s="86"/>
+      <c r="K29" s="86"/>
+      <c r="L29" s="86"/>
+      <c r="M29" s="87"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="88"/>
+      <c r="Q29" s="86"/>
+      <c r="R29" s="86"/>
+      <c r="S29" s="86"/>
+      <c r="T29" s="86"/>
+      <c r="U29" s="86"/>
+      <c r="V29" s="86"/>
+    </row>
+    <row r="30" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A30" s="39"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="40"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="40"/>
+      <c r="M30" s="40"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="40"/>
+      <c r="P30" s="40"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="40"/>
+      <c r="S30" s="40"/>
+      <c r="T30" s="40"/>
+      <c r="U30" s="40"/>
+      <c r="V30" s="40"/>
+    </row>
+    <row r="31" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A31" s="52" t="s">
         <v>111</v>
       </c>
-      <c r="Q20" s="154"/>
-      <c r="R20" s="154"/>
-      <c r="S20" s="154"/>
-      <c r="T20" s="154">
-        <v>3</v>
-      </c>
-      <c r="U20" s="154"/>
-      <c r="V20" s="154"/>
-    </row>
-    <row r="21" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A21" s="39"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="40"/>
-      <c r="P21" s="40"/>
-      <c r="Q21" s="40"/>
-      <c r="R21" s="40"/>
-      <c r="S21" s="40"/>
-      <c r="T21" s="40"/>
-      <c r="U21" s="40"/>
-      <c r="V21" s="40"/>
-    </row>
-    <row r="22" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A22" s="52" t="s">
-        <v>112</v>
-      </c>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="53"/>
-      <c r="N22" s="53"/>
-      <c r="O22" s="53"/>
-      <c r="P22" s="53"/>
-      <c r="Q22" s="53"/>
-      <c r="R22" s="53"/>
-      <c r="S22" s="53"/>
-      <c r="T22" s="53"/>
-      <c r="U22" s="53"/>
-      <c r="V22" s="57"/>
-    </row>
-    <row r="23" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A23" s="43" t="s">
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="53"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="53"/>
+      <c r="O31" s="53"/>
+      <c r="P31" s="53"/>
+      <c r="Q31" s="53"/>
+      <c r="R31" s="53"/>
+      <c r="S31" s="53"/>
+      <c r="T31" s="53"/>
+      <c r="U31" s="53"/>
+      <c r="V31" s="57"/>
+    </row>
+    <row r="32" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A32" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="178" t="s">
+      <c r="B32" s="178" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="178"/>
-      <c r="D23" s="178"/>
-      <c r="E23" s="178"/>
-      <c r="F23" s="178"/>
-      <c r="G23" s="178"/>
-      <c r="H23" s="178"/>
-      <c r="I23" s="178" t="s">
-        <v>54</v>
-      </c>
-      <c r="J23" s="178"/>
-      <c r="K23" s="178"/>
-      <c r="L23" s="178"/>
-      <c r="M23" s="178" t="s">
+      <c r="C32" s="178"/>
+      <c r="D32" s="178"/>
+      <c r="E32" s="178"/>
+      <c r="F32" s="178"/>
+      <c r="G32" s="178"/>
+      <c r="H32" s="178"/>
+      <c r="I32" s="178" t="s">
+        <v>53</v>
+      </c>
+      <c r="J32" s="178"/>
+      <c r="K32" s="178"/>
+      <c r="L32" s="178"/>
+      <c r="M32" s="178" t="s">
         <v>42</v>
       </c>
-      <c r="N23" s="178"/>
-      <c r="O23" s="178"/>
-      <c r="P23" s="179" t="s">
+      <c r="N32" s="178"/>
+      <c r="O32" s="178"/>
+      <c r="P32" s="179" t="s">
         <v>45</v>
       </c>
-      <c r="Q23" s="179"/>
-      <c r="R23" s="179"/>
-      <c r="S23" s="179"/>
-      <c r="T23" s="138" t="s">
-        <v>81</v>
-      </c>
-      <c r="U23" s="139"/>
-      <c r="V23" s="140"/>
-    </row>
-    <row r="24" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A24" s="44">
-        <v>1</v>
-      </c>
-      <c r="B24" s="180" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" s="181"/>
-      <c r="D24" s="181"/>
-      <c r="E24" s="181"/>
-      <c r="F24" s="181"/>
-      <c r="G24" s="181"/>
-      <c r="H24" s="181"/>
-      <c r="I24" s="156" t="s">
-        <v>69</v>
-      </c>
-      <c r="J24" s="152"/>
-      <c r="K24" s="152"/>
-      <c r="L24" s="153"/>
-      <c r="M24" s="182" t="s">
-        <v>48</v>
-      </c>
-      <c r="N24" s="150"/>
-      <c r="O24" s="150"/>
-      <c r="P24" s="164" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q24" s="154"/>
-      <c r="R24" s="154"/>
-      <c r="S24" s="154"/>
-      <c r="T24" s="154" t="s">
-        <v>113</v>
-      </c>
-      <c r="U24" s="154"/>
-      <c r="V24" s="154"/>
-    </row>
-    <row r="25" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A25" s="44">
-        <v>2</v>
-      </c>
-      <c r="B25" s="180" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" s="181"/>
-      <c r="D25" s="181"/>
-      <c r="E25" s="181"/>
-      <c r="F25" s="181"/>
-      <c r="G25" s="181"/>
-      <c r="H25" s="181"/>
-      <c r="I25" s="156" t="s">
-        <v>69</v>
-      </c>
-      <c r="J25" s="152"/>
-      <c r="K25" s="152"/>
-      <c r="L25" s="153"/>
-      <c r="M25" s="182" t="s">
-        <v>48</v>
-      </c>
-      <c r="N25" s="150"/>
-      <c r="O25" s="150"/>
-      <c r="P25" s="164" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q25" s="154"/>
-      <c r="R25" s="154"/>
-      <c r="S25" s="154"/>
-      <c r="T25" s="154" t="s">
-        <v>115</v>
-      </c>
-      <c r="U25" s="154"/>
-      <c r="V25" s="154"/>
-    </row>
-    <row r="26" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A26" s="44">
-        <v>3</v>
-      </c>
-      <c r="B26" s="184" t="s">
-        <v>116</v>
-      </c>
-      <c r="C26" s="181"/>
-      <c r="D26" s="181"/>
-      <c r="E26" s="181"/>
-      <c r="F26" s="181"/>
-      <c r="G26" s="181"/>
-      <c r="H26" s="185"/>
-      <c r="I26" s="156" t="s">
-        <v>69</v>
-      </c>
-      <c r="J26" s="152"/>
-      <c r="K26" s="152"/>
-      <c r="L26" s="153"/>
-      <c r="M26" s="182" t="s">
-        <v>48</v>
-      </c>
-      <c r="N26" s="150"/>
-      <c r="O26" s="150"/>
-      <c r="P26" s="154" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q26" s="154"/>
-      <c r="R26" s="154"/>
-      <c r="S26" s="154"/>
-      <c r="T26" s="154" t="s">
-        <v>118</v>
-      </c>
-      <c r="U26" s="154"/>
-      <c r="V26" s="154"/>
-    </row>
-    <row r="27" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A28" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="B28" s="53"/>
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="53"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="53"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="53"/>
-      <c r="M28" s="53"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
-      <c r="P28" s="53"/>
-      <c r="Q28" s="53"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="53"/>
-      <c r="T28" s="53"/>
-      <c r="U28" s="53"/>
-      <c r="V28" s="57"/>
-    </row>
-    <row r="29" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A29" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="178" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="178"/>
-      <c r="D29" s="178"/>
-      <c r="E29" s="178"/>
-      <c r="F29" s="178"/>
-      <c r="G29" s="178"/>
-      <c r="H29" s="178"/>
-      <c r="I29" s="178" t="s">
-        <v>54</v>
-      </c>
-      <c r="J29" s="178"/>
-      <c r="K29" s="178"/>
-      <c r="L29" s="178"/>
-      <c r="M29" s="178" t="s">
-        <v>42</v>
-      </c>
-      <c r="N29" s="178"/>
-      <c r="O29" s="178"/>
-      <c r="P29" s="179" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q29" s="179"/>
-      <c r="R29" s="179"/>
-      <c r="S29" s="179"/>
-      <c r="T29" s="138" t="s">
-        <v>81</v>
-      </c>
-      <c r="U29" s="139"/>
-      <c r="V29" s="140"/>
-    </row>
-    <row r="30" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A30" s="44">
-        <v>1</v>
-      </c>
-      <c r="B30" s="180" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" s="181"/>
-      <c r="D30" s="181"/>
-      <c r="E30" s="181"/>
-      <c r="F30" s="181"/>
-      <c r="G30" s="181"/>
-      <c r="H30" s="181"/>
-      <c r="I30" s="156" t="s">
-        <v>69</v>
-      </c>
-      <c r="J30" s="152"/>
-      <c r="K30" s="152"/>
-      <c r="L30" s="153"/>
-      <c r="M30" s="182" t="s">
-        <v>48</v>
-      </c>
-      <c r="N30" s="150"/>
-      <c r="O30" s="150"/>
-      <c r="P30" s="164" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q30" s="154"/>
-      <c r="R30" s="154"/>
-      <c r="S30" s="154"/>
-      <c r="T30" s="154" t="s">
-        <v>113</v>
-      </c>
-      <c r="U30" s="154"/>
-      <c r="V30" s="154"/>
-    </row>
-    <row r="31" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A31" s="44">
-        <v>2</v>
-      </c>
-      <c r="B31" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="156" t="s">
-        <v>69</v>
-      </c>
-      <c r="J31" s="152"/>
-      <c r="K31" s="152"/>
-      <c r="L31" s="153"/>
-      <c r="M31" s="182" t="s">
-        <v>48</v>
-      </c>
-      <c r="N31" s="150"/>
-      <c r="O31" s="150"/>
-      <c r="P31" s="164" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q31" s="154"/>
-      <c r="R31" s="154"/>
-      <c r="S31" s="154"/>
-      <c r="T31" s="154" t="s">
-        <v>120</v>
-      </c>
-      <c r="U31" s="154"/>
-      <c r="V31" s="154"/>
-    </row>
-    <row r="32" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A32" s="44">
-        <v>3</v>
-      </c>
-      <c r="B32" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="C32" s="50"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="156" t="s">
-        <v>69</v>
-      </c>
-      <c r="J32" s="152"/>
-      <c r="K32" s="152"/>
-      <c r="L32" s="153"/>
-      <c r="M32" s="182" t="s">
-        <v>48</v>
-      </c>
-      <c r="N32" s="150"/>
-      <c r="O32" s="150"/>
-      <c r="P32" s="154" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q32" s="154"/>
-      <c r="R32" s="154"/>
-      <c r="S32" s="154"/>
-      <c r="T32" s="164" t="s">
-        <v>122</v>
-      </c>
-      <c r="U32" s="154"/>
-      <c r="V32" s="154"/>
+      <c r="Q32" s="179"/>
+      <c r="R32" s="179"/>
+      <c r="S32" s="179"/>
+      <c r="T32" s="124" t="s">
+        <v>80</v>
+      </c>
+      <c r="U32" s="125"/>
+      <c r="V32" s="126"/>
     </row>
     <row r="33" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A33" s="44">
-        <v>4</v>
-      </c>
-      <c r="B33" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="156" t="s">
-        <v>69</v>
-      </c>
-      <c r="J33" s="152"/>
-      <c r="K33" s="152"/>
-      <c r="L33" s="153"/>
-      <c r="M33" s="182" t="s">
-        <v>48</v>
-      </c>
-      <c r="N33" s="150"/>
-      <c r="O33" s="150"/>
-      <c r="P33" s="154" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q33" s="154"/>
-      <c r="R33" s="154"/>
-      <c r="S33" s="154"/>
-      <c r="T33" s="154" t="s">
-        <v>125</v>
-      </c>
-      <c r="U33" s="154"/>
-      <c r="V33" s="154"/>
+        <v>1</v>
+      </c>
+      <c r="B33" s="180" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="181"/>
+      <c r="D33" s="181"/>
+      <c r="E33" s="181"/>
+      <c r="F33" s="181"/>
+      <c r="G33" s="181"/>
+      <c r="H33" s="181"/>
+      <c r="I33" s="153" t="s">
+        <v>68</v>
+      </c>
+      <c r="J33" s="156"/>
+      <c r="K33" s="156"/>
+      <c r="L33" s="154"/>
+      <c r="M33" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="N33" s="168"/>
+      <c r="O33" s="168"/>
+      <c r="P33" s="159" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q33" s="152"/>
+      <c r="R33" s="152"/>
+      <c r="S33" s="152"/>
+      <c r="T33" s="152" t="s">
+        <v>112</v>
+      </c>
+      <c r="U33" s="152"/>
+      <c r="V33" s="152"/>
     </row>
     <row r="34" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A34" s="44">
+        <v>2</v>
+      </c>
+      <c r="B34" s="180" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="181"/>
+      <c r="D34" s="181"/>
+      <c r="E34" s="181"/>
+      <c r="F34" s="181"/>
+      <c r="G34" s="181"/>
+      <c r="H34" s="181"/>
+      <c r="I34" s="153" t="s">
+        <v>68</v>
+      </c>
+      <c r="J34" s="156"/>
+      <c r="K34" s="156"/>
+      <c r="L34" s="154"/>
+      <c r="M34" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="N34" s="168"/>
+      <c r="O34" s="168"/>
+      <c r="P34" s="159" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q34" s="152"/>
+      <c r="R34" s="152"/>
+      <c r="S34" s="152"/>
+      <c r="T34" s="152" t="s">
+        <v>114</v>
+      </c>
+      <c r="U34" s="152"/>
+      <c r="V34" s="152"/>
+    </row>
+    <row r="35" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A35" s="44">
+        <v>3</v>
+      </c>
+      <c r="B35" s="182" t="s">
+        <v>115</v>
+      </c>
+      <c r="C35" s="181"/>
+      <c r="D35" s="181"/>
+      <c r="E35" s="181"/>
+      <c r="F35" s="181"/>
+      <c r="G35" s="181"/>
+      <c r="H35" s="183"/>
+      <c r="I35" s="153" t="s">
+        <v>68</v>
+      </c>
+      <c r="J35" s="156"/>
+      <c r="K35" s="156"/>
+      <c r="L35" s="154"/>
+      <c r="M35" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="N35" s="168"/>
+      <c r="O35" s="168"/>
+      <c r="P35" s="152" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q35" s="152"/>
+      <c r="R35" s="152"/>
+      <c r="S35" s="152"/>
+      <c r="T35" s="152" t="s">
+        <v>117</v>
+      </c>
+      <c r="U35" s="152"/>
+      <c r="V35" s="152"/>
+    </row>
+    <row r="36" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A37" s="52" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="53"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="53"/>
+      <c r="N37" s="53"/>
+      <c r="O37" s="53"/>
+      <c r="P37" s="53"/>
+      <c r="Q37" s="53"/>
+      <c r="R37" s="53"/>
+      <c r="S37" s="53"/>
+      <c r="T37" s="53"/>
+      <c r="U37" s="53"/>
+      <c r="V37" s="57"/>
+    </row>
+    <row r="38" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A38" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" s="178" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="178"/>
+      <c r="D38" s="178"/>
+      <c r="E38" s="178"/>
+      <c r="F38" s="178"/>
+      <c r="G38" s="178"/>
+      <c r="H38" s="178"/>
+      <c r="I38" s="178" t="s">
+        <v>53</v>
+      </c>
+      <c r="J38" s="178"/>
+      <c r="K38" s="178"/>
+      <c r="L38" s="178"/>
+      <c r="M38" s="178" t="s">
+        <v>42</v>
+      </c>
+      <c r="N38" s="178"/>
+      <c r="O38" s="178"/>
+      <c r="P38" s="179" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q38" s="179"/>
+      <c r="R38" s="179"/>
+      <c r="S38" s="179"/>
+      <c r="T38" s="124" t="s">
+        <v>80</v>
+      </c>
+      <c r="U38" s="125"/>
+      <c r="V38" s="126"/>
+    </row>
+    <row r="39" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A39" s="44">
+        <v>1</v>
+      </c>
+      <c r="B39" s="180" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="181"/>
+      <c r="D39" s="181"/>
+      <c r="E39" s="181"/>
+      <c r="F39" s="181"/>
+      <c r="G39" s="181"/>
+      <c r="H39" s="181"/>
+      <c r="I39" s="153" t="s">
+        <v>68</v>
+      </c>
+      <c r="J39" s="156"/>
+      <c r="K39" s="156"/>
+      <c r="L39" s="154"/>
+      <c r="M39" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="N39" s="168"/>
+      <c r="O39" s="168"/>
+      <c r="P39" s="159" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q39" s="152"/>
+      <c r="R39" s="152"/>
+      <c r="S39" s="152"/>
+      <c r="T39" s="152" t="s">
+        <v>112</v>
+      </c>
+      <c r="U39" s="152"/>
+      <c r="V39" s="152"/>
+    </row>
+    <row r="40" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A40" s="44">
+        <v>2</v>
+      </c>
+      <c r="B40" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="47"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="47"/>
+      <c r="G40" s="47"/>
+      <c r="H40" s="47"/>
+      <c r="I40" s="153" t="s">
+        <v>68</v>
+      </c>
+      <c r="J40" s="156"/>
+      <c r="K40" s="156"/>
+      <c r="L40" s="154"/>
+      <c r="M40" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="N40" s="168"/>
+      <c r="O40" s="168"/>
+      <c r="P40" s="159" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q40" s="152"/>
+      <c r="R40" s="152"/>
+      <c r="S40" s="152"/>
+      <c r="T40" s="152" t="s">
+        <v>119</v>
+      </c>
+      <c r="U40" s="152"/>
+      <c r="V40" s="152"/>
+    </row>
+    <row r="41" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A41" s="44">
+        <v>3</v>
+      </c>
+      <c r="B41" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41" s="50"/>
+      <c r="D41" s="50"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="50"/>
+      <c r="G41" s="50"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="153" t="s">
+        <v>68</v>
+      </c>
+      <c r="J41" s="156"/>
+      <c r="K41" s="156"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="N41" s="168"/>
+      <c r="O41" s="168"/>
+      <c r="P41" s="152" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q41" s="152"/>
+      <c r="R41" s="152"/>
+      <c r="S41" s="152"/>
+      <c r="T41" s="159" t="s">
+        <v>121</v>
+      </c>
+      <c r="U41" s="152"/>
+      <c r="V41" s="152"/>
+    </row>
+    <row r="42" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A42" s="44">
+        <v>4</v>
+      </c>
+      <c r="B42" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" s="50"/>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="50"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="153" t="s">
+        <v>68</v>
+      </c>
+      <c r="J42" s="156"/>
+      <c r="K42" s="156"/>
+      <c r="L42" s="154"/>
+      <c r="M42" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="N42" s="168"/>
+      <c r="O42" s="168"/>
+      <c r="P42" s="152" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q42" s="152"/>
+      <c r="R42" s="152"/>
+      <c r="S42" s="152"/>
+      <c r="T42" s="152" t="s">
+        <v>124</v>
+      </c>
+      <c r="U42" s="152"/>
+      <c r="V42" s="152"/>
+    </row>
+    <row r="43" spans="1:22" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A43" s="44">
         <v>5</v>
       </c>
-      <c r="B34" s="51" t="s">
+      <c r="B43" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43" s="50"/>
+      <c r="D43" s="50"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="50"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="54"/>
+      <c r="I43" s="153" t="s">
+        <v>68</v>
+      </c>
+      <c r="J43" s="156"/>
+      <c r="K43" s="156"/>
+      <c r="L43" s="154"/>
+      <c r="M43" s="174" t="s">
+        <v>47</v>
+      </c>
+      <c r="N43" s="168"/>
+      <c r="O43" s="168"/>
+      <c r="P43" s="152" t="s">
         <v>126</v>
       </c>
-      <c r="C34" s="50"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="54"/>
-      <c r="I34" s="156" t="s">
-        <v>69</v>
-      </c>
-      <c r="J34" s="152"/>
-      <c r="K34" s="152"/>
-      <c r="L34" s="153"/>
-      <c r="M34" s="182" t="s">
-        <v>48</v>
-      </c>
-      <c r="N34" s="150"/>
-      <c r="O34" s="150"/>
-      <c r="P34" s="154" t="s">
+      <c r="Q43" s="152"/>
+      <c r="R43" s="152"/>
+      <c r="S43" s="152"/>
+      <c r="T43" s="152" t="s">
         <v>127</v>
       </c>
-      <c r="Q34" s="154"/>
-      <c r="R34" s="154"/>
-      <c r="S34" s="154"/>
-      <c r="T34" s="154" t="s">
-        <v>128</v>
-      </c>
-      <c r="U34" s="154"/>
-      <c r="V34" s="154"/>
+      <c r="U43" s="152"/>
+      <c r="V43" s="152"/>
     </row>
   </sheetData>
-  <mergeCells count="121">
+  <mergeCells count="127">
+    <mergeCell ref="B17:C25"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="T9:V9"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="P8:S8"/>
+    <mergeCell ref="T8:V8"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="P15:S15"/>
+    <mergeCell ref="T15:V15"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="P16:S16"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="P14:S14"/>
+    <mergeCell ref="T14:V14"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="P17:S17"/>
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="P18:S18"/>
+    <mergeCell ref="T18:V18"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="P19:S19"/>
+    <mergeCell ref="T19:V19"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="P20:S20"/>
+    <mergeCell ref="T20:V20"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="P21:S21"/>
+    <mergeCell ref="T21:V21"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="P22:S22"/>
+    <mergeCell ref="T22:V22"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="P23:S23"/>
+    <mergeCell ref="T23:V23"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P24:S24"/>
+    <mergeCell ref="T24:V24"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="P25:S25"/>
+    <mergeCell ref="T25:V25"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="P32:S32"/>
+    <mergeCell ref="T32:V32"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="P33:S33"/>
+    <mergeCell ref="T33:V33"/>
+    <mergeCell ref="B34:H34"/>
     <mergeCell ref="I34:L34"/>
     <mergeCell ref="M34:O34"/>
     <mergeCell ref="P34:S34"/>
     <mergeCell ref="T34:V34"/>
-    <mergeCell ref="B12:B20"/>
-    <mergeCell ref="D13:D20"/>
-    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="P35:S35"/>
+    <mergeCell ref="T35:V35"/>
+    <mergeCell ref="M41:O41"/>
+    <mergeCell ref="P41:S41"/>
+    <mergeCell ref="T41:V41"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="M42:O42"/>
+    <mergeCell ref="P42:S42"/>
+    <mergeCell ref="T42:V42"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="P38:S38"/>
+    <mergeCell ref="T38:V38"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="M39:O39"/>
+    <mergeCell ref="P39:S39"/>
+    <mergeCell ref="T39:V39"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="M43:O43"/>
+    <mergeCell ref="P43:S43"/>
+    <mergeCell ref="T43:V43"/>
+    <mergeCell ref="D18:D25"/>
+    <mergeCell ref="E19:E24"/>
     <mergeCell ref="Q1:Q2"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="T1:T2"/>
@@ -5921,107 +6267,11 @@
     <mergeCell ref="M1:P2"/>
     <mergeCell ref="I3:L4"/>
     <mergeCell ref="M3:P4"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="M31:O31"/>
-    <mergeCell ref="P31:S31"/>
-    <mergeCell ref="T31:V31"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="M32:O32"/>
-    <mergeCell ref="P32:S32"/>
-    <mergeCell ref="T32:V32"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="P33:S33"/>
-    <mergeCell ref="T33:V33"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="P29:S29"/>
-    <mergeCell ref="T29:V29"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="P30:S30"/>
-    <mergeCell ref="T30:V30"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="P25:S25"/>
-    <mergeCell ref="T25:V25"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="P26:S26"/>
-    <mergeCell ref="T26:V26"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="P23:S23"/>
-    <mergeCell ref="T23:V23"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P24:S24"/>
-    <mergeCell ref="T24:V24"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="P18:S18"/>
-    <mergeCell ref="T18:V18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="P19:S19"/>
-    <mergeCell ref="T19:V19"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="M20:O20"/>
-    <mergeCell ref="P20:S20"/>
-    <mergeCell ref="T20:V20"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="P15:S15"/>
-    <mergeCell ref="T15:V15"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="P16:S16"/>
-    <mergeCell ref="T16:V16"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="P17:S17"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="P12:S12"/>
-    <mergeCell ref="T12:V12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="P13:S13"/>
-    <mergeCell ref="T13:V13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="P14:S14"/>
-    <mergeCell ref="T14:V14"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="P11:S11"/>
-    <mergeCell ref="T11:V11"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="R5:V5"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="P8:S8"/>
-    <mergeCell ref="T8:V8"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="T9:V9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="P10:S10"/>
-    <mergeCell ref="T10:V10"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="M40:O40"/>
+    <mergeCell ref="P40:S40"/>
+    <mergeCell ref="T40:V40"/>
+    <mergeCell ref="I41:L41"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6048,162 +6298,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="111" t="s">
-        <v>129</v>
-      </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="120" t="s">
+      <c r="A1" s="97" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="126" t="s">
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="130" t="s">
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="142" t="s">
+      <c r="R1" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="143"/>
-      <c r="T1" s="135" t="s">
+      <c r="S1" s="129"/>
+      <c r="T1" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="141" t="s">
+      <c r="U1" s="127" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="132"/>
+      <c r="V1" s="118"/>
     </row>
     <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="114"/>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="129"/>
-      <c r="O2" s="129"/>
-      <c r="P2" s="129"/>
-      <c r="Q2" s="130"/>
-      <c r="R2" s="145"/>
-      <c r="S2" s="146"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="133"/>
-      <c r="V2" s="134"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="115"/>
+      <c r="O2" s="115"/>
+      <c r="P2" s="115"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="131"/>
+      <c r="S2" s="132"/>
+      <c r="T2" s="124"/>
+      <c r="U2" s="119"/>
+      <c r="V2" s="120"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A3" s="114"/>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="120" t="s">
+      <c r="A3" s="100"/>
+      <c r="B3" s="101"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="121"/>
-      <c r="K3" s="121"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="126" t="s">
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="112" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="127"/>
-      <c r="O3" s="127"/>
-      <c r="P3" s="127"/>
-      <c r="Q3" s="130" t="s">
+      <c r="N3" s="113"/>
+      <c r="O3" s="113"/>
+      <c r="P3" s="113"/>
+      <c r="Q3" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="142" t="s">
+      <c r="R3" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="143"/>
-      <c r="T3" s="130" t="s">
+      <c r="S3" s="129"/>
+      <c r="T3" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="U3" s="131" t="s">
-        <v>241</v>
-      </c>
-      <c r="V3" s="132"/>
+      <c r="U3" s="117" t="s">
+        <v>240</v>
+      </c>
+      <c r="V3" s="118"/>
     </row>
     <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A4" s="117"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="123"/>
-      <c r="J4" s="124"/>
-      <c r="K4" s="124"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="128"/>
-      <c r="N4" s="129"/>
-      <c r="O4" s="129"/>
-      <c r="P4" s="129"/>
-      <c r="Q4" s="130"/>
-      <c r="R4" s="145"/>
-      <c r="S4" s="146"/>
-      <c r="T4" s="130"/>
-      <c r="U4" s="133"/>
-      <c r="V4" s="134"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110"/>
+      <c r="M4" s="114"/>
+      <c r="N4" s="115"/>
+      <c r="O4" s="115"/>
+      <c r="P4" s="115"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="131"/>
+      <c r="S4" s="132"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="119"/>
+      <c r="V4" s="120"/>
     </row>
     <row r="5" spans="1:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="170" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="157"/>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="158" t="s">
+      <c r="B5" s="170"/>
+      <c r="C5" s="170"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="158"/>
-      <c r="G5" s="158"/>
-      <c r="H5" s="158"/>
-      <c r="I5" s="157" t="s">
+      <c r="F5" s="171"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="170" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="157"/>
-      <c r="K5" s="157"/>
-      <c r="L5" s="157"/>
-      <c r="M5" s="158" t="s">
+      <c r="J5" s="170"/>
+      <c r="K5" s="170"/>
+      <c r="L5" s="170"/>
+      <c r="M5" s="171" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="158"/>
-      <c r="O5" s="158"/>
-      <c r="P5" s="158"/>
+      <c r="N5" s="171"/>
+      <c r="O5" s="171"/>
+      <c r="P5" s="171"/>
       <c r="Q5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="R5" s="158" t="s">
+      <c r="R5" s="171" t="s">
         <v>26</v>
       </c>
-      <c r="S5" s="158"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="158"/>
-      <c r="V5" s="158"/>
+      <c r="S5" s="171"/>
+      <c r="T5" s="171"/>
+      <c r="U5" s="171"/>
+      <c r="V5" s="171"/>
     </row>
     <row r="6" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A6" s="35"/>
@@ -6213,7 +6463,7 @@
     </row>
     <row r="8" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A8" s="35" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:22" s="32" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -6285,6 +6535,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="R5:V5"/>
+    <mergeCell ref="A1:H4"/>
+    <mergeCell ref="I1:L2"/>
+    <mergeCell ref="M1:P2"/>
+    <mergeCell ref="I3:L4"/>
+    <mergeCell ref="M3:P4"/>
     <mergeCell ref="U1:V2"/>
     <mergeCell ref="U3:V4"/>
     <mergeCell ref="Q1:Q2"/>
@@ -6293,16 +6553,6 @@
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="R1:S2"/>
     <mergeCell ref="R3:S4"/>
-    <mergeCell ref="A1:H4"/>
-    <mergeCell ref="I1:L2"/>
-    <mergeCell ref="M1:P2"/>
-    <mergeCell ref="I3:L4"/>
-    <mergeCell ref="M3:P4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="R5:V5"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6313,7 +6563,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="6" width="3.6640625" style="5"/>
@@ -6332,166 +6582,166 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="111" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="120" t="s">
+      <c r="A1" s="97" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="121"/>
-      <c r="K1" s="126" t="s">
+      <c r="J1" s="107"/>
+      <c r="K1" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="135" t="s">
+      <c r="L1" s="121" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="142" t="s">
+      <c r="M1" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="130" t="s">
+      <c r="N1" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="130"/>
-      <c r="P1" s="141" t="s">
+      <c r="O1" s="116"/>
+      <c r="P1" s="127" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="132"/>
+      <c r="Q1" s="118"/>
     </row>
     <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A2" s="114"/>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="145"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="130"/>
-      <c r="P2" s="133"/>
-      <c r="Q2" s="134"/>
+      <c r="A2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="131"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="119"/>
+      <c r="Q2" s="120"/>
     </row>
     <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A3" s="114"/>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="120" t="s">
+      <c r="A3" s="100"/>
+      <c r="B3" s="101"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="121"/>
-      <c r="K3" s="126" t="s">
+      <c r="J3" s="107"/>
+      <c r="K3" s="112" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="135" t="s">
+      <c r="L3" s="121" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="142" t="s">
+      <c r="M3" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="130" t="s">
+      <c r="N3" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="130"/>
-      <c r="P3" s="131" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q3" s="132"/>
+      <c r="O3" s="116"/>
+      <c r="P3" s="117" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q3" s="118"/>
     </row>
     <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A4" s="117"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="123"/>
-      <c r="J4" s="124"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="138"/>
-      <c r="M4" s="145"/>
-      <c r="N4" s="130"/>
-      <c r="O4" s="130"/>
-      <c r="P4" s="133"/>
-      <c r="Q4" s="134"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="131"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="116"/>
+      <c r="P4" s="119"/>
+      <c r="Q4" s="120"/>
     </row>
     <row r="5" spans="1:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A5" s="157" t="s">
+      <c r="A5" s="170" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="157"/>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="158" t="s">
+      <c r="B5" s="170"/>
+      <c r="C5" s="170"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="158"/>
-      <c r="G5" s="158"/>
-      <c r="H5" s="158"/>
-      <c r="I5" s="157" t="s">
+      <c r="F5" s="171"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="170" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="157"/>
+      <c r="J5" s="170"/>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="M5" s="158" t="s">
+      <c r="M5" s="171" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="158"/>
-      <c r="O5" s="158"/>
-      <c r="P5" s="158"/>
-      <c r="Q5" s="158"/>
+      <c r="N5" s="171"/>
+      <c r="O5" s="171"/>
+      <c r="P5" s="171"/>
+      <c r="Q5" s="171"/>
     </row>
     <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A6" s="194" t="s">
+      <c r="A6" s="195" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="195"/>
+      <c r="C6" s="195"/>
+      <c r="D6" s="195"/>
+      <c r="E6" s="195"/>
+      <c r="F6" s="195"/>
+      <c r="G6" s="195"/>
+      <c r="H6" s="196" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="194"/>
-      <c r="C6" s="194"/>
-      <c r="D6" s="194"/>
-      <c r="E6" s="194"/>
-      <c r="F6" s="194"/>
-      <c r="G6" s="194"/>
-      <c r="H6" s="195" t="s">
+      <c r="I6" s="197"/>
+      <c r="J6" s="197"/>
+      <c r="K6" s="197"/>
+      <c r="L6" s="197"/>
+      <c r="M6" s="197"/>
+      <c r="N6" s="197"/>
+      <c r="O6" s="196" t="s">
         <v>133</v>
       </c>
-      <c r="I6" s="196"/>
-      <c r="J6" s="196"/>
-      <c r="K6" s="196"/>
-      <c r="L6" s="196"/>
-      <c r="M6" s="196"/>
-      <c r="N6" s="196"/>
-      <c r="O6" s="195" t="s">
-        <v>134</v>
-      </c>
-      <c r="P6" s="196"/>
-      <c r="Q6" s="196"/>
+      <c r="P6" s="197"/>
+      <c r="Q6" s="197"/>
     </row>
     <row r="7" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A7" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -6506,165 +6756,165 @@
     </row>
     <row r="8" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A8" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O8" s="11"/>
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A9" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="4"/>
       <c r="J9" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="O9" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="O9" s="11" t="s">
-        <v>140</v>
-      </c>
     </row>
     <row r="10" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A10" s="189" t="s">
-        <v>251</v>
-      </c>
-      <c r="B10" s="190"/>
-      <c r="C10" s="190"/>
-      <c r="D10" s="190"/>
-      <c r="E10" s="190"/>
+      <c r="A10" s="198" t="s">
+        <v>248</v>
+      </c>
+      <c r="B10" s="199"/>
+      <c r="C10" s="199"/>
+      <c r="D10" s="199"/>
+      <c r="E10" s="199"/>
       <c r="H10" s="11"/>
       <c r="I10" s="4"/>
       <c r="O10" s="11"/>
     </row>
     <row r="11" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A11" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="4"/>
-      <c r="J11" s="201" t="s">
-        <v>142</v>
-      </c>
-      <c r="K11" s="202"/>
+      <c r="J11" s="202" t="s">
+        <v>141</v>
+      </c>
+      <c r="K11" s="203"/>
       <c r="L11" s="73" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O11" s="11"/>
     </row>
     <row r="12" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A12" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="4"/>
       <c r="J12" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K12" s="22"/>
       <c r="L12" s="23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O12" s="11"/>
     </row>
     <row r="13" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A13" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="4"/>
       <c r="J13" s="21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K13" s="22"/>
       <c r="L13" s="23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O13" s="11"/>
     </row>
     <row r="14" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A14" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="H14" s="11"/>
       <c r="I14" s="4"/>
       <c r="J14" s="21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K14" s="22"/>
       <c r="L14" s="23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O14" s="11"/>
     </row>
     <row r="15" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A15" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
       <c r="H15" s="11"/>
       <c r="I15" s="4"/>
       <c r="J15" s="21" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K15" s="22"/>
       <c r="L15" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O15" s="11"/>
     </row>
     <row r="16" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A16" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H16" s="11"/>
       <c r="J16" s="21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K16" s="22"/>
       <c r="L16" s="23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O16" s="11"/>
     </row>
     <row r="17" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A17" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
       <c r="H17" s="11"/>
       <c r="J17" s="21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K17" s="22"/>
       <c r="L17" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O17" s="11"/>
     </row>
     <row r="18" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A18" s="86" t="s">
-        <v>236</v>
+      <c r="A18" s="85" t="s">
+        <v>235</v>
       </c>
       <c r="H18" s="11"/>
-      <c r="J18" s="86"/>
-      <c r="K18" s="86"/>
-      <c r="L18" s="86"/>
+      <c r="J18" s="85"/>
+      <c r="K18" s="85"/>
+      <c r="L18" s="85"/>
       <c r="O18" s="11"/>
     </row>
     <row r="19" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -6673,11 +6923,11 @@
     </row>
     <row r="20" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A20" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O20" s="11"/>
     </row>
@@ -6685,7 +6935,7 @@
       <c r="A21" s="11"/>
       <c r="H21" s="11"/>
       <c r="J21" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O21" s="11"/>
     </row>
@@ -6693,7 +6943,7 @@
       <c r="A22" s="11"/>
       <c r="H22" s="11"/>
       <c r="J22" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O22" s="11"/>
     </row>
@@ -6702,93 +6952,93 @@
       <c r="G23" s="12"/>
       <c r="H23" s="11"/>
       <c r="J23" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="K23" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="K23" s="24" t="s">
+      <c r="L23" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="L23" s="24" t="s">
-        <v>159</v>
-      </c>
       <c r="M23" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O23" s="11"/>
     </row>
     <row r="24" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A24" s="11"/>
       <c r="H24" s="11"/>
-      <c r="J24" s="203" t="s">
+      <c r="J24" s="204" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="K24" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="L24" s="25" t="s">
+      <c r="M24" s="27" t="s">
         <v>161</v>
-      </c>
-      <c r="M24" s="27" t="s">
-        <v>162</v>
       </c>
       <c r="O24" s="11"/>
     </row>
     <row r="25" spans="1:15" s="3" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A25" s="11"/>
       <c r="H25" s="11"/>
-      <c r="J25" s="204"/>
+      <c r="J25" s="205"/>
       <c r="K25" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="L25" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="L25" s="28" t="s">
+      <c r="M25" s="27" t="s">
         <v>164</v>
-      </c>
-      <c r="M25" s="27" t="s">
-        <v>165</v>
       </c>
       <c r="O25" s="11"/>
     </row>
     <row r="26" spans="1:15" s="3" customFormat="1" ht="47.1" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A26" s="11"/>
       <c r="H26" s="11"/>
-      <c r="J26" s="204"/>
+      <c r="J26" s="205"/>
       <c r="K26" s="75" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L26" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M26" s="27" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O26" s="11"/>
     </row>
     <row r="27" spans="1:15" s="3" customFormat="1" ht="45.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A27" s="11"/>
       <c r="H27" s="11"/>
-      <c r="J27" s="204"/>
+      <c r="J27" s="205"/>
       <c r="K27" s="75" t="s">
+        <v>189</v>
+      </c>
+      <c r="L27" s="74" t="s">
         <v>190</v>
       </c>
-      <c r="L27" s="74" t="s">
-        <v>191</v>
-      </c>
       <c r="M27" s="27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O27" s="11"/>
     </row>
     <row r="28" spans="1:15" s="3" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A28" s="11"/>
       <c r="H28" s="11"/>
-      <c r="J28" s="204"/>
+      <c r="J28" s="205"/>
       <c r="K28" s="75" t="s">
+        <v>187</v>
+      </c>
+      <c r="L28" s="74" t="s">
         <v>188</v>
       </c>
-      <c r="L28" s="74" t="s">
-        <v>189</v>
-      </c>
       <c r="M28" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O28" s="11"/>
     </row>
@@ -6796,15 +7046,15 @@
       <c r="A29" s="10"/>
       <c r="H29" s="10"/>
       <c r="I29" s="3"/>
-      <c r="J29" s="93" t="s">
-        <v>91</v>
-      </c>
-      <c r="K29" s="94"/>
+      <c r="J29" s="94" t="s">
+        <v>90</v>
+      </c>
+      <c r="K29" s="95"/>
       <c r="L29" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="M29" s="27" t="s">
         <v>169</v>
-      </c>
-      <c r="M29" s="27" t="s">
-        <v>170</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="10"/>
@@ -6822,15 +7072,15 @@
     </row>
     <row r="31" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A31" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H31" s="10"/>
       <c r="I31" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J31" s="3"/>
       <c r="O31" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -6838,7 +7088,7 @@
       <c r="H32" s="10"/>
       <c r="I32" s="4"/>
       <c r="J32" s="77" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O32" s="10"/>
     </row>
@@ -6859,7 +7109,7 @@
       <c r="H34" s="10"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O34" s="10"/>
     </row>
@@ -6873,14 +7123,14 @@
       <c r="G35" s="14"/>
       <c r="H35" s="10"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="205" t="s">
-        <v>219</v>
-      </c>
-      <c r="K35" s="206"/>
-      <c r="L35" s="205" t="s">
+      <c r="J35" s="206" t="s">
         <v>218</v>
       </c>
-      <c r="M35" s="206"/>
+      <c r="K35" s="207"/>
+      <c r="L35" s="206" t="s">
+        <v>217</v>
+      </c>
+      <c r="M35" s="207"/>
       <c r="O35" s="10"/>
     </row>
     <row r="36" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -6893,14 +7143,14 @@
       <c r="G36" s="14"/>
       <c r="H36" s="10"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="197" t="s">
-        <v>57</v>
-      </c>
-      <c r="K36" s="198"/>
-      <c r="L36" s="199" t="s">
-        <v>225</v>
-      </c>
-      <c r="M36" s="200"/>
+      <c r="J36" s="191" t="s">
+        <v>56</v>
+      </c>
+      <c r="K36" s="192"/>
+      <c r="L36" s="193" t="s">
+        <v>224</v>
+      </c>
+      <c r="M36" s="194"/>
       <c r="O36" s="10"/>
     </row>
     <row r="37" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -6913,14 +7163,14 @@
       <c r="G37" s="14"/>
       <c r="H37" s="10"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="197" t="s">
-        <v>215</v>
-      </c>
-      <c r="K37" s="198"/>
-      <c r="L37" s="199" t="s">
-        <v>226</v>
-      </c>
-      <c r="M37" s="200"/>
+      <c r="J37" s="191" t="s">
+        <v>214</v>
+      </c>
+      <c r="K37" s="192"/>
+      <c r="L37" s="193" t="s">
+        <v>225</v>
+      </c>
+      <c r="M37" s="194"/>
       <c r="O37" s="10"/>
     </row>
     <row r="38" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -6933,14 +7183,14 @@
       <c r="G38" s="14"/>
       <c r="H38" s="10"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="197" t="s">
-        <v>101</v>
-      </c>
-      <c r="K38" s="198"/>
-      <c r="L38" s="199" t="s">
-        <v>227</v>
-      </c>
-      <c r="M38" s="200"/>
+      <c r="J38" s="191" t="s">
+        <v>100</v>
+      </c>
+      <c r="K38" s="192"/>
+      <c r="L38" s="193" t="s">
+        <v>226</v>
+      </c>
+      <c r="M38" s="194"/>
       <c r="O38" s="10"/>
     </row>
     <row r="39" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -6953,14 +7203,14 @@
       <c r="G39" s="14"/>
       <c r="H39" s="10"/>
       <c r="I39" s="3"/>
-      <c r="J39" s="197" t="s">
-        <v>67</v>
-      </c>
-      <c r="K39" s="198"/>
-      <c r="L39" s="197" t="s">
-        <v>228</v>
-      </c>
-      <c r="M39" s="198"/>
+      <c r="J39" s="191" t="s">
+        <v>66</v>
+      </c>
+      <c r="K39" s="192"/>
+      <c r="L39" s="191" t="s">
+        <v>227</v>
+      </c>
+      <c r="M39" s="192"/>
       <c r="O39" s="10"/>
     </row>
     <row r="40" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -6973,14 +7223,14 @@
       <c r="G40" s="14"/>
       <c r="H40" s="10"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="197" t="s">
-        <v>216</v>
-      </c>
-      <c r="K40" s="198"/>
-      <c r="L40" s="197" t="s">
-        <v>229</v>
-      </c>
-      <c r="M40" s="198"/>
+      <c r="J40" s="191" t="s">
+        <v>215</v>
+      </c>
+      <c r="K40" s="192"/>
+      <c r="L40" s="191" t="s">
+        <v>228</v>
+      </c>
+      <c r="M40" s="192"/>
       <c r="O40" s="10"/>
     </row>
     <row r="41" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -6993,14 +7243,14 @@
       <c r="G41" s="14"/>
       <c r="H41" s="10"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="197" t="s">
-        <v>217</v>
-      </c>
-      <c r="K41" s="198"/>
-      <c r="L41" s="197" t="s">
-        <v>230</v>
-      </c>
-      <c r="M41" s="198"/>
+      <c r="J41" s="191" t="s">
+        <v>216</v>
+      </c>
+      <c r="K41" s="192"/>
+      <c r="L41" s="191" t="s">
+        <v>229</v>
+      </c>
+      <c r="M41" s="192"/>
       <c r="O41" s="10"/>
     </row>
     <row r="42" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7025,7 +7275,7 @@
       <c r="H43" s="10"/>
       <c r="I43" s="3"/>
       <c r="J43" s="76" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O43" s="10"/>
     </row>
@@ -7039,7 +7289,7 @@
       <c r="H44" s="10"/>
       <c r="I44" s="3"/>
       <c r="J44" s="76" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O44" s="10"/>
     </row>
@@ -7053,7 +7303,7 @@
       <c r="H45" s="10"/>
       <c r="I45" s="3"/>
       <c r="J45" s="76" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O45" s="10"/>
     </row>
@@ -7079,7 +7329,7 @@
       <c r="H47" s="10"/>
       <c r="I47" s="3"/>
       <c r="J47" s="76" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O47" s="10"/>
     </row>
@@ -7093,14 +7343,14 @@
       <c r="H48" s="10"/>
       <c r="I48" s="3"/>
       <c r="J48" s="73" t="s">
-        <v>202</v>
-      </c>
-      <c r="K48" s="193" t="s">
-        <v>210</v>
-      </c>
-      <c r="L48" s="193"/>
+        <v>201</v>
+      </c>
+      <c r="K48" s="201" t="s">
+        <v>209</v>
+      </c>
+      <c r="L48" s="201"/>
       <c r="M48" s="82" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O48" s="10"/>
     </row>
@@ -7114,14 +7364,14 @@
       <c r="H49" s="10"/>
       <c r="I49" s="3"/>
       <c r="J49" s="80" t="s">
-        <v>62</v>
-      </c>
-      <c r="K49" s="191" t="s">
-        <v>203</v>
-      </c>
-      <c r="L49" s="191"/>
+        <v>61</v>
+      </c>
+      <c r="K49" s="189" t="s">
+        <v>202</v>
+      </c>
+      <c r="L49" s="189"/>
       <c r="M49" s="81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O49" s="10"/>
     </row>
@@ -7135,14 +7385,14 @@
       <c r="H50" s="10"/>
       <c r="I50" s="3"/>
       <c r="J50" s="80" t="s">
-        <v>64</v>
-      </c>
-      <c r="K50" s="191" t="s">
-        <v>204</v>
-      </c>
-      <c r="L50" s="191"/>
+        <v>63</v>
+      </c>
+      <c r="K50" s="189" t="s">
+        <v>203</v>
+      </c>
+      <c r="L50" s="189"/>
       <c r="M50" s="81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O50" s="10"/>
     </row>
@@ -7156,14 +7406,14 @@
       <c r="H51" s="10"/>
       <c r="I51" s="3"/>
       <c r="J51" s="80" t="s">
-        <v>57</v>
-      </c>
-      <c r="K51" s="191" t="s">
-        <v>205</v>
-      </c>
-      <c r="L51" s="192"/>
+        <v>56</v>
+      </c>
+      <c r="K51" s="189" t="s">
+        <v>204</v>
+      </c>
+      <c r="L51" s="200"/>
       <c r="M51" s="81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O51" s="10"/>
     </row>
@@ -7177,14 +7427,14 @@
       <c r="H52" s="10"/>
       <c r="I52" s="3"/>
       <c r="J52" s="80" t="s">
-        <v>198</v>
-      </c>
-      <c r="K52" s="191" t="s">
-        <v>206</v>
-      </c>
-      <c r="L52" s="192"/>
+        <v>197</v>
+      </c>
+      <c r="K52" s="189" t="s">
+        <v>205</v>
+      </c>
+      <c r="L52" s="200"/>
       <c r="M52" s="81" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O52" s="10"/>
     </row>
@@ -7198,14 +7448,14 @@
       <c r="H53" s="10"/>
       <c r="I53" s="3"/>
       <c r="J53" s="80" t="s">
-        <v>199</v>
-      </c>
-      <c r="K53" s="191" t="s">
-        <v>207</v>
-      </c>
-      <c r="L53" s="192"/>
+        <v>198</v>
+      </c>
+      <c r="K53" s="189" t="s">
+        <v>206</v>
+      </c>
+      <c r="L53" s="200"/>
       <c r="M53" s="81" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O53" s="10"/>
     </row>
@@ -7219,14 +7469,14 @@
       <c r="H54" s="10"/>
       <c r="I54" s="3"/>
       <c r="J54" s="80" t="s">
-        <v>200</v>
-      </c>
-      <c r="K54" s="191" t="s">
-        <v>208</v>
-      </c>
-      <c r="L54" s="192"/>
+        <v>199</v>
+      </c>
+      <c r="K54" s="189" t="s">
+        <v>207</v>
+      </c>
+      <c r="L54" s="200"/>
       <c r="M54" s="81" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O54" s="10"/>
     </row>
@@ -7240,12 +7490,12 @@
       <c r="H55" s="10"/>
       <c r="I55" s="3"/>
       <c r="J55" s="80" t="s">
-        <v>201</v>
-      </c>
-      <c r="K55" s="191" t="s">
-        <v>209</v>
-      </c>
-      <c r="L55" s="192"/>
+        <v>200</v>
+      </c>
+      <c r="K55" s="189" t="s">
+        <v>208</v>
+      </c>
+      <c r="L55" s="200"/>
       <c r="M55" s="81"/>
       <c r="O55" s="10"/>
     </row>
@@ -7275,7 +7525,7 @@
       <c r="H57" s="10"/>
       <c r="I57" s="4"/>
       <c r="J57" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O57" s="10"/>
     </row>
@@ -7290,7 +7540,7 @@
       <c r="H58" s="10"/>
       <c r="I58" s="4"/>
       <c r="J58" s="76" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O58" s="10"/>
     </row>
@@ -7315,14 +7565,14 @@
     </row>
     <row r="60" spans="1:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A60" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H60" s="11"/>
       <c r="I60" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="O60" s="11" t="s">
         <v>175</v>
-      </c>
-      <c r="O60" s="11" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
@@ -7336,7 +7586,7 @@
       <c r="H61" s="10"/>
       <c r="I61" s="3"/>
       <c r="J61" s="76" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
@@ -7348,10 +7598,10 @@
       <c r="A62" s="11"/>
       <c r="H62" s="11"/>
       <c r="J62" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="K62" s="20" t="s">
         <v>177</v>
-      </c>
-      <c r="K62" s="20" t="s">
-        <v>178</v>
       </c>
       <c r="L62" s="20" t="s">
         <v>46</v>
@@ -7362,13 +7612,13 @@
       <c r="A63" s="11"/>
       <c r="H63" s="11"/>
       <c r="J63" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K63" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L63" s="23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O63" s="11"/>
     </row>
@@ -7376,40 +7626,40 @@
       <c r="A64" s="11"/>
       <c r="H64" s="11"/>
       <c r="J64" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K64" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L64" s="23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O64" s="11"/>
     </row>
     <row r="65" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="H65" s="11"/>
-      <c r="J65" s="191" t="s">
-        <v>88</v>
+      <c r="J65" s="189" t="s">
+        <v>87</v>
       </c>
       <c r="K65" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="L65" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="L65" s="23" t="s">
+      <c r="O65" s="11" t="s">
         <v>181</v>
-      </c>
-      <c r="O65" s="11" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="66" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A66" s="11"/>
       <c r="H66" s="11"/>
-      <c r="J66" s="191"/>
+      <c r="J66" s="189"/>
       <c r="K66" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="L66" s="23" t="s">
         <v>183</v>
-      </c>
-      <c r="L66" s="23" t="s">
-        <v>184</v>
       </c>
       <c r="O66" s="11"/>
     </row>
@@ -7423,10 +7673,10 @@
       <c r="H68" s="11"/>
       <c r="I68" s="4"/>
       <c r="J68" s="77" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O68" s="11"/>
     </row>
@@ -7435,10 +7685,10 @@
       <c r="H69" s="11"/>
       <c r="I69" s="2"/>
       <c r="J69" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K69" s="20" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L69" s="20" t="s">
         <v>46</v>
@@ -7451,13 +7701,13 @@
       <c r="A70" s="11"/>
       <c r="H70" s="11"/>
       <c r="J70" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K70" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L70" s="23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
@@ -7467,13 +7717,13 @@
       <c r="A71" s="11"/>
       <c r="H71" s="11"/>
       <c r="J71" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K71" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L71" s="23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
@@ -7483,14 +7733,14 @@
       <c r="A72" s="11"/>
       <c r="H72" s="11"/>
       <c r="I72" s="2"/>
-      <c r="J72" s="191" t="s">
-        <v>88</v>
+      <c r="J72" s="190" t="s">
+        <v>251</v>
       </c>
       <c r="K72" s="23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L72" s="23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
@@ -7500,9 +7750,9 @@
       <c r="A73" s="11"/>
       <c r="H73" s="11"/>
       <c r="I73" s="2"/>
-      <c r="J73" s="191"/>
+      <c r="J73" s="189"/>
       <c r="K73" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L73" s="29">
         <v>0</v>
@@ -7515,46 +7765,168 @@
       <c r="A74" s="11"/>
       <c r="H74" s="11"/>
       <c r="I74" s="2"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="2"/>
-      <c r="L74" s="2"/>
+      <c r="J74" s="79"/>
+      <c r="L74" s="30"/>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
       <c r="O74" s="11"/>
     </row>
-    <row r="75" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="75" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A75" s="11"/>
+      <c r="H75" s="11"/>
       <c r="I75" s="2"/>
-      <c r="K75" s="2"/>
-      <c r="L75" s="2"/>
+      <c r="J75" s="77" t="s">
+        <v>253</v>
+      </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
-    </row>
-    <row r="76" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="O75" s="11"/>
+    </row>
+    <row r="76" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A76" s="11"/>
+      <c r="H76" s="11"/>
       <c r="I76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
+      <c r="J76" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="K76" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="L76" s="20" t="s">
+        <v>46</v>
+      </c>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
-    </row>
-    <row r="77" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="I77" s="3"/>
-      <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
-      <c r="L77" s="3"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3"/>
+      <c r="O76" s="11"/>
+    </row>
+    <row r="77" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A77" s="11"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="90" t="s">
+        <v>252</v>
+      </c>
+      <c r="K77" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="L77" s="80" t="s">
+        <v>254</v>
+      </c>
+      <c r="M77" s="2"/>
+      <c r="N77" s="2"/>
+      <c r="O77" s="11"/>
+    </row>
+    <row r="78" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A78" s="11"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="2"/>
+      <c r="M78" s="2"/>
+      <c r="N78" s="2"/>
+      <c r="O78" s="11"/>
+    </row>
+    <row r="79" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A79" s="11"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="77" t="s">
+        <v>255</v>
+      </c>
+      <c r="M79" s="2"/>
+      <c r="N79" s="2"/>
+      <c r="O79" s="11"/>
+    </row>
+    <row r="80" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="K80" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="L80" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M80" s="2"/>
+      <c r="N80" s="2"/>
+      <c r="O80" s="11"/>
+    </row>
+    <row r="81" spans="1:15" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A81" s="11"/>
+      <c r="H81" s="11"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="90" t="s">
+        <v>252</v>
+      </c>
+      <c r="K81" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="L81" s="80" t="s">
+        <v>254</v>
+      </c>
+      <c r="M81" s="2"/>
+      <c r="N81" s="2"/>
+      <c r="O81" s="11"/>
+    </row>
+    <row r="82" spans="1:15" s="3" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A82" s="11"/>
+      <c r="H82" s="11"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2"/>
+      <c r="N82" s="2"/>
+      <c r="O82" s="11"/>
+    </row>
+    <row r="83" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="I83" s="2"/>
+      <c r="K83" s="2"/>
+      <c r="L83" s="2"/>
+      <c r="M83" s="2"/>
+      <c r="N83" s="2"/>
+    </row>
+    <row r="84" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="I84" s="2"/>
+      <c r="K84" s="2"/>
+      <c r="L84" s="2"/>
+      <c r="M84" s="2"/>
+      <c r="N84" s="2"/>
+    </row>
+    <row r="85" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="I85" s="3"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="3"/>
+      <c r="L85" s="3"/>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="A1:H4"/>
-    <mergeCell ref="N3:O4"/>
-    <mergeCell ref="P3:Q4"/>
-    <mergeCell ref="N1:O2"/>
-    <mergeCell ref="P1:Q2"/>
-    <mergeCell ref="I3:J4"/>
-    <mergeCell ref="I1:J2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J24:J28"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:Q6"/>
     <mergeCell ref="J65:J66"/>
     <mergeCell ref="J72:J73"/>
     <mergeCell ref="K1:K2"/>
@@ -7571,29 +7943,15 @@
     <mergeCell ref="L36:M36"/>
     <mergeCell ref="J37:K37"/>
     <mergeCell ref="L37:M37"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="K53:L53"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J24:J28"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="A1:H4"/>
+    <mergeCell ref="N3:O4"/>
+    <mergeCell ref="P3:Q4"/>
+    <mergeCell ref="N1:O2"/>
+    <mergeCell ref="P1:Q2"/>
+    <mergeCell ref="I3:J4"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="M3:M4"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
